--- a/AAII_Financials/Quarterly/DAO_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/DAO_QTR_FIN.xlsx
@@ -5,7 +5,7 @@
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Stocks_Automation\AAII_Financials\Quarterly\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Private\Investing\Automation\AAII\AAII_Financials\Quarterly\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -17,12 +17,12 @@
   <definedNames>
     <definedName name="Ticker">#REF!</definedName>
   </definedNames>
-  <calcPr calcId="152511" calcMode="manual" concurrentCalc="0"/>
+  <calcPr calcId="152511" calcMode="manual"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="323" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="331" uniqueCount="92">
   <si>
     <t>DAO</t>
   </si>
@@ -656,352 +656,377 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AA102"/>
+  <dimension ref="A5:AC102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="6.42578125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="19" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="23" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="27" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="21" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="25" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="29" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:27" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:29" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:27" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:29" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:27" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:29" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45291</v>
+      </c>
+      <c r="E7" s="2">
+        <v>45199</v>
+      </c>
+      <c r="F7" s="2">
         <v>45107</v>
       </c>
-      <c r="E7" s="2">
+      <c r="G7" s="2">
         <v>45016</v>
       </c>
-      <c r="F7" s="2">
+      <c r="H7" s="2">
         <v>44926</v>
       </c>
-      <c r="G7" s="2">
+      <c r="I7" s="2">
         <v>44834</v>
       </c>
-      <c r="H7" s="2">
+      <c r="J7" s="2">
         <v>44742</v>
       </c>
-      <c r="I7" s="2">
+      <c r="K7" s="2">
         <v>44651</v>
       </c>
-      <c r="J7" s="2">
+      <c r="L7" s="2">
         <v>44561</v>
       </c>
-      <c r="K7" s="2">
+      <c r="M7" s="2">
         <v>44469</v>
       </c>
-      <c r="L7" s="2">
+      <c r="N7" s="2">
         <v>44377</v>
       </c>
-      <c r="M7" s="2">
+      <c r="O7" s="2">
         <v>44286</v>
       </c>
-      <c r="N7" s="2">
+      <c r="P7" s="2">
         <v>44196</v>
       </c>
-      <c r="O7" s="2">
+      <c r="Q7" s="2">
         <v>44104</v>
       </c>
-      <c r="P7" s="2">
+      <c r="R7" s="2">
         <v>44012</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="S7" s="2">
         <v>43921</v>
       </c>
-      <c r="R7" s="2">
+      <c r="T7" s="2">
         <v>43830</v>
       </c>
-      <c r="S7" s="2">
+      <c r="U7" s="2">
         <v>43738</v>
       </c>
-      <c r="T7" s="2">
+      <c r="V7" s="2">
         <v>43646</v>
       </c>
-      <c r="U7" s="2">
+      <c r="W7" s="2">
         <v>43555</v>
       </c>
-      <c r="V7" s="2">
+      <c r="X7" s="2">
         <v>43465</v>
       </c>
-      <c r="W7" s="2">
+      <c r="Y7" s="2">
         <v>43373</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Z7" s="2">
         <v>43281</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="AA7" s="2">
         <v>43190</v>
       </c>
-      <c r="Z7" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="AA7" s="2" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="8" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="AB7" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="AC7" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:29" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D8" s="3">
-        <v>166600</v>
+        <v>205800</v>
       </c>
       <c r="E8" s="3">
-        <v>160600</v>
+        <v>213900</v>
       </c>
       <c r="F8" s="3">
-        <v>200800</v>
+        <v>167700</v>
       </c>
       <c r="G8" s="3">
-        <v>193600</v>
+        <v>161700</v>
       </c>
       <c r="H8" s="3">
-        <v>132000</v>
+        <v>202100</v>
       </c>
       <c r="I8" s="3">
+        <v>195000</v>
+      </c>
+      <c r="J8" s="3">
+        <v>132900</v>
+      </c>
+      <c r="K8" s="3">
         <v>165800</v>
       </c>
-      <c r="J8" s="3">
+      <c r="L8" s="3">
         <v>554500</v>
       </c>
-      <c r="K8" s="3">
+      <c r="M8" s="3">
         <v>197200</v>
       </c>
-      <c r="L8" s="3">
+      <c r="N8" s="3">
         <v>139300</v>
-      </c>
-      <c r="M8" s="3">
-        <v>132000</v>
-      </c>
-      <c r="N8" s="3">
-        <v>64900</v>
       </c>
       <c r="O8" s="3">
         <v>132000</v>
       </c>
       <c r="P8" s="3">
+        <v>64900</v>
+      </c>
+      <c r="Q8" s="3">
+        <v>132000</v>
+      </c>
+      <c r="R8" s="3">
         <v>91800</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="S8" s="3">
         <v>84800</v>
       </c>
-      <c r="R8" s="3">
+      <c r="T8" s="3">
         <v>63200</v>
       </c>
-      <c r="S8" s="3">
+      <c r="U8" s="3">
         <v>53300</v>
       </c>
-      <c r="T8" s="3">
+      <c r="V8" s="3">
         <v>49300</v>
       </c>
-      <c r="U8" s="3">
+      <c r="W8" s="3">
         <v>34300</v>
       </c>
-      <c r="V8" s="3">
+      <c r="X8" s="3">
         <v>33400</v>
       </c>
-      <c r="W8" s="3">
+      <c r="Y8" s="3">
         <v>25300</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Z8" s="3">
         <v>27000</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="AA8" s="3">
         <v>19300</v>
       </c>
-      <c r="Z8" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="AA8" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="9" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="AB8" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AC8" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="9" spans="1:29" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D9" s="3">
-        <v>88300</v>
+        <v>103100</v>
       </c>
       <c r="E9" s="3">
-        <v>77500</v>
+        <v>94400</v>
       </c>
       <c r="F9" s="3">
-        <v>93800</v>
+        <v>88900</v>
       </c>
       <c r="G9" s="3">
-        <v>88700</v>
+        <v>78000</v>
       </c>
       <c r="H9" s="3">
-        <v>75500</v>
+        <v>94400</v>
       </c>
       <c r="I9" s="3">
+        <v>89300</v>
+      </c>
+      <c r="J9" s="3">
+        <v>76000</v>
+      </c>
+      <c r="K9" s="3">
         <v>77100</v>
       </c>
-      <c r="J9" s="3">
+      <c r="L9" s="3">
         <v>279900</v>
       </c>
-      <c r="K9" s="3">
+      <c r="M9" s="3">
         <v>85500</v>
       </c>
-      <c r="L9" s="3">
+      <c r="N9" s="3">
         <v>68200</v>
       </c>
-      <c r="M9" s="3">
+      <c r="O9" s="3">
         <v>62900</v>
       </c>
-      <c r="N9" s="3">
+      <c r="P9" s="3">
         <v>120900</v>
       </c>
-      <c r="O9" s="3">
+      <c r="Q9" s="3">
         <v>71400</v>
       </c>
-      <c r="P9" s="3">
+      <c r="R9" s="3">
         <v>50400</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="S9" s="3">
         <v>47900</v>
       </c>
-      <c r="R9" s="3">
+      <c r="T9" s="3">
         <v>44300</v>
       </c>
-      <c r="S9" s="3">
+      <c r="U9" s="3">
         <v>39500</v>
       </c>
-      <c r="T9" s="3">
+      <c r="V9" s="3">
         <v>33100</v>
       </c>
-      <c r="U9" s="3">
+      <c r="W9" s="3">
         <v>26300</v>
       </c>
-      <c r="V9" s="3">
+      <c r="X9" s="3">
         <v>23500</v>
       </c>
-      <c r="W9" s="3">
+      <c r="Y9" s="3">
         <v>19400</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Z9" s="3">
         <v>17200</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="AA9" s="3">
         <v>13900</v>
       </c>
-      <c r="Z9" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="AA9" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="10" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="AB9" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AC9" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:29" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
-        <v>78300</v>
+        <v>102700</v>
       </c>
       <c r="E10" s="3">
-        <v>83100</v>
+        <v>119500</v>
       </c>
       <c r="F10" s="3">
-        <v>107000</v>
+        <v>78800</v>
       </c>
       <c r="G10" s="3">
-        <v>105000</v>
+        <v>83700</v>
       </c>
       <c r="H10" s="3">
-        <v>56600</v>
+        <v>107700</v>
       </c>
       <c r="I10" s="3">
+        <v>105700</v>
+      </c>
+      <c r="J10" s="3">
+        <v>57000</v>
+      </c>
+      <c r="K10" s="3">
         <v>88600</v>
       </c>
-      <c r="J10" s="3">
+      <c r="L10" s="3">
         <v>274600</v>
       </c>
-      <c r="K10" s="3">
+      <c r="M10" s="3">
         <v>111700</v>
       </c>
-      <c r="L10" s="3">
+      <c r="N10" s="3">
         <v>71100</v>
       </c>
-      <c r="M10" s="3">
+      <c r="O10" s="3">
         <v>69100</v>
       </c>
-      <c r="N10" s="3">
+      <c r="P10" s="3">
         <v>-56100</v>
       </c>
-      <c r="O10" s="3">
+      <c r="Q10" s="3">
         <v>60600</v>
       </c>
-      <c r="P10" s="3">
+      <c r="R10" s="3">
         <v>41500</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="S10" s="3">
         <v>36900</v>
       </c>
-      <c r="R10" s="3">
+      <c r="T10" s="3">
         <v>18800</v>
       </c>
-      <c r="S10" s="3">
+      <c r="U10" s="3">
         <v>13700</v>
       </c>
-      <c r="T10" s="3">
+      <c r="V10" s="3">
         <v>16200</v>
       </c>
-      <c r="U10" s="3">
+      <c r="W10" s="3">
         <v>8000</v>
       </c>
-      <c r="V10" s="3">
+      <c r="X10" s="3">
         <v>9900</v>
       </c>
-      <c r="W10" s="3">
+      <c r="Y10" s="3">
         <v>5900</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Z10" s="3">
         <v>9800</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="AA10" s="3">
         <v>5400</v>
       </c>
-      <c r="Z10" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="AA10" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="11" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="AB10" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AC10" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:29" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -1029,85 +1054,93 @@
       <c r="Y11" s="3"/>
       <c r="Z11" s="3"/>
       <c r="AA11" s="3"/>
-    </row>
-    <row r="12" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="AB11" s="3"/>
+      <c r="AC11" s="3"/>
+    </row>
+    <row r="12" spans="1:29" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D12" s="3">
-        <v>28300</v>
+        <v>23400</v>
       </c>
       <c r="E12" s="3">
-        <v>25200</v>
+        <v>26000</v>
       </c>
       <c r="F12" s="3">
-        <v>24800</v>
+        <v>28500</v>
       </c>
       <c r="G12" s="3">
-        <v>29400</v>
+        <v>25400</v>
       </c>
       <c r="H12" s="3">
-        <v>28800</v>
+        <v>25000</v>
       </c>
       <c r="I12" s="3">
+        <v>29600</v>
+      </c>
+      <c r="J12" s="3">
+        <v>29000</v>
+      </c>
+      <c r="K12" s="3">
         <v>28000</v>
       </c>
-      <c r="J12" s="3">
+      <c r="L12" s="3">
         <v>83900</v>
       </c>
-      <c r="K12" s="3">
+      <c r="M12" s="3">
         <v>27500</v>
       </c>
-      <c r="L12" s="3">
+      <c r="N12" s="3">
         <v>20700</v>
-      </c>
-      <c r="M12" s="3">
-        <v>17800</v>
-      </c>
-      <c r="N12" s="3">
-        <v>10500</v>
       </c>
       <c r="O12" s="3">
         <v>17800</v>
       </c>
       <c r="P12" s="3">
+        <v>10500</v>
+      </c>
+      <c r="Q12" s="3">
+        <v>17800</v>
+      </c>
+      <c r="R12" s="3">
         <v>13500</v>
       </c>
-      <c r="Q12" s="3">
+      <c r="S12" s="3">
         <v>13200</v>
       </c>
-      <c r="R12" s="3">
+      <c r="T12" s="3">
         <v>13700</v>
       </c>
-      <c r="S12" s="3">
+      <c r="U12" s="3">
         <v>11500</v>
       </c>
-      <c r="T12" s="3">
+      <c r="V12" s="3">
         <v>8600</v>
       </c>
-      <c r="U12" s="3">
+      <c r="W12" s="3">
         <v>8300</v>
       </c>
-      <c r="V12" s="3">
+      <c r="X12" s="3">
         <v>7300</v>
       </c>
-      <c r="W12" s="3">
+      <c r="Y12" s="3">
         <v>7700</v>
       </c>
-      <c r="X12" s="3">
+      <c r="Z12" s="3">
         <v>5400</v>
       </c>
-      <c r="Y12" s="3">
+      <c r="AA12" s="3">
         <v>6100</v>
       </c>
-      <c r="Z12" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="AA12" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="13" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="AB12" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AC12" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:29" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1183,8 +1216,14 @@
       <c r="AA13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="AB13" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:29" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -1206,15 +1245,15 @@
       <c r="I14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="J14" s="3">
+      <c r="J14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="K14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L14" s="3">
         <v>7800</v>
       </c>
-      <c r="K14" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L14" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M14" s="3" t="s">
         <v>3</v>
       </c>
@@ -1227,11 +1266,11 @@
       <c r="P14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q14" s="3">
-        <v>0</v>
-      </c>
-      <c r="R14" s="3">
-        <v>0</v>
+      <c r="Q14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R14" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="S14" s="3">
         <v>0</v>
@@ -1260,8 +1299,14 @@
       <c r="AA14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="AB14" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:29" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1337,8 +1382,14 @@
       <c r="AA15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="AB15" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:29" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1363,162 +1414,176 @@
       <c r="Y16" s="3"/>
       <c r="Z16" s="3"/>
       <c r="AA16" s="3"/>
-    </row>
-    <row r="17" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB16" s="3"/>
+      <c r="AC16" s="3"/>
+    </row>
+    <row r="17" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
-        <v>206500</v>
+        <v>195200</v>
       </c>
       <c r="E17" s="3">
-        <v>187700</v>
+        <v>221900</v>
       </c>
       <c r="F17" s="3">
-        <v>197400</v>
+        <v>207900</v>
       </c>
       <c r="G17" s="3">
-        <v>223900</v>
+        <v>188900</v>
       </c>
       <c r="H17" s="3">
-        <v>194900</v>
+        <v>198700</v>
       </c>
       <c r="I17" s="3">
+        <v>225400</v>
+      </c>
+      <c r="J17" s="3">
+        <v>196200</v>
+      </c>
+      <c r="K17" s="3">
         <v>183000</v>
       </c>
-      <c r="J17" s="3">
+      <c r="L17" s="3">
         <v>684700</v>
       </c>
-      <c r="K17" s="3">
+      <c r="M17" s="3">
         <v>215600</v>
       </c>
-      <c r="L17" s="3">
+      <c r="N17" s="3">
         <v>175500</v>
       </c>
-      <c r="M17" s="3">
+      <c r="O17" s="3">
         <v>161800</v>
       </c>
-      <c r="N17" s="3">
+      <c r="P17" s="3">
         <v>-4900</v>
       </c>
-      <c r="O17" s="3">
+      <c r="Q17" s="3">
         <v>263800</v>
       </c>
-      <c r="P17" s="3">
+      <c r="R17" s="3">
         <v>133600</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="S17" s="3">
         <v>112300</v>
       </c>
-      <c r="R17" s="3">
+      <c r="T17" s="3">
         <v>94600</v>
       </c>
-      <c r="S17" s="3">
+      <c r="U17" s="3">
         <v>89400</v>
       </c>
-      <c r="T17" s="3">
+      <c r="V17" s="3">
         <v>62000</v>
       </c>
-      <c r="U17" s="3">
+      <c r="W17" s="3">
         <v>46400</v>
       </c>
-      <c r="V17" s="3">
+      <c r="X17" s="3">
         <v>40700</v>
       </c>
-      <c r="W17" s="3">
+      <c r="Y17" s="3">
         <v>37800</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Z17" s="3">
         <v>31300</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="AA17" s="3">
         <v>26700</v>
       </c>
-      <c r="Z17" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="AA17" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="18" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB17" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AC17" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
-        <v>-39900</v>
+        <v>10600</v>
       </c>
       <c r="E18" s="3">
-        <v>-27000</v>
+        <v>-8000</v>
       </c>
       <c r="F18" s="3">
+        <v>-40200</v>
+      </c>
+      <c r="G18" s="3">
+        <v>-27200</v>
+      </c>
+      <c r="H18" s="3">
         <v>3400</v>
       </c>
-      <c r="G18" s="3">
-        <v>-30200</v>
-      </c>
-      <c r="H18" s="3">
-        <v>-62900</v>
-      </c>
       <c r="I18" s="3">
+        <v>-30500</v>
+      </c>
+      <c r="J18" s="3">
+        <v>-63300</v>
+      </c>
+      <c r="K18" s="3">
         <v>-17300</v>
       </c>
-      <c r="J18" s="3">
+      <c r="L18" s="3">
         <v>-130200</v>
       </c>
-      <c r="K18" s="3">
+      <c r="M18" s="3">
         <v>-18400</v>
       </c>
-      <c r="L18" s="3">
+      <c r="N18" s="3">
         <v>-36200</v>
       </c>
-      <c r="M18" s="3">
+      <c r="O18" s="3">
         <v>-29800</v>
       </c>
-      <c r="N18" s="3">
+      <c r="P18" s="3">
         <v>69800</v>
       </c>
-      <c r="O18" s="3">
+      <c r="Q18" s="3">
         <v>-131700</v>
       </c>
-      <c r="P18" s="3">
+      <c r="R18" s="3">
         <v>-41700</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="S18" s="3">
         <v>-27600</v>
       </c>
-      <c r="R18" s="3">
+      <c r="T18" s="3">
         <v>-31400</v>
       </c>
-      <c r="S18" s="3">
+      <c r="U18" s="3">
         <v>-36100</v>
       </c>
-      <c r="T18" s="3">
+      <c r="V18" s="3">
         <v>-12700</v>
       </c>
-      <c r="U18" s="3">
+      <c r="W18" s="3">
         <v>-12000</v>
       </c>
-      <c r="V18" s="3">
+      <c r="X18" s="3">
         <v>-7300</v>
       </c>
-      <c r="W18" s="3">
+      <c r="Y18" s="3">
         <v>-12400</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Z18" s="3">
         <v>-4400</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="AA18" s="3">
         <v>-7500</v>
       </c>
-      <c r="Z18" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="AA18" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="19" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB18" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AC18" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1546,200 +1611,214 @@
       <c r="Y19" s="3"/>
       <c r="Z19" s="3"/>
       <c r="AA19" s="3"/>
-    </row>
-    <row r="20" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB19" s="3"/>
+      <c r="AC19" s="3"/>
+    </row>
+    <row r="20" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>-100</v>
+      </c>
+      <c r="E20" s="3">
+        <v>-2600</v>
+      </c>
+      <c r="F20" s="3">
         <v>1100</v>
       </c>
-      <c r="E20" s="3">
+      <c r="G20" s="3">
         <v>1200</v>
       </c>
-      <c r="F20" s="3">
+      <c r="H20" s="3">
         <v>900</v>
       </c>
-      <c r="G20" s="3">
+      <c r="I20" s="3">
         <v>6100</v>
       </c>
-      <c r="H20" s="3">
+      <c r="J20" s="3">
         <v>700</v>
       </c>
-      <c r="I20" s="3">
+      <c r="K20" s="3">
         <v>5300</v>
       </c>
-      <c r="J20" s="3">
+      <c r="L20" s="3">
         <v>7700</v>
       </c>
-      <c r="K20" s="3">
+      <c r="M20" s="3">
         <v>900</v>
       </c>
-      <c r="L20" s="3">
+      <c r="N20" s="3">
         <v>4300</v>
       </c>
-      <c r="M20" s="3">
+      <c r="O20" s="3">
         <v>500</v>
       </c>
-      <c r="N20" s="3">
+      <c r="P20" s="3">
         <v>700</v>
       </c>
-      <c r="O20" s="3">
+      <c r="Q20" s="3">
         <v>2400</v>
       </c>
-      <c r="P20" s="3">
+      <c r="R20" s="3">
         <v>3700</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="S20" s="3">
         <v>1400</v>
       </c>
-      <c r="R20" s="3">
+      <c r="T20" s="3">
         <v>200</v>
       </c>
-      <c r="S20" s="3">
+      <c r="U20" s="3">
         <v>800</v>
       </c>
-      <c r="T20" s="3">
+      <c r="V20" s="3">
         <v>1200</v>
       </c>
-      <c r="U20" s="3">
+      <c r="W20" s="3">
         <v>-1800</v>
       </c>
-      <c r="V20" s="3">
+      <c r="X20" s="3">
         <v>-800</v>
       </c>
-      <c r="W20" s="3">
+      <c r="Y20" s="3">
         <v>3200</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Z20" s="3">
         <v>1700</v>
       </c>
-      <c r="Y20" s="3">
+      <c r="AA20" s="3">
         <v>-1100</v>
       </c>
-      <c r="Z20" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="AA20" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="21" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB20" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AC20" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="E21" s="3">
-        <v>-24800</v>
-      </c>
-      <c r="F21" s="3">
+      <c r="E21" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F21" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G21" s="3">
+        <v>-25000</v>
+      </c>
+      <c r="H21" s="3">
         <v>6000</v>
       </c>
-      <c r="G21" s="3">
-        <v>-22500</v>
-      </c>
-      <c r="H21" s="3">
-        <v>-60600</v>
-      </c>
       <c r="I21" s="3">
+        <v>-22700</v>
+      </c>
+      <c r="J21" s="3">
+        <v>-61100</v>
+      </c>
+      <c r="K21" s="3">
         <v>-10900</v>
       </c>
-      <c r="J21" s="3">
+      <c r="L21" s="3">
         <v>-118400</v>
       </c>
-      <c r="K21" s="3">
+      <c r="M21" s="3">
         <v>-16400</v>
       </c>
-      <c r="L21" s="3">
+      <c r="N21" s="3">
         <v>-31100</v>
       </c>
-      <c r="M21" s="3">
+      <c r="O21" s="3">
         <v>-28600</v>
       </c>
-      <c r="N21" s="3">
+      <c r="P21" s="3">
         <v>71200</v>
       </c>
-      <c r="O21" s="3">
+      <c r="Q21" s="3">
         <v>-128700</v>
       </c>
-      <c r="P21" s="3">
+      <c r="R21" s="3">
         <v>-37500</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="S21" s="3">
         <v>-25600</v>
       </c>
-      <c r="R21" s="3">
+      <c r="T21" s="3">
         <v>-30700</v>
       </c>
-      <c r="S21" s="3">
+      <c r="U21" s="3">
         <v>-35000</v>
       </c>
-      <c r="T21" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="U21" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V21" s="3" t="s">
         <v>3</v>
       </c>
       <c r="W21" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="X21" s="3">
+      <c r="X21" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Y21" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Z21" s="3">
         <v>-2300</v>
       </c>
-      <c r="Y21" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Z21" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AA21" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="22" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB21" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AC21" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="22" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>2600</v>
+      </c>
+      <c r="E22" s="3">
+        <v>2500</v>
+      </c>
+      <c r="F22" s="3">
         <v>2400</v>
       </c>
-      <c r="E22" s="3">
+      <c r="G22" s="3">
         <v>2200</v>
       </c>
-      <c r="F22" s="3">
+      <c r="H22" s="3">
         <v>2000</v>
       </c>
-      <c r="G22" s="3">
+      <c r="I22" s="3">
         <v>1700</v>
       </c>
-      <c r="H22" s="3">
+      <c r="J22" s="3">
         <v>1400</v>
       </c>
-      <c r="I22" s="3">
+      <c r="K22" s="3">
         <v>1200</v>
       </c>
-      <c r="J22" s="3">
+      <c r="L22" s="3">
         <v>4400</v>
-      </c>
-      <c r="K22" s="3">
-        <v>1100</v>
-      </c>
-      <c r="L22" s="3">
-        <v>1100</v>
       </c>
       <c r="M22" s="3">
         <v>1100</v>
       </c>
-      <c r="N22" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="O22" s="3" t="s">
-        <v>3</v>
+      <c r="N22" s="3">
+        <v>1100</v>
+      </c>
+      <c r="O22" s="3">
+        <v>1100</v>
       </c>
       <c r="P22" s="3" t="s">
         <v>3</v>
@@ -1753,11 +1832,11 @@
       <c r="S22" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="T22" s="3">
-        <v>0</v>
-      </c>
-      <c r="U22" s="3">
-        <v>0</v>
+      <c r="T22" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="U22" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="V22" s="3">
         <v>0</v>
@@ -1777,162 +1856,180 @@
       <c r="AA22" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB22" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
-        <v>-41200</v>
+        <v>7900</v>
       </c>
       <c r="E23" s="3">
-        <v>-28000</v>
+        <v>-13100</v>
       </c>
       <c r="F23" s="3">
+        <v>-41500</v>
+      </c>
+      <c r="G23" s="3">
+        <v>-28200</v>
+      </c>
+      <c r="H23" s="3">
         <v>2300</v>
       </c>
-      <c r="G23" s="3">
-        <v>-25900</v>
-      </c>
-      <c r="H23" s="3">
-        <v>-63500</v>
-      </c>
       <c r="I23" s="3">
+        <v>-26000</v>
+      </c>
+      <c r="J23" s="3">
+        <v>-63900</v>
+      </c>
+      <c r="K23" s="3">
         <v>-13200</v>
       </c>
-      <c r="J23" s="3">
+      <c r="L23" s="3">
         <v>-127000</v>
       </c>
-      <c r="K23" s="3">
+      <c r="M23" s="3">
         <v>-18600</v>
       </c>
-      <c r="L23" s="3">
+      <c r="N23" s="3">
         <v>-33100</v>
       </c>
-      <c r="M23" s="3">
+      <c r="O23" s="3">
         <v>-30400</v>
       </c>
-      <c r="N23" s="3">
+      <c r="P23" s="3">
         <v>70600</v>
       </c>
-      <c r="O23" s="3">
+      <c r="Q23" s="3">
         <v>-129400</v>
       </c>
-      <c r="P23" s="3">
+      <c r="R23" s="3">
         <v>-38000</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="S23" s="3">
         <v>-26200</v>
       </c>
-      <c r="R23" s="3">
+      <c r="T23" s="3">
         <v>-31200</v>
       </c>
-      <c r="S23" s="3">
+      <c r="U23" s="3">
         <v>-35400</v>
       </c>
-      <c r="T23" s="3">
+      <c r="V23" s="3">
         <v>-11500</v>
       </c>
-      <c r="U23" s="3">
+      <c r="W23" s="3">
         <v>-13900</v>
       </c>
-      <c r="V23" s="3">
+      <c r="X23" s="3">
         <v>-8100</v>
       </c>
-      <c r="W23" s="3">
+      <c r="Y23" s="3">
         <v>-9300</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Z23" s="3">
         <v>-2600</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="AA23" s="3">
         <v>-8500</v>
       </c>
-      <c r="Z23" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="AA23" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="24" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB23" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AC23" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="24" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
-        <v>700</v>
+        <v>100</v>
       </c>
       <c r="E24" s="3">
         <v>400</v>
       </c>
       <c r="F24" s="3">
+        <v>700</v>
+      </c>
+      <c r="G24" s="3">
+        <v>400</v>
+      </c>
+      <c r="H24" s="3">
         <v>1900</v>
       </c>
-      <c r="G24" s="3">
+      <c r="I24" s="3">
         <v>-200</v>
       </c>
-      <c r="H24" s="3">
+      <c r="J24" s="3">
         <v>100</v>
       </c>
-      <c r="I24" s="3">
+      <c r="K24" s="3">
         <v>100</v>
       </c>
-      <c r="J24" s="3">
+      <c r="L24" s="3">
         <v>900</v>
       </c>
-      <c r="K24" s="3">
+      <c r="M24" s="3">
         <v>400</v>
       </c>
-      <c r="L24" s="3">
+      <c r="N24" s="3">
         <v>400</v>
       </c>
-      <c r="M24" s="3">
+      <c r="O24" s="3">
         <v>200</v>
       </c>
-      <c r="N24" s="3">
+      <c r="P24" s="3">
         <v>100</v>
       </c>
-      <c r="O24" s="3">
-        <v>0</v>
-      </c>
-      <c r="P24" s="3">
-        <v>0</v>
-      </c>
       <c r="Q24" s="3">
+        <v>0</v>
+      </c>
+      <c r="R24" s="3">
+        <v>0</v>
+      </c>
+      <c r="S24" s="3">
         <v>300</v>
       </c>
-      <c r="R24" s="3">
-        <v>0</v>
-      </c>
-      <c r="S24" s="3">
-        <v>100</v>
-      </c>
       <c r="T24" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="U24" s="3">
         <v>100</v>
       </c>
       <c r="V24" s="3">
+        <v>100</v>
+      </c>
+      <c r="W24" s="3">
+        <v>100</v>
+      </c>
+      <c r="X24" s="3">
         <v>500</v>
-      </c>
-      <c r="W24" s="3">
-        <v>500</v>
-      </c>
-      <c r="X24" s="3">
-        <v>200</v>
       </c>
       <c r="Y24" s="3">
         <v>500</v>
       </c>
-      <c r="Z24" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="AA24" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="25" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="Z24" s="3">
+        <v>200</v>
+      </c>
+      <c r="AA24" s="3">
+        <v>500</v>
+      </c>
+      <c r="AB24" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AC24" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="25" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2008,162 +2105,180 @@
       <c r="AA25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB25" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
-        <v>-41900</v>
+        <v>7800</v>
       </c>
       <c r="E26" s="3">
-        <v>-28500</v>
+        <v>-13500</v>
       </c>
       <c r="F26" s="3">
+        <v>-42200</v>
+      </c>
+      <c r="G26" s="3">
+        <v>-28600</v>
+      </c>
+      <c r="H26" s="3">
         <v>400</v>
       </c>
-      <c r="G26" s="3">
-        <v>-25700</v>
-      </c>
-      <c r="H26" s="3">
-        <v>-63600</v>
-      </c>
       <c r="I26" s="3">
+        <v>-25900</v>
+      </c>
+      <c r="J26" s="3">
+        <v>-64000</v>
+      </c>
+      <c r="K26" s="3">
         <v>-13300</v>
       </c>
-      <c r="J26" s="3">
+      <c r="L26" s="3">
         <v>-127900</v>
       </c>
-      <c r="K26" s="3">
+      <c r="M26" s="3">
         <v>-18900</v>
       </c>
-      <c r="L26" s="3">
+      <c r="N26" s="3">
         <v>-33500</v>
       </c>
-      <c r="M26" s="3">
+      <c r="O26" s="3">
         <v>-30600</v>
       </c>
-      <c r="N26" s="3">
+      <c r="P26" s="3">
         <v>70500</v>
       </c>
-      <c r="O26" s="3">
+      <c r="Q26" s="3">
         <v>-129400</v>
       </c>
-      <c r="P26" s="3">
+      <c r="R26" s="3">
         <v>-38000</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="S26" s="3">
         <v>-26500</v>
       </c>
-      <c r="R26" s="3">
+      <c r="T26" s="3">
         <v>-31200</v>
       </c>
-      <c r="S26" s="3">
+      <c r="U26" s="3">
         <v>-35500</v>
       </c>
-      <c r="T26" s="3">
+      <c r="V26" s="3">
         <v>-11600</v>
       </c>
-      <c r="U26" s="3">
+      <c r="W26" s="3">
         <v>-14000</v>
       </c>
-      <c r="V26" s="3">
+      <c r="X26" s="3">
         <v>-8600</v>
       </c>
-      <c r="W26" s="3">
+      <c r="Y26" s="3">
         <v>-9800</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Z26" s="3">
         <v>-2800</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="AA26" s="3">
         <v>-9000</v>
       </c>
-      <c r="Z26" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="AA26" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="27" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB26" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AC26" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="27" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
-        <v>-41300</v>
+        <v>7900</v>
       </c>
       <c r="E27" s="3">
-        <v>-28200</v>
+        <v>-14300</v>
       </c>
       <c r="F27" s="3">
+        <v>-41600</v>
+      </c>
+      <c r="G27" s="3">
+        <v>-28400</v>
+      </c>
+      <c r="H27" s="3">
         <v>1700</v>
       </c>
-      <c r="G27" s="3">
-        <v>-25400</v>
-      </c>
-      <c r="H27" s="3">
-        <v>-62700</v>
-      </c>
       <c r="I27" s="3">
+        <v>-25600</v>
+      </c>
+      <c r="J27" s="3">
+        <v>-63100</v>
+      </c>
+      <c r="K27" s="3">
         <v>-13200</v>
       </c>
-      <c r="J27" s="3">
+      <c r="L27" s="3">
         <v>-123600</v>
       </c>
-      <c r="K27" s="3">
+      <c r="M27" s="3">
         <v>-18300</v>
       </c>
-      <c r="L27" s="3">
+      <c r="N27" s="3">
         <v>-33400</v>
       </c>
-      <c r="M27" s="3">
+      <c r="O27" s="3">
         <v>-30500</v>
       </c>
-      <c r="N27" s="3">
+      <c r="P27" s="3">
         <v>70500</v>
       </c>
-      <c r="O27" s="3">
+      <c r="Q27" s="3">
         <v>-129400</v>
       </c>
-      <c r="P27" s="3">
+      <c r="R27" s="3">
         <v>-38000</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="S27" s="3">
         <v>-26500</v>
       </c>
-      <c r="R27" s="3">
+      <c r="T27" s="3">
         <v>-31700</v>
       </c>
-      <c r="S27" s="3">
+      <c r="U27" s="3">
         <v>-37300</v>
       </c>
-      <c r="T27" s="3">
+      <c r="V27" s="3">
         <v>-13400</v>
       </c>
-      <c r="U27" s="3">
+      <c r="W27" s="3">
         <v>-15500</v>
       </c>
-      <c r="V27" s="3">
+      <c r="X27" s="3">
         <v>-10200</v>
       </c>
-      <c r="W27" s="3">
+      <c r="Y27" s="3">
         <v>-11200</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Z27" s="3">
         <v>-4200</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="AA27" s="3">
         <v>-8900</v>
       </c>
-      <c r="Z27" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="AA27" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="28" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB27" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AC27" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="28" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2239,8 +2354,14 @@
       <c r="AA28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB28" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2260,34 +2381,34 @@
         <v>0</v>
       </c>
       <c r="I29" s="3">
+        <v>0</v>
+      </c>
+      <c r="J29" s="3">
+        <v>0</v>
+      </c>
+      <c r="K29" s="3">
         <v>-800</v>
       </c>
-      <c r="J29" s="3">
+      <c r="L29" s="3">
         <v>-13800</v>
       </c>
-      <c r="K29" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L29" s="3">
+      <c r="M29" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N29" s="3">
         <v>-41200</v>
       </c>
-      <c r="M29" s="3">
+      <c r="O29" s="3">
         <v>-14800</v>
       </c>
-      <c r="N29" s="3">
+      <c r="P29" s="3">
         <v>-132800</v>
       </c>
-      <c r="O29" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="P29" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Q29" s="3">
-        <v>0</v>
-      </c>
-      <c r="R29" s="3">
-        <v>0</v>
+      <c r="Q29" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R29" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="S29" s="3">
         <v>0</v>
@@ -2316,8 +2437,14 @@
       <c r="AA29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB29" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2393,8 +2520,14 @@
       <c r="AA30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB30" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2470,162 +2603,180 @@
       <c r="AA31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB31" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>100</v>
+      </c>
+      <c r="E32" s="3">
+        <v>2600</v>
+      </c>
+      <c r="F32" s="3">
         <v>-1100</v>
       </c>
-      <c r="E32" s="3">
+      <c r="G32" s="3">
         <v>-1200</v>
       </c>
-      <c r="F32" s="3">
+      <c r="H32" s="3">
         <v>-900</v>
       </c>
-      <c r="G32" s="3">
+      <c r="I32" s="3">
         <v>-6100</v>
       </c>
-      <c r="H32" s="3">
+      <c r="J32" s="3">
         <v>-700</v>
       </c>
-      <c r="I32" s="3">
+      <c r="K32" s="3">
         <v>-5300</v>
       </c>
-      <c r="J32" s="3">
+      <c r="L32" s="3">
         <v>-7700</v>
       </c>
-      <c r="K32" s="3">
+      <c r="M32" s="3">
         <v>-900</v>
       </c>
-      <c r="L32" s="3">
+      <c r="N32" s="3">
         <v>-4300</v>
       </c>
-      <c r="M32" s="3">
+      <c r="O32" s="3">
         <v>-500</v>
       </c>
-      <c r="N32" s="3">
+      <c r="P32" s="3">
         <v>-700</v>
       </c>
-      <c r="O32" s="3">
+      <c r="Q32" s="3">
         <v>-2400</v>
       </c>
-      <c r="P32" s="3">
+      <c r="R32" s="3">
         <v>-3700</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="S32" s="3">
         <v>-1400</v>
       </c>
-      <c r="R32" s="3">
+      <c r="T32" s="3">
         <v>-200</v>
       </c>
-      <c r="S32" s="3">
+      <c r="U32" s="3">
         <v>-800</v>
       </c>
-      <c r="T32" s="3">
+      <c r="V32" s="3">
         <v>-1200</v>
       </c>
-      <c r="U32" s="3">
+      <c r="W32" s="3">
         <v>1800</v>
       </c>
-      <c r="V32" s="3">
+      <c r="X32" s="3">
         <v>800</v>
       </c>
-      <c r="W32" s="3">
+      <c r="Y32" s="3">
         <v>-3200</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Z32" s="3">
         <v>-1700</v>
       </c>
-      <c r="Y32" s="3">
+      <c r="AA32" s="3">
         <v>1100</v>
       </c>
-      <c r="Z32" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="AA32" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="33" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB32" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AC32" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="33" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
-        <v>-41300</v>
+        <v>7900</v>
       </c>
       <c r="E33" s="3">
-        <v>-28200</v>
+        <v>-14300</v>
       </c>
       <c r="F33" s="3">
+        <v>-41600</v>
+      </c>
+      <c r="G33" s="3">
+        <v>-28400</v>
+      </c>
+      <c r="H33" s="3">
         <v>1700</v>
       </c>
-      <c r="G33" s="3">
-        <v>-25400</v>
-      </c>
-      <c r="H33" s="3">
-        <v>-62700</v>
-      </c>
       <c r="I33" s="3">
+        <v>-25600</v>
+      </c>
+      <c r="J33" s="3">
+        <v>-63100</v>
+      </c>
+      <c r="K33" s="3">
         <v>-14000</v>
       </c>
-      <c r="J33" s="3">
+      <c r="L33" s="3">
         <v>-137500</v>
       </c>
-      <c r="K33" s="3">
+      <c r="M33" s="3">
         <v>-18300</v>
       </c>
-      <c r="L33" s="3">
+      <c r="N33" s="3">
         <v>-74500</v>
       </c>
-      <c r="M33" s="3">
+      <c r="O33" s="3">
         <v>-45400</v>
       </c>
-      <c r="N33" s="3">
+      <c r="P33" s="3">
         <v>-62300</v>
       </c>
-      <c r="O33" s="3">
+      <c r="Q33" s="3">
         <v>-129400</v>
       </c>
-      <c r="P33" s="3">
+      <c r="R33" s="3">
         <v>-38000</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="S33" s="3">
         <v>-26500</v>
       </c>
-      <c r="R33" s="3">
+      <c r="T33" s="3">
         <v>-31700</v>
       </c>
-      <c r="S33" s="3">
+      <c r="U33" s="3">
         <v>-37300</v>
       </c>
-      <c r="T33" s="3">
+      <c r="V33" s="3">
         <v>-13400</v>
       </c>
-      <c r="U33" s="3">
+      <c r="W33" s="3">
         <v>-15500</v>
       </c>
-      <c r="V33" s="3">
+      <c r="X33" s="3">
         <v>-10200</v>
       </c>
-      <c r="W33" s="3">
+      <c r="Y33" s="3">
         <v>-11200</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Z33" s="3">
         <v>-4200</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="AA33" s="3">
         <v>-8900</v>
       </c>
-      <c r="Z33" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="AA33" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="34" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB33" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AC33" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="34" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2701,167 +2852,185 @@
       <c r="AA34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB34" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
-        <v>-41300</v>
+        <v>7900</v>
       </c>
       <c r="E35" s="3">
-        <v>-28200</v>
+        <v>-14300</v>
       </c>
       <c r="F35" s="3">
+        <v>-41600</v>
+      </c>
+      <c r="G35" s="3">
+        <v>-28400</v>
+      </c>
+      <c r="H35" s="3">
         <v>1700</v>
       </c>
-      <c r="G35" s="3">
-        <v>-25400</v>
-      </c>
-      <c r="H35" s="3">
-        <v>-62700</v>
-      </c>
       <c r="I35" s="3">
+        <v>-25600</v>
+      </c>
+      <c r="J35" s="3">
+        <v>-63100</v>
+      </c>
+      <c r="K35" s="3">
         <v>-14000</v>
       </c>
-      <c r="J35" s="3">
+      <c r="L35" s="3">
         <v>-137500</v>
       </c>
-      <c r="K35" s="3">
+      <c r="M35" s="3">
         <v>-18300</v>
       </c>
-      <c r="L35" s="3">
+      <c r="N35" s="3">
         <v>-74500</v>
       </c>
-      <c r="M35" s="3">
+      <c r="O35" s="3">
         <v>-45400</v>
       </c>
-      <c r="N35" s="3">
+      <c r="P35" s="3">
         <v>-62300</v>
       </c>
-      <c r="O35" s="3">
+      <c r="Q35" s="3">
         <v>-129400</v>
       </c>
-      <c r="P35" s="3">
+      <c r="R35" s="3">
         <v>-38000</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="S35" s="3">
         <v>-26500</v>
       </c>
-      <c r="R35" s="3">
+      <c r="T35" s="3">
         <v>-31700</v>
       </c>
-      <c r="S35" s="3">
+      <c r="U35" s="3">
         <v>-37300</v>
       </c>
-      <c r="T35" s="3">
+      <c r="V35" s="3">
         <v>-13400</v>
       </c>
-      <c r="U35" s="3">
+      <c r="W35" s="3">
         <v>-15500</v>
       </c>
-      <c r="V35" s="3">
+      <c r="X35" s="3">
         <v>-10200</v>
       </c>
-      <c r="W35" s="3">
+      <c r="Y35" s="3">
         <v>-11200</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Z35" s="3">
         <v>-4200</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="AA35" s="3">
         <v>-8900</v>
       </c>
-      <c r="Z35" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="AA35" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="37" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB35" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AC35" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="37" spans="2:29" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:27" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45291</v>
+      </c>
+      <c r="E38" s="2">
+        <v>45199</v>
+      </c>
+      <c r="F38" s="2">
         <v>45107</v>
       </c>
-      <c r="E38" s="2">
+      <c r="G38" s="2">
         <v>45016</v>
       </c>
-      <c r="F38" s="2">
+      <c r="H38" s="2">
         <v>44926</v>
       </c>
-      <c r="G38" s="2">
+      <c r="I38" s="2">
         <v>44834</v>
       </c>
-      <c r="H38" s="2">
+      <c r="J38" s="2">
         <v>44742</v>
       </c>
-      <c r="I38" s="2">
+      <c r="K38" s="2">
         <v>44651</v>
       </c>
-      <c r="J38" s="2">
+      <c r="L38" s="2">
         <v>44561</v>
       </c>
-      <c r="K38" s="2">
+      <c r="M38" s="2">
         <v>44469</v>
       </c>
-      <c r="L38" s="2">
+      <c r="N38" s="2">
         <v>44377</v>
       </c>
-      <c r="M38" s="2">
+      <c r="O38" s="2">
         <v>44286</v>
       </c>
-      <c r="N38" s="2">
+      <c r="P38" s="2">
         <v>44196</v>
       </c>
-      <c r="O38" s="2">
+      <c r="Q38" s="2">
         <v>44104</v>
       </c>
-      <c r="P38" s="2">
+      <c r="R38" s="2">
         <v>44012</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="S38" s="2">
         <v>43921</v>
       </c>
-      <c r="R38" s="2">
+      <c r="T38" s="2">
         <v>43830</v>
       </c>
-      <c r="S38" s="2">
+      <c r="U38" s="2">
         <v>43738</v>
       </c>
-      <c r="T38" s="2">
+      <c r="V38" s="2">
         <v>43646</v>
       </c>
-      <c r="U38" s="2">
+      <c r="W38" s="2">
         <v>43555</v>
       </c>
-      <c r="V38" s="2">
+      <c r="X38" s="2">
         <v>43465</v>
       </c>
-      <c r="W38" s="2">
+      <c r="Y38" s="2">
         <v>43373</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Z38" s="2">
         <v>43281</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="AA38" s="2">
         <v>43190</v>
       </c>
-      <c r="Z38" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="AA38" s="2" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="39" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB38" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="AC38" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="39" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2889,8 +3058,10 @@
       <c r="Y39" s="3"/>
       <c r="Z39" s="3"/>
       <c r="AA39" s="3"/>
-    </row>
-    <row r="40" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB39" s="3"/>
+      <c r="AC39" s="3"/>
+    </row>
+    <row r="40" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2918,68 +3089,70 @@
       <c r="Y40" s="3"/>
       <c r="Z40" s="3"/>
       <c r="AA40" s="3"/>
-    </row>
-    <row r="41" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB40" s="3"/>
+      <c r="AC40" s="3"/>
+    </row>
+    <row r="41" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
-        <v>90800</v>
+        <v>63200</v>
       </c>
       <c r="E41" s="3">
-        <v>80000</v>
+        <v>47000</v>
       </c>
       <c r="F41" s="3">
-        <v>108200</v>
+        <v>91500</v>
       </c>
       <c r="G41" s="3">
-        <v>98300</v>
+        <v>80500</v>
       </c>
       <c r="H41" s="3">
-        <v>94900</v>
+        <v>108900</v>
       </c>
       <c r="I41" s="3">
+        <v>99000</v>
+      </c>
+      <c r="J41" s="3">
+        <v>95500</v>
+      </c>
+      <c r="K41" s="3">
         <v>57300</v>
       </c>
-      <c r="J41" s="3">
+      <c r="L41" s="3">
         <v>44600</v>
       </c>
-      <c r="K41" s="3">
+      <c r="M41" s="3">
         <v>70200</v>
       </c>
-      <c r="L41" s="3">
+      <c r="N41" s="3">
         <v>117900</v>
       </c>
-      <c r="M41" s="3">
+      <c r="O41" s="3">
         <v>257300</v>
       </c>
-      <c r="N41" s="3">
+      <c r="P41" s="3">
         <v>84800</v>
       </c>
-      <c r="O41" s="3">
+      <c r="Q41" s="3">
         <v>11500</v>
       </c>
-      <c r="P41" s="3">
+      <c r="R41" s="3">
         <v>18500</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="S41" s="3">
         <v>20100</v>
       </c>
-      <c r="R41" s="3">
+      <c r="T41" s="3">
         <v>26700</v>
       </c>
-      <c r="S41" s="3">
+      <c r="U41" s="3">
         <v>8500</v>
       </c>
-      <c r="T41" s="3">
+      <c r="V41" s="3">
         <v>8000</v>
       </c>
-      <c r="U41" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="V41" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W41" s="3" t="s">
         <v>3</v>
       </c>
@@ -2995,68 +3168,74 @@
       <c r="AA41" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="42" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB41" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AC41" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="42" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>10000</v>
+      </c>
+      <c r="E42" s="3">
+        <v>3100</v>
+      </c>
+      <c r="F42" s="3">
         <v>3000</v>
-      </c>
-      <c r="E42" s="3">
-        <v>3000</v>
-      </c>
-      <c r="F42" s="3">
-        <v>32100</v>
       </c>
       <c r="G42" s="3">
         <v>3000</v>
       </c>
       <c r="H42" s="3">
-        <v>2900</v>
+        <v>32300</v>
       </c>
       <c r="I42" s="3">
+        <v>3000</v>
+      </c>
+      <c r="J42" s="3">
+        <v>3000</v>
+      </c>
+      <c r="K42" s="3">
         <v>900</v>
       </c>
-      <c r="J42" s="3">
+      <c r="L42" s="3">
         <v>69600</v>
       </c>
-      <c r="K42" s="3">
+      <c r="M42" s="3">
         <v>58300</v>
       </c>
-      <c r="L42" s="3">
+      <c r="N42" s="3">
         <v>146500</v>
       </c>
-      <c r="M42" s="3">
+      <c r="O42" s="3">
         <v>47000</v>
       </c>
-      <c r="N42" s="3">
+      <c r="P42" s="3">
         <v>81500</v>
       </c>
-      <c r="O42" s="3">
+      <c r="Q42" s="3">
         <v>155400</v>
       </c>
-      <c r="P42" s="3">
+      <c r="R42" s="3">
         <v>245400</v>
       </c>
-      <c r="Q42" s="3">
+      <c r="S42" s="3">
         <v>242400</v>
       </c>
-      <c r="R42" s="3">
+      <c r="T42" s="3">
         <v>222800</v>
       </c>
-      <c r="S42" s="3">
+      <c r="U42" s="3">
         <v>16200</v>
       </c>
-      <c r="T42" s="3">
+      <c r="V42" s="3">
         <v>38000</v>
       </c>
-      <c r="U42" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="V42" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W42" s="3" t="s">
         <v>3</v>
       </c>
@@ -3072,68 +3251,74 @@
       <c r="AA42" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="43" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB42" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AC42" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="43" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
-        <v>53400</v>
+        <v>52800</v>
       </c>
       <c r="E43" s="3">
-        <v>37000</v>
+        <v>50200</v>
       </c>
       <c r="F43" s="3">
-        <v>57000</v>
+        <v>53800</v>
       </c>
       <c r="G43" s="3">
-        <v>46900</v>
+        <v>37200</v>
       </c>
       <c r="H43" s="3">
-        <v>48700</v>
+        <v>57400</v>
       </c>
       <c r="I43" s="3">
+        <v>47200</v>
+      </c>
+      <c r="J43" s="3">
+        <v>49000</v>
+      </c>
+      <c r="K43" s="3">
         <v>41500</v>
       </c>
-      <c r="J43" s="3">
+      <c r="L43" s="3">
         <v>35100</v>
       </c>
-      <c r="K43" s="3">
+      <c r="M43" s="3">
         <v>35300</v>
       </c>
-      <c r="L43" s="3">
+      <c r="N43" s="3">
         <v>44300</v>
       </c>
-      <c r="M43" s="3">
+      <c r="O43" s="3">
         <v>35100</v>
       </c>
-      <c r="N43" s="3">
+      <c r="P43" s="3">
         <v>38000</v>
       </c>
-      <c r="O43" s="3">
+      <c r="Q43" s="3">
         <v>50100</v>
       </c>
-      <c r="P43" s="3">
+      <c r="R43" s="3">
         <v>34900</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="S43" s="3">
         <v>36800</v>
       </c>
-      <c r="R43" s="3">
+      <c r="T43" s="3">
         <v>33200</v>
       </c>
-      <c r="S43" s="3">
+      <c r="U43" s="3">
         <v>27800</v>
       </c>
-      <c r="T43" s="3">
+      <c r="V43" s="3">
         <v>31100</v>
       </c>
-      <c r="U43" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="V43" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W43" s="3" t="s">
         <v>3</v>
       </c>
@@ -3149,68 +3334,74 @@
       <c r="AA43" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="44" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB43" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AC43" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="44" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
-        <v>25200</v>
+        <v>30200</v>
       </c>
       <c r="E44" s="3">
-        <v>30300</v>
+        <v>24700</v>
       </c>
       <c r="F44" s="3">
-        <v>32100</v>
+        <v>25400</v>
       </c>
       <c r="G44" s="3">
-        <v>23500</v>
+        <v>30500</v>
       </c>
       <c r="H44" s="3">
-        <v>29300</v>
+        <v>32300</v>
       </c>
       <c r="I44" s="3">
+        <v>23700</v>
+      </c>
+      <c r="J44" s="3">
         <v>29500</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
+        <v>29500</v>
+      </c>
+      <c r="L44" s="3">
         <v>35300</v>
       </c>
-      <c r="K44" s="3">
+      <c r="M44" s="3">
         <v>38000</v>
       </c>
-      <c r="L44" s="3">
+      <c r="N44" s="3">
         <v>38600</v>
       </c>
-      <c r="M44" s="3">
+      <c r="O44" s="3">
         <v>37400</v>
       </c>
-      <c r="N44" s="3">
+      <c r="P44" s="3">
         <v>20700</v>
       </c>
-      <c r="O44" s="3">
+      <c r="Q44" s="3">
         <v>13500</v>
       </c>
-      <c r="P44" s="3">
+      <c r="R44" s="3">
         <v>13700</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="S44" s="3">
         <v>10300</v>
       </c>
-      <c r="R44" s="3">
+      <c r="T44" s="3">
         <v>11300</v>
       </c>
-      <c r="S44" s="3">
+      <c r="U44" s="3">
         <v>8100</v>
       </c>
-      <c r="T44" s="3">
+      <c r="V44" s="3">
         <v>5000</v>
       </c>
-      <c r="U44" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="V44" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W44" s="3" t="s">
         <v>3</v>
       </c>
@@ -3226,68 +3417,74 @@
       <c r="AA44" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="45" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB44" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AC44" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="45" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
-        <v>26700</v>
+        <v>24500</v>
       </c>
       <c r="E45" s="3">
-        <v>24400</v>
+        <v>32400</v>
       </c>
       <c r="F45" s="3">
-        <v>28800</v>
+        <v>26900</v>
       </c>
       <c r="G45" s="3">
-        <v>59700</v>
+        <v>24500</v>
       </c>
       <c r="H45" s="3">
-        <v>103500</v>
+        <v>29000</v>
       </c>
       <c r="I45" s="3">
+        <v>60100</v>
+      </c>
+      <c r="J45" s="3">
+        <v>104200</v>
+      </c>
+      <c r="K45" s="3">
         <v>129100</v>
       </c>
-      <c r="J45" s="3">
+      <c r="L45" s="3">
         <v>128800</v>
       </c>
-      <c r="K45" s="3">
+      <c r="M45" s="3">
         <v>85400</v>
       </c>
-      <c r="L45" s="3">
+      <c r="N45" s="3">
         <v>33100</v>
       </c>
-      <c r="M45" s="3">
+      <c r="O45" s="3">
         <v>27600</v>
       </c>
-      <c r="N45" s="3">
+      <c r="P45" s="3">
         <v>32800</v>
       </c>
-      <c r="O45" s="3">
+      <c r="Q45" s="3">
         <v>29600</v>
       </c>
-      <c r="P45" s="3">
+      <c r="R45" s="3">
         <v>17500</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="S45" s="3">
         <v>18600</v>
       </c>
-      <c r="R45" s="3">
+      <c r="T45" s="3">
         <v>18600</v>
       </c>
-      <c r="S45" s="3">
+      <c r="U45" s="3">
         <v>16200</v>
       </c>
-      <c r="T45" s="3">
+      <c r="V45" s="3">
         <v>11300</v>
       </c>
-      <c r="U45" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="V45" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W45" s="3" t="s">
         <v>3</v>
       </c>
@@ -3303,68 +3500,74 @@
       <c r="AA45" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="46" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AC45" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="46" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
-        <v>199200</v>
+        <v>180700</v>
       </c>
       <c r="E46" s="3">
-        <v>174600</v>
+        <v>157300</v>
       </c>
       <c r="F46" s="3">
-        <v>258200</v>
+        <v>200600</v>
       </c>
       <c r="G46" s="3">
-        <v>231400</v>
+        <v>175800</v>
       </c>
       <c r="H46" s="3">
-        <v>279300</v>
+        <v>260000</v>
       </c>
       <c r="I46" s="3">
+        <v>233000</v>
+      </c>
+      <c r="J46" s="3">
+        <v>281200</v>
+      </c>
+      <c r="K46" s="3">
         <v>258300</v>
       </c>
-      <c r="J46" s="3">
+      <c r="L46" s="3">
         <v>313400</v>
       </c>
-      <c r="K46" s="3">
+      <c r="M46" s="3">
         <v>287200</v>
       </c>
-      <c r="L46" s="3">
+      <c r="N46" s="3">
         <v>380400</v>
       </c>
-      <c r="M46" s="3">
+      <c r="O46" s="3">
         <v>404400</v>
       </c>
-      <c r="N46" s="3">
+      <c r="P46" s="3">
         <v>257700</v>
       </c>
-      <c r="O46" s="3">
+      <c r="Q46" s="3">
         <v>260200</v>
       </c>
-      <c r="P46" s="3">
+      <c r="R46" s="3">
         <v>330000</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="S46" s="3">
         <v>328200</v>
       </c>
-      <c r="R46" s="3">
+      <c r="T46" s="3">
         <v>312600</v>
       </c>
-      <c r="S46" s="3">
+      <c r="U46" s="3">
         <v>76800</v>
       </c>
-      <c r="T46" s="3">
+      <c r="V46" s="3">
         <v>93400</v>
       </c>
-      <c r="U46" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="V46" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W46" s="3" t="s">
         <v>3</v>
       </c>
@@ -3380,50 +3583,56 @@
       <c r="AA46" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="47" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB46" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AC46" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="47" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
-        <v>12100</v>
+        <v>7100</v>
       </c>
       <c r="E47" s="3">
-        <v>12500</v>
+        <v>9000</v>
       </c>
       <c r="F47" s="3">
-        <v>12500</v>
+        <v>12200</v>
       </c>
       <c r="G47" s="3">
+        <v>12600</v>
+      </c>
+      <c r="H47" s="3">
+        <v>12600</v>
+      </c>
+      <c r="I47" s="3">
         <v>9300</v>
       </c>
-      <c r="H47" s="3">
-        <v>9700</v>
-      </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
+        <v>9800</v>
+      </c>
+      <c r="K47" s="3">
         <v>3800</v>
       </c>
-      <c r="J47" s="3">
+      <c r="L47" s="3">
         <v>4500</v>
       </c>
-      <c r="K47" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L47" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M47" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N47" s="3">
+      <c r="N47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P47" s="3">
         <v>5900</v>
       </c>
-      <c r="O47" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="P47" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q47" s="3" t="s">
         <v>3</v>
       </c>
@@ -3433,11 +3642,11 @@
       <c r="S47" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="T47" s="3">
-        <v>0</v>
-      </c>
-      <c r="U47" s="3">
-        <v>0</v>
+      <c r="T47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="U47" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="V47" s="3">
         <v>0</v>
@@ -3457,68 +3666,74 @@
       <c r="AA47" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB47" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
-        <v>23100</v>
+        <v>22200</v>
       </c>
       <c r="E48" s="3">
-        <v>22000</v>
+        <v>24100</v>
       </c>
       <c r="F48" s="3">
-        <v>23500</v>
+        <v>23300</v>
       </c>
       <c r="G48" s="3">
-        <v>25600</v>
+        <v>22200</v>
       </c>
       <c r="H48" s="3">
-        <v>27300</v>
+        <v>23700</v>
       </c>
       <c r="I48" s="3">
-        <v>28300</v>
+        <v>25800</v>
       </c>
       <c r="J48" s="3">
         <v>27400</v>
       </c>
       <c r="K48" s="3">
+        <v>28300</v>
+      </c>
+      <c r="L48" s="3">
+        <v>27400</v>
+      </c>
+      <c r="M48" s="3">
         <v>31400</v>
       </c>
-      <c r="L48" s="3">
+      <c r="N48" s="3">
         <v>28600</v>
       </c>
-      <c r="M48" s="3">
+      <c r="O48" s="3">
         <v>21000</v>
       </c>
-      <c r="N48" s="3">
+      <c r="P48" s="3">
         <v>21100</v>
       </c>
-      <c r="O48" s="3">
+      <c r="Q48" s="3">
         <v>18100</v>
       </c>
-      <c r="P48" s="3">
+      <c r="R48" s="3">
         <v>11900</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="S48" s="3">
         <v>7600</v>
       </c>
-      <c r="R48" s="3">
+      <c r="T48" s="3">
         <v>7500</v>
       </c>
-      <c r="S48" s="3">
+      <c r="U48" s="3">
         <v>6100</v>
       </c>
-      <c r="T48" s="3">
+      <c r="V48" s="3">
         <v>3500</v>
       </c>
-      <c r="U48" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="V48" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W48" s="3" t="s">
         <v>3</v>
       </c>
@@ -3534,38 +3749,44 @@
       <c r="AA48" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="49" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB48" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AC48" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="49" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>15300</v>
+      </c>
+      <c r="E49" s="3">
+        <v>15300</v>
+      </c>
+      <c r="F49" s="3">
+        <v>15300</v>
+      </c>
+      <c r="G49" s="3">
+        <v>15300</v>
+      </c>
+      <c r="H49" s="3">
+        <v>15300</v>
+      </c>
+      <c r="I49" s="3">
+        <v>15300</v>
+      </c>
+      <c r="J49" s="3">
+        <v>15300</v>
+      </c>
+      <c r="K49" s="3">
         <v>15200</v>
       </c>
-      <c r="E49" s="3">
+      <c r="L49" s="3">
         <v>15200</v>
       </c>
-      <c r="F49" s="3">
-        <v>15200</v>
-      </c>
-      <c r="G49" s="3">
-        <v>15200</v>
-      </c>
-      <c r="H49" s="3">
-        <v>15200</v>
-      </c>
-      <c r="I49" s="3">
-        <v>15200</v>
-      </c>
-      <c r="J49" s="3">
-        <v>15200</v>
-      </c>
-      <c r="K49" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L49" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M49" s="3" t="s">
         <v>3</v>
       </c>
@@ -3578,11 +3799,11 @@
       <c r="P49" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q49" s="3">
-        <v>0</v>
-      </c>
-      <c r="R49" s="3">
-        <v>0</v>
+      <c r="Q49" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R49" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="S49" s="3">
         <v>0</v>
@@ -3611,8 +3832,14 @@
       <c r="AA49" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="50" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB49" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC49" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -3688,8 +3915,14 @@
       <c r="AA50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB50" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -3765,68 +3998,74 @@
       <c r="AA51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB51" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>6300</v>
+      </c>
+      <c r="E52" s="3">
+        <v>6500</v>
+      </c>
+      <c r="F52" s="3">
         <v>5300</v>
       </c>
-      <c r="E52" s="3">
+      <c r="G52" s="3">
         <v>4700</v>
       </c>
-      <c r="F52" s="3">
-        <v>4800</v>
-      </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
+        <v>4900</v>
+      </c>
+      <c r="I52" s="3">
         <v>5300</v>
       </c>
-      <c r="H52" s="3">
-        <v>5100</v>
-      </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
+        <v>5200</v>
+      </c>
+      <c r="K52" s="3">
         <v>5000</v>
       </c>
-      <c r="J52" s="3">
+      <c r="L52" s="3">
         <v>3200</v>
       </c>
-      <c r="K52" s="3">
+      <c r="M52" s="3">
         <v>30000</v>
       </c>
-      <c r="L52" s="3">
+      <c r="N52" s="3">
         <v>14700</v>
       </c>
-      <c r="M52" s="3">
+      <c r="O52" s="3">
         <v>11000</v>
       </c>
-      <c r="N52" s="3">
+      <c r="P52" s="3">
         <v>3400</v>
       </c>
-      <c r="O52" s="3">
+      <c r="Q52" s="3">
         <v>3900</v>
       </c>
-      <c r="P52" s="3">
+      <c r="R52" s="3">
         <v>3200</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="S52" s="3">
         <v>2100</v>
       </c>
-      <c r="R52" s="3">
+      <c r="T52" s="3">
         <v>1300</v>
       </c>
-      <c r="S52" s="3">
+      <c r="U52" s="3">
         <v>800</v>
       </c>
-      <c r="T52" s="3">
+      <c r="V52" s="3">
         <v>800</v>
       </c>
-      <c r="U52" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="V52" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W52" s="3" t="s">
         <v>3</v>
       </c>
@@ -3842,8 +4081,14 @@
       <c r="AA52" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="53" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB52" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AC52" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="53" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -3919,68 +4164,74 @@
       <c r="AA53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB53" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
-        <v>254900</v>
+        <v>231600</v>
       </c>
       <c r="E54" s="3">
-        <v>229000</v>
+        <v>212000</v>
       </c>
       <c r="F54" s="3">
-        <v>314300</v>
+        <v>256600</v>
       </c>
       <c r="G54" s="3">
-        <v>286800</v>
+        <v>230500</v>
       </c>
       <c r="H54" s="3">
-        <v>336700</v>
+        <v>316400</v>
       </c>
       <c r="I54" s="3">
+        <v>288700</v>
+      </c>
+      <c r="J54" s="3">
+        <v>339000</v>
+      </c>
+      <c r="K54" s="3">
         <v>310600</v>
       </c>
-      <c r="J54" s="3">
+      <c r="L54" s="3">
         <v>363700</v>
       </c>
-      <c r="K54" s="3">
+      <c r="M54" s="3">
         <v>348600</v>
       </c>
-      <c r="L54" s="3">
+      <c r="N54" s="3">
         <v>423600</v>
       </c>
-      <c r="M54" s="3">
+      <c r="O54" s="3">
         <v>436300</v>
       </c>
-      <c r="N54" s="3">
+      <c r="P54" s="3">
         <v>288200</v>
       </c>
-      <c r="O54" s="3">
+      <c r="Q54" s="3">
         <v>282200</v>
       </c>
-      <c r="P54" s="3">
+      <c r="R54" s="3">
         <v>345100</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="S54" s="3">
         <v>337900</v>
       </c>
-      <c r="R54" s="3">
+      <c r="T54" s="3">
         <v>321300</v>
       </c>
-      <c r="S54" s="3">
+      <c r="U54" s="3">
         <v>83700</v>
       </c>
-      <c r="T54" s="3">
+      <c r="V54" s="3">
         <v>97700</v>
       </c>
-      <c r="U54" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="V54" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W54" s="3" t="s">
         <v>3</v>
       </c>
@@ -3996,8 +4247,14 @@
       <c r="AA54" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="55" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB54" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AC54" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="55" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -4025,8 +4282,10 @@
       <c r="Y55" s="3"/>
       <c r="Z55" s="3"/>
       <c r="AA55" s="3"/>
-    </row>
-    <row r="56" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB55" s="3"/>
+      <c r="AC55" s="3"/>
+    </row>
+    <row r="56" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -4054,68 +4313,70 @@
       <c r="Y56" s="3"/>
       <c r="Z56" s="3"/>
       <c r="AA56" s="3"/>
-    </row>
-    <row r="57" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB56" s="3"/>
+      <c r="AC56" s="3"/>
+    </row>
+    <row r="57" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
-        <v>17900</v>
+        <v>22100</v>
       </c>
       <c r="E57" s="3">
-        <v>16900</v>
+        <v>22700</v>
       </c>
       <c r="F57" s="3">
-        <v>39000</v>
+        <v>18000</v>
       </c>
       <c r="G57" s="3">
-        <v>24800</v>
+        <v>17000</v>
       </c>
       <c r="H57" s="3">
-        <v>21000</v>
+        <v>39300</v>
       </c>
       <c r="I57" s="3">
+        <v>25000</v>
+      </c>
+      <c r="J57" s="3">
+        <v>21100</v>
+      </c>
+      <c r="K57" s="3">
         <v>18400</v>
       </c>
-      <c r="J57" s="3">
+      <c r="L57" s="3">
         <v>22200</v>
       </c>
-      <c r="K57" s="3">
+      <c r="M57" s="3">
         <v>16600</v>
       </c>
-      <c r="L57" s="3">
+      <c r="N57" s="3">
         <v>10600</v>
       </c>
-      <c r="M57" s="3">
+      <c r="O57" s="3">
         <v>17500</v>
       </c>
-      <c r="N57" s="3">
+      <c r="P57" s="3">
         <v>19700</v>
       </c>
-      <c r="O57" s="3">
+      <c r="Q57" s="3">
         <v>17600</v>
       </c>
-      <c r="P57" s="3">
+      <c r="R57" s="3">
         <v>15200</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="S57" s="3">
         <v>14900</v>
       </c>
-      <c r="R57" s="3">
+      <c r="T57" s="3">
         <v>9700</v>
       </c>
-      <c r="S57" s="3">
+      <c r="U57" s="3">
         <v>7200</v>
       </c>
-      <c r="T57" s="3">
+      <c r="V57" s="3">
         <v>5300</v>
       </c>
-      <c r="U57" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="V57" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W57" s="3" t="s">
         <v>3</v>
       </c>
@@ -4131,68 +4392,74 @@
       <c r="AA57" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="58" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB57" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AC57" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="58" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
-        <v>201100</v>
+        <v>122100</v>
       </c>
       <c r="E58" s="3">
-        <v>197100</v>
+        <v>122100</v>
       </c>
       <c r="F58" s="3">
+        <v>202400</v>
+      </c>
+      <c r="G58" s="3">
+        <v>198500</v>
+      </c>
+      <c r="H58" s="3">
+        <v>122100</v>
+      </c>
+      <c r="I58" s="3">
+        <v>122100</v>
+      </c>
+      <c r="J58" s="3">
+        <v>122100</v>
+      </c>
+      <c r="K58" s="3">
         <v>121200</v>
       </c>
-      <c r="G58" s="3">
+      <c r="L58" s="3">
         <v>121200</v>
       </c>
-      <c r="H58" s="3">
-        <v>121200</v>
-      </c>
-      <c r="I58" s="3">
-        <v>121200</v>
-      </c>
-      <c r="J58" s="3">
-        <v>121200</v>
-      </c>
-      <c r="K58" s="3">
+      <c r="M58" s="3">
         <v>124800</v>
       </c>
-      <c r="L58" s="3">
+      <c r="N58" s="3">
         <v>124800</v>
       </c>
-      <c r="M58" s="3">
+      <c r="O58" s="3">
         <v>122200</v>
       </c>
-      <c r="N58" s="3">
+      <c r="P58" s="3">
         <v>122200</v>
       </c>
-      <c r="O58" s="3">
+      <c r="Q58" s="3">
         <v>129400</v>
       </c>
-      <c r="P58" s="3">
+      <c r="R58" s="3">
         <v>129400</v>
       </c>
-      <c r="Q58" s="3">
+      <c r="S58" s="3">
         <v>137500</v>
       </c>
-      <c r="R58" s="3">
+      <c r="T58" s="3">
         <v>135200</v>
       </c>
-      <c r="S58" s="3">
+      <c r="U58" s="3">
         <v>135200</v>
       </c>
-      <c r="T58" s="3">
+      <c r="V58" s="3">
         <v>134100</v>
       </c>
-      <c r="U58" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="V58" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W58" s="3" t="s">
         <v>3</v>
       </c>
@@ -4208,68 +4475,74 @@
       <c r="AA58" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="59" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB58" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AC58" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="59" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>309000</v>
+        <v>286700</v>
       </c>
       <c r="E59" s="3">
-        <v>241400</v>
+        <v>272900</v>
       </c>
       <c r="F59" s="3">
-        <v>278700</v>
+        <v>311100</v>
       </c>
       <c r="G59" s="3">
-        <v>266000</v>
+        <v>243100</v>
       </c>
       <c r="H59" s="3">
-        <v>296500</v>
+        <v>280600</v>
       </c>
       <c r="I59" s="3">
+        <v>267800</v>
+      </c>
+      <c r="J59" s="3">
+        <v>298500</v>
+      </c>
+      <c r="K59" s="3">
         <v>226700</v>
       </c>
-      <c r="J59" s="3">
+      <c r="L59" s="3">
         <v>275500</v>
       </c>
-      <c r="K59" s="3">
+      <c r="M59" s="3">
         <v>293600</v>
       </c>
-      <c r="L59" s="3">
+      <c r="N59" s="3">
         <v>375700</v>
       </c>
-      <c r="M59" s="3">
+      <c r="O59" s="3">
         <v>312500</v>
       </c>
-      <c r="N59" s="3">
+      <c r="P59" s="3">
         <v>330500</v>
       </c>
-      <c r="O59" s="3">
+      <c r="Q59" s="3">
         <v>268200</v>
       </c>
-      <c r="P59" s="3">
+      <c r="R59" s="3">
         <v>204700</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="S59" s="3">
         <v>157000</v>
       </c>
-      <c r="R59" s="3">
+      <c r="T59" s="3">
         <v>126000</v>
       </c>
-      <c r="S59" s="3">
+      <c r="U59" s="3">
         <v>93900</v>
       </c>
-      <c r="T59" s="3">
+      <c r="V59" s="3">
         <v>76900</v>
       </c>
-      <c r="U59" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="V59" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W59" s="3" t="s">
         <v>3</v>
       </c>
@@ -4285,68 +4558,74 @@
       <c r="AA59" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="60" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB59" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AC59" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="60" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
-        <v>527900</v>
+        <v>430900</v>
       </c>
       <c r="E60" s="3">
-        <v>455500</v>
+        <v>417600</v>
       </c>
       <c r="F60" s="3">
-        <v>438900</v>
+        <v>531500</v>
       </c>
       <c r="G60" s="3">
-        <v>412000</v>
+        <v>458600</v>
       </c>
       <c r="H60" s="3">
-        <v>438700</v>
+        <v>441900</v>
       </c>
       <c r="I60" s="3">
+        <v>414800</v>
+      </c>
+      <c r="J60" s="3">
+        <v>441700</v>
+      </c>
+      <c r="K60" s="3">
         <v>366300</v>
       </c>
-      <c r="J60" s="3">
+      <c r="L60" s="3">
         <v>418900</v>
       </c>
-      <c r="K60" s="3">
+      <c r="M60" s="3">
         <v>435000</v>
       </c>
-      <c r="L60" s="3">
+      <c r="N60" s="3">
         <v>511100</v>
       </c>
-      <c r="M60" s="3">
+      <c r="O60" s="3">
         <v>452200</v>
       </c>
-      <c r="N60" s="3">
+      <c r="P60" s="3">
         <v>472400</v>
       </c>
-      <c r="O60" s="3">
+      <c r="Q60" s="3">
         <v>415100</v>
       </c>
-      <c r="P60" s="3">
+      <c r="R60" s="3">
         <v>349200</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="S60" s="3">
         <v>309300</v>
       </c>
-      <c r="R60" s="3">
+      <c r="T60" s="3">
         <v>270800</v>
       </c>
-      <c r="S60" s="3">
+      <c r="U60" s="3">
         <v>236300</v>
       </c>
-      <c r="T60" s="3">
+      <c r="V60" s="3">
         <v>216400</v>
       </c>
-      <c r="U60" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="V60" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W60" s="3" t="s">
         <v>3</v>
       </c>
@@ -4362,38 +4641,44 @@
       <c r="AA60" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="61" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB60" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AC60" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="61" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
-        <v>0</v>
+        <v>87600</v>
       </c>
       <c r="E61" s="3">
-        <v>0</v>
+        <v>83800</v>
       </c>
       <c r="F61" s="3">
-        <v>72100</v>
+        <v>0</v>
       </c>
       <c r="G61" s="3">
-        <v>68600</v>
+        <v>0</v>
       </c>
       <c r="H61" s="3">
-        <v>64900</v>
+        <v>72600</v>
       </c>
       <c r="I61" s="3">
+        <v>69100</v>
+      </c>
+      <c r="J61" s="3">
+        <v>65300</v>
+      </c>
+      <c r="K61" s="3">
         <v>48200</v>
       </c>
-      <c r="J61" s="3">
+      <c r="L61" s="3">
         <v>35200</v>
       </c>
-      <c r="K61" s="3">
-        <v>0</v>
-      </c>
-      <c r="L61" s="3">
-        <v>0</v>
-      </c>
       <c r="M61" s="3">
         <v>0</v>
       </c>
@@ -4439,65 +4724,71 @@
       <c r="AA61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB61" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
-        <v>8000</v>
+        <v>9100</v>
       </c>
       <c r="E62" s="3">
-        <v>7100</v>
+        <v>10000</v>
       </c>
       <c r="F62" s="3">
+        <v>8100</v>
+      </c>
+      <c r="G62" s="3">
         <v>7200</v>
       </c>
-      <c r="G62" s="3">
-        <v>8400</v>
-      </c>
       <c r="H62" s="3">
-        <v>8600</v>
+        <v>7300</v>
       </c>
       <c r="I62" s="3">
+        <v>8500</v>
+      </c>
+      <c r="J62" s="3">
+        <v>8700</v>
+      </c>
+      <c r="K62" s="3">
         <v>7700</v>
       </c>
-      <c r="J62" s="3">
+      <c r="L62" s="3">
         <v>10400</v>
       </c>
-      <c r="K62" s="3">
+      <c r="M62" s="3">
         <v>15100</v>
       </c>
-      <c r="L62" s="3">
+      <c r="N62" s="3">
         <v>13800</v>
       </c>
-      <c r="M62" s="3">
+      <c r="O62" s="3">
         <v>10900</v>
       </c>
-      <c r="N62" s="3">
+      <c r="P62" s="3">
         <v>11700</v>
       </c>
-      <c r="O62" s="3">
+      <c r="Q62" s="3">
         <v>10300</v>
       </c>
-      <c r="P62" s="3">
+      <c r="R62" s="3">
         <v>6400</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="S62" s="3">
         <v>3900</v>
       </c>
-      <c r="R62" s="3">
+      <c r="T62" s="3">
         <v>4100</v>
       </c>
-      <c r="S62" s="3">
+      <c r="U62" s="3">
         <v>2100</v>
       </c>
-      <c r="T62" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="U62" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V62" s="3" t="s">
         <v>3</v>
       </c>
@@ -4507,17 +4798,23 @@
       <c r="X62" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Y62" s="3">
-        <v>0</v>
-      </c>
-      <c r="Z62" s="3">
-        <v>0</v>
+      <c r="Y62" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Z62" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="AA62" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="63" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB62" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC62" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="63" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -4593,8 +4890,14 @@
       <c r="AA63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB63" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -4670,8 +4973,14 @@
       <c r="AA64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB64" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -4747,68 +5056,74 @@
       <c r="AA65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB65" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
-        <v>543200</v>
+        <v>535600</v>
       </c>
       <c r="E66" s="3">
-        <v>470400</v>
+        <v>519600</v>
       </c>
       <c r="F66" s="3">
-        <v>526300</v>
+        <v>546900</v>
       </c>
       <c r="G66" s="3">
-        <v>498300</v>
+        <v>473600</v>
       </c>
       <c r="H66" s="3">
-        <v>521800</v>
+        <v>529800</v>
       </c>
       <c r="I66" s="3">
+        <v>501700</v>
+      </c>
+      <c r="J66" s="3">
+        <v>525300</v>
+      </c>
+      <c r="K66" s="3">
         <v>432700</v>
       </c>
-      <c r="J66" s="3">
+      <c r="L66" s="3">
         <v>475200</v>
       </c>
-      <c r="K66" s="3">
+      <c r="M66" s="3">
         <v>464600</v>
       </c>
-      <c r="L66" s="3">
+      <c r="N66" s="3">
         <v>524800</v>
       </c>
-      <c r="M66" s="3">
+      <c r="O66" s="3">
         <v>463100</v>
       </c>
-      <c r="N66" s="3">
+      <c r="P66" s="3">
         <v>484200</v>
       </c>
-      <c r="O66" s="3">
+      <c r="Q66" s="3">
         <v>425500</v>
       </c>
-      <c r="P66" s="3">
+      <c r="R66" s="3">
         <v>355800</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="S66" s="3">
         <v>313400</v>
       </c>
-      <c r="R66" s="3">
+      <c r="T66" s="3">
         <v>275100</v>
       </c>
-      <c r="S66" s="3">
+      <c r="U66" s="3">
         <v>238600</v>
       </c>
-      <c r="T66" s="3">
+      <c r="V66" s="3">
         <v>216600</v>
       </c>
-      <c r="U66" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="V66" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W66" s="3" t="s">
         <v>3</v>
       </c>
@@ -4824,8 +5139,14 @@
       <c r="AA66" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="67" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB66" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AC66" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="67" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -4853,8 +5174,10 @@
       <c r="Y67" s="3"/>
       <c r="Z67" s="3"/>
       <c r="AA67" s="3"/>
-    </row>
-    <row r="68" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB67" s="3"/>
+      <c r="AC67" s="3"/>
+    </row>
+    <row r="68" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -4930,8 +5253,14 @@
       <c r="AA68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB68" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -5007,8 +5336,14 @@
       <c r="AA69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB69" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -5058,17 +5393,17 @@
         <v>0</v>
       </c>
       <c r="S70" s="3">
+        <v>0</v>
+      </c>
+      <c r="T70" s="3">
+        <v>0</v>
+      </c>
+      <c r="U70" s="3">
         <v>75900</v>
       </c>
-      <c r="T70" s="3">
+      <c r="V70" s="3">
         <v>73600</v>
       </c>
-      <c r="U70" s="3">
-        <v>0</v>
-      </c>
-      <c r="V70" s="3">
-        <v>0</v>
-      </c>
       <c r="W70" s="3">
         <v>0</v>
       </c>
@@ -5084,8 +5419,14 @@
       <c r="AA70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB70" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -5161,8 +5502,14 @@
       <c r="AA71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB71" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
@@ -5172,14 +5519,14 @@
       <c r="E72" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="F72" s="3">
-        <v>-744800</v>
+      <c r="F72" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="G72" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="H72" s="3" t="s">
-        <v>3</v>
+      <c r="H72" s="3">
+        <v>-749800</v>
       </c>
       <c r="I72" s="3" t="s">
         <v>3</v>
@@ -5196,33 +5543,33 @@
       <c r="M72" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N72" s="3">
+      <c r="N72" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O72" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P72" s="3">
         <v>-511000</v>
       </c>
-      <c r="O72" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="P72" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q72" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="R72" s="3">
+      <c r="R72" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S72" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="T72" s="3">
         <v>-295400</v>
       </c>
-      <c r="S72" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="V72" s="3">
         <v>-224700</v>
       </c>
-      <c r="U72" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="V72" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W72" s="3" t="s">
         <v>3</v>
       </c>
@@ -5238,8 +5585,14 @@
       <c r="AA72" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="73" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB72" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AC72" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="73" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -5315,8 +5668,14 @@
       <c r="AA73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB73" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -5392,8 +5751,14 @@
       <c r="AA74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB74" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -5469,68 +5834,74 @@
       <c r="AA75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB75" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
-        <v>-288300</v>
+        <v>-304000</v>
       </c>
       <c r="E76" s="3">
-        <v>-241400</v>
+        <v>-307600</v>
       </c>
       <c r="F76" s="3">
-        <v>-212000</v>
+        <v>-290200</v>
       </c>
       <c r="G76" s="3">
-        <v>-211600</v>
+        <v>-243000</v>
       </c>
       <c r="H76" s="3">
-        <v>-185100</v>
+        <v>-213400</v>
       </c>
       <c r="I76" s="3">
+        <v>-213000</v>
+      </c>
+      <c r="J76" s="3">
+        <v>-186400</v>
+      </c>
+      <c r="K76" s="3">
         <v>-122100</v>
       </c>
-      <c r="J76" s="3">
+      <c r="L76" s="3">
         <v>-111400</v>
       </c>
-      <c r="K76" s="3">
+      <c r="M76" s="3">
         <v>-116000</v>
       </c>
-      <c r="L76" s="3">
+      <c r="N76" s="3">
         <v>-101200</v>
       </c>
-      <c r="M76" s="3">
+      <c r="O76" s="3">
         <v>-26700</v>
       </c>
-      <c r="N76" s="3">
+      <c r="P76" s="3">
         <v>-196000</v>
       </c>
-      <c r="O76" s="3">
+      <c r="Q76" s="3">
         <v>-143300</v>
       </c>
-      <c r="P76" s="3">
+      <c r="R76" s="3">
         <v>-10700</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="S76" s="3">
         <v>24500</v>
       </c>
-      <c r="R76" s="3">
+      <c r="T76" s="3">
         <v>46200</v>
       </c>
-      <c r="S76" s="3">
+      <c r="U76" s="3">
         <v>-230800</v>
       </c>
-      <c r="T76" s="3">
+      <c r="V76" s="3">
         <v>-192500</v>
       </c>
-      <c r="U76" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="V76" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W76" s="3" t="s">
         <v>3</v>
       </c>
@@ -5546,8 +5917,14 @@
       <c r="AA76" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="77" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB76" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AC76" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="77" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -5623,167 +6000,185 @@
       <c r="AA77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB77" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:29" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:27" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45291</v>
+      </c>
+      <c r="E80" s="2">
+        <v>45199</v>
+      </c>
+      <c r="F80" s="2">
         <v>45107</v>
       </c>
-      <c r="E80" s="2">
+      <c r="G80" s="2">
         <v>45016</v>
       </c>
-      <c r="F80" s="2">
+      <c r="H80" s="2">
         <v>44926</v>
       </c>
-      <c r="G80" s="2">
+      <c r="I80" s="2">
         <v>44834</v>
       </c>
-      <c r="H80" s="2">
+      <c r="J80" s="2">
         <v>44742</v>
       </c>
-      <c r="I80" s="2">
+      <c r="K80" s="2">
         <v>44651</v>
       </c>
-      <c r="J80" s="2">
+      <c r="L80" s="2">
         <v>44561</v>
       </c>
-      <c r="K80" s="2">
+      <c r="M80" s="2">
         <v>44469</v>
       </c>
-      <c r="L80" s="2">
+      <c r="N80" s="2">
         <v>44377</v>
       </c>
-      <c r="M80" s="2">
+      <c r="O80" s="2">
         <v>44286</v>
       </c>
-      <c r="N80" s="2">
+      <c r="P80" s="2">
         <v>44196</v>
       </c>
-      <c r="O80" s="2">
+      <c r="Q80" s="2">
         <v>44104</v>
       </c>
-      <c r="P80" s="2">
+      <c r="R80" s="2">
         <v>44012</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="S80" s="2">
         <v>43921</v>
       </c>
-      <c r="R80" s="2">
+      <c r="T80" s="2">
         <v>43830</v>
       </c>
-      <c r="S80" s="2">
+      <c r="U80" s="2">
         <v>43738</v>
       </c>
-      <c r="T80" s="2">
+      <c r="V80" s="2">
         <v>43646</v>
       </c>
-      <c r="U80" s="2">
+      <c r="W80" s="2">
         <v>43555</v>
       </c>
-      <c r="V80" s="2">
+      <c r="X80" s="2">
         <v>43465</v>
       </c>
-      <c r="W80" s="2">
+      <c r="Y80" s="2">
         <v>43373</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Z80" s="2">
         <v>43281</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="AA80" s="2">
         <v>43190</v>
       </c>
-      <c r="Z80" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="AA80" s="2" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="81" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB80" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="AC80" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="81" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
-        <v>-41300</v>
+        <v>7900</v>
       </c>
       <c r="E81" s="3">
-        <v>-28200</v>
+        <v>-14300</v>
       </c>
       <c r="F81" s="3">
+        <v>-41600</v>
+      </c>
+      <c r="G81" s="3">
+        <v>-28400</v>
+      </c>
+      <c r="H81" s="3">
         <v>1700</v>
       </c>
-      <c r="G81" s="3">
-        <v>-25400</v>
-      </c>
-      <c r="H81" s="3">
-        <v>-62700</v>
-      </c>
       <c r="I81" s="3">
+        <v>-25600</v>
+      </c>
+      <c r="J81" s="3">
+        <v>-63100</v>
+      </c>
+      <c r="K81" s="3">
         <v>-14000</v>
       </c>
-      <c r="J81" s="3">
+      <c r="L81" s="3">
         <v>-137500</v>
       </c>
-      <c r="K81" s="3">
+      <c r="M81" s="3">
         <v>-18300</v>
       </c>
-      <c r="L81" s="3">
+      <c r="N81" s="3">
         <v>-74500</v>
       </c>
-      <c r="M81" s="3">
+      <c r="O81" s="3">
         <v>-45400</v>
       </c>
-      <c r="N81" s="3">
+      <c r="P81" s="3">
         <v>-62300</v>
       </c>
-      <c r="O81" s="3">
+      <c r="Q81" s="3">
         <v>-129400</v>
       </c>
-      <c r="P81" s="3">
+      <c r="R81" s="3">
         <v>-38000</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="S81" s="3">
         <v>-26500</v>
       </c>
-      <c r="R81" s="3">
+      <c r="T81" s="3">
         <v>-31700</v>
       </c>
-      <c r="S81" s="3">
+      <c r="U81" s="3">
         <v>-37300</v>
       </c>
-      <c r="T81" s="3">
+      <c r="V81" s="3">
         <v>-13400</v>
       </c>
-      <c r="U81" s="3">
+      <c r="W81" s="3">
         <v>-15500</v>
       </c>
-      <c r="V81" s="3">
+      <c r="X81" s="3">
         <v>-10200</v>
       </c>
-      <c r="W81" s="3">
+      <c r="Y81" s="3">
         <v>-11200</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Z81" s="3">
         <v>-4200</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="AA81" s="3">
         <v>-8900</v>
       </c>
-      <c r="Z81" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="AA81" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="82" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB81" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AC81" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="82" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -5811,65 +6206,67 @@
       <c r="Y82" s="3"/>
       <c r="Z82" s="3"/>
       <c r="AA82" s="3"/>
-    </row>
-    <row r="83" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB82" s="3"/>
+      <c r="AC82" s="3"/>
+    </row>
+    <row r="83" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="E83" s="3">
-        <v>1000</v>
-      </c>
-      <c r="F83" s="3">
+      <c r="E83" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F83" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G83" s="3">
+        <v>1100</v>
+      </c>
+      <c r="H83" s="3">
         <v>1600</v>
       </c>
-      <c r="G83" s="3">
+      <c r="I83" s="3">
         <v>1600</v>
       </c>
-      <c r="H83" s="3">
+      <c r="J83" s="3">
         <v>1500</v>
-      </c>
-      <c r="I83" s="3">
-        <v>1100</v>
-      </c>
-      <c r="J83" s="3">
-        <v>4200</v>
       </c>
       <c r="K83" s="3">
         <v>1100</v>
       </c>
       <c r="L83" s="3">
+        <v>4200</v>
+      </c>
+      <c r="M83" s="3">
+        <v>1100</v>
+      </c>
+      <c r="N83" s="3">
         <v>800</v>
       </c>
-      <c r="M83" s="3">
+      <c r="O83" s="3">
         <v>800</v>
       </c>
-      <c r="N83" s="3">
+      <c r="P83" s="3">
         <v>700</v>
       </c>
-      <c r="O83" s="3">
+      <c r="Q83" s="3">
         <v>600</v>
-      </c>
-      <c r="P83" s="3">
-        <v>500</v>
-      </c>
-      <c r="Q83" s="3">
-        <v>500</v>
       </c>
       <c r="R83" s="3">
         <v>500</v>
       </c>
       <c r="S83" s="3">
+        <v>500</v>
+      </c>
+      <c r="T83" s="3">
+        <v>500</v>
+      </c>
+      <c r="U83" s="3">
         <v>400</v>
       </c>
-      <c r="T83" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="U83" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V83" s="3" t="s">
         <v>3</v>
       </c>
@@ -5879,17 +6276,23 @@
       <c r="X83" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Y83" s="3">
-        <v>0</v>
-      </c>
-      <c r="Z83" s="3">
-        <v>0</v>
+      <c r="Y83" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Z83" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="AA83" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="84" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB83" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC83" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -5965,8 +6368,14 @@
       <c r="AA84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB84" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -6042,8 +6451,14 @@
       <c r="AA85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB85" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -6119,8 +6534,14 @@
       <c r="AA86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB86" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -6196,8 +6617,14 @@
       <c r="AA87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB87" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -6273,65 +6700,71 @@
       <c r="AA88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB88" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
-        <v>-42000</v>
+        <v>19900</v>
       </c>
       <c r="E89" s="3">
-        <v>60300</v>
-      </c>
-      <c r="F89" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="G89" s="3" t="s">
-        <v>3</v>
+        <v>22500</v>
+      </c>
+      <c r="F89" s="3">
+        <v>-42300</v>
+      </c>
+      <c r="G89" s="3">
+        <v>60800</v>
       </c>
       <c r="H89" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="I89" s="3">
+      <c r="I89" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J89" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="K89" s="3">
         <v>58800</v>
       </c>
-      <c r="J89" s="3">
+      <c r="L89" s="3">
         <v>-185900</v>
       </c>
-      <c r="K89" s="3">
+      <c r="M89" s="3">
         <v>89400</v>
       </c>
-      <c r="L89" s="3">
+      <c r="N89" s="3">
         <v>35400</v>
       </c>
-      <c r="M89" s="3">
+      <c r="O89" s="3">
         <v>72100</v>
       </c>
-      <c r="N89" s="3">
+      <c r="P89" s="3">
         <v>-147200</v>
       </c>
-      <c r="O89" s="3">
+      <c r="Q89" s="3">
         <v>87400</v>
       </c>
-      <c r="P89" s="3">
+      <c r="R89" s="3">
         <v>21000</v>
       </c>
-      <c r="Q89" s="3">
-        <v>0</v>
-      </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
+        <v>0</v>
+      </c>
+      <c r="T89" s="3">
         <v>-48300</v>
       </c>
-      <c r="S89" s="3">
+      <c r="U89" s="3">
         <v>21900</v>
       </c>
-      <c r="T89" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="U89" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V89" s="3" t="s">
         <v>3</v>
       </c>
@@ -6341,17 +6774,23 @@
       <c r="X89" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Y89" s="3">
-        <v>0</v>
-      </c>
-      <c r="Z89" s="3">
-        <v>0</v>
+      <c r="Y89" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Z89" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="AA89" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="90" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB89" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC89" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="90" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -6379,64 +6818,66 @@
       <c r="Y90" s="3"/>
       <c r="Z90" s="3"/>
       <c r="AA90" s="3"/>
-    </row>
-    <row r="91" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB90" s="3"/>
+      <c r="AC90" s="3"/>
+    </row>
+    <row r="91" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
-        <v>-900</v>
+        <v>-13200</v>
       </c>
       <c r="E91" s="3">
-        <v>-100</v>
+        <v>-1900</v>
       </c>
       <c r="F91" s="3">
-        <v>-9200</v>
+        <v>-6100</v>
       </c>
       <c r="G91" s="3">
-        <v>-1000</v>
+        <v>-500</v>
       </c>
       <c r="H91" s="3">
-        <v>-2800</v>
+        <v>-62200</v>
       </c>
       <c r="I91" s="3">
+        <v>-6500</v>
+      </c>
+      <c r="J91" s="3">
+        <v>-17900</v>
+      </c>
+      <c r="K91" s="3">
         <v>-3400</v>
       </c>
-      <c r="J91" s="3">
+      <c r="L91" s="3">
         <v>-1900</v>
       </c>
-      <c r="K91" s="3">
+      <c r="M91" s="3">
         <v>-11400</v>
       </c>
-      <c r="L91" s="3">
+      <c r="N91" s="3">
         <v>-15900</v>
       </c>
-      <c r="M91" s="3">
+      <c r="O91" s="3">
         <v>-1600</v>
       </c>
-      <c r="N91" s="3">
+      <c r="P91" s="3">
         <v>-2200</v>
       </c>
-      <c r="O91" s="3">
+      <c r="Q91" s="3">
         <v>-1800</v>
       </c>
-      <c r="P91" s="3">
+      <c r="R91" s="3">
         <v>-600</v>
-      </c>
-      <c r="Q91" s="3">
-        <v>-700</v>
-      </c>
-      <c r="R91" s="3">
-        <v>-700</v>
       </c>
       <c r="S91" s="3">
         <v>-700</v>
       </c>
-      <c r="T91" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="U91" s="3" t="s">
-        <v>3</v>
+      <c r="T91" s="3">
+        <v>-700</v>
+      </c>
+      <c r="U91" s="3">
+        <v>-700</v>
       </c>
       <c r="V91" s="3" t="s">
         <v>3</v>
@@ -6447,17 +6888,23 @@
       <c r="X91" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Y91" s="3">
-        <v>0</v>
-      </c>
-      <c r="Z91" s="3">
-        <v>0</v>
+      <c r="Y91" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Z91" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="AA91" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="92" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB91" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC91" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -6533,8 +6980,14 @@
       <c r="AA92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB92" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -6610,8 +7063,14 @@
       <c r="AA93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB93" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
@@ -6687,8 +7146,14 @@
       <c r="AA94" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="95" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB94" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC94" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="95" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -6716,8 +7181,10 @@
       <c r="Y95" s="3"/>
       <c r="Z95" s="3"/>
       <c r="AA95" s="3"/>
-    </row>
-    <row r="96" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB95" s="3"/>
+      <c r="AC95" s="3"/>
+    </row>
+    <row r="96" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -6793,8 +7260,14 @@
       <c r="AA96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB96" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -6870,8 +7343,14 @@
       <c r="AA97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB97" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -6947,8 +7426,14 @@
       <c r="AA98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB98" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -7024,8 +7509,14 @@
       <c r="AA99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB99" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
@@ -7101,8 +7592,14 @@
       <c r="AA100" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="101" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB100" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC100" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="101" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -7178,8 +7675,14 @@
       <c r="AA101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB101" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
@@ -7253,6 +7756,12 @@
         <v>0</v>
       </c>
       <c r="AA102" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB102" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC102" s="3">
         <v>0</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/DAO_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/DAO_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="331" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="341" uniqueCount="92">
   <si>
     <t>DAO</t>
   </si>
@@ -656,377 +656,390 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AC102"/>
+  <dimension ref="A5:AD102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="6.42578125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="21" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="25" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="29" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="30" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="22" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="26" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="30" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="31" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:29" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:29" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:30" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:29" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:30" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45382</v>
+      </c>
+      <c r="E7" s="2">
         <v>45291</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45199</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45107</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45016</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>44926</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>44834</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44742</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44651</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44561</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44469</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44377</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44286</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44196</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44104</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44012</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>43921</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>43830</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>43738</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>43646</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>43555</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43465</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>43373</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43281</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43190</v>
       </c>
-      <c r="AB7" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="AC7" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="8" spans="1:29" x14ac:dyDescent="0.2">
+      <c r="AD7" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:30" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D8" s="3">
-        <v>205800</v>
+        <v>192300</v>
       </c>
       <c r="E8" s="3">
-        <v>213900</v>
+        <v>204500</v>
       </c>
       <c r="F8" s="3">
-        <v>167700</v>
+        <v>212600</v>
       </c>
       <c r="G8" s="3">
-        <v>161700</v>
+        <v>166700</v>
       </c>
       <c r="H8" s="3">
-        <v>202100</v>
+        <v>160700</v>
       </c>
       <c r="I8" s="3">
-        <v>195000</v>
+        <v>200900</v>
       </c>
       <c r="J8" s="3">
+        <v>193800</v>
+      </c>
+      <c r="K8" s="3">
         <v>132900</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>165800</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>554500</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>197200</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>139300</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>132000</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>64900</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>132000</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>91800</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>84800</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>63200</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>53300</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>49300</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>34300</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>33400</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>25300</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>27000</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>19300</v>
       </c>
-      <c r="AB8" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AC8" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="9" spans="1:29" x14ac:dyDescent="0.2">
+      <c r="AD8" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="9" spans="1:30" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D9" s="3">
-        <v>103100</v>
+        <v>98100</v>
       </c>
       <c r="E9" s="3">
-        <v>94400</v>
+        <v>102500</v>
       </c>
       <c r="F9" s="3">
-        <v>88900</v>
+        <v>93800</v>
       </c>
       <c r="G9" s="3">
-        <v>78000</v>
+        <v>88300</v>
       </c>
       <c r="H9" s="3">
-        <v>94400</v>
+        <v>77600</v>
       </c>
       <c r="I9" s="3">
-        <v>89300</v>
+        <v>93900</v>
       </c>
       <c r="J9" s="3">
+        <v>88700</v>
+      </c>
+      <c r="K9" s="3">
         <v>76000</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>77100</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>279900</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>85500</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>68200</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>62900</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>120900</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>71400</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>50400</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>47900</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>44300</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>39500</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>33100</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>26300</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Y9" s="3">
         <v>23500</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="Z9" s="3">
         <v>19400</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AA9" s="3">
         <v>17200</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AB9" s="3">
         <v>13900</v>
       </c>
-      <c r="AB9" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AC9" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="10" spans="1:29" x14ac:dyDescent="0.2">
+      <c r="AD9" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:30" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
-        <v>102700</v>
+        <v>94200</v>
       </c>
       <c r="E10" s="3">
-        <v>119500</v>
+        <v>102100</v>
       </c>
       <c r="F10" s="3">
-        <v>78800</v>
+        <v>118800</v>
       </c>
       <c r="G10" s="3">
-        <v>83700</v>
+        <v>78400</v>
       </c>
       <c r="H10" s="3">
-        <v>107700</v>
+        <v>83200</v>
       </c>
       <c r="I10" s="3">
-        <v>105700</v>
+        <v>107000</v>
       </c>
       <c r="J10" s="3">
+        <v>105000</v>
+      </c>
+      <c r="K10" s="3">
         <v>57000</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>88600</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>274600</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>111700</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>71100</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>69100</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>-56100</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>60600</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>41500</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>36900</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>18800</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>13700</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>16200</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>8000</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Y10" s="3">
         <v>9900</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="Z10" s="3">
         <v>5900</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AA10" s="3">
         <v>9800</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AB10" s="3">
         <v>5400</v>
       </c>
-      <c r="AB10" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AC10" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="11" spans="1:29" x14ac:dyDescent="0.2">
+      <c r="AD10" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:30" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -1056,91 +1069,95 @@
       <c r="AA11" s="3"/>
       <c r="AB11" s="3"/>
       <c r="AC11" s="3"/>
-    </row>
-    <row r="12" spans="1:29" x14ac:dyDescent="0.2">
+      <c r="AD11" s="3"/>
+    </row>
+    <row r="12" spans="1:30" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D12" s="3">
-        <v>23400</v>
+        <v>20300</v>
       </c>
       <c r="E12" s="3">
-        <v>26000</v>
+        <v>23200</v>
       </c>
       <c r="F12" s="3">
-        <v>28500</v>
+        <v>25900</v>
       </c>
       <c r="G12" s="3">
-        <v>25400</v>
+        <v>28300</v>
       </c>
       <c r="H12" s="3">
-        <v>25000</v>
+        <v>25300</v>
       </c>
       <c r="I12" s="3">
-        <v>29600</v>
+        <v>24800</v>
       </c>
       <c r="J12" s="3">
+        <v>29400</v>
+      </c>
+      <c r="K12" s="3">
         <v>29000</v>
       </c>
-      <c r="K12" s="3">
+      <c r="L12" s="3">
         <v>28000</v>
       </c>
-      <c r="L12" s="3">
+      <c r="M12" s="3">
         <v>83900</v>
       </c>
-      <c r="M12" s="3">
+      <c r="N12" s="3">
         <v>27500</v>
       </c>
-      <c r="N12" s="3">
+      <c r="O12" s="3">
         <v>20700</v>
       </c>
-      <c r="O12" s="3">
+      <c r="P12" s="3">
         <v>17800</v>
       </c>
-      <c r="P12" s="3">
+      <c r="Q12" s="3">
         <v>10500</v>
       </c>
-      <c r="Q12" s="3">
+      <c r="R12" s="3">
         <v>17800</v>
       </c>
-      <c r="R12" s="3">
+      <c r="S12" s="3">
         <v>13500</v>
       </c>
-      <c r="S12" s="3">
+      <c r="T12" s="3">
         <v>13200</v>
       </c>
-      <c r="T12" s="3">
+      <c r="U12" s="3">
         <v>13700</v>
       </c>
-      <c r="U12" s="3">
+      <c r="V12" s="3">
         <v>11500</v>
       </c>
-      <c r="V12" s="3">
+      <c r="W12" s="3">
         <v>8600</v>
       </c>
-      <c r="W12" s="3">
+      <c r="X12" s="3">
         <v>8300</v>
       </c>
-      <c r="X12" s="3">
+      <c r="Y12" s="3">
         <v>7300</v>
       </c>
-      <c r="Y12" s="3">
+      <c r="Z12" s="3">
         <v>7700</v>
       </c>
-      <c r="Z12" s="3">
+      <c r="AA12" s="3">
         <v>5400</v>
       </c>
-      <c r="AA12" s="3">
+      <c r="AB12" s="3">
         <v>6100</v>
       </c>
-      <c r="AB12" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AC12" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="13" spans="1:29" x14ac:dyDescent="0.2">
+      <c r="AD12" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:30" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1222,8 +1239,11 @@
       <c r="AC13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:29" x14ac:dyDescent="0.2">
+      <c r="AD13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:30" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -1251,12 +1271,12 @@
       <c r="K14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L14" s="3">
+      <c r="L14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M14" s="3">
         <v>7800</v>
       </c>
-      <c r="M14" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N14" s="3" t="s">
         <v>3</v>
       </c>
@@ -1272,8 +1292,8 @@
       <c r="R14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="S14" s="3">
-        <v>0</v>
+      <c r="S14" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="T14" s="3">
         <v>0</v>
@@ -1305,8 +1325,11 @@
       <c r="AC14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:29" x14ac:dyDescent="0.2">
+      <c r="AD14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:30" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1388,8 +1411,11 @@
       <c r="AC15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:29" x14ac:dyDescent="0.2">
+      <c r="AD15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:30" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1416,174 +1442,181 @@
       <c r="AA16" s="3"/>
       <c r="AB16" s="3"/>
       <c r="AC16" s="3"/>
-    </row>
-    <row r="17" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD16" s="3"/>
+    </row>
+    <row r="17" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
-        <v>195200</v>
+        <v>188200</v>
       </c>
       <c r="E17" s="3">
-        <v>221900</v>
+        <v>194000</v>
       </c>
       <c r="F17" s="3">
-        <v>207900</v>
+        <v>220600</v>
       </c>
       <c r="G17" s="3">
-        <v>188900</v>
+        <v>206700</v>
       </c>
       <c r="H17" s="3">
-        <v>198700</v>
+        <v>187800</v>
       </c>
       <c r="I17" s="3">
-        <v>225400</v>
+        <v>197500</v>
       </c>
       <c r="J17" s="3">
+        <v>224000</v>
+      </c>
+      <c r="K17" s="3">
         <v>196200</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>183000</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>684700</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>215600</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>175500</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>161800</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>-4900</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>263800</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>133600</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>112300</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>94600</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>89400</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>62000</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>46400</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>40700</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>37800</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>31300</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>26700</v>
       </c>
-      <c r="AB17" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AC17" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="18" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD17" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
-        <v>10600</v>
+        <v>4100</v>
       </c>
       <c r="E18" s="3">
+        <v>10500</v>
+      </c>
+      <c r="F18" s="3">
         <v>-8000</v>
       </c>
-      <c r="F18" s="3">
-        <v>-40200</v>
-      </c>
       <c r="G18" s="3">
-        <v>-27200</v>
+        <v>-40000</v>
       </c>
       <c r="H18" s="3">
+        <v>-27000</v>
+      </c>
+      <c r="I18" s="3">
         <v>3400</v>
       </c>
-      <c r="I18" s="3">
-        <v>-30500</v>
-      </c>
       <c r="J18" s="3">
+        <v>-30300</v>
+      </c>
+      <c r="K18" s="3">
         <v>-63300</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>-17300</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>-130200</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>-18400</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>-36200</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>-29800</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>69800</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>-131700</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>-41700</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>-27600</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>-31400</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>-36100</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>-12700</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>-12000</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>-7300</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>-12400</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>-4400</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>-7500</v>
       </c>
-      <c r="AB18" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AC18" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="19" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD18" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1613,91 +1646,95 @@
       <c r="AA19" s="3"/>
       <c r="AB19" s="3"/>
       <c r="AC19" s="3"/>
-    </row>
-    <row r="20" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD19" s="3"/>
+    </row>
+    <row r="20" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>500</v>
+      </c>
+      <c r="E20" s="3">
         <v>-100</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>-2600</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>1100</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>1200</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>900</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>6100</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>700</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>5300</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>7700</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>900</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>4300</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>500</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>700</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>2400</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>3700</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>1400</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>200</v>
       </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3">
         <v>800</v>
       </c>
-      <c r="V20" s="3">
+      <c r="W20" s="3">
         <v>1200</v>
       </c>
-      <c r="W20" s="3">
+      <c r="X20" s="3">
         <v>-1800</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Y20" s="3">
         <v>-800</v>
       </c>
-      <c r="Y20" s="3">
+      <c r="Z20" s="3">
         <v>3200</v>
       </c>
-      <c r="Z20" s="3">
+      <c r="AA20" s="3">
         <v>1700</v>
       </c>
-      <c r="AA20" s="3">
+      <c r="AB20" s="3">
         <v>-1100</v>
       </c>
-      <c r="AB20" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AC20" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="21" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD20" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
@@ -1710,54 +1747,54 @@
       <c r="F21" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="G21" s="3">
-        <v>-25000</v>
+      <c r="G21" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="H21" s="3">
+        <v>-24800</v>
+      </c>
+      <c r="I21" s="3">
         <v>6000</v>
       </c>
-      <c r="I21" s="3">
-        <v>-22700</v>
-      </c>
       <c r="J21" s="3">
+        <v>-22600</v>
+      </c>
+      <c r="K21" s="3">
         <v>-61100</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>-10900</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>-118400</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>-16400</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>-31100</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>-28600</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>71200</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>-128700</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>-37500</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>-25600</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>-30700</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>-35000</v>
       </c>
-      <c r="V21" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W21" s="3" t="s">
         <v>3</v>
       </c>
@@ -1767,52 +1804,55 @@
       <c r="Y21" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="Z21" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AA21" s="3">
         <v>-2300</v>
       </c>
-      <c r="AA21" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AB21" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AC21" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="22" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD21" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="22" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>2800</v>
+      </c>
+      <c r="E22" s="3">
         <v>2600</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
         <v>2500</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>2400</v>
       </c>
-      <c r="G22" s="3">
+      <c r="H22" s="3">
         <v>2200</v>
       </c>
-      <c r="H22" s="3">
+      <c r="I22" s="3">
         <v>2000</v>
       </c>
-      <c r="I22" s="3">
+      <c r="J22" s="3">
         <v>1700</v>
       </c>
-      <c r="J22" s="3">
+      <c r="K22" s="3">
         <v>1400</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>1200</v>
       </c>
-      <c r="L22" s="3">
+      <c r="M22" s="3">
         <v>4400</v>
-      </c>
-      <c r="M22" s="3">
-        <v>1100</v>
       </c>
       <c r="N22" s="3">
         <v>1100</v>
@@ -1820,8 +1860,8 @@
       <c r="O22" s="3">
         <v>1100</v>
       </c>
-      <c r="P22" s="3" t="s">
-        <v>3</v>
+      <c r="P22" s="3">
+        <v>1100</v>
       </c>
       <c r="Q22" s="3" t="s">
         <v>3</v>
@@ -1838,8 +1878,8 @@
       <c r="U22" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="V22" s="3">
-        <v>0</v>
+      <c r="V22" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="W22" s="3">
         <v>0</v>
@@ -1862,147 +1902,153 @@
       <c r="AC22" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
-        <v>7900</v>
+        <v>1900</v>
       </c>
       <c r="E23" s="3">
-        <v>-13100</v>
+        <v>7800</v>
       </c>
       <c r="F23" s="3">
-        <v>-41500</v>
+        <v>-13000</v>
       </c>
       <c r="G23" s="3">
-        <v>-28200</v>
+        <v>-41200</v>
       </c>
       <c r="H23" s="3">
+        <v>-28000</v>
+      </c>
+      <c r="I23" s="3">
         <v>2300</v>
       </c>
-      <c r="I23" s="3">
-        <v>-26000</v>
-      </c>
       <c r="J23" s="3">
+        <v>-25900</v>
+      </c>
+      <c r="K23" s="3">
         <v>-63900</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>-13200</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>-127000</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>-18600</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>-33100</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>-30400</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>70600</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>-129400</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>-38000</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>-26200</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>-31200</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>-35400</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>-11500</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>-13900</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>-8100</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>-9300</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>-2600</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>-8500</v>
       </c>
-      <c r="AB23" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AC23" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="24" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD23" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="24" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>-100</v>
+      </c>
+      <c r="E24" s="3">
         <v>100</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>400</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>700</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>400</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>1900</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>-200</v>
-      </c>
-      <c r="J24" s="3">
-        <v>100</v>
       </c>
       <c r="K24" s="3">
         <v>100</v>
       </c>
       <c r="L24" s="3">
+        <v>100</v>
+      </c>
+      <c r="M24" s="3">
         <v>900</v>
-      </c>
-      <c r="M24" s="3">
-        <v>400</v>
       </c>
       <c r="N24" s="3">
         <v>400</v>
       </c>
       <c r="O24" s="3">
+        <v>400</v>
+      </c>
+      <c r="P24" s="3">
         <v>200</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>100</v>
       </c>
-      <c r="Q24" s="3">
-        <v>0</v>
-      </c>
       <c r="R24" s="3">
         <v>0</v>
       </c>
       <c r="S24" s="3">
+        <v>0</v>
+      </c>
+      <c r="T24" s="3">
         <v>300</v>
       </c>
-      <c r="T24" s="3">
-        <v>0</v>
-      </c>
       <c r="U24" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="V24" s="3">
         <v>100</v>
@@ -2011,25 +2057,28 @@
         <v>100</v>
       </c>
       <c r="X24" s="3">
-        <v>500</v>
+        <v>100</v>
       </c>
       <c r="Y24" s="3">
         <v>500</v>
       </c>
       <c r="Z24" s="3">
+        <v>500</v>
+      </c>
+      <c r="AA24" s="3">
         <v>200</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AB24" s="3">
         <v>500</v>
       </c>
-      <c r="AB24" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AC24" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="25" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD24" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="25" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2111,174 +2160,183 @@
       <c r="AC25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>2000</v>
+      </c>
+      <c r="E26" s="3">
         <v>7800</v>
       </c>
-      <c r="E26" s="3">
-        <v>-13500</v>
-      </c>
       <c r="F26" s="3">
-        <v>-42200</v>
+        <v>-13400</v>
       </c>
       <c r="G26" s="3">
-        <v>-28600</v>
+        <v>-41900</v>
       </c>
       <c r="H26" s="3">
+        <v>-28500</v>
+      </c>
+      <c r="I26" s="3">
         <v>400</v>
       </c>
-      <c r="I26" s="3">
-        <v>-25900</v>
-      </c>
       <c r="J26" s="3">
+        <v>-25700</v>
+      </c>
+      <c r="K26" s="3">
         <v>-64000</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>-13300</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>-127900</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>-18900</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>-33500</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>-30600</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>70500</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>-129400</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>-38000</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>-26500</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>-31200</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>-35500</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>-11600</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>-14000</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>-8600</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>-9800</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>-2800</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>-9000</v>
       </c>
-      <c r="AB26" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AC26" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="27" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD26" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="27" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
-        <v>7900</v>
+        <v>1700</v>
       </c>
       <c r="E27" s="3">
-        <v>-14300</v>
+        <v>7800</v>
       </c>
       <c r="F27" s="3">
-        <v>-41600</v>
+        <v>-14200</v>
       </c>
       <c r="G27" s="3">
-        <v>-28400</v>
+        <v>-41300</v>
       </c>
       <c r="H27" s="3">
+        <v>-28200</v>
+      </c>
+      <c r="I27" s="3">
         <v>1700</v>
       </c>
-      <c r="I27" s="3">
-        <v>-25600</v>
-      </c>
       <c r="J27" s="3">
+        <v>-25400</v>
+      </c>
+      <c r="K27" s="3">
         <v>-63100</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>-13200</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>-123600</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>-18300</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>-33400</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>-30500</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>70500</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>-129400</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>-38000</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>-26500</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>-31700</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>-37300</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>-13400</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>-15500</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>-10200</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>-11200</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>-4200</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>-8900</v>
       </c>
-      <c r="AB27" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AC27" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="28" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD27" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="28" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2360,13 +2418,16 @@
       <c r="AC28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="D29" s="3">
-        <v>0</v>
+      <c r="D29" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="E29" s="3">
         <v>0</v>
@@ -2387,31 +2448,31 @@
         <v>0</v>
       </c>
       <c r="K29" s="3">
+        <v>0</v>
+      </c>
+      <c r="L29" s="3">
         <v>-800</v>
       </c>
-      <c r="L29" s="3">
+      <c r="M29" s="3">
         <v>-13800</v>
       </c>
-      <c r="M29" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="N29" s="3">
+      <c r="N29" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O29" s="3">
         <v>-41200</v>
       </c>
-      <c r="O29" s="3">
+      <c r="P29" s="3">
         <v>-14800</v>
       </c>
-      <c r="P29" s="3">
+      <c r="Q29" s="3">
         <v>-132800</v>
       </c>
-      <c r="Q29" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R29" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="S29" s="3">
-        <v>0</v>
+      <c r="S29" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="T29" s="3">
         <v>0</v>
@@ -2443,8 +2504,11 @@
       <c r="AC29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2526,8 +2590,11 @@
       <c r="AC30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2609,174 +2676,183 @@
       <c r="AC31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>-500</v>
+      </c>
+      <c r="E32" s="3">
         <v>100</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>2600</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>-1100</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>-1200</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>-900</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>-6100</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>-700</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>-5300</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>-7700</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>-900</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>-4300</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>-500</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>-700</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>-2400</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>-3700</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>-1400</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>-200</v>
       </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3">
         <v>-800</v>
       </c>
-      <c r="V32" s="3">
+      <c r="W32" s="3">
         <v>-1200</v>
       </c>
-      <c r="W32" s="3">
+      <c r="X32" s="3">
         <v>1800</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Y32" s="3">
         <v>800</v>
       </c>
-      <c r="Y32" s="3">
+      <c r="Z32" s="3">
         <v>-3200</v>
       </c>
-      <c r="Z32" s="3">
+      <c r="AA32" s="3">
         <v>-1700</v>
       </c>
-      <c r="AA32" s="3">
+      <c r="AB32" s="3">
         <v>1100</v>
       </c>
-      <c r="AB32" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AC32" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="33" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD32" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="33" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
-        <v>7900</v>
+        <v>1700</v>
       </c>
       <c r="E33" s="3">
-        <v>-14300</v>
+        <v>7800</v>
       </c>
       <c r="F33" s="3">
-        <v>-41600</v>
+        <v>-14200</v>
       </c>
       <c r="G33" s="3">
-        <v>-28400</v>
+        <v>-41300</v>
       </c>
       <c r="H33" s="3">
+        <v>-28200</v>
+      </c>
+      <c r="I33" s="3">
         <v>1700</v>
       </c>
-      <c r="I33" s="3">
-        <v>-25600</v>
-      </c>
       <c r="J33" s="3">
+        <v>-25400</v>
+      </c>
+      <c r="K33" s="3">
         <v>-63100</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>-14000</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>-137500</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>-18300</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>-74500</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>-45400</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>-62300</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>-129400</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>-38000</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>-26500</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>-31700</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>-37300</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>-13400</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>-15500</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>-10200</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>-11200</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>-4200</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>-8900</v>
       </c>
-      <c r="AB33" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AC33" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="34" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD33" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="34" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2858,179 +2934,188 @@
       <c r="AC34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
-        <v>7900</v>
+        <v>1700</v>
       </c>
       <c r="E35" s="3">
-        <v>-14300</v>
+        <v>7800</v>
       </c>
       <c r="F35" s="3">
-        <v>-41600</v>
+        <v>-14200</v>
       </c>
       <c r="G35" s="3">
-        <v>-28400</v>
+        <v>-41300</v>
       </c>
       <c r="H35" s="3">
+        <v>-28200</v>
+      </c>
+      <c r="I35" s="3">
         <v>1700</v>
       </c>
-      <c r="I35" s="3">
-        <v>-25600</v>
-      </c>
       <c r="J35" s="3">
+        <v>-25400</v>
+      </c>
+      <c r="K35" s="3">
         <v>-63100</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>-14000</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>-137500</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>-18300</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>-74500</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>-45400</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>-62300</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>-129400</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>-38000</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>-26500</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>-31700</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>-37300</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>-13400</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>-15500</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>-10200</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>-11200</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>-4200</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>-8900</v>
       </c>
-      <c r="AB35" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AC35" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="37" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD35" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="37" spans="2:30" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:29" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45382</v>
+      </c>
+      <c r="E38" s="2">
         <v>45291</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45199</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45107</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45016</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>44926</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>44834</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44742</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44651</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44561</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44469</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44377</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44286</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44196</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44104</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44012</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>43921</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>43830</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>43738</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>43646</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>43555</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43465</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>43373</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43281</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43190</v>
       </c>
-      <c r="AB38" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="AC38" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="39" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD38" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="39" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3060,8 +3145,9 @@
       <c r="AA39" s="3"/>
       <c r="AB39" s="3"/>
       <c r="AC39" s="3"/>
-    </row>
-    <row r="40" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD39" s="3"/>
+    </row>
+    <row r="40" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3091,71 +3177,72 @@
       <c r="AA40" s="3"/>
       <c r="AB40" s="3"/>
       <c r="AC40" s="3"/>
-    </row>
-    <row r="41" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD40" s="3"/>
+    </row>
+    <row r="41" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
-        <v>63200</v>
+        <v>36300</v>
       </c>
       <c r="E41" s="3">
-        <v>47000</v>
+        <v>62800</v>
       </c>
       <c r="F41" s="3">
-        <v>91500</v>
+        <v>46700</v>
       </c>
       <c r="G41" s="3">
-        <v>80500</v>
+        <v>90900</v>
       </c>
       <c r="H41" s="3">
-        <v>108900</v>
+        <v>80000</v>
       </c>
       <c r="I41" s="3">
-        <v>99000</v>
+        <v>108300</v>
       </c>
       <c r="J41" s="3">
+        <v>98400</v>
+      </c>
+      <c r="K41" s="3">
         <v>95500</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>57300</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>44600</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>70200</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>117900</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>257300</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>84800</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>11500</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>18500</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>20100</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>26700</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>8500</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>8000</v>
       </c>
-      <c r="W41" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X41" s="3" t="s">
         <v>3</v>
       </c>
@@ -3174,16 +3261,19 @@
       <c r="AC41" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="42" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD41" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="42" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>8600</v>
+      </c>
+      <c r="E42" s="3">
         <v>10000</v>
-      </c>
-      <c r="E42" s="3">
-        <v>3100</v>
       </c>
       <c r="F42" s="3">
         <v>3000</v>
@@ -3192,53 +3282,53 @@
         <v>3000</v>
       </c>
       <c r="H42" s="3">
-        <v>32300</v>
+        <v>3000</v>
       </c>
       <c r="I42" s="3">
-        <v>3000</v>
+        <v>32100</v>
       </c>
       <c r="J42" s="3">
         <v>3000</v>
       </c>
       <c r="K42" s="3">
+        <v>3000</v>
+      </c>
+      <c r="L42" s="3">
         <v>900</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>69600</v>
       </c>
-      <c r="M42" s="3">
+      <c r="N42" s="3">
         <v>58300</v>
       </c>
-      <c r="N42" s="3">
+      <c r="O42" s="3">
         <v>146500</v>
       </c>
-      <c r="O42" s="3">
+      <c r="P42" s="3">
         <v>47000</v>
       </c>
-      <c r="P42" s="3">
+      <c r="Q42" s="3">
         <v>81500</v>
       </c>
-      <c r="Q42" s="3">
+      <c r="R42" s="3">
         <v>155400</v>
       </c>
-      <c r="R42" s="3">
+      <c r="S42" s="3">
         <v>245400</v>
       </c>
-      <c r="S42" s="3">
+      <c r="T42" s="3">
         <v>242400</v>
       </c>
-      <c r="T42" s="3">
+      <c r="U42" s="3">
         <v>222800</v>
       </c>
-      <c r="U42" s="3">
+      <c r="V42" s="3">
         <v>16200</v>
       </c>
-      <c r="V42" s="3">
+      <c r="W42" s="3">
         <v>38000</v>
       </c>
-      <c r="W42" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X42" s="3" t="s">
         <v>3</v>
       </c>
@@ -3257,71 +3347,74 @@
       <c r="AC42" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="43" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD42" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="43" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
-        <v>52800</v>
+        <v>57000</v>
       </c>
       <c r="E43" s="3">
-        <v>50200</v>
+        <v>52500</v>
       </c>
       <c r="F43" s="3">
-        <v>53800</v>
+        <v>49800</v>
       </c>
       <c r="G43" s="3">
-        <v>37200</v>
+        <v>53400</v>
       </c>
       <c r="H43" s="3">
-        <v>57400</v>
+        <v>37000</v>
       </c>
       <c r="I43" s="3">
-        <v>47200</v>
+        <v>57100</v>
       </c>
       <c r="J43" s="3">
+        <v>46900</v>
+      </c>
+      <c r="K43" s="3">
         <v>49000</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>41500</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>35100</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>35300</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>44300</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>35100</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>38000</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>50100</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>34900</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>36800</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>33200</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>27800</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>31100</v>
       </c>
-      <c r="W43" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X43" s="3" t="s">
         <v>3</v>
       </c>
@@ -3340,71 +3433,74 @@
       <c r="AC43" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="44" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD43" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="44" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
-        <v>30200</v>
+        <v>26200</v>
       </c>
       <c r="E44" s="3">
-        <v>24700</v>
+        <v>30000</v>
       </c>
       <c r="F44" s="3">
-        <v>25400</v>
+        <v>24500</v>
       </c>
       <c r="G44" s="3">
-        <v>30500</v>
+        <v>25200</v>
       </c>
       <c r="H44" s="3">
-        <v>32300</v>
+        <v>30300</v>
       </c>
       <c r="I44" s="3">
-        <v>23700</v>
+        <v>32100</v>
       </c>
       <c r="J44" s="3">
-        <v>29500</v>
+        <v>23500</v>
       </c>
       <c r="K44" s="3">
         <v>29500</v>
       </c>
       <c r="L44" s="3">
+        <v>29500</v>
+      </c>
+      <c r="M44" s="3">
         <v>35300</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>38000</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>38600</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>37400</v>
       </c>
-      <c r="P44" s="3">
+      <c r="Q44" s="3">
         <v>20700</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="R44" s="3">
         <v>13500</v>
       </c>
-      <c r="R44" s="3">
+      <c r="S44" s="3">
         <v>13700</v>
       </c>
-      <c r="S44" s="3">
+      <c r="T44" s="3">
         <v>10300</v>
       </c>
-      <c r="T44" s="3">
+      <c r="U44" s="3">
         <v>11300</v>
       </c>
-      <c r="U44" s="3">
+      <c r="V44" s="3">
         <v>8100</v>
       </c>
-      <c r="V44" s="3">
+      <c r="W44" s="3">
         <v>5000</v>
       </c>
-      <c r="W44" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X44" s="3" t="s">
         <v>3</v>
       </c>
@@ -3423,71 +3519,74 @@
       <c r="AC44" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="45" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD44" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="45" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
-        <v>24500</v>
+        <v>27100</v>
       </c>
       <c r="E45" s="3">
-        <v>32400</v>
+        <v>24300</v>
       </c>
       <c r="F45" s="3">
-        <v>26900</v>
+        <v>32200</v>
       </c>
       <c r="G45" s="3">
-        <v>24500</v>
+        <v>26800</v>
       </c>
       <c r="H45" s="3">
-        <v>29000</v>
+        <v>24400</v>
       </c>
       <c r="I45" s="3">
-        <v>60100</v>
+        <v>28800</v>
       </c>
       <c r="J45" s="3">
+        <v>59700</v>
+      </c>
+      <c r="K45" s="3">
         <v>104200</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>129100</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>128800</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>85400</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>33100</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>27600</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>32800</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>29600</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>17500</v>
-      </c>
-      <c r="S45" s="3">
-        <v>18600</v>
       </c>
       <c r="T45" s="3">
         <v>18600</v>
       </c>
       <c r="U45" s="3">
+        <v>18600</v>
+      </c>
+      <c r="V45" s="3">
         <v>16200</v>
       </c>
-      <c r="V45" s="3">
+      <c r="W45" s="3">
         <v>11300</v>
       </c>
-      <c r="W45" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X45" s="3" t="s">
         <v>3</v>
       </c>
@@ -3506,71 +3605,74 @@
       <c r="AC45" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="46" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD45" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="46" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
-        <v>180700</v>
+        <v>155300</v>
       </c>
       <c r="E46" s="3">
-        <v>157300</v>
+        <v>179600</v>
       </c>
       <c r="F46" s="3">
-        <v>200600</v>
+        <v>156300</v>
       </c>
       <c r="G46" s="3">
-        <v>175800</v>
+        <v>199300</v>
       </c>
       <c r="H46" s="3">
-        <v>260000</v>
+        <v>174700</v>
       </c>
       <c r="I46" s="3">
-        <v>233000</v>
+        <v>258400</v>
       </c>
       <c r="J46" s="3">
+        <v>231500</v>
+      </c>
+      <c r="K46" s="3">
         <v>281200</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>258300</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>313400</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>287200</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>380400</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>404400</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>257700</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>260200</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>330000</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>328200</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>312600</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>76800</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>93400</v>
       </c>
-      <c r="W46" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X46" s="3" t="s">
         <v>3</v>
       </c>
@@ -3589,53 +3691,56 @@
       <c r="AC46" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="47" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD46" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="47" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>6800</v>
+      </c>
+      <c r="E47" s="3">
         <v>7100</v>
       </c>
-      <c r="E47" s="3">
-        <v>9000</v>
-      </c>
       <c r="F47" s="3">
-        <v>12200</v>
+        <v>8900</v>
       </c>
       <c r="G47" s="3">
-        <v>12600</v>
+        <v>12100</v>
       </c>
       <c r="H47" s="3">
-        <v>12600</v>
+        <v>12500</v>
       </c>
       <c r="I47" s="3">
+        <v>12500</v>
+      </c>
+      <c r="J47" s="3">
         <v>9300</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>9800</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>3800</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>4500</v>
       </c>
-      <c r="M47" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N47" s="3" t="s">
         <v>3</v>
       </c>
       <c r="O47" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P47" s="3">
+      <c r="P47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q47" s="3">
         <v>5900</v>
       </c>
-      <c r="Q47" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R47" s="3" t="s">
         <v>3</v>
       </c>
@@ -3648,8 +3753,8 @@
       <c r="U47" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="V47" s="3">
-        <v>0</v>
+      <c r="V47" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="W47" s="3">
         <v>0</v>
@@ -3672,71 +3777,74 @@
       <c r="AC47" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
-        <v>22200</v>
+        <v>21500</v>
       </c>
       <c r="E48" s="3">
-        <v>24100</v>
+        <v>22100</v>
       </c>
       <c r="F48" s="3">
-        <v>23300</v>
+        <v>23900</v>
       </c>
       <c r="G48" s="3">
-        <v>22200</v>
+        <v>23100</v>
       </c>
       <c r="H48" s="3">
-        <v>23700</v>
+        <v>22000</v>
       </c>
       <c r="I48" s="3">
-        <v>25800</v>
+        <v>23600</v>
       </c>
       <c r="J48" s="3">
+        <v>25700</v>
+      </c>
+      <c r="K48" s="3">
         <v>27400</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>28300</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>27400</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>31400</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>28600</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>21000</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>21100</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>18100</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>11900</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>7600</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>7500</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>6100</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>3500</v>
       </c>
-      <c r="W48" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X48" s="3" t="s">
         <v>3</v>
       </c>
@@ -3755,40 +3863,43 @@
       <c r="AC48" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="49" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD48" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="49" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>15200</v>
+      </c>
+      <c r="E49" s="3">
+        <v>15200</v>
+      </c>
+      <c r="F49" s="3">
+        <v>15200</v>
+      </c>
+      <c r="G49" s="3">
+        <v>15200</v>
+      </c>
+      <c r="H49" s="3">
+        <v>15200</v>
+      </c>
+      <c r="I49" s="3">
+        <v>15200</v>
+      </c>
+      <c r="J49" s="3">
+        <v>15200</v>
+      </c>
+      <c r="K49" s="3">
         <v>15300</v>
-      </c>
-      <c r="E49" s="3">
-        <v>15300</v>
-      </c>
-      <c r="F49" s="3">
-        <v>15300</v>
-      </c>
-      <c r="G49" s="3">
-        <v>15300</v>
-      </c>
-      <c r="H49" s="3">
-        <v>15300</v>
-      </c>
-      <c r="I49" s="3">
-        <v>15300</v>
-      </c>
-      <c r="J49" s="3">
-        <v>15300</v>
-      </c>
-      <c r="K49" s="3">
-        <v>15200</v>
       </c>
       <c r="L49" s="3">
         <v>15200</v>
       </c>
-      <c r="M49" s="3" t="s">
-        <v>3</v>
+      <c r="M49" s="3">
+        <v>15200</v>
       </c>
       <c r="N49" s="3" t="s">
         <v>3</v>
@@ -3805,8 +3916,8 @@
       <c r="R49" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="S49" s="3">
-        <v>0</v>
+      <c r="S49" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="T49" s="3">
         <v>0</v>
@@ -3838,8 +3949,11 @@
       <c r="AC49" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="50" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD49" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -3921,8 +4035,11 @@
       <c r="AC50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4004,70 +4121,73 @@
       <c r="AC51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
-        <v>6300</v>
+        <v>7700</v>
       </c>
       <c r="E52" s="3">
-        <v>6500</v>
+        <v>6200</v>
       </c>
       <c r="F52" s="3">
+        <v>6400</v>
+      </c>
+      <c r="G52" s="3">
         <v>5300</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>4700</v>
       </c>
-      <c r="H52" s="3">
-        <v>4900</v>
-      </c>
       <c r="I52" s="3">
+        <v>4800</v>
+      </c>
+      <c r="J52" s="3">
         <v>5300</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>5200</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>5000</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>3200</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>30000</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>14700</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>11000</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>3400</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>3900</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>3200</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>2100</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>1300</v>
-      </c>
-      <c r="U52" s="3">
-        <v>800</v>
       </c>
       <c r="V52" s="3">
         <v>800</v>
       </c>
-      <c r="W52" s="3" t="s">
-        <v>3</v>
+      <c r="W52" s="3">
+        <v>800</v>
       </c>
       <c r="X52" s="3" t="s">
         <v>3</v>
@@ -4087,8 +4207,11 @@
       <c r="AC52" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="53" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD52" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="53" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -4170,71 +4293,74 @@
       <c r="AC53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
-        <v>231600</v>
+        <v>206400</v>
       </c>
       <c r="E54" s="3">
-        <v>212000</v>
+        <v>230200</v>
       </c>
       <c r="F54" s="3">
-        <v>256600</v>
+        <v>210700</v>
       </c>
       <c r="G54" s="3">
-        <v>230500</v>
+        <v>255100</v>
       </c>
       <c r="H54" s="3">
-        <v>316400</v>
+        <v>229100</v>
       </c>
       <c r="I54" s="3">
-        <v>288700</v>
+        <v>314500</v>
       </c>
       <c r="J54" s="3">
+        <v>286900</v>
+      </c>
+      <c r="K54" s="3">
         <v>339000</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>310600</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>363700</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>348600</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>423600</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>436300</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>288200</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>282200</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>345100</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>337900</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>321300</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>83700</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>97700</v>
       </c>
-      <c r="W54" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X54" s="3" t="s">
         <v>3</v>
       </c>
@@ -4253,8 +4379,11 @@
       <c r="AC54" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="55" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD54" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="55" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -4284,8 +4413,9 @@
       <c r="AA55" s="3"/>
       <c r="AB55" s="3"/>
       <c r="AC55" s="3"/>
-    </row>
-    <row r="56" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD55" s="3"/>
+    </row>
+    <row r="56" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -4315,71 +4445,72 @@
       <c r="AA56" s="3"/>
       <c r="AB56" s="3"/>
       <c r="AC56" s="3"/>
-    </row>
-    <row r="57" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD56" s="3"/>
+    </row>
+    <row r="57" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
-        <v>22100</v>
+        <v>16500</v>
       </c>
       <c r="E57" s="3">
-        <v>22700</v>
+        <v>22000</v>
       </c>
       <c r="F57" s="3">
-        <v>18000</v>
+        <v>22500</v>
       </c>
       <c r="G57" s="3">
-        <v>17000</v>
+        <v>17900</v>
       </c>
       <c r="H57" s="3">
-        <v>39300</v>
+        <v>16900</v>
       </c>
       <c r="I57" s="3">
-        <v>25000</v>
+        <v>39000</v>
       </c>
       <c r="J57" s="3">
+        <v>24800</v>
+      </c>
+      <c r="K57" s="3">
         <v>21100</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>18400</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>22200</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>16600</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>10600</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>17500</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>19700</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>17600</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>15200</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>14900</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>9700</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>7200</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>5300</v>
       </c>
-      <c r="W57" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X57" s="3" t="s">
         <v>3</v>
       </c>
@@ -4398,71 +4529,74 @@
       <c r="AC57" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="58" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD57" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="58" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>121300</v>
+      </c>
+      <c r="E58" s="3">
+        <v>121300</v>
+      </c>
+      <c r="F58" s="3">
+        <v>121300</v>
+      </c>
+      <c r="G58" s="3">
+        <v>201200</v>
+      </c>
+      <c r="H58" s="3">
+        <v>197300</v>
+      </c>
+      <c r="I58" s="3">
+        <v>121300</v>
+      </c>
+      <c r="J58" s="3">
+        <v>121300</v>
+      </c>
+      <c r="K58" s="3">
         <v>122100</v>
-      </c>
-      <c r="E58" s="3">
-        <v>122100</v>
-      </c>
-      <c r="F58" s="3">
-        <v>202400</v>
-      </c>
-      <c r="G58" s="3">
-        <v>198500</v>
-      </c>
-      <c r="H58" s="3">
-        <v>122100</v>
-      </c>
-      <c r="I58" s="3">
-        <v>122100</v>
-      </c>
-      <c r="J58" s="3">
-        <v>122100</v>
-      </c>
-      <c r="K58" s="3">
-        <v>121200</v>
       </c>
       <c r="L58" s="3">
         <v>121200</v>
       </c>
       <c r="M58" s="3">
-        <v>124800</v>
+        <v>121200</v>
       </c>
       <c r="N58" s="3">
         <v>124800</v>
       </c>
       <c r="O58" s="3">
-        <v>122200</v>
+        <v>124800</v>
       </c>
       <c r="P58" s="3">
         <v>122200</v>
       </c>
       <c r="Q58" s="3">
-        <v>129400</v>
+        <v>122200</v>
       </c>
       <c r="R58" s="3">
         <v>129400</v>
       </c>
       <c r="S58" s="3">
+        <v>129400</v>
+      </c>
+      <c r="T58" s="3">
         <v>137500</v>
-      </c>
-      <c r="T58" s="3">
-        <v>135200</v>
       </c>
       <c r="U58" s="3">
         <v>135200</v>
       </c>
       <c r="V58" s="3">
+        <v>135200</v>
+      </c>
+      <c r="W58" s="3">
         <v>134100</v>
       </c>
-      <c r="W58" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X58" s="3" t="s">
         <v>3</v>
       </c>
@@ -4481,71 +4615,74 @@
       <c r="AC58" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="59" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD58" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="59" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>286700</v>
+        <v>234400</v>
       </c>
       <c r="E59" s="3">
-        <v>272900</v>
+        <v>284900</v>
       </c>
       <c r="F59" s="3">
-        <v>311100</v>
+        <v>271200</v>
       </c>
       <c r="G59" s="3">
-        <v>243100</v>
+        <v>309200</v>
       </c>
       <c r="H59" s="3">
-        <v>280600</v>
+        <v>241600</v>
       </c>
       <c r="I59" s="3">
-        <v>267800</v>
+        <v>278800</v>
       </c>
       <c r="J59" s="3">
+        <v>266100</v>
+      </c>
+      <c r="K59" s="3">
         <v>298500</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>226700</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>275500</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>293600</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>375700</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>312500</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>330500</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>268200</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>204700</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>157000</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>126000</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>93900</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>76900</v>
       </c>
-      <c r="W59" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X59" s="3" t="s">
         <v>3</v>
       </c>
@@ -4564,71 +4701,74 @@
       <c r="AC59" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="60" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD59" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="60" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
-        <v>430900</v>
+        <v>372300</v>
       </c>
       <c r="E60" s="3">
-        <v>417600</v>
+        <v>428200</v>
       </c>
       <c r="F60" s="3">
-        <v>531500</v>
+        <v>415100</v>
       </c>
       <c r="G60" s="3">
-        <v>458600</v>
+        <v>528200</v>
       </c>
       <c r="H60" s="3">
-        <v>441900</v>
+        <v>455800</v>
       </c>
       <c r="I60" s="3">
-        <v>414800</v>
+        <v>439200</v>
       </c>
       <c r="J60" s="3">
+        <v>412300</v>
+      </c>
+      <c r="K60" s="3">
         <v>441700</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>366300</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>418900</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>435000</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>511100</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>452200</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>472400</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>415100</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>349200</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>309300</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>270800</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>236300</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>216400</v>
       </c>
-      <c r="W60" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X60" s="3" t="s">
         <v>3</v>
       </c>
@@ -4647,41 +4787,44 @@
       <c r="AC60" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="61" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD60" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="61" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
-        <v>87600</v>
+        <v>121700</v>
       </c>
       <c r="E61" s="3">
-        <v>83800</v>
+        <v>87100</v>
       </c>
       <c r="F61" s="3">
-        <v>0</v>
+        <v>83300</v>
       </c>
       <c r="G61" s="3">
         <v>0</v>
       </c>
       <c r="H61" s="3">
-        <v>72600</v>
+        <v>0</v>
       </c>
       <c r="I61" s="3">
-        <v>69100</v>
+        <v>72200</v>
       </c>
       <c r="J61" s="3">
+        <v>68700</v>
+      </c>
+      <c r="K61" s="3">
         <v>65300</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>48200</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>35200</v>
       </c>
-      <c r="M61" s="3">
-        <v>0</v>
-      </c>
       <c r="N61" s="3">
         <v>0</v>
       </c>
@@ -4730,68 +4873,71 @@
       <c r="AC61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>9000</v>
+      </c>
+      <c r="E62" s="3">
         <v>9100</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>10000</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>8100</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
+        <v>7100</v>
+      </c>
+      <c r="I62" s="3">
         <v>7200</v>
       </c>
-      <c r="H62" s="3">
-        <v>7300</v>
-      </c>
-      <c r="I62" s="3">
-        <v>8500</v>
-      </c>
       <c r="J62" s="3">
+        <v>8400</v>
+      </c>
+      <c r="K62" s="3">
         <v>8700</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>7700</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>10400</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>15100</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>13800</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>10900</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>11700</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>10300</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>6400</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>3900</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>4100</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>2100</v>
       </c>
-      <c r="V62" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W62" s="3" t="s">
         <v>3</v>
       </c>
@@ -4804,8 +4950,8 @@
       <c r="Z62" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="AA62" s="3">
-        <v>0</v>
+      <c r="AA62" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="AB62" s="3">
         <v>0</v>
@@ -4813,8 +4959,11 @@
       <c r="AC62" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="63" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD62" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="63" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -4896,8 +5045,11 @@
       <c r="AC63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -4979,8 +5131,11 @@
       <c r="AC64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -5062,71 +5217,74 @@
       <c r="AC65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
-        <v>535600</v>
+        <v>511200</v>
       </c>
       <c r="E66" s="3">
-        <v>519600</v>
+        <v>532300</v>
       </c>
       <c r="F66" s="3">
-        <v>546900</v>
+        <v>516400</v>
       </c>
       <c r="G66" s="3">
-        <v>473600</v>
+        <v>543500</v>
       </c>
       <c r="H66" s="3">
-        <v>529800</v>
+        <v>470700</v>
       </c>
       <c r="I66" s="3">
-        <v>501700</v>
+        <v>526600</v>
       </c>
       <c r="J66" s="3">
+        <v>498600</v>
+      </c>
+      <c r="K66" s="3">
         <v>525300</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>432700</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>475200</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>464600</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>524800</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>463100</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>484200</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>425500</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>355800</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>313400</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>275100</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>238600</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>216600</v>
       </c>
-      <c r="W66" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X66" s="3" t="s">
         <v>3</v>
       </c>
@@ -5145,8 +5303,11 @@
       <c r="AC66" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="67" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD66" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="67" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -5176,8 +5337,9 @@
       <c r="AA67" s="3"/>
       <c r="AB67" s="3"/>
       <c r="AC67" s="3"/>
-    </row>
-    <row r="68" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD67" s="3"/>
+    </row>
+    <row r="68" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -5259,8 +5421,11 @@
       <c r="AC68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -5342,8 +5507,11 @@
       <c r="AC69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -5399,14 +5567,14 @@
         <v>0</v>
       </c>
       <c r="U70" s="3">
+        <v>0</v>
+      </c>
+      <c r="V70" s="3">
         <v>75900</v>
       </c>
-      <c r="V70" s="3">
+      <c r="W70" s="3">
         <v>73600</v>
       </c>
-      <c r="W70" s="3">
-        <v>0</v>
-      </c>
       <c r="X70" s="3">
         <v>0</v>
       </c>
@@ -5425,8 +5593,11 @@
       <c r="AC70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -5508,16 +5679,19 @@
       <c r="AC71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="E72" s="3" t="s">
-        <v>3</v>
+      <c r="E72" s="3">
+        <v>-821200</v>
       </c>
       <c r="F72" s="3" t="s">
         <v>3</v>
@@ -5525,11 +5699,11 @@
       <c r="G72" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="H72" s="3">
-        <v>-749800</v>
-      </c>
-      <c r="I72" s="3" t="s">
-        <v>3</v>
+      <c r="H72" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I72" s="3">
+        <v>-745200</v>
       </c>
       <c r="J72" s="3" t="s">
         <v>3</v>
@@ -5549,30 +5723,30 @@
       <c r="O72" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P72" s="3">
+      <c r="P72" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q72" s="3">
         <v>-511000</v>
       </c>
-      <c r="Q72" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R72" s="3" t="s">
         <v>3</v>
       </c>
       <c r="S72" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="T72" s="3">
+      <c r="T72" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="U72" s="3">
         <v>-295400</v>
       </c>
-      <c r="U72" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="V72" s="3">
+      <c r="V72" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="W72" s="3">
         <v>-224700</v>
       </c>
-      <c r="W72" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X72" s="3" t="s">
         <v>3</v>
       </c>
@@ -5591,8 +5765,11 @@
       <c r="AC72" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="73" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD72" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="73" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -5674,8 +5851,11 @@
       <c r="AC73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -5757,8 +5937,11 @@
       <c r="AC74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -5840,71 +6023,74 @@
       <c r="AC75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
-        <v>-304000</v>
+        <v>-304800</v>
       </c>
       <c r="E76" s="3">
-        <v>-307600</v>
+        <v>-302100</v>
       </c>
       <c r="F76" s="3">
-        <v>-290200</v>
+        <v>-305600</v>
       </c>
       <c r="G76" s="3">
-        <v>-243000</v>
+        <v>-288400</v>
       </c>
       <c r="H76" s="3">
-        <v>-213400</v>
+        <v>-241500</v>
       </c>
       <c r="I76" s="3">
-        <v>-213000</v>
+        <v>-212100</v>
       </c>
       <c r="J76" s="3">
+        <v>-211700</v>
+      </c>
+      <c r="K76" s="3">
         <v>-186400</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>-122100</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>-111400</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>-116000</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>-101200</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>-26700</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>-196000</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>-143300</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>-10700</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>24500</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>46200</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>-230800</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>-192500</v>
       </c>
-      <c r="W76" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X76" s="3" t="s">
         <v>3</v>
       </c>
@@ -5923,8 +6109,11 @@
       <c r="AC76" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="77" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD76" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="77" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -6006,179 +6195,188 @@
       <c r="AC77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:30" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:29" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45382</v>
+      </c>
+      <c r="E80" s="2">
         <v>45291</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45199</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45107</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45016</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>44926</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>44834</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44742</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44651</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44561</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44469</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44377</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44286</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44196</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44104</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44012</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>43921</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>43830</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>43738</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>43646</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>43555</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43465</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>43373</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43281</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43190</v>
       </c>
-      <c r="AB80" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="AC80" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="81" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD80" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="81" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
-        <v>7900</v>
+        <v>1700</v>
       </c>
       <c r="E81" s="3">
-        <v>-14300</v>
+        <v>7800</v>
       </c>
       <c r="F81" s="3">
-        <v>-41600</v>
+        <v>-14200</v>
       </c>
       <c r="G81" s="3">
-        <v>-28400</v>
+        <v>-41300</v>
       </c>
       <c r="H81" s="3">
+        <v>-28200</v>
+      </c>
+      <c r="I81" s="3">
         <v>1700</v>
       </c>
-      <c r="I81" s="3">
-        <v>-25600</v>
-      </c>
       <c r="J81" s="3">
+        <v>-25400</v>
+      </c>
+      <c r="K81" s="3">
         <v>-63100</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>-14000</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>-137500</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>-18300</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>-74500</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>-45400</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>-62300</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>-129400</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>-38000</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>-26500</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>-31700</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>-37300</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>-13400</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>-15500</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>-10200</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>-11200</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>-4200</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>-8900</v>
       </c>
-      <c r="AB81" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AC81" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="82" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD81" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="82" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -6208,8 +6406,9 @@
       <c r="AA82" s="3"/>
       <c r="AB82" s="3"/>
       <c r="AC82" s="3"/>
-    </row>
-    <row r="83" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD82" s="3"/>
+    </row>
+    <row r="83" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
@@ -6222,41 +6421,41 @@
       <c r="F83" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="G83" s="3">
+      <c r="G83" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H83" s="3">
         <v>1100</v>
-      </c>
-      <c r="H83" s="3">
-        <v>1600</v>
       </c>
       <c r="I83" s="3">
         <v>1600</v>
       </c>
       <c r="J83" s="3">
+        <v>1600</v>
+      </c>
+      <c r="K83" s="3">
         <v>1500</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>1100</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>4200</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>1100</v>
-      </c>
-      <c r="N83" s="3">
-        <v>800</v>
       </c>
       <c r="O83" s="3">
         <v>800</v>
       </c>
       <c r="P83" s="3">
+        <v>800</v>
+      </c>
+      <c r="Q83" s="3">
         <v>700</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>600</v>
-      </c>
-      <c r="R83" s="3">
-        <v>500</v>
       </c>
       <c r="S83" s="3">
         <v>500</v>
@@ -6265,11 +6464,11 @@
         <v>500</v>
       </c>
       <c r="U83" s="3">
+        <v>500</v>
+      </c>
+      <c r="V83" s="3">
         <v>400</v>
       </c>
-      <c r="V83" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W83" s="3" t="s">
         <v>3</v>
       </c>
@@ -6282,8 +6481,8 @@
       <c r="Z83" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="AA83" s="3">
-        <v>0</v>
+      <c r="AA83" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="AB83" s="3">
         <v>0</v>
@@ -6291,8 +6490,11 @@
       <c r="AC83" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="84" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD83" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -6374,8 +6576,11 @@
       <c r="AC84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -6457,8 +6662,11 @@
       <c r="AC85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -6540,8 +6748,11 @@
       <c r="AC86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -6623,8 +6834,11 @@
       <c r="AC87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -6706,25 +6920,28 @@
       <c r="AC88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
-        <v>19900</v>
+        <v>54000</v>
       </c>
       <c r="E89" s="3">
-        <v>22500</v>
+        <v>-101200</v>
       </c>
       <c r="F89" s="3">
-        <v>-42300</v>
+        <v>22300</v>
       </c>
       <c r="G89" s="3">
-        <v>60800</v>
-      </c>
-      <c r="H89" s="3" t="s">
-        <v>3</v>
+        <v>-42000</v>
+      </c>
+      <c r="H89" s="3">
+        <v>60400</v>
       </c>
       <c r="I89" s="3" t="s">
         <v>3</v>
@@ -6732,42 +6949,42 @@
       <c r="J89" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K89" s="3">
+      <c r="K89" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L89" s="3">
         <v>58800</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>-185900</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>89400</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>35400</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>72100</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>-147200</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>87400</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>21000</v>
       </c>
-      <c r="S89" s="3">
-        <v>0</v>
-      </c>
       <c r="T89" s="3">
+        <v>0</v>
+      </c>
+      <c r="U89" s="3">
         <v>-48300</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>21900</v>
       </c>
-      <c r="V89" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W89" s="3" t="s">
         <v>3</v>
       </c>
@@ -6780,8 +6997,8 @@
       <c r="Z89" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="AA89" s="3">
-        <v>0</v>
+      <c r="AA89" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="AB89" s="3">
         <v>0</v>
@@ -6789,8 +7006,11 @@
       <c r="AC89" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="90" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD89" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="90" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -6820,58 +7040,59 @@
       <c r="AA90" s="3"/>
       <c r="AB90" s="3"/>
       <c r="AC90" s="3"/>
-    </row>
-    <row r="91" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD90" s="3"/>
+    </row>
+    <row r="91" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-2500</v>
+      </c>
+      <c r="E91" s="3">
         <v>-13200</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-1900</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-6100</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-500</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-62200</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-6500</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-17900</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-3400</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-1900</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-11400</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-15900</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-1600</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-2200</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-1800</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-600</v>
-      </c>
-      <c r="S91" s="3">
-        <v>-700</v>
       </c>
       <c r="T91" s="3">
         <v>-700</v>
@@ -6879,8 +7100,8 @@
       <c r="U91" s="3">
         <v>-700</v>
       </c>
-      <c r="V91" s="3" t="s">
-        <v>3</v>
+      <c r="V91" s="3">
+        <v>-700</v>
       </c>
       <c r="W91" s="3" t="s">
         <v>3</v>
@@ -6894,8 +7115,8 @@
       <c r="Z91" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="AA91" s="3">
-        <v>0</v>
+      <c r="AA91" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="AB91" s="3">
         <v>0</v>
@@ -6903,8 +7124,11 @@
       <c r="AC91" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="92" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD91" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -6986,8 +7210,11 @@
       <c r="AC92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -7069,31 +7296,34 @@
       <c r="AC93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
-      <c r="D94" s="3">
-        <v>0</v>
+      <c r="D94" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="E94" s="3">
-        <v>0</v>
-      </c>
-      <c r="F94" s="3">
-        <v>0</v>
-      </c>
-      <c r="G94" s="3">
-        <v>0</v>
-      </c>
-      <c r="H94" s="3">
-        <v>0</v>
-      </c>
-      <c r="I94" s="3">
-        <v>0</v>
-      </c>
-      <c r="J94" s="3">
-        <v>0</v>
+        <v>-1800</v>
+      </c>
+      <c r="F94" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G94" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H94" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I94" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J94" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K94" s="3">
         <v>0</v>
@@ -7152,8 +7382,11 @@
       <c r="AC94" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="95" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD94" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="95" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -7183,8 +7416,9 @@
       <c r="AA95" s="3"/>
       <c r="AB95" s="3"/>
       <c r="AC95" s="3"/>
-    </row>
-    <row r="96" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD95" s="3"/>
+    </row>
+    <row r="96" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -7266,8 +7500,11 @@
       <c r="AC96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -7349,8 +7586,11 @@
       <c r="AC97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -7432,8 +7672,11 @@
       <c r="AC98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -7515,8 +7758,11 @@
       <c r="AC99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
@@ -7598,8 +7844,11 @@
       <c r="AC100" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="101" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD100" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="101" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -7681,8 +7930,11 @@
       <c r="AC101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
@@ -7762,6 +8014,9 @@
         <v>0</v>
       </c>
       <c r="AC102" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD102" s="3">
         <v>0</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/DAO_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/DAO_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="341" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="347" uniqueCount="92">
   <si>
     <t>DAO</t>
   </si>
@@ -656,390 +656,403 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AD102"/>
+  <dimension ref="A5:AE102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="6.42578125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="22" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="26" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="30" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="19" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="23" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="27" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="31" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:30" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:30" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:31" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:30" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:31" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45473</v>
+      </c>
+      <c r="E7" s="2">
         <v>45382</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45291</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45199</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45107</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45016</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>44926</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44834</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44742</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44651</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44561</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44469</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44377</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44286</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44196</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44104</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44012</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>43921</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>43830</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>43738</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>43646</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43555</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>43465</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43373</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43281</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43190</v>
       </c>
-      <c r="AC7" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="AD7" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="8" spans="1:30" x14ac:dyDescent="0.2">
+      <c r="AE7" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:31" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D8" s="3">
-        <v>192300</v>
+        <v>186300</v>
       </c>
       <c r="E8" s="3">
-        <v>204500</v>
+        <v>196200</v>
       </c>
       <c r="F8" s="3">
-        <v>212600</v>
+        <v>208700</v>
       </c>
       <c r="G8" s="3">
-        <v>166700</v>
+        <v>216900</v>
       </c>
       <c r="H8" s="3">
-        <v>160700</v>
+        <v>170100</v>
       </c>
       <c r="I8" s="3">
-        <v>200900</v>
+        <v>164000</v>
       </c>
       <c r="J8" s="3">
+        <v>205000</v>
+      </c>
+      <c r="K8" s="3">
         <v>193800</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>132900</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>165800</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>554500</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>197200</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>139300</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>132000</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>64900</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>132000</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>91800</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>84800</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>63200</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>53300</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>49300</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>34300</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>33400</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>25300</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>27000</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>19300</v>
       </c>
-      <c r="AC8" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AD8" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="9" spans="1:30" x14ac:dyDescent="0.2">
+      <c r="AE8" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="9" spans="1:31" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D9" s="3">
-        <v>98100</v>
+        <v>96600</v>
       </c>
       <c r="E9" s="3">
-        <v>102500</v>
+        <v>100100</v>
       </c>
       <c r="F9" s="3">
-        <v>93800</v>
+        <v>104600</v>
       </c>
       <c r="G9" s="3">
-        <v>88300</v>
+        <v>95700</v>
       </c>
       <c r="H9" s="3">
-        <v>77600</v>
+        <v>90200</v>
       </c>
       <c r="I9" s="3">
-        <v>93900</v>
+        <v>79100</v>
       </c>
       <c r="J9" s="3">
+        <v>95800</v>
+      </c>
+      <c r="K9" s="3">
         <v>88700</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>76000</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>77100</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>279900</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>85500</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>68200</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>62900</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>120900</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>71400</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>50400</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>47900</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>44300</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>39500</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>33100</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Y9" s="3">
         <v>26300</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="Z9" s="3">
         <v>23500</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AA9" s="3">
         <v>19400</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AB9" s="3">
         <v>17200</v>
       </c>
-      <c r="AB9" s="3">
+      <c r="AC9" s="3">
         <v>13900</v>
       </c>
-      <c r="AC9" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AD9" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="10" spans="1:30" x14ac:dyDescent="0.2">
+      <c r="AE9" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:31" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
-        <v>94200</v>
+        <v>89800</v>
       </c>
       <c r="E10" s="3">
-        <v>102100</v>
+        <v>96100</v>
       </c>
       <c r="F10" s="3">
-        <v>118800</v>
+        <v>104200</v>
       </c>
       <c r="G10" s="3">
-        <v>78400</v>
+        <v>121200</v>
       </c>
       <c r="H10" s="3">
-        <v>83200</v>
+        <v>80000</v>
       </c>
       <c r="I10" s="3">
-        <v>107000</v>
+        <v>84900</v>
       </c>
       <c r="J10" s="3">
+        <v>109200</v>
+      </c>
+      <c r="K10" s="3">
         <v>105000</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>57000</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>88600</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>274600</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>111700</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>71100</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>69100</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>-56100</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>60600</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>41500</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>36900</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>18800</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>13700</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>16200</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Y10" s="3">
         <v>8000</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="Z10" s="3">
         <v>9900</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AA10" s="3">
         <v>5900</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AB10" s="3">
         <v>9800</v>
       </c>
-      <c r="AB10" s="3">
+      <c r="AC10" s="3">
         <v>5400</v>
       </c>
-      <c r="AC10" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AD10" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="11" spans="1:30" x14ac:dyDescent="0.2">
+      <c r="AE10" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:31" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -1070,94 +1083,98 @@
       <c r="AB11" s="3"/>
       <c r="AC11" s="3"/>
       <c r="AD11" s="3"/>
-    </row>
-    <row r="12" spans="1:30" x14ac:dyDescent="0.2">
+      <c r="AE11" s="3"/>
+    </row>
+    <row r="12" spans="1:31" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D12" s="3">
-        <v>20300</v>
+        <v>21600</v>
       </c>
       <c r="E12" s="3">
-        <v>23200</v>
+        <v>20700</v>
       </c>
       <c r="F12" s="3">
-        <v>25900</v>
+        <v>23700</v>
       </c>
       <c r="G12" s="3">
-        <v>28300</v>
+        <v>26400</v>
       </c>
       <c r="H12" s="3">
+        <v>28900</v>
+      </c>
+      <c r="I12" s="3">
+        <v>25800</v>
+      </c>
+      <c r="J12" s="3">
         <v>25300</v>
       </c>
-      <c r="I12" s="3">
-        <v>24800</v>
-      </c>
-      <c r="J12" s="3">
+      <c r="K12" s="3">
         <v>29400</v>
       </c>
-      <c r="K12" s="3">
+      <c r="L12" s="3">
         <v>29000</v>
       </c>
-      <c r="L12" s="3">
+      <c r="M12" s="3">
         <v>28000</v>
       </c>
-      <c r="M12" s="3">
+      <c r="N12" s="3">
         <v>83900</v>
       </c>
-      <c r="N12" s="3">
+      <c r="O12" s="3">
         <v>27500</v>
       </c>
-      <c r="O12" s="3">
+      <c r="P12" s="3">
         <v>20700</v>
       </c>
-      <c r="P12" s="3">
+      <c r="Q12" s="3">
         <v>17800</v>
       </c>
-      <c r="Q12" s="3">
+      <c r="R12" s="3">
         <v>10500</v>
       </c>
-      <c r="R12" s="3">
+      <c r="S12" s="3">
         <v>17800</v>
       </c>
-      <c r="S12" s="3">
+      <c r="T12" s="3">
         <v>13500</v>
       </c>
-      <c r="T12" s="3">
+      <c r="U12" s="3">
         <v>13200</v>
       </c>
-      <c r="U12" s="3">
+      <c r="V12" s="3">
         <v>13700</v>
       </c>
-      <c r="V12" s="3">
+      <c r="W12" s="3">
         <v>11500</v>
       </c>
-      <c r="W12" s="3">
+      <c r="X12" s="3">
         <v>8600</v>
       </c>
-      <c r="X12" s="3">
+      <c r="Y12" s="3">
         <v>8300</v>
       </c>
-      <c r="Y12" s="3">
+      <c r="Z12" s="3">
         <v>7300</v>
       </c>
-      <c r="Z12" s="3">
+      <c r="AA12" s="3">
         <v>7700</v>
       </c>
-      <c r="AA12" s="3">
+      <c r="AB12" s="3">
         <v>5400</v>
       </c>
-      <c r="AB12" s="3">
+      <c r="AC12" s="3">
         <v>6100</v>
       </c>
-      <c r="AC12" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AD12" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="13" spans="1:30" x14ac:dyDescent="0.2">
+      <c r="AE12" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:31" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1242,8 +1259,11 @@
       <c r="AD13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:30" x14ac:dyDescent="0.2">
+      <c r="AE13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:31" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -1274,12 +1294,12 @@
       <c r="L14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M14" s="3">
+      <c r="M14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N14" s="3">
         <v>7800</v>
       </c>
-      <c r="N14" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O14" s="3" t="s">
         <v>3</v>
       </c>
@@ -1295,8 +1315,8 @@
       <c r="S14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="T14" s="3">
-        <v>0</v>
+      <c r="T14" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="U14" s="3">
         <v>0</v>
@@ -1328,8 +1348,11 @@
       <c r="AD14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:30" x14ac:dyDescent="0.2">
+      <c r="AE14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:31" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1414,8 +1437,11 @@
       <c r="AD15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:30" x14ac:dyDescent="0.2">
+      <c r="AE15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:31" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1443,180 +1469,187 @@
       <c r="AB16" s="3"/>
       <c r="AC16" s="3"/>
       <c r="AD16" s="3"/>
-    </row>
-    <row r="17" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE16" s="3"/>
+    </row>
+    <row r="17" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
-        <v>188200</v>
+        <v>196600</v>
       </c>
       <c r="E17" s="3">
-        <v>194000</v>
+        <v>192000</v>
       </c>
       <c r="F17" s="3">
-        <v>220600</v>
+        <v>198000</v>
       </c>
       <c r="G17" s="3">
-        <v>206700</v>
+        <v>225100</v>
       </c>
       <c r="H17" s="3">
-        <v>187800</v>
+        <v>210900</v>
       </c>
       <c r="I17" s="3">
-        <v>197500</v>
+        <v>191600</v>
       </c>
       <c r="J17" s="3">
+        <v>201500</v>
+      </c>
+      <c r="K17" s="3">
         <v>224000</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>196200</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>183000</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>684700</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>215600</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>175500</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>161800</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>-4900</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>263800</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>133600</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>112300</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>94600</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>89400</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>62000</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>46400</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>40700</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>37800</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>31300</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>26700</v>
       </c>
-      <c r="AC17" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AD17" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="18" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE17" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
-        <v>4100</v>
+        <v>-10200</v>
       </c>
       <c r="E18" s="3">
-        <v>10500</v>
+        <v>4200</v>
       </c>
       <c r="F18" s="3">
-        <v>-8000</v>
+        <v>10800</v>
       </c>
       <c r="G18" s="3">
-        <v>-40000</v>
+        <v>-8100</v>
       </c>
       <c r="H18" s="3">
-        <v>-27000</v>
+        <v>-40800</v>
       </c>
       <c r="I18" s="3">
-        <v>3400</v>
+        <v>-27600</v>
       </c>
       <c r="J18" s="3">
+        <v>3500</v>
+      </c>
+      <c r="K18" s="3">
         <v>-30300</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>-63300</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>-17300</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>-130200</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>-18400</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>-36200</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>-29800</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>69800</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>-131700</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>-41700</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>-27600</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>-31400</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>-36100</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>-12700</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>-12000</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>-7300</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>-12400</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>-4400</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>-7500</v>
       </c>
-      <c r="AC18" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AD18" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="19" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE18" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1647,94 +1680,98 @@
       <c r="AB19" s="3"/>
       <c r="AC19" s="3"/>
       <c r="AD19" s="3"/>
-    </row>
-    <row r="20" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE19" s="3"/>
+    </row>
+    <row r="20" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>0</v>
+      </c>
+      <c r="E20" s="3">
         <v>500</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>-100</v>
       </c>
-      <c r="F20" s="3">
-        <v>-2600</v>
-      </c>
       <c r="G20" s="3">
+        <v>-2700</v>
+      </c>
+      <c r="H20" s="3">
         <v>1100</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>1200</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
+        <v>1000</v>
+      </c>
+      <c r="K20" s="3">
+        <v>6100</v>
+      </c>
+      <c r="L20" s="3">
+        <v>700</v>
+      </c>
+      <c r="M20" s="3">
+        <v>5300</v>
+      </c>
+      <c r="N20" s="3">
+        <v>7700</v>
+      </c>
+      <c r="O20" s="3">
         <v>900</v>
       </c>
-      <c r="J20" s="3">
-        <v>6100</v>
-      </c>
-      <c r="K20" s="3">
+      <c r="P20" s="3">
+        <v>4300</v>
+      </c>
+      <c r="Q20" s="3">
+        <v>500</v>
+      </c>
+      <c r="R20" s="3">
         <v>700</v>
       </c>
-      <c r="L20" s="3">
-        <v>5300</v>
-      </c>
-      <c r="M20" s="3">
-        <v>7700</v>
-      </c>
-      <c r="N20" s="3">
-        <v>900</v>
-      </c>
-      <c r="O20" s="3">
-        <v>4300</v>
-      </c>
-      <c r="P20" s="3">
-        <v>500</v>
-      </c>
-      <c r="Q20" s="3">
-        <v>700</v>
-      </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>2400</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>3700</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>1400</v>
       </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3">
         <v>200</v>
       </c>
-      <c r="V20" s="3">
+      <c r="W20" s="3">
         <v>800</v>
       </c>
-      <c r="W20" s="3">
+      <c r="X20" s="3">
         <v>1200</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Y20" s="3">
         <v>-1800</v>
       </c>
-      <c r="Y20" s="3">
+      <c r="Z20" s="3">
         <v>-800</v>
       </c>
-      <c r="Z20" s="3">
+      <c r="AA20" s="3">
         <v>3200</v>
       </c>
-      <c r="AA20" s="3">
+      <c r="AB20" s="3">
         <v>1700</v>
       </c>
-      <c r="AB20" s="3">
+      <c r="AC20" s="3">
         <v>-1100</v>
       </c>
-      <c r="AC20" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AD20" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="21" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE20" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
@@ -1750,54 +1787,54 @@
       <c r="G21" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="H21" s="3">
-        <v>-24800</v>
+      <c r="H21" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="I21" s="3">
-        <v>6000</v>
+        <v>-25300</v>
       </c>
       <c r="J21" s="3">
+        <v>6100</v>
+      </c>
+      <c r="K21" s="3">
         <v>-22600</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>-61100</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>-10900</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>-118400</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>-16400</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>-31100</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>-28600</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>71200</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>-128700</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>-37500</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>-25600</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>-30700</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>-35000</v>
       </c>
-      <c r="W21" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X21" s="3" t="s">
         <v>3</v>
       </c>
@@ -1807,55 +1844,58 @@
       <c r="Z21" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AA21" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AB21" s="3">
         <v>-2300</v>
       </c>
-      <c r="AB21" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AC21" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AD21" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="22" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE21" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="22" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
-        <v>2800</v>
+        <v>2900</v>
       </c>
       <c r="E22" s="3">
-        <v>2600</v>
+        <v>2900</v>
       </c>
       <c r="F22" s="3">
+        <v>2700</v>
+      </c>
+      <c r="G22" s="3">
         <v>2500</v>
       </c>
-      <c r="G22" s="3">
+      <c r="H22" s="3">
         <v>2400</v>
       </c>
-      <c r="H22" s="3">
+      <c r="I22" s="3">
         <v>2200</v>
       </c>
-      <c r="I22" s="3">
-        <v>2000</v>
-      </c>
       <c r="J22" s="3">
+        <v>2100</v>
+      </c>
+      <c r="K22" s="3">
         <v>1700</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>1400</v>
       </c>
-      <c r="L22" s="3">
+      <c r="M22" s="3">
         <v>1200</v>
       </c>
-      <c r="M22" s="3">
+      <c r="N22" s="3">
         <v>4400</v>
-      </c>
-      <c r="N22" s="3">
-        <v>1100</v>
       </c>
       <c r="O22" s="3">
         <v>1100</v>
@@ -1863,8 +1903,8 @@
       <c r="P22" s="3">
         <v>1100</v>
       </c>
-      <c r="Q22" s="3" t="s">
-        <v>3</v>
+      <c r="Q22" s="3">
+        <v>1100</v>
       </c>
       <c r="R22" s="3" t="s">
         <v>3</v>
@@ -1881,8 +1921,8 @@
       <c r="V22" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="W22" s="3">
-        <v>0</v>
+      <c r="W22" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="X22" s="3">
         <v>0</v>
@@ -1905,153 +1945,159 @@
       <c r="AD22" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-13200</v>
+      </c>
+      <c r="E23" s="3">
         <v>1900</v>
       </c>
-      <c r="E23" s="3">
-        <v>7800</v>
-      </c>
       <c r="F23" s="3">
-        <v>-13000</v>
+        <v>8000</v>
       </c>
       <c r="G23" s="3">
-        <v>-41200</v>
+        <v>-13300</v>
       </c>
       <c r="H23" s="3">
-        <v>-28000</v>
+        <v>-42100</v>
       </c>
       <c r="I23" s="3">
-        <v>2300</v>
+        <v>-28600</v>
       </c>
       <c r="J23" s="3">
+        <v>2400</v>
+      </c>
+      <c r="K23" s="3">
         <v>-25900</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>-63900</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>-13200</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>-127000</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>-18600</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>-33100</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>-30400</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>70600</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>-129400</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>-38000</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>-26200</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>-31200</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>-35400</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>-11500</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>-13900</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>-8100</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>-9300</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>-2600</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>-8500</v>
       </c>
-      <c r="AC23" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AD23" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="24" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE23" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="24" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>1000</v>
+      </c>
+      <c r="E24" s="3">
         <v>-100</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>100</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>400</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>700</v>
       </c>
-      <c r="H24" s="3">
-        <v>400</v>
-      </c>
       <c r="I24" s="3">
-        <v>1900</v>
+        <v>500</v>
       </c>
       <c r="J24" s="3">
+        <v>2000</v>
+      </c>
+      <c r="K24" s="3">
         <v>-200</v>
-      </c>
-      <c r="K24" s="3">
-        <v>100</v>
       </c>
       <c r="L24" s="3">
         <v>100</v>
       </c>
       <c r="M24" s="3">
+        <v>100</v>
+      </c>
+      <c r="N24" s="3">
         <v>900</v>
-      </c>
-      <c r="N24" s="3">
-        <v>400</v>
       </c>
       <c r="O24" s="3">
         <v>400</v>
       </c>
       <c r="P24" s="3">
+        <v>400</v>
+      </c>
+      <c r="Q24" s="3">
         <v>200</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>100</v>
       </c>
-      <c r="R24" s="3">
-        <v>0</v>
-      </c>
       <c r="S24" s="3">
         <v>0</v>
       </c>
       <c r="T24" s="3">
+        <v>0</v>
+      </c>
+      <c r="U24" s="3">
         <v>300</v>
       </c>
-      <c r="U24" s="3">
-        <v>0</v>
-      </c>
       <c r="V24" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="W24" s="3">
         <v>100</v>
@@ -2060,25 +2106,28 @@
         <v>100</v>
       </c>
       <c r="Y24" s="3">
-        <v>500</v>
+        <v>100</v>
       </c>
       <c r="Z24" s="3">
         <v>500</v>
       </c>
       <c r="AA24" s="3">
+        <v>500</v>
+      </c>
+      <c r="AB24" s="3">
         <v>200</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AC24" s="3">
         <v>500</v>
       </c>
-      <c r="AC24" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AD24" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="25" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE24" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="25" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2163,180 +2212,189 @@
       <c r="AD25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-14200</v>
+      </c>
+      <c r="E26" s="3">
         <v>2000</v>
       </c>
-      <c r="E26" s="3">
-        <v>7800</v>
-      </c>
       <c r="F26" s="3">
-        <v>-13400</v>
+        <v>7900</v>
       </c>
       <c r="G26" s="3">
-        <v>-41900</v>
+        <v>-13700</v>
       </c>
       <c r="H26" s="3">
-        <v>-28500</v>
+        <v>-42700</v>
       </c>
       <c r="I26" s="3">
+        <v>-29100</v>
+      </c>
+      <c r="J26" s="3">
         <v>400</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>-25700</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>-64000</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>-13300</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>-127900</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>-18900</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>-33500</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>-30600</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>70500</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>-129400</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>-38000</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>-26500</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>-31200</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>-35500</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>-11600</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>-14000</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>-8600</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>-9800</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>-2800</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>-9000</v>
       </c>
-      <c r="AC26" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AD26" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="27" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE26" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="27" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-14000</v>
+      </c>
+      <c r="E27" s="3">
+        <v>1800</v>
+      </c>
+      <c r="F27" s="3">
+        <v>8000</v>
+      </c>
+      <c r="G27" s="3">
+        <v>-14500</v>
+      </c>
+      <c r="H27" s="3">
+        <v>-42200</v>
+      </c>
+      <c r="I27" s="3">
+        <v>-28800</v>
+      </c>
+      <c r="J27" s="3">
         <v>1700</v>
       </c>
-      <c r="E27" s="3">
-        <v>7800</v>
-      </c>
-      <c r="F27" s="3">
-        <v>-14200</v>
-      </c>
-      <c r="G27" s="3">
-        <v>-41300</v>
-      </c>
-      <c r="H27" s="3">
-        <v>-28200</v>
-      </c>
-      <c r="I27" s="3">
-        <v>1700</v>
-      </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>-25400</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>-63100</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>-13200</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>-123600</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>-18300</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>-33400</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>-30500</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>70500</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>-129400</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>-38000</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>-26500</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>-31700</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>-37300</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>-13400</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>-15500</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>-10200</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>-11200</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>-4200</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>-8900</v>
       </c>
-      <c r="AC27" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AD27" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="28" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE27" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="28" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2421,16 +2479,19 @@
       <c r="AD28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
       <c r="D29" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="E29" s="3">
-        <v>0</v>
+      <c r="E29" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="F29" s="3">
         <v>0</v>
@@ -2451,31 +2512,31 @@
         <v>0</v>
       </c>
       <c r="L29" s="3">
+        <v>0</v>
+      </c>
+      <c r="M29" s="3">
         <v>-800</v>
       </c>
-      <c r="M29" s="3">
+      <c r="N29" s="3">
         <v>-13800</v>
       </c>
-      <c r="N29" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="O29" s="3">
+      <c r="O29" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P29" s="3">
         <v>-41200</v>
       </c>
-      <c r="P29" s="3">
+      <c r="Q29" s="3">
         <v>-14800</v>
       </c>
-      <c r="Q29" s="3">
+      <c r="R29" s="3">
         <v>-132800</v>
       </c>
-      <c r="R29" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S29" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="T29" s="3">
-        <v>0</v>
+      <c r="T29" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="U29" s="3">
         <v>0</v>
@@ -2507,8 +2568,11 @@
       <c r="AD29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2593,8 +2657,11 @@
       <c r="AD30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2679,180 +2746,189 @@
       <c r="AD31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>0</v>
+      </c>
+      <c r="E32" s="3">
         <v>-500</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>100</v>
       </c>
-      <c r="F32" s="3">
-        <v>2600</v>
-      </c>
       <c r="G32" s="3">
+        <v>2700</v>
+      </c>
+      <c r="H32" s="3">
         <v>-1100</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>-1200</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
+        <v>-1000</v>
+      </c>
+      <c r="K32" s="3">
+        <v>-6100</v>
+      </c>
+      <c r="L32" s="3">
+        <v>-700</v>
+      </c>
+      <c r="M32" s="3">
+        <v>-5300</v>
+      </c>
+      <c r="N32" s="3">
+        <v>-7700</v>
+      </c>
+      <c r="O32" s="3">
         <v>-900</v>
       </c>
-      <c r="J32" s="3">
-        <v>-6100</v>
-      </c>
-      <c r="K32" s="3">
+      <c r="P32" s="3">
+        <v>-4300</v>
+      </c>
+      <c r="Q32" s="3">
+        <v>-500</v>
+      </c>
+      <c r="R32" s="3">
         <v>-700</v>
       </c>
-      <c r="L32" s="3">
-        <v>-5300</v>
-      </c>
-      <c r="M32" s="3">
-        <v>-7700</v>
-      </c>
-      <c r="N32" s="3">
-        <v>-900</v>
-      </c>
-      <c r="O32" s="3">
-        <v>-4300</v>
-      </c>
-      <c r="P32" s="3">
-        <v>-500</v>
-      </c>
-      <c r="Q32" s="3">
-        <v>-700</v>
-      </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>-2400</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>-3700</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>-1400</v>
       </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3">
         <v>-200</v>
       </c>
-      <c r="V32" s="3">
+      <c r="W32" s="3">
         <v>-800</v>
       </c>
-      <c r="W32" s="3">
+      <c r="X32" s="3">
         <v>-1200</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Y32" s="3">
         <v>1800</v>
       </c>
-      <c r="Y32" s="3">
+      <c r="Z32" s="3">
         <v>800</v>
       </c>
-      <c r="Z32" s="3">
+      <c r="AA32" s="3">
         <v>-3200</v>
       </c>
-      <c r="AA32" s="3">
+      <c r="AB32" s="3">
         <v>-1700</v>
       </c>
-      <c r="AB32" s="3">
+      <c r="AC32" s="3">
         <v>1100</v>
       </c>
-      <c r="AC32" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AD32" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="33" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE32" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="33" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-14000</v>
+      </c>
+      <c r="E33" s="3">
+        <v>1800</v>
+      </c>
+      <c r="F33" s="3">
+        <v>8000</v>
+      </c>
+      <c r="G33" s="3">
+        <v>-14500</v>
+      </c>
+      <c r="H33" s="3">
+        <v>-42200</v>
+      </c>
+      <c r="I33" s="3">
+        <v>-28800</v>
+      </c>
+      <c r="J33" s="3">
         <v>1700</v>
       </c>
-      <c r="E33" s="3">
-        <v>7800</v>
-      </c>
-      <c r="F33" s="3">
-        <v>-14200</v>
-      </c>
-      <c r="G33" s="3">
-        <v>-41300</v>
-      </c>
-      <c r="H33" s="3">
-        <v>-28200</v>
-      </c>
-      <c r="I33" s="3">
-        <v>1700</v>
-      </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>-25400</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>-63100</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>-14000</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>-137500</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>-18300</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>-74500</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>-45400</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>-62300</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>-129400</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>-38000</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>-26500</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>-31700</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>-37300</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>-13400</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>-15500</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>-10200</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>-11200</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>-4200</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>-8900</v>
       </c>
-      <c r="AC33" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AD33" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="34" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE33" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="34" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2937,185 +3013,194 @@
       <c r="AD34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-14000</v>
+      </c>
+      <c r="E35" s="3">
+        <v>1800</v>
+      </c>
+      <c r="F35" s="3">
+        <v>8000</v>
+      </c>
+      <c r="G35" s="3">
+        <v>-14500</v>
+      </c>
+      <c r="H35" s="3">
+        <v>-42200</v>
+      </c>
+      <c r="I35" s="3">
+        <v>-28800</v>
+      </c>
+      <c r="J35" s="3">
         <v>1700</v>
       </c>
-      <c r="E35" s="3">
-        <v>7800</v>
-      </c>
-      <c r="F35" s="3">
-        <v>-14200</v>
-      </c>
-      <c r="G35" s="3">
-        <v>-41300</v>
-      </c>
-      <c r="H35" s="3">
-        <v>-28200</v>
-      </c>
-      <c r="I35" s="3">
-        <v>1700</v>
-      </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>-25400</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>-63100</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>-14000</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>-137500</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>-18300</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>-74500</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>-45400</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>-62300</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>-129400</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>-38000</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>-26500</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>-31700</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>-37300</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>-13400</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>-15500</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>-10200</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>-11200</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>-4200</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>-8900</v>
       </c>
-      <c r="AC35" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AD35" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="37" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE35" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="37" spans="2:31" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:30" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45473</v>
+      </c>
+      <c r="E38" s="2">
         <v>45382</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45291</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45199</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45107</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45016</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>44926</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44834</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44742</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44651</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44561</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44469</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44377</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44286</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44196</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44104</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44012</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>43921</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>43830</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>43738</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>43646</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43555</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>43465</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43373</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43281</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43190</v>
       </c>
-      <c r="AC38" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="AD38" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="39" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE38" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="39" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3146,8 +3231,9 @@
       <c r="AB39" s="3"/>
       <c r="AC39" s="3"/>
       <c r="AD39" s="3"/>
-    </row>
-    <row r="40" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE39" s="3"/>
+    </row>
+    <row r="40" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3178,74 +3264,75 @@
       <c r="AB40" s="3"/>
       <c r="AC40" s="3"/>
       <c r="AD40" s="3"/>
-    </row>
-    <row r="41" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE40" s="3"/>
+    </row>
+    <row r="41" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
-        <v>36300</v>
+        <v>70600</v>
       </c>
       <c r="E41" s="3">
-        <v>62800</v>
+        <v>37100</v>
       </c>
       <c r="F41" s="3">
-        <v>46700</v>
+        <v>64100</v>
       </c>
       <c r="G41" s="3">
-        <v>90900</v>
+        <v>47600</v>
       </c>
       <c r="H41" s="3">
-        <v>80000</v>
+        <v>92700</v>
       </c>
       <c r="I41" s="3">
-        <v>108300</v>
+        <v>81700</v>
       </c>
       <c r="J41" s="3">
+        <v>110500</v>
+      </c>
+      <c r="K41" s="3">
         <v>98400</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>95500</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>57300</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>44600</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>70200</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>117900</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>257300</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>84800</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>11500</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>18500</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>20100</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>26700</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>8500</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>8000</v>
       </c>
-      <c r="X41" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y41" s="3" t="s">
         <v>3</v>
       </c>
@@ -3264,74 +3351,77 @@
       <c r="AD41" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="42" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE41" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="42" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
-        <v>8600</v>
+        <v>8900</v>
       </c>
       <c r="E42" s="3">
-        <v>10000</v>
+        <v>8800</v>
       </c>
       <c r="F42" s="3">
-        <v>3000</v>
+        <v>10200</v>
       </c>
       <c r="G42" s="3">
-        <v>3000</v>
+        <v>3100</v>
       </c>
       <c r="H42" s="3">
-        <v>3000</v>
+        <v>3100</v>
       </c>
       <c r="I42" s="3">
-        <v>32100</v>
+        <v>3100</v>
       </c>
       <c r="J42" s="3">
-        <v>3000</v>
+        <v>32800</v>
       </c>
       <c r="K42" s="3">
         <v>3000</v>
       </c>
       <c r="L42" s="3">
+        <v>3000</v>
+      </c>
+      <c r="M42" s="3">
         <v>900</v>
       </c>
-      <c r="M42" s="3">
+      <c r="N42" s="3">
         <v>69600</v>
       </c>
-      <c r="N42" s="3">
+      <c r="O42" s="3">
         <v>58300</v>
       </c>
-      <c r="O42" s="3">
+      <c r="P42" s="3">
         <v>146500</v>
       </c>
-      <c r="P42" s="3">
+      <c r="Q42" s="3">
         <v>47000</v>
       </c>
-      <c r="Q42" s="3">
+      <c r="R42" s="3">
         <v>81500</v>
       </c>
-      <c r="R42" s="3">
+      <c r="S42" s="3">
         <v>155400</v>
       </c>
-      <c r="S42" s="3">
+      <c r="T42" s="3">
         <v>245400</v>
       </c>
-      <c r="T42" s="3">
+      <c r="U42" s="3">
         <v>242400</v>
       </c>
-      <c r="U42" s="3">
+      <c r="V42" s="3">
         <v>222800</v>
       </c>
-      <c r="V42" s="3">
+      <c r="W42" s="3">
         <v>16200</v>
       </c>
-      <c r="W42" s="3">
+      <c r="X42" s="3">
         <v>38000</v>
       </c>
-      <c r="X42" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y42" s="3" t="s">
         <v>3</v>
       </c>
@@ -3350,74 +3440,77 @@
       <c r="AD42" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="43" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE42" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="43" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
-        <v>57000</v>
+        <v>65000</v>
       </c>
       <c r="E43" s="3">
-        <v>52500</v>
+        <v>58200</v>
       </c>
       <c r="F43" s="3">
-        <v>49800</v>
+        <v>53600</v>
       </c>
       <c r="G43" s="3">
-        <v>53400</v>
+        <v>50900</v>
       </c>
       <c r="H43" s="3">
-        <v>37000</v>
+        <v>54500</v>
       </c>
       <c r="I43" s="3">
-        <v>57100</v>
+        <v>37700</v>
       </c>
       <c r="J43" s="3">
+        <v>58200</v>
+      </c>
+      <c r="K43" s="3">
         <v>46900</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>49000</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>41500</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>35100</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>35300</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>44300</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>35100</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>38000</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>50100</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>34900</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>36800</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>33200</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>27800</v>
       </c>
-      <c r="W43" s="3">
+      <c r="X43" s="3">
         <v>31100</v>
       </c>
-      <c r="X43" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y43" s="3" t="s">
         <v>3</v>
       </c>
@@ -3436,74 +3529,77 @@
       <c r="AD43" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="44" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE43" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="44" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
-        <v>26200</v>
+        <v>27600</v>
       </c>
       <c r="E44" s="3">
-        <v>30000</v>
+        <v>26700</v>
       </c>
       <c r="F44" s="3">
-        <v>24500</v>
+        <v>30600</v>
       </c>
       <c r="G44" s="3">
-        <v>25200</v>
+        <v>25000</v>
       </c>
       <c r="H44" s="3">
-        <v>30300</v>
+        <v>25800</v>
       </c>
       <c r="I44" s="3">
-        <v>32100</v>
+        <v>30900</v>
       </c>
       <c r="J44" s="3">
+        <v>32700</v>
+      </c>
+      <c r="K44" s="3">
         <v>23500</v>
-      </c>
-      <c r="K44" s="3">
-        <v>29500</v>
       </c>
       <c r="L44" s="3">
         <v>29500</v>
       </c>
       <c r="M44" s="3">
+        <v>29500</v>
+      </c>
+      <c r="N44" s="3">
         <v>35300</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>38000</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>38600</v>
       </c>
-      <c r="P44" s="3">
+      <c r="Q44" s="3">
         <v>37400</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="R44" s="3">
         <v>20700</v>
       </c>
-      <c r="R44" s="3">
+      <c r="S44" s="3">
         <v>13500</v>
       </c>
-      <c r="S44" s="3">
+      <c r="T44" s="3">
         <v>13700</v>
       </c>
-      <c r="T44" s="3">
+      <c r="U44" s="3">
         <v>10300</v>
       </c>
-      <c r="U44" s="3">
+      <c r="V44" s="3">
         <v>11300</v>
       </c>
-      <c r="V44" s="3">
+      <c r="W44" s="3">
         <v>8100</v>
       </c>
-      <c r="W44" s="3">
+      <c r="X44" s="3">
         <v>5000</v>
       </c>
-      <c r="X44" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y44" s="3" t="s">
         <v>3</v>
       </c>
@@ -3522,74 +3618,77 @@
       <c r="AD44" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="45" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE44" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="45" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
-        <v>27100</v>
+        <v>25200</v>
       </c>
       <c r="E45" s="3">
-        <v>24300</v>
+        <v>27700</v>
       </c>
       <c r="F45" s="3">
-        <v>32200</v>
+        <v>24800</v>
       </c>
       <c r="G45" s="3">
-        <v>26800</v>
+        <v>32800</v>
       </c>
       <c r="H45" s="3">
-        <v>24400</v>
+        <v>27300</v>
       </c>
       <c r="I45" s="3">
-        <v>28800</v>
+        <v>24900</v>
       </c>
       <c r="J45" s="3">
+        <v>29400</v>
+      </c>
+      <c r="K45" s="3">
         <v>59700</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>104200</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>129100</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>128800</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>85400</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>33100</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>27600</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>32800</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>29600</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>17500</v>
-      </c>
-      <c r="T45" s="3">
-        <v>18600</v>
       </c>
       <c r="U45" s="3">
         <v>18600</v>
       </c>
       <c r="V45" s="3">
+        <v>18600</v>
+      </c>
+      <c r="W45" s="3">
         <v>16200</v>
       </c>
-      <c r="W45" s="3">
+      <c r="X45" s="3">
         <v>11300</v>
       </c>
-      <c r="X45" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y45" s="3" t="s">
         <v>3</v>
       </c>
@@ -3608,74 +3707,77 @@
       <c r="AD45" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="46" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE45" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="46" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
-        <v>155300</v>
+        <v>197300</v>
       </c>
       <c r="E46" s="3">
-        <v>179600</v>
+        <v>158400</v>
       </c>
       <c r="F46" s="3">
-        <v>156300</v>
+        <v>183300</v>
       </c>
       <c r="G46" s="3">
-        <v>199300</v>
+        <v>159500</v>
       </c>
       <c r="H46" s="3">
-        <v>174700</v>
+        <v>203400</v>
       </c>
       <c r="I46" s="3">
-        <v>258400</v>
+        <v>178300</v>
       </c>
       <c r="J46" s="3">
+        <v>263600</v>
+      </c>
+      <c r="K46" s="3">
         <v>231500</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>281200</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>258300</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>313400</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>287200</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>380400</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>404400</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>257700</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>260200</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>330000</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>328200</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>312600</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>76800</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>93400</v>
       </c>
-      <c r="X46" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y46" s="3" t="s">
         <v>3</v>
       </c>
@@ -3694,56 +3796,59 @@
       <c r="AD46" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="47" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE46" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="47" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
-        <v>6800</v>
+        <v>10900</v>
       </c>
       <c r="E47" s="3">
-        <v>7100</v>
+        <v>7000</v>
       </c>
       <c r="F47" s="3">
-        <v>8900</v>
+        <v>7200</v>
       </c>
       <c r="G47" s="3">
-        <v>12100</v>
+        <v>9100</v>
       </c>
       <c r="H47" s="3">
-        <v>12500</v>
+        <v>12300</v>
       </c>
       <c r="I47" s="3">
-        <v>12500</v>
+        <v>12800</v>
       </c>
       <c r="J47" s="3">
+        <v>12800</v>
+      </c>
+      <c r="K47" s="3">
         <v>9300</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>9800</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>3800</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>4500</v>
       </c>
-      <c r="N47" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O47" s="3" t="s">
         <v>3</v>
       </c>
       <c r="P47" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q47" s="3">
+      <c r="Q47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R47" s="3">
         <v>5900</v>
       </c>
-      <c r="R47" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S47" s="3" t="s">
         <v>3</v>
       </c>
@@ -3756,8 +3861,8 @@
       <c r="V47" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="W47" s="3">
-        <v>0</v>
+      <c r="W47" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="X47" s="3">
         <v>0</v>
@@ -3780,74 +3885,77 @@
       <c r="AD47" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
-        <v>21500</v>
+        <v>21000</v>
       </c>
       <c r="E48" s="3">
-        <v>22100</v>
+        <v>21900</v>
       </c>
       <c r="F48" s="3">
-        <v>23900</v>
+        <v>22500</v>
       </c>
       <c r="G48" s="3">
-        <v>23100</v>
+        <v>24400</v>
       </c>
       <c r="H48" s="3">
-        <v>22000</v>
+        <v>23600</v>
       </c>
       <c r="I48" s="3">
-        <v>23600</v>
+        <v>22500</v>
       </c>
       <c r="J48" s="3">
+        <v>24000</v>
+      </c>
+      <c r="K48" s="3">
         <v>25700</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>27400</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>28300</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>27400</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>31400</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>28600</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>21000</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>21100</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>18100</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>11900</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>7600</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>7500</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>6100</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>3500</v>
       </c>
-      <c r="X48" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y48" s="3" t="s">
         <v>3</v>
       </c>
@@ -3866,43 +3974,46 @@
       <c r="AD48" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="49" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE48" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="49" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>15500</v>
+      </c>
+      <c r="E49" s="3">
+        <v>15500</v>
+      </c>
+      <c r="F49" s="3">
+        <v>15500</v>
+      </c>
+      <c r="G49" s="3">
+        <v>15500</v>
+      </c>
+      <c r="H49" s="3">
+        <v>15500</v>
+      </c>
+      <c r="I49" s="3">
+        <v>15500</v>
+      </c>
+      <c r="J49" s="3">
+        <v>15500</v>
+      </c>
+      <c r="K49" s="3">
         <v>15200</v>
       </c>
-      <c r="E49" s="3">
-        <v>15200</v>
-      </c>
-      <c r="F49" s="3">
-        <v>15200</v>
-      </c>
-      <c r="G49" s="3">
-        <v>15200</v>
-      </c>
-      <c r="H49" s="3">
-        <v>15200</v>
-      </c>
-      <c r="I49" s="3">
-        <v>15200</v>
-      </c>
-      <c r="J49" s="3">
-        <v>15200</v>
-      </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>15300</v>
-      </c>
-      <c r="L49" s="3">
-        <v>15200</v>
       </c>
       <c r="M49" s="3">
         <v>15200</v>
       </c>
-      <c r="N49" s="3" t="s">
-        <v>3</v>
+      <c r="N49" s="3">
+        <v>15200</v>
       </c>
       <c r="O49" s="3" t="s">
         <v>3</v>
@@ -3919,8 +4030,8 @@
       <c r="S49" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="T49" s="3">
-        <v>0</v>
+      <c r="T49" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="U49" s="3">
         <v>0</v>
@@ -3952,8 +4063,11 @@
       <c r="AD49" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="50" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE49" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4038,8 +4152,11 @@
       <c r="AD50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4124,73 +4241,76 @@
       <c r="AD51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
-        <v>7700</v>
+        <v>6500</v>
       </c>
       <c r="E52" s="3">
-        <v>6200</v>
+        <v>7800</v>
       </c>
       <c r="F52" s="3">
-        <v>6400</v>
+        <v>6300</v>
       </c>
       <c r="G52" s="3">
-        <v>5300</v>
+        <v>6600</v>
       </c>
       <c r="H52" s="3">
-        <v>4700</v>
+        <v>5400</v>
       </c>
       <c r="I52" s="3">
         <v>4800</v>
       </c>
       <c r="J52" s="3">
+        <v>4900</v>
+      </c>
+      <c r="K52" s="3">
         <v>5300</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>5200</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>5000</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>3200</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>30000</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>14700</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>11000</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>3400</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>3900</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>3200</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>2100</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>1300</v>
-      </c>
-      <c r="V52" s="3">
-        <v>800</v>
       </c>
       <c r="W52" s="3">
         <v>800</v>
       </c>
-      <c r="X52" s="3" t="s">
-        <v>3</v>
+      <c r="X52" s="3">
+        <v>800</v>
       </c>
       <c r="Y52" s="3" t="s">
         <v>3</v>
@@ -4210,8 +4330,11 @@
       <c r="AD52" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="53" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE52" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="53" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -4296,74 +4419,77 @@
       <c r="AD53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
-        <v>206400</v>
+        <v>251200</v>
       </c>
       <c r="E54" s="3">
-        <v>230200</v>
+        <v>210600</v>
       </c>
       <c r="F54" s="3">
-        <v>210700</v>
+        <v>234900</v>
       </c>
       <c r="G54" s="3">
-        <v>255100</v>
+        <v>215000</v>
       </c>
       <c r="H54" s="3">
-        <v>229100</v>
+        <v>260300</v>
       </c>
       <c r="I54" s="3">
-        <v>314500</v>
+        <v>233800</v>
       </c>
       <c r="J54" s="3">
+        <v>320900</v>
+      </c>
+      <c r="K54" s="3">
         <v>286900</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>339000</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>310600</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>363700</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>348600</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>423600</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>436300</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>288200</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>282200</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>345100</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>337900</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>321300</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>83700</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>97700</v>
       </c>
-      <c r="X54" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y54" s="3" t="s">
         <v>3</v>
       </c>
@@ -4382,8 +4508,11 @@
       <c r="AD54" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="55" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE54" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="55" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -4414,8 +4543,9 @@
       <c r="AB55" s="3"/>
       <c r="AC55" s="3"/>
       <c r="AD55" s="3"/>
-    </row>
-    <row r="56" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE55" s="3"/>
+    </row>
+    <row r="56" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -4446,74 +4576,75 @@
       <c r="AB56" s="3"/>
       <c r="AC56" s="3"/>
       <c r="AD56" s="3"/>
-    </row>
-    <row r="57" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE56" s="3"/>
+    </row>
+    <row r="57" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
-        <v>16500</v>
+        <v>15600</v>
       </c>
       <c r="E57" s="3">
-        <v>22000</v>
+        <v>16900</v>
       </c>
       <c r="F57" s="3">
-        <v>22500</v>
+        <v>22400</v>
       </c>
       <c r="G57" s="3">
-        <v>17900</v>
+        <v>23000</v>
       </c>
       <c r="H57" s="3">
-        <v>16900</v>
+        <v>18300</v>
       </c>
       <c r="I57" s="3">
-        <v>39000</v>
+        <v>17300</v>
       </c>
       <c r="J57" s="3">
+        <v>39800</v>
+      </c>
+      <c r="K57" s="3">
         <v>24800</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>21100</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>18400</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>22200</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>16600</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>10600</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>17500</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>19700</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>17600</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>15200</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>14900</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>9700</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>7200</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>5300</v>
       </c>
-      <c r="X57" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y57" s="3" t="s">
         <v>3</v>
       </c>
@@ -4532,74 +4663,77 @@
       <c r="AD57" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="58" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE57" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="58" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>123800</v>
+      </c>
+      <c r="E58" s="3">
+        <v>123800</v>
+      </c>
+      <c r="F58" s="3">
+        <v>123800</v>
+      </c>
+      <c r="G58" s="3">
+        <v>123800</v>
+      </c>
+      <c r="H58" s="3">
+        <v>205300</v>
+      </c>
+      <c r="I58" s="3">
+        <v>201300</v>
+      </c>
+      <c r="J58" s="3">
+        <v>123800</v>
+      </c>
+      <c r="K58" s="3">
         <v>121300</v>
       </c>
-      <c r="E58" s="3">
-        <v>121300</v>
-      </c>
-      <c r="F58" s="3">
-        <v>121300</v>
-      </c>
-      <c r="G58" s="3">
-        <v>201200</v>
-      </c>
-      <c r="H58" s="3">
-        <v>197300</v>
-      </c>
-      <c r="I58" s="3">
-        <v>121300</v>
-      </c>
-      <c r="J58" s="3">
-        <v>121300</v>
-      </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>122100</v>
-      </c>
-      <c r="L58" s="3">
-        <v>121200</v>
       </c>
       <c r="M58" s="3">
         <v>121200</v>
       </c>
       <c r="N58" s="3">
-        <v>124800</v>
+        <v>121200</v>
       </c>
       <c r="O58" s="3">
         <v>124800</v>
       </c>
       <c r="P58" s="3">
-        <v>122200</v>
+        <v>124800</v>
       </c>
       <c r="Q58" s="3">
         <v>122200</v>
       </c>
       <c r="R58" s="3">
-        <v>129400</v>
+        <v>122200</v>
       </c>
       <c r="S58" s="3">
         <v>129400</v>
       </c>
       <c r="T58" s="3">
+        <v>129400</v>
+      </c>
+      <c r="U58" s="3">
         <v>137500</v>
-      </c>
-      <c r="U58" s="3">
-        <v>135200</v>
       </c>
       <c r="V58" s="3">
         <v>135200</v>
       </c>
       <c r="W58" s="3">
+        <v>135200</v>
+      </c>
+      <c r="X58" s="3">
         <v>134100</v>
       </c>
-      <c r="X58" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y58" s="3" t="s">
         <v>3</v>
       </c>
@@ -4618,74 +4752,77 @@
       <c r="AD58" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="59" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE58" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="59" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>234400</v>
+        <v>295800</v>
       </c>
       <c r="E59" s="3">
-        <v>284900</v>
+        <v>239200</v>
       </c>
       <c r="F59" s="3">
-        <v>271200</v>
+        <v>290700</v>
       </c>
       <c r="G59" s="3">
-        <v>309200</v>
+        <v>276800</v>
       </c>
       <c r="H59" s="3">
-        <v>241600</v>
+        <v>315500</v>
       </c>
       <c r="I59" s="3">
-        <v>278800</v>
+        <v>246500</v>
       </c>
       <c r="J59" s="3">
+        <v>284500</v>
+      </c>
+      <c r="K59" s="3">
         <v>266100</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>298500</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>226700</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>275500</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>293600</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>375700</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>312500</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>330500</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>268200</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>204700</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>157000</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>126000</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>93900</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>76900</v>
       </c>
-      <c r="X59" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y59" s="3" t="s">
         <v>3</v>
       </c>
@@ -4704,74 +4841,77 @@
       <c r="AD59" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="60" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE59" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="60" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
-        <v>372300</v>
+        <v>435200</v>
       </c>
       <c r="E60" s="3">
-        <v>428200</v>
+        <v>379800</v>
       </c>
       <c r="F60" s="3">
+        <v>436900</v>
+      </c>
+      <c r="G60" s="3">
+        <v>423500</v>
+      </c>
+      <c r="H60" s="3">
+        <v>539000</v>
+      </c>
+      <c r="I60" s="3">
+        <v>465100</v>
+      </c>
+      <c r="J60" s="3">
+        <v>448100</v>
+      </c>
+      <c r="K60" s="3">
+        <v>412300</v>
+      </c>
+      <c r="L60" s="3">
+        <v>441700</v>
+      </c>
+      <c r="M60" s="3">
+        <v>366300</v>
+      </c>
+      <c r="N60" s="3">
+        <v>418900</v>
+      </c>
+      <c r="O60" s="3">
+        <v>435000</v>
+      </c>
+      <c r="P60" s="3">
+        <v>511100</v>
+      </c>
+      <c r="Q60" s="3">
+        <v>452200</v>
+      </c>
+      <c r="R60" s="3">
+        <v>472400</v>
+      </c>
+      <c r="S60" s="3">
         <v>415100</v>
       </c>
-      <c r="G60" s="3">
-        <v>528200</v>
-      </c>
-      <c r="H60" s="3">
-        <v>455800</v>
-      </c>
-      <c r="I60" s="3">
-        <v>439200</v>
-      </c>
-      <c r="J60" s="3">
-        <v>412300</v>
-      </c>
-      <c r="K60" s="3">
-        <v>441700</v>
-      </c>
-      <c r="L60" s="3">
-        <v>366300</v>
-      </c>
-      <c r="M60" s="3">
-        <v>418900</v>
-      </c>
-      <c r="N60" s="3">
-        <v>435000</v>
-      </c>
-      <c r="O60" s="3">
-        <v>511100</v>
-      </c>
-      <c r="P60" s="3">
-        <v>452200</v>
-      </c>
-      <c r="Q60" s="3">
-        <v>472400</v>
-      </c>
-      <c r="R60" s="3">
-        <v>415100</v>
-      </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>349200</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>309300</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>270800</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>236300</v>
       </c>
-      <c r="W60" s="3">
+      <c r="X60" s="3">
         <v>216400</v>
       </c>
-      <c r="X60" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y60" s="3" t="s">
         <v>3</v>
       </c>
@@ -4790,44 +4930,47 @@
       <c r="AD60" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="61" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE60" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="61" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
-        <v>121700</v>
+        <v>127700</v>
       </c>
       <c r="E61" s="3">
-        <v>87100</v>
+        <v>124200</v>
       </c>
       <c r="F61" s="3">
-        <v>83300</v>
+        <v>88900</v>
       </c>
       <c r="G61" s="3">
-        <v>0</v>
+        <v>85000</v>
       </c>
       <c r="H61" s="3">
         <v>0</v>
       </c>
       <c r="I61" s="3">
-        <v>72200</v>
+        <v>0</v>
       </c>
       <c r="J61" s="3">
+        <v>73600</v>
+      </c>
+      <c r="K61" s="3">
         <v>68700</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>65300</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>48200</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>35200</v>
       </c>
-      <c r="N61" s="3">
-        <v>0</v>
-      </c>
       <c r="O61" s="3">
         <v>0</v>
       </c>
@@ -4876,71 +5019,74 @@
       <c r="AD61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
-        <v>9000</v>
+        <v>8300</v>
       </c>
       <c r="E62" s="3">
-        <v>9100</v>
+        <v>9200</v>
       </c>
       <c r="F62" s="3">
-        <v>10000</v>
+        <v>9300</v>
       </c>
       <c r="G62" s="3">
-        <v>8100</v>
+        <v>10200</v>
       </c>
       <c r="H62" s="3">
-        <v>7100</v>
+        <v>8200</v>
       </c>
       <c r="I62" s="3">
-        <v>7200</v>
+        <v>7300</v>
       </c>
       <c r="J62" s="3">
+        <v>7400</v>
+      </c>
+      <c r="K62" s="3">
         <v>8400</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>8700</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>7700</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>10400</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>15100</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>13800</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>10900</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>11700</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>10300</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>6400</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>3900</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>4100</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>2100</v>
       </c>
-      <c r="W62" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X62" s="3" t="s">
         <v>3</v>
       </c>
@@ -4953,8 +5099,8 @@
       <c r="AA62" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="AB62" s="3">
-        <v>0</v>
+      <c r="AB62" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="AC62" s="3">
         <v>0</v>
@@ -4962,8 +5108,11 @@
       <c r="AD62" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="63" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE62" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="63" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -5048,8 +5197,11 @@
       <c r="AD63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -5134,8 +5286,11 @@
       <c r="AD64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -5220,74 +5375,77 @@
       <c r="AD65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
-        <v>511200</v>
+        <v>579500</v>
       </c>
       <c r="E66" s="3">
-        <v>532300</v>
+        <v>521700</v>
       </c>
       <c r="F66" s="3">
-        <v>516400</v>
+        <v>543200</v>
       </c>
       <c r="G66" s="3">
-        <v>543500</v>
+        <v>526900</v>
       </c>
       <c r="H66" s="3">
-        <v>470700</v>
+        <v>554600</v>
       </c>
       <c r="I66" s="3">
-        <v>526600</v>
+        <v>480300</v>
       </c>
       <c r="J66" s="3">
+        <v>537300</v>
+      </c>
+      <c r="K66" s="3">
         <v>498600</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>525300</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>432700</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>475200</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>464600</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>524800</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>463100</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>484200</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>425500</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>355800</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>313400</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>275100</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>238600</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>216600</v>
       </c>
-      <c r="X66" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y66" s="3" t="s">
         <v>3</v>
       </c>
@@ -5306,8 +5464,11 @@
       <c r="AD66" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="67" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE66" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="67" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -5338,8 +5499,9 @@
       <c r="AB67" s="3"/>
       <c r="AC67" s="3"/>
       <c r="AD67" s="3"/>
-    </row>
-    <row r="68" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE67" s="3"/>
+    </row>
+    <row r="68" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -5424,8 +5586,11 @@
       <c r="AD68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -5510,8 +5675,11 @@
       <c r="AD69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -5570,14 +5738,14 @@
         <v>0</v>
       </c>
       <c r="V70" s="3">
+        <v>0</v>
+      </c>
+      <c r="W70" s="3">
         <v>75900</v>
       </c>
-      <c r="W70" s="3">
+      <c r="X70" s="3">
         <v>73600</v>
       </c>
-      <c r="X70" s="3">
-        <v>0</v>
-      </c>
       <c r="Y70" s="3">
         <v>0</v>
       </c>
@@ -5596,8 +5764,11 @@
       <c r="AD70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -5682,19 +5853,22 @@
       <c r="AD71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="E72" s="3">
-        <v>-821200</v>
-      </c>
-      <c r="F72" s="3" t="s">
-        <v>3</v>
+      <c r="E72" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F72" s="3">
+        <v>-837900</v>
       </c>
       <c r="G72" s="3" t="s">
         <v>3</v>
@@ -5702,11 +5876,11 @@
       <c r="H72" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="I72" s="3">
-        <v>-745200</v>
-      </c>
-      <c r="J72" s="3" t="s">
-        <v>3</v>
+      <c r="I72" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J72" s="3">
+        <v>-760400</v>
       </c>
       <c r="K72" s="3" t="s">
         <v>3</v>
@@ -5726,30 +5900,30 @@
       <c r="P72" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="Q72" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R72" s="3">
         <v>-511000</v>
       </c>
-      <c r="R72" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S72" s="3" t="s">
         <v>3</v>
       </c>
       <c r="T72" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="U72" s="3">
+      <c r="U72" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="V72" s="3">
         <v>-295400</v>
       </c>
-      <c r="V72" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="W72" s="3">
+      <c r="W72" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="X72" s="3">
         <v>-224700</v>
       </c>
-      <c r="X72" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y72" s="3" t="s">
         <v>3</v>
       </c>
@@ -5768,8 +5942,11 @@
       <c r="AD72" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="73" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE72" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="73" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -5854,8 +6031,11 @@
       <c r="AD73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -5940,8 +6120,11 @@
       <c r="AD74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -6026,74 +6209,77 @@
       <c r="AD75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
-        <v>-304800</v>
+        <v>-328300</v>
       </c>
       <c r="E76" s="3">
-        <v>-302100</v>
+        <v>-311000</v>
       </c>
       <c r="F76" s="3">
-        <v>-305600</v>
+        <v>-308300</v>
       </c>
       <c r="G76" s="3">
-        <v>-288400</v>
+        <v>-311900</v>
       </c>
       <c r="H76" s="3">
-        <v>-241500</v>
+        <v>-294300</v>
       </c>
       <c r="I76" s="3">
-        <v>-212100</v>
+        <v>-246500</v>
       </c>
       <c r="J76" s="3">
+        <v>-216400</v>
+      </c>
+      <c r="K76" s="3">
         <v>-211700</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>-186400</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>-122100</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>-111400</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>-116000</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>-101200</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>-26700</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>-196000</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>-143300</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>-10700</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>24500</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>46200</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>-230800</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>-192500</v>
       </c>
-      <c r="X76" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y76" s="3" t="s">
         <v>3</v>
       </c>
@@ -6112,8 +6298,11 @@
       <c r="AD76" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="77" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE76" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="77" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -6198,185 +6387,194 @@
       <c r="AD77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:31" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:30" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45473</v>
+      </c>
+      <c r="E80" s="2">
         <v>45382</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45291</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45199</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45107</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45016</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>44926</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44834</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44742</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44651</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44561</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44469</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44377</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44286</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44196</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44104</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44012</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>43921</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>43830</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>43738</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>43646</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43555</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>43465</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43373</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43281</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43190</v>
       </c>
-      <c r="AC80" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="AD80" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="81" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE80" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="81" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-14000</v>
+      </c>
+      <c r="E81" s="3">
+        <v>1800</v>
+      </c>
+      <c r="F81" s="3">
+        <v>8000</v>
+      </c>
+      <c r="G81" s="3">
+        <v>-14500</v>
+      </c>
+      <c r="H81" s="3">
+        <v>-42200</v>
+      </c>
+      <c r="I81" s="3">
+        <v>-28800</v>
+      </c>
+      <c r="J81" s="3">
         <v>1700</v>
       </c>
-      <c r="E81" s="3">
-        <v>7800</v>
-      </c>
-      <c r="F81" s="3">
-        <v>-14200</v>
-      </c>
-      <c r="G81" s="3">
-        <v>-41300</v>
-      </c>
-      <c r="H81" s="3">
-        <v>-28200</v>
-      </c>
-      <c r="I81" s="3">
-        <v>1700</v>
-      </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>-25400</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>-63100</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>-14000</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>-137500</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>-18300</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>-74500</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>-45400</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>-62300</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>-129400</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>-38000</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>-26500</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>-31700</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>-37300</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>-13400</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>-15500</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>-10200</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>-11200</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>-4200</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>-8900</v>
       </c>
-      <c r="AC81" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AD81" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="82" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE81" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="82" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -6407,8 +6605,9 @@
       <c r="AB82" s="3"/>
       <c r="AC82" s="3"/>
       <c r="AD82" s="3"/>
-    </row>
-    <row r="83" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE82" s="3"/>
+    </row>
+    <row r="83" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
@@ -6424,41 +6623,41 @@
       <c r="G83" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="H83" s="3">
+      <c r="H83" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I83" s="3">
         <v>1100</v>
-      </c>
-      <c r="I83" s="3">
-        <v>1600</v>
       </c>
       <c r="J83" s="3">
         <v>1600</v>
       </c>
       <c r="K83" s="3">
+        <v>1600</v>
+      </c>
+      <c r="L83" s="3">
         <v>1500</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>1100</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>4200</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>1100</v>
-      </c>
-      <c r="O83" s="3">
-        <v>800</v>
       </c>
       <c r="P83" s="3">
         <v>800</v>
       </c>
       <c r="Q83" s="3">
+        <v>800</v>
+      </c>
+      <c r="R83" s="3">
         <v>700</v>
       </c>
-      <c r="R83" s="3">
+      <c r="S83" s="3">
         <v>600</v>
-      </c>
-      <c r="S83" s="3">
-        <v>500</v>
       </c>
       <c r="T83" s="3">
         <v>500</v>
@@ -6467,11 +6666,11 @@
         <v>500</v>
       </c>
       <c r="V83" s="3">
+        <v>500</v>
+      </c>
+      <c r="W83" s="3">
         <v>400</v>
       </c>
-      <c r="W83" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X83" s="3" t="s">
         <v>3</v>
       </c>
@@ -6484,8 +6683,8 @@
       <c r="AA83" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="AB83" s="3">
-        <v>0</v>
+      <c r="AB83" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="AC83" s="3">
         <v>0</v>
@@ -6493,8 +6692,11 @@
       <c r="AD83" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="84" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE83" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -6579,8 +6781,11 @@
       <c r="AD84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -6665,8 +6870,11 @@
       <c r="AD85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -6751,8 +6959,11 @@
       <c r="AD86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -6837,8 +7048,11 @@
       <c r="AD87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -6923,28 +7137,31 @@
       <c r="AD88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
-        <v>54000</v>
+        <v>-19800</v>
       </c>
       <c r="E89" s="3">
-        <v>-101200</v>
+        <v>55100</v>
       </c>
       <c r="F89" s="3">
-        <v>22300</v>
+        <v>-103300</v>
       </c>
       <c r="G89" s="3">
-        <v>-42000</v>
+        <v>22800</v>
       </c>
       <c r="H89" s="3">
-        <v>60400</v>
-      </c>
-      <c r="I89" s="3" t="s">
-        <v>3</v>
+        <v>-42900</v>
+      </c>
+      <c r="I89" s="3">
+        <v>61600</v>
       </c>
       <c r="J89" s="3" t="s">
         <v>3</v>
@@ -6952,42 +7169,42 @@
       <c r="K89" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L89" s="3">
+      <c r="L89" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M89" s="3">
         <v>58800</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>-185900</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>89400</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>35400</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>72100</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>-147200</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>87400</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>21000</v>
       </c>
-      <c r="T89" s="3">
-        <v>0</v>
-      </c>
       <c r="U89" s="3">
+        <v>0</v>
+      </c>
+      <c r="V89" s="3">
         <v>-48300</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>21900</v>
       </c>
-      <c r="W89" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X89" s="3" t="s">
         <v>3</v>
       </c>
@@ -7000,8 +7217,8 @@
       <c r="AA89" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="AB89" s="3">
-        <v>0</v>
+      <c r="AB89" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="AC89" s="3">
         <v>0</v>
@@ -7009,8 +7226,11 @@
       <c r="AD89" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="90" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE89" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="90" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -7041,61 +7261,62 @@
       <c r="AB90" s="3"/>
       <c r="AC90" s="3"/>
       <c r="AD90" s="3"/>
-    </row>
-    <row r="91" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE90" s="3"/>
+    </row>
+    <row r="91" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-1300</v>
+      </c>
+      <c r="E91" s="3">
         <v>-2500</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-13200</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-1900</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-6100</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-500</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-62200</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-6500</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-17900</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-3400</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-1900</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-11400</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-15900</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-1600</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-2200</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-1800</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-600</v>
-      </c>
-      <c r="T91" s="3">
-        <v>-700</v>
       </c>
       <c r="U91" s="3">
         <v>-700</v>
@@ -7103,8 +7324,8 @@
       <c r="V91" s="3">
         <v>-700</v>
       </c>
-      <c r="W91" s="3" t="s">
-        <v>3</v>
+      <c r="W91" s="3">
+        <v>-700</v>
       </c>
       <c r="X91" s="3" t="s">
         <v>3</v>
@@ -7118,8 +7339,8 @@
       <c r="AA91" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="AB91" s="3">
-        <v>0</v>
+      <c r="AB91" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="AC91" s="3">
         <v>0</v>
@@ -7127,8 +7348,11 @@
       <c r="AD91" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="92" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE91" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -7213,8 +7437,11 @@
       <c r="AD92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -7299,19 +7526,22 @@
       <c r="AD93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="E94" s="3">
-        <v>-1800</v>
-      </c>
-      <c r="F94" s="3" t="s">
-        <v>3</v>
+      <c r="E94" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F94" s="3">
+        <v>-1900</v>
       </c>
       <c r="G94" s="3" t="s">
         <v>3</v>
@@ -7325,8 +7555,8 @@
       <c r="J94" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K94" s="3">
-        <v>0</v>
+      <c r="K94" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="L94" s="3">
         <v>0</v>
@@ -7385,8 +7615,11 @@
       <c r="AD94" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="95" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE94" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="95" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -7417,8 +7650,9 @@
       <c r="AB95" s="3"/>
       <c r="AC95" s="3"/>
       <c r="AD95" s="3"/>
-    </row>
-    <row r="96" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE95" s="3"/>
+    </row>
+    <row r="96" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -7503,8 +7737,11 @@
       <c r="AD96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -7589,8 +7826,11 @@
       <c r="AD97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -7675,8 +7915,11 @@
       <c r="AD98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -7761,8 +8004,11 @@
       <c r="AD99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
@@ -7847,8 +8093,11 @@
       <c r="AD100" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="101" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE100" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="101" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -7933,8 +8182,11 @@
       <c r="AD101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
@@ -8017,6 +8269,9 @@
         <v>0</v>
       </c>
       <c r="AD102" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE102" s="3">
         <v>0</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/DAO_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/DAO_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="347" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="387" uniqueCount="92">
   <si>
     <t>DAO</t>
   </si>
@@ -656,403 +656,416 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AE102"/>
+  <dimension ref="A5:AF102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="6.42578125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="19" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="23" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="27" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="30" max="31" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="32" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="16" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="20" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="24" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="28" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="31" max="32" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="33" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:31" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:31" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:32" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:31" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:32" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45565</v>
+      </c>
+      <c r="E7" s="2">
         <v>45473</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45382</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45291</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45199</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45107</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45016</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44926</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44834</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44742</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44651</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44561</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44469</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44377</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44286</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44196</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44104</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44012</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>43921</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>43830</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>43738</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43646</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>43555</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43465</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43373</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43281</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43190</v>
       </c>
-      <c r="AD7" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="AE7" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="8" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="AF7" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:32" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D8" s="3">
-        <v>186300</v>
+        <v>224200</v>
       </c>
       <c r="E8" s="3">
-        <v>196200</v>
+        <v>181900</v>
       </c>
       <c r="F8" s="3">
-        <v>208700</v>
+        <v>192800</v>
       </c>
       <c r="G8" s="3">
-        <v>216900</v>
+        <v>208800</v>
       </c>
       <c r="H8" s="3">
-        <v>170100</v>
+        <v>210900</v>
       </c>
       <c r="I8" s="3">
-        <v>164000</v>
+        <v>166400</v>
       </c>
       <c r="J8" s="3">
+        <v>169300</v>
+      </c>
+      <c r="K8" s="3">
         <v>205000</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>193800</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>132900</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>165800</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>554500</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>197200</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>139300</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>132000</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>64900</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>132000</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>91800</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>84800</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>63200</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>53300</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>49300</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>34300</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>33400</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>25300</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>27000</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AD8" s="3">
         <v>19300</v>
       </c>
-      <c r="AD8" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AE8" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="9" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="AF8" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="9" spans="1:32" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D9" s="3">
-        <v>96600</v>
+        <v>111600</v>
       </c>
       <c r="E9" s="3">
-        <v>100100</v>
+        <v>94300</v>
       </c>
       <c r="F9" s="3">
+        <v>98400</v>
+      </c>
+      <c r="G9" s="3">
         <v>104600</v>
       </c>
-      <c r="G9" s="3">
-        <v>95700</v>
-      </c>
       <c r="H9" s="3">
-        <v>90200</v>
+        <v>93100</v>
       </c>
       <c r="I9" s="3">
-        <v>79100</v>
+        <v>88200</v>
       </c>
       <c r="J9" s="3">
+        <v>81700</v>
+      </c>
+      <c r="K9" s="3">
         <v>95800</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>88700</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>76000</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>77100</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>279900</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>85500</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>68200</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>62900</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>120900</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>71400</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>50400</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>47900</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>44300</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>39500</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Y9" s="3">
         <v>33100</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="Z9" s="3">
         <v>26300</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AA9" s="3">
         <v>23500</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AB9" s="3">
         <v>19400</v>
       </c>
-      <c r="AB9" s="3">
+      <c r="AC9" s="3">
         <v>17200</v>
       </c>
-      <c r="AC9" s="3">
+      <c r="AD9" s="3">
         <v>13900</v>
       </c>
-      <c r="AD9" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AE9" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="10" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="AF9" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:32" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
-        <v>89800</v>
+        <v>112500</v>
       </c>
       <c r="E10" s="3">
-        <v>96100</v>
+        <v>87600</v>
       </c>
       <c r="F10" s="3">
+        <v>94400</v>
+      </c>
+      <c r="G10" s="3">
         <v>104200</v>
       </c>
-      <c r="G10" s="3">
-        <v>121200</v>
-      </c>
       <c r="H10" s="3">
-        <v>80000</v>
+        <v>117800</v>
       </c>
       <c r="I10" s="3">
-        <v>84900</v>
+        <v>78200</v>
       </c>
       <c r="J10" s="3">
+        <v>87600</v>
+      </c>
+      <c r="K10" s="3">
         <v>109200</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>105000</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>57000</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>88600</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>274600</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>111700</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>71100</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>69100</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>-56100</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>60600</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>41500</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>36900</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>18800</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>13700</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Y10" s="3">
         <v>16200</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="Z10" s="3">
         <v>8000</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AA10" s="3">
         <v>9900</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AB10" s="3">
         <v>5900</v>
       </c>
-      <c r="AB10" s="3">
+      <c r="AC10" s="3">
         <v>9800</v>
       </c>
-      <c r="AC10" s="3">
+      <c r="AD10" s="3">
         <v>5400</v>
       </c>
-      <c r="AD10" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AE10" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="11" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="AF10" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:32" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -1084,97 +1097,101 @@
       <c r="AC11" s="3"/>
       <c r="AD11" s="3"/>
       <c r="AE11" s="3"/>
-    </row>
-    <row r="12" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="AF11" s="3"/>
+    </row>
+    <row r="12" spans="1:32" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D12" s="3">
-        <v>21600</v>
+        <v>17000</v>
       </c>
       <c r="E12" s="3">
+        <v>21100</v>
+      </c>
+      <c r="F12" s="3">
+        <v>20300</v>
+      </c>
+      <c r="G12" s="3">
+        <v>23700</v>
+      </c>
+      <c r="H12" s="3">
+        <v>25700</v>
+      </c>
+      <c r="I12" s="3">
+        <v>28300</v>
+      </c>
+      <c r="J12" s="3">
+        <v>26600</v>
+      </c>
+      <c r="K12" s="3">
+        <v>25300</v>
+      </c>
+      <c r="L12" s="3">
+        <v>29400</v>
+      </c>
+      <c r="M12" s="3">
+        <v>29000</v>
+      </c>
+      <c r="N12" s="3">
+        <v>28000</v>
+      </c>
+      <c r="O12" s="3">
+        <v>83900</v>
+      </c>
+      <c r="P12" s="3">
+        <v>27500</v>
+      </c>
+      <c r="Q12" s="3">
         <v>20700</v>
       </c>
-      <c r="F12" s="3">
-        <v>23700</v>
-      </c>
-      <c r="G12" s="3">
-        <v>26400</v>
-      </c>
-      <c r="H12" s="3">
-        <v>28900</v>
-      </c>
-      <c r="I12" s="3">
-        <v>25800</v>
-      </c>
-      <c r="J12" s="3">
-        <v>25300</v>
-      </c>
-      <c r="K12" s="3">
-        <v>29400</v>
-      </c>
-      <c r="L12" s="3">
-        <v>29000</v>
-      </c>
-      <c r="M12" s="3">
-        <v>28000</v>
-      </c>
-      <c r="N12" s="3">
-        <v>83900</v>
-      </c>
-      <c r="O12" s="3">
-        <v>27500</v>
-      </c>
-      <c r="P12" s="3">
-        <v>20700</v>
-      </c>
-      <c r="Q12" s="3">
+      <c r="R12" s="3">
         <v>17800</v>
       </c>
-      <c r="R12" s="3">
+      <c r="S12" s="3">
         <v>10500</v>
       </c>
-      <c r="S12" s="3">
+      <c r="T12" s="3">
         <v>17800</v>
       </c>
-      <c r="T12" s="3">
+      <c r="U12" s="3">
         <v>13500</v>
       </c>
-      <c r="U12" s="3">
+      <c r="V12" s="3">
         <v>13200</v>
       </c>
-      <c r="V12" s="3">
+      <c r="W12" s="3">
         <v>13700</v>
       </c>
-      <c r="W12" s="3">
+      <c r="X12" s="3">
         <v>11500</v>
       </c>
-      <c r="X12" s="3">
+      <c r="Y12" s="3">
         <v>8600</v>
       </c>
-      <c r="Y12" s="3">
+      <c r="Z12" s="3">
         <v>8300</v>
       </c>
-      <c r="Z12" s="3">
+      <c r="AA12" s="3">
         <v>7300</v>
       </c>
-      <c r="AA12" s="3">
+      <c r="AB12" s="3">
         <v>7700</v>
       </c>
-      <c r="AB12" s="3">
+      <c r="AC12" s="3">
         <v>5400</v>
       </c>
-      <c r="AC12" s="3">
+      <c r="AD12" s="3">
         <v>6100</v>
       </c>
-      <c r="AD12" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AE12" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="13" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="AF12" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:32" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1262,8 +1279,11 @@
       <c r="AE13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="AF13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:32" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -1276,8 +1296,8 @@
       <c r="F14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="G14" s="3" t="s">
-        <v>3</v>
+      <c r="G14" s="3">
+        <v>6100</v>
       </c>
       <c r="H14" s="3" t="s">
         <v>3</v>
@@ -1297,12 +1317,12 @@
       <c r="M14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N14" s="3">
+      <c r="N14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O14" s="3">
         <v>7800</v>
       </c>
-      <c r="O14" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P14" s="3" t="s">
         <v>3</v>
       </c>
@@ -1318,8 +1338,8 @@
       <c r="T14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="U14" s="3">
-        <v>0</v>
+      <c r="U14" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="V14" s="3">
         <v>0</v>
@@ -1351,31 +1371,34 @@
       <c r="AE14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="AF14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:32" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
-        <v>0</v>
+        <v>1100</v>
       </c>
       <c r="E15" s="3">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="F15" s="3">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="G15" s="3">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="H15" s="3">
-        <v>0</v>
+        <v>1400</v>
       </c>
       <c r="I15" s="3">
-        <v>0</v>
+        <v>1500</v>
       </c>
       <c r="J15" s="3">
-        <v>0</v>
+        <v>1500</v>
       </c>
       <c r="K15" s="3">
         <v>0</v>
@@ -1440,8 +1463,11 @@
       <c r="AE15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="AF15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:32" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1470,186 +1496,193 @@
       <c r="AC16" s="3"/>
       <c r="AD16" s="3"/>
       <c r="AE16" s="3"/>
-    </row>
-    <row r="17" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF16" s="3"/>
+    </row>
+    <row r="17" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
-        <v>196600</v>
+        <v>208900</v>
       </c>
       <c r="E17" s="3">
-        <v>192000</v>
+        <v>191900</v>
       </c>
       <c r="F17" s="3">
+        <v>188600</v>
+      </c>
+      <c r="G17" s="3">
         <v>198000</v>
       </c>
-      <c r="G17" s="3">
-        <v>225100</v>
-      </c>
       <c r="H17" s="3">
-        <v>210900</v>
+        <v>218800</v>
       </c>
       <c r="I17" s="3">
-        <v>191600</v>
+        <v>206200</v>
       </c>
       <c r="J17" s="3">
+        <v>197800</v>
+      </c>
+      <c r="K17" s="3">
         <v>201500</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>224000</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>196200</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>183000</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>684700</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>215600</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>175500</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>161800</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>-4900</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>263800</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>133600</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>112300</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>94600</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>89400</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>62000</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>46400</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>40700</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>37800</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>31300</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>26700</v>
       </c>
-      <c r="AD17" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AE17" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="18" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF17" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
-        <v>-10200</v>
+        <v>15300</v>
       </c>
       <c r="E18" s="3">
-        <v>4200</v>
+        <v>-10000</v>
       </c>
       <c r="F18" s="3">
+        <v>4100</v>
+      </c>
+      <c r="G18" s="3">
         <v>10800</v>
       </c>
-      <c r="G18" s="3">
-        <v>-8100</v>
-      </c>
       <c r="H18" s="3">
-        <v>-40800</v>
+        <v>-7900</v>
       </c>
       <c r="I18" s="3">
+        <v>-39900</v>
+      </c>
+      <c r="J18" s="3">
+        <v>-28500</v>
+      </c>
+      <c r="K18" s="3">
+        <v>3500</v>
+      </c>
+      <c r="L18" s="3">
+        <v>-30300</v>
+      </c>
+      <c r="M18" s="3">
+        <v>-63300</v>
+      </c>
+      <c r="N18" s="3">
+        <v>-17300</v>
+      </c>
+      <c r="O18" s="3">
+        <v>-130200</v>
+      </c>
+      <c r="P18" s="3">
+        <v>-18400</v>
+      </c>
+      <c r="Q18" s="3">
+        <v>-36200</v>
+      </c>
+      <c r="R18" s="3">
+        <v>-29800</v>
+      </c>
+      <c r="S18" s="3">
+        <v>69800</v>
+      </c>
+      <c r="T18" s="3">
+        <v>-131700</v>
+      </c>
+      <c r="U18" s="3">
+        <v>-41700</v>
+      </c>
+      <c r="V18" s="3">
         <v>-27600</v>
       </c>
-      <c r="J18" s="3">
-        <v>3500</v>
-      </c>
-      <c r="K18" s="3">
-        <v>-30300</v>
-      </c>
-      <c r="L18" s="3">
-        <v>-63300</v>
-      </c>
-      <c r="M18" s="3">
-        <v>-17300</v>
-      </c>
-      <c r="N18" s="3">
-        <v>-130200</v>
-      </c>
-      <c r="O18" s="3">
-        <v>-18400</v>
-      </c>
-      <c r="P18" s="3">
-        <v>-36200</v>
-      </c>
-      <c r="Q18" s="3">
-        <v>-29800</v>
-      </c>
-      <c r="R18" s="3">
-        <v>69800</v>
-      </c>
-      <c r="S18" s="3">
-        <v>-131700</v>
-      </c>
-      <c r="T18" s="3">
-        <v>-41700</v>
-      </c>
-      <c r="U18" s="3">
-        <v>-27600</v>
-      </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>-31400</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>-36100</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>-12700</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>-12000</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>-7300</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>-12400</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>-4400</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>-7500</v>
       </c>
-      <c r="AD18" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AE18" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="19" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF18" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1681,163 +1714,167 @@
       <c r="AC19" s="3"/>
       <c r="AD19" s="3"/>
       <c r="AE19" s="3"/>
-    </row>
-    <row r="20" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF19" s="3"/>
+    </row>
+    <row r="20" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
-        <v>0</v>
+        <v>300</v>
       </c>
       <c r="E20" s="3">
+        <v>100</v>
+      </c>
+      <c r="F20" s="3">
+        <v>-400</v>
+      </c>
+      <c r="G20" s="3">
+        <v>-5700</v>
+      </c>
+      <c r="H20" s="3">
+        <v>2900</v>
+      </c>
+      <c r="I20" s="3">
+        <v>-800</v>
+      </c>
+      <c r="J20" s="3">
+        <v>-900</v>
+      </c>
+      <c r="K20" s="3">
+        <v>1000</v>
+      </c>
+      <c r="L20" s="3">
+        <v>6100</v>
+      </c>
+      <c r="M20" s="3">
+        <v>700</v>
+      </c>
+      <c r="N20" s="3">
+        <v>5300</v>
+      </c>
+      <c r="O20" s="3">
+        <v>7700</v>
+      </c>
+      <c r="P20" s="3">
+        <v>900</v>
+      </c>
+      <c r="Q20" s="3">
+        <v>4300</v>
+      </c>
+      <c r="R20" s="3">
         <v>500</v>
       </c>
-      <c r="F20" s="3">
-        <v>-100</v>
-      </c>
-      <c r="G20" s="3">
-        <v>-2700</v>
-      </c>
-      <c r="H20" s="3">
-        <v>1100</v>
-      </c>
-      <c r="I20" s="3">
+      <c r="S20" s="3">
+        <v>700</v>
+      </c>
+      <c r="T20" s="3">
+        <v>2400</v>
+      </c>
+      <c r="U20" s="3">
+        <v>3700</v>
+      </c>
+      <c r="V20" s="3">
+        <v>1400</v>
+      </c>
+      <c r="W20" s="3">
+        <v>200</v>
+      </c>
+      <c r="X20" s="3">
+        <v>800</v>
+      </c>
+      <c r="Y20" s="3">
         <v>1200</v>
       </c>
-      <c r="J20" s="3">
-        <v>1000</v>
-      </c>
-      <c r="K20" s="3">
-        <v>6100</v>
-      </c>
-      <c r="L20" s="3">
-        <v>700</v>
-      </c>
-      <c r="M20" s="3">
-        <v>5300</v>
-      </c>
-      <c r="N20" s="3">
-        <v>7700</v>
-      </c>
-      <c r="O20" s="3">
-        <v>900</v>
-      </c>
-      <c r="P20" s="3">
-        <v>4300</v>
-      </c>
-      <c r="Q20" s="3">
-        <v>500</v>
-      </c>
-      <c r="R20" s="3">
-        <v>700</v>
-      </c>
-      <c r="S20" s="3">
-        <v>2400</v>
-      </c>
-      <c r="T20" s="3">
-        <v>3700</v>
-      </c>
-      <c r="U20" s="3">
-        <v>1400</v>
-      </c>
-      <c r="V20" s="3">
-        <v>200</v>
-      </c>
-      <c r="W20" s="3">
-        <v>800</v>
-      </c>
-      <c r="X20" s="3">
-        <v>1200</v>
-      </c>
-      <c r="Y20" s="3">
+      <c r="Z20" s="3">
         <v>-1800</v>
       </c>
-      <c r="Z20" s="3">
+      <c r="AA20" s="3">
         <v>-800</v>
       </c>
-      <c r="AA20" s="3">
+      <c r="AB20" s="3">
         <v>3200</v>
       </c>
-      <c r="AB20" s="3">
+      <c r="AC20" s="3">
         <v>1700</v>
       </c>
-      <c r="AC20" s="3">
+      <c r="AD20" s="3">
         <v>-1100</v>
       </c>
-      <c r="AD20" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AE20" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="21" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF20" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="D21" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="E21" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="F21" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="G21" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="H21" s="3" t="s">
-        <v>3</v>
+      <c r="D21" s="3">
+        <v>16100</v>
+      </c>
+      <c r="E21" s="3">
+        <v>-9100</v>
+      </c>
+      <c r="F21" s="3">
+        <v>5600</v>
+      </c>
+      <c r="G21" s="3">
+        <v>17500</v>
+      </c>
+      <c r="H21" s="3">
+        <v>-9400</v>
       </c>
       <c r="I21" s="3">
-        <v>-25300</v>
+        <v>-37600</v>
       </c>
       <c r="J21" s="3">
+        <v>-26000</v>
+      </c>
+      <c r="K21" s="3">
         <v>6100</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>-22600</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>-61100</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>-10900</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>-118400</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>-16400</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>-31100</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>-28600</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>71200</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>-128700</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>-37500</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>-25600</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>-30700</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>-35000</v>
       </c>
-      <c r="X21" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y21" s="3" t="s">
         <v>3</v>
       </c>
@@ -1847,58 +1884,61 @@
       <c r="AA21" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AB21" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AC21" s="3">
         <v>-2300</v>
       </c>
-      <c r="AC21" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AD21" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AE21" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="22" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF21" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="22" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
-        <v>2900</v>
+        <v>2200</v>
       </c>
       <c r="E22" s="3">
         <v>2900</v>
       </c>
       <c r="F22" s="3">
+        <v>2800</v>
+      </c>
+      <c r="G22" s="3">
         <v>2700</v>
-      </c>
-      <c r="G22" s="3">
-        <v>2500</v>
       </c>
       <c r="H22" s="3">
         <v>2400</v>
       </c>
       <c r="I22" s="3">
-        <v>2200</v>
+        <v>2400</v>
       </c>
       <c r="J22" s="3">
+        <v>2300</v>
+      </c>
+      <c r="K22" s="3">
         <v>2100</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>1700</v>
       </c>
-      <c r="L22" s="3">
+      <c r="M22" s="3">
         <v>1400</v>
       </c>
-      <c r="M22" s="3">
+      <c r="N22" s="3">
         <v>1200</v>
       </c>
-      <c r="N22" s="3">
+      <c r="O22" s="3">
         <v>4400</v>
-      </c>
-      <c r="O22" s="3">
-        <v>1100</v>
       </c>
       <c r="P22" s="3">
         <v>1100</v>
@@ -1906,8 +1946,8 @@
       <c r="Q22" s="3">
         <v>1100</v>
       </c>
-      <c r="R22" s="3" t="s">
-        <v>3</v>
+      <c r="R22" s="3">
+        <v>1100</v>
       </c>
       <c r="S22" s="3" t="s">
         <v>3</v>
@@ -1924,8 +1964,8 @@
       <c r="W22" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="X22" s="3">
-        <v>0</v>
+      <c r="X22" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="Y22" s="3">
         <v>0</v>
@@ -1948,159 +1988,165 @@
       <c r="AE22" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>13000</v>
+      </c>
+      <c r="E23" s="3">
+        <v>-12800</v>
+      </c>
+      <c r="F23" s="3">
+        <v>1900</v>
+      </c>
+      <c r="G23" s="3">
+        <v>8000</v>
+      </c>
+      <c r="H23" s="3">
+        <v>-12900</v>
+      </c>
+      <c r="I23" s="3">
+        <v>-41100</v>
+      </c>
+      <c r="J23" s="3">
+        <v>-29500</v>
+      </c>
+      <c r="K23" s="3">
+        <v>2400</v>
+      </c>
+      <c r="L23" s="3">
+        <v>-25900</v>
+      </c>
+      <c r="M23" s="3">
+        <v>-63900</v>
+      </c>
+      <c r="N23" s="3">
         <v>-13200</v>
       </c>
-      <c r="E23" s="3">
-        <v>1900</v>
-      </c>
-      <c r="F23" s="3">
-        <v>8000</v>
-      </c>
-      <c r="G23" s="3">
-        <v>-13300</v>
-      </c>
-      <c r="H23" s="3">
-        <v>-42100</v>
-      </c>
-      <c r="I23" s="3">
-        <v>-28600</v>
-      </c>
-      <c r="J23" s="3">
-        <v>2400</v>
-      </c>
-      <c r="K23" s="3">
-        <v>-25900</v>
-      </c>
-      <c r="L23" s="3">
-        <v>-63900</v>
-      </c>
-      <c r="M23" s="3">
-        <v>-13200</v>
-      </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>-127000</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>-18600</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>-33100</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>-30400</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>70600</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>-129400</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>-38000</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>-26200</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>-31200</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>-35400</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>-11500</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>-13900</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>-8100</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>-9300</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>-2600</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>-8500</v>
       </c>
-      <c r="AD23" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AE23" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="24" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF23" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="24" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>300</v>
+      </c>
+      <c r="E24" s="3">
         <v>1000</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>-100</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>100</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>400</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>700</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>500</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>2000</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>-200</v>
-      </c>
-      <c r="L24" s="3">
-        <v>100</v>
       </c>
       <c r="M24" s="3">
         <v>100</v>
       </c>
       <c r="N24" s="3">
+        <v>100</v>
+      </c>
+      <c r="O24" s="3">
         <v>900</v>
-      </c>
-      <c r="O24" s="3">
-        <v>400</v>
       </c>
       <c r="P24" s="3">
         <v>400</v>
       </c>
       <c r="Q24" s="3">
+        <v>400</v>
+      </c>
+      <c r="R24" s="3">
         <v>200</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>100</v>
       </c>
-      <c r="S24" s="3">
-        <v>0</v>
-      </c>
       <c r="T24" s="3">
         <v>0</v>
       </c>
       <c r="U24" s="3">
+        <v>0</v>
+      </c>
+      <c r="V24" s="3">
         <v>300</v>
       </c>
-      <c r="V24" s="3">
-        <v>0</v>
-      </c>
       <c r="W24" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="X24" s="3">
         <v>100</v>
@@ -2109,25 +2155,28 @@
         <v>100</v>
       </c>
       <c r="Z24" s="3">
-        <v>500</v>
+        <v>100</v>
       </c>
       <c r="AA24" s="3">
         <v>500</v>
       </c>
       <c r="AB24" s="3">
+        <v>500</v>
+      </c>
+      <c r="AC24" s="3">
         <v>200</v>
       </c>
-      <c r="AC24" s="3">
+      <c r="AD24" s="3">
         <v>500</v>
       </c>
-      <c r="AD24" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AE24" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="25" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF24" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="25" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2215,186 +2264,195 @@
       <c r="AE25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
-        <v>-14200</v>
+        <v>12700</v>
       </c>
       <c r="E26" s="3">
+        <v>-13800</v>
+      </c>
+      <c r="F26" s="3">
         <v>2000</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>7900</v>
       </c>
-      <c r="G26" s="3">
-        <v>-13700</v>
-      </c>
       <c r="H26" s="3">
-        <v>-42700</v>
+        <v>-13300</v>
       </c>
       <c r="I26" s="3">
-        <v>-29100</v>
+        <v>-41800</v>
       </c>
       <c r="J26" s="3">
+        <v>-30000</v>
+      </c>
+      <c r="K26" s="3">
         <v>400</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>-25700</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>-64000</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>-13300</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>-127900</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>-18900</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>-33500</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>-30600</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>70500</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>-129400</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>-38000</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>-26500</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>-31200</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>-35500</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>-11600</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>-14000</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>-8600</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>-9800</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>-2800</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>-9000</v>
       </c>
-      <c r="AD26" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AE26" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="27" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF26" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="27" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
-        <v>-14000</v>
+        <v>12300</v>
       </c>
       <c r="E27" s="3">
-        <v>1800</v>
+        <v>-13700</v>
       </c>
       <c r="F27" s="3">
+        <v>1700</v>
+      </c>
+      <c r="G27" s="3">
         <v>8000</v>
       </c>
-      <c r="G27" s="3">
-        <v>-14500</v>
-      </c>
       <c r="H27" s="3">
-        <v>-42200</v>
+        <v>-14100</v>
       </c>
       <c r="I27" s="3">
-        <v>-28800</v>
+        <v>-41300</v>
       </c>
       <c r="J27" s="3">
+        <v>-29700</v>
+      </c>
+      <c r="K27" s="3">
         <v>1700</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>-25400</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>-63100</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>-13200</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>-123600</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>-18300</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>-33400</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>-30500</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>70500</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>-129400</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>-38000</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>-26500</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>-31700</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>-37300</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>-13400</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>-15500</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>-10200</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>-11200</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>-4200</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>-8900</v>
       </c>
-      <c r="AD27" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AE27" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="28" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF27" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="28" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2482,16 +2540,19 @@
       <c r="AE28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="D29" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="E29" s="3" t="s">
-        <v>3</v>
+      <c r="D29" s="3">
+        <v>0</v>
+      </c>
+      <c r="E29" s="3">
+        <v>0</v>
       </c>
       <c r="F29" s="3">
         <v>0</v>
@@ -2515,31 +2576,31 @@
         <v>0</v>
       </c>
       <c r="M29" s="3">
+        <v>0</v>
+      </c>
+      <c r="N29" s="3">
         <v>-800</v>
       </c>
-      <c r="N29" s="3">
+      <c r="O29" s="3">
         <v>-13800</v>
       </c>
-      <c r="O29" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="P29" s="3">
+      <c r="P29" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q29" s="3">
         <v>-41200</v>
       </c>
-      <c r="Q29" s="3">
+      <c r="R29" s="3">
         <v>-14800</v>
       </c>
-      <c r="R29" s="3">
+      <c r="S29" s="3">
         <v>-132800</v>
       </c>
-      <c r="S29" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T29" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="U29" s="3">
-        <v>0</v>
+      <c r="U29" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="V29" s="3">
         <v>0</v>
@@ -2571,8 +2632,11 @@
       <c r="AE29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2660,8 +2724,11 @@
       <c r="AE30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2749,186 +2816,195 @@
       <c r="AE31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
-        <v>0</v>
+        <v>-300</v>
       </c>
       <c r="E32" s="3">
+        <v>-100</v>
+      </c>
+      <c r="F32" s="3">
+        <v>400</v>
+      </c>
+      <c r="G32" s="3">
+        <v>5700</v>
+      </c>
+      <c r="H32" s="3">
+        <v>-2900</v>
+      </c>
+      <c r="I32" s="3">
+        <v>800</v>
+      </c>
+      <c r="J32" s="3">
+        <v>900</v>
+      </c>
+      <c r="K32" s="3">
+        <v>-1000</v>
+      </c>
+      <c r="L32" s="3">
+        <v>-6100</v>
+      </c>
+      <c r="M32" s="3">
+        <v>-700</v>
+      </c>
+      <c r="N32" s="3">
+        <v>-5300</v>
+      </c>
+      <c r="O32" s="3">
+        <v>-7700</v>
+      </c>
+      <c r="P32" s="3">
+        <v>-900</v>
+      </c>
+      <c r="Q32" s="3">
+        <v>-4300</v>
+      </c>
+      <c r="R32" s="3">
         <v>-500</v>
       </c>
-      <c r="F32" s="3">
-        <v>100</v>
-      </c>
-      <c r="G32" s="3">
-        <v>2700</v>
-      </c>
-      <c r="H32" s="3">
-        <v>-1100</v>
-      </c>
-      <c r="I32" s="3">
+      <c r="S32" s="3">
+        <v>-700</v>
+      </c>
+      <c r="T32" s="3">
+        <v>-2400</v>
+      </c>
+      <c r="U32" s="3">
+        <v>-3700</v>
+      </c>
+      <c r="V32" s="3">
+        <v>-1400</v>
+      </c>
+      <c r="W32" s="3">
+        <v>-200</v>
+      </c>
+      <c r="X32" s="3">
+        <v>-800</v>
+      </c>
+      <c r="Y32" s="3">
         <v>-1200</v>
       </c>
-      <c r="J32" s="3">
-        <v>-1000</v>
-      </c>
-      <c r="K32" s="3">
-        <v>-6100</v>
-      </c>
-      <c r="L32" s="3">
-        <v>-700</v>
-      </c>
-      <c r="M32" s="3">
-        <v>-5300</v>
-      </c>
-      <c r="N32" s="3">
-        <v>-7700</v>
-      </c>
-      <c r="O32" s="3">
-        <v>-900</v>
-      </c>
-      <c r="P32" s="3">
-        <v>-4300</v>
-      </c>
-      <c r="Q32" s="3">
-        <v>-500</v>
-      </c>
-      <c r="R32" s="3">
-        <v>-700</v>
-      </c>
-      <c r="S32" s="3">
-        <v>-2400</v>
-      </c>
-      <c r="T32" s="3">
-        <v>-3700</v>
-      </c>
-      <c r="U32" s="3">
-        <v>-1400</v>
-      </c>
-      <c r="V32" s="3">
-        <v>-200</v>
-      </c>
-      <c r="W32" s="3">
-        <v>-800</v>
-      </c>
-      <c r="X32" s="3">
-        <v>-1200</v>
-      </c>
-      <c r="Y32" s="3">
+      <c r="Z32" s="3">
         <v>1800</v>
       </c>
-      <c r="Z32" s="3">
+      <c r="AA32" s="3">
         <v>800</v>
       </c>
-      <c r="AA32" s="3">
+      <c r="AB32" s="3">
         <v>-3200</v>
       </c>
-      <c r="AB32" s="3">
+      <c r="AC32" s="3">
         <v>-1700</v>
       </c>
-      <c r="AC32" s="3">
+      <c r="AD32" s="3">
         <v>1100</v>
       </c>
-      <c r="AD32" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AE32" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="33" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF32" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="33" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>12300</v>
+      </c>
+      <c r="E33" s="3">
+        <v>-13700</v>
+      </c>
+      <c r="F33" s="3">
+        <v>1700</v>
+      </c>
+      <c r="G33" s="3">
+        <v>8000</v>
+      </c>
+      <c r="H33" s="3">
+        <v>-14100</v>
+      </c>
+      <c r="I33" s="3">
+        <v>-41300</v>
+      </c>
+      <c r="J33" s="3">
+        <v>-29700</v>
+      </c>
+      <c r="K33" s="3">
+        <v>1700</v>
+      </c>
+      <c r="L33" s="3">
+        <v>-25400</v>
+      </c>
+      <c r="M33" s="3">
+        <v>-63100</v>
+      </c>
+      <c r="N33" s="3">
         <v>-14000</v>
       </c>
-      <c r="E33" s="3">
-        <v>1800</v>
-      </c>
-      <c r="F33" s="3">
-        <v>8000</v>
-      </c>
-      <c r="G33" s="3">
-        <v>-14500</v>
-      </c>
-      <c r="H33" s="3">
-        <v>-42200</v>
-      </c>
-      <c r="I33" s="3">
-        <v>-28800</v>
-      </c>
-      <c r="J33" s="3">
-        <v>1700</v>
-      </c>
-      <c r="K33" s="3">
-        <v>-25400</v>
-      </c>
-      <c r="L33" s="3">
-        <v>-63100</v>
-      </c>
-      <c r="M33" s="3">
-        <v>-14000</v>
-      </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>-137500</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>-18300</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>-74500</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>-45400</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>-62300</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>-129400</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>-38000</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>-26500</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>-31700</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>-37300</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>-13400</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>-15500</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>-10200</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>-11200</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>-4200</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>-8900</v>
       </c>
-      <c r="AD33" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AE33" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="34" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF33" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="34" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3016,191 +3092,200 @@
       <c r="AE34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>12300</v>
+      </c>
+      <c r="E35" s="3">
+        <v>-13700</v>
+      </c>
+      <c r="F35" s="3">
+        <v>1700</v>
+      </c>
+      <c r="G35" s="3">
+        <v>8000</v>
+      </c>
+      <c r="H35" s="3">
+        <v>-14100</v>
+      </c>
+      <c r="I35" s="3">
+        <v>-41300</v>
+      </c>
+      <c r="J35" s="3">
+        <v>-29700</v>
+      </c>
+      <c r="K35" s="3">
+        <v>1700</v>
+      </c>
+      <c r="L35" s="3">
+        <v>-25400</v>
+      </c>
+      <c r="M35" s="3">
+        <v>-63100</v>
+      </c>
+      <c r="N35" s="3">
         <v>-14000</v>
       </c>
-      <c r="E35" s="3">
-        <v>1800</v>
-      </c>
-      <c r="F35" s="3">
-        <v>8000</v>
-      </c>
-      <c r="G35" s="3">
-        <v>-14500</v>
-      </c>
-      <c r="H35" s="3">
-        <v>-42200</v>
-      </c>
-      <c r="I35" s="3">
-        <v>-28800</v>
-      </c>
-      <c r="J35" s="3">
-        <v>1700</v>
-      </c>
-      <c r="K35" s="3">
-        <v>-25400</v>
-      </c>
-      <c r="L35" s="3">
-        <v>-63100</v>
-      </c>
-      <c r="M35" s="3">
-        <v>-14000</v>
-      </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>-137500</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>-18300</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>-74500</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>-45400</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>-62300</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>-129400</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>-38000</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>-26500</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>-31700</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>-37300</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>-13400</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>-15500</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>-10200</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>-11200</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>-4200</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>-8900</v>
       </c>
-      <c r="AD35" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AE35" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="37" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF35" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="37" spans="2:32" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:31" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45565</v>
+      </c>
+      <c r="E38" s="2">
         <v>45473</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45382</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45291</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45199</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45107</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45016</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44926</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44834</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44742</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44651</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44561</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44469</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44377</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44286</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44196</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44104</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44012</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>43921</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>43830</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>43738</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43646</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>43555</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43465</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43373</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43281</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43190</v>
       </c>
-      <c r="AD38" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="AE38" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="39" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF38" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="39" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3232,8 +3317,9 @@
       <c r="AC39" s="3"/>
       <c r="AD39" s="3"/>
       <c r="AE39" s="3"/>
-    </row>
-    <row r="40" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF39" s="3"/>
+    </row>
+    <row r="40" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3265,77 +3351,78 @@
       <c r="AC40" s="3"/>
       <c r="AD40" s="3"/>
       <c r="AE40" s="3"/>
-    </row>
-    <row r="41" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF40" s="3"/>
+    </row>
+    <row r="41" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
-        <v>70600</v>
+        <v>60000</v>
       </c>
       <c r="E41" s="3">
-        <v>37100</v>
+        <v>68900</v>
       </c>
       <c r="F41" s="3">
+        <v>36400</v>
+      </c>
+      <c r="G41" s="3">
         <v>64100</v>
       </c>
-      <c r="G41" s="3">
-        <v>47600</v>
-      </c>
       <c r="H41" s="3">
-        <v>92700</v>
+        <v>46300</v>
       </c>
       <c r="I41" s="3">
-        <v>81700</v>
+        <v>90700</v>
       </c>
       <c r="J41" s="3">
+        <v>84300</v>
+      </c>
+      <c r="K41" s="3">
         <v>110500</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>98400</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>95500</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>57300</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>44600</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>70200</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>117900</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>257300</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>84800</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>11500</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>18500</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>20100</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>26700</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>8500</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>8000</v>
       </c>
-      <c r="Y41" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z41" s="3" t="s">
         <v>3</v>
       </c>
@@ -3354,77 +3441,80 @@
       <c r="AE41" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="42" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF41" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="42" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
-        <v>8900</v>
+        <v>9000</v>
       </c>
       <c r="E42" s="3">
-        <v>8800</v>
+        <v>8600</v>
       </c>
       <c r="F42" s="3">
+        <v>8700</v>
+      </c>
+      <c r="G42" s="3">
         <v>10200</v>
       </c>
-      <c r="G42" s="3">
-        <v>3100</v>
-      </c>
       <c r="H42" s="3">
-        <v>3100</v>
+        <v>3000</v>
       </c>
       <c r="I42" s="3">
-        <v>3100</v>
+        <v>3000</v>
       </c>
       <c r="J42" s="3">
+        <v>3200</v>
+      </c>
+      <c r="K42" s="3">
         <v>32800</v>
-      </c>
-      <c r="K42" s="3">
-        <v>3000</v>
       </c>
       <c r="L42" s="3">
         <v>3000</v>
       </c>
       <c r="M42" s="3">
+        <v>3000</v>
+      </c>
+      <c r="N42" s="3">
         <v>900</v>
       </c>
-      <c r="N42" s="3">
+      <c r="O42" s="3">
         <v>69600</v>
       </c>
-      <c r="O42" s="3">
+      <c r="P42" s="3">
         <v>58300</v>
       </c>
-      <c r="P42" s="3">
+      <c r="Q42" s="3">
         <v>146500</v>
       </c>
-      <c r="Q42" s="3">
+      <c r="R42" s="3">
         <v>47000</v>
       </c>
-      <c r="R42" s="3">
+      <c r="S42" s="3">
         <v>81500</v>
       </c>
-      <c r="S42" s="3">
+      <c r="T42" s="3">
         <v>155400</v>
       </c>
-      <c r="T42" s="3">
+      <c r="U42" s="3">
         <v>245400</v>
       </c>
-      <c r="U42" s="3">
+      <c r="V42" s="3">
         <v>242400</v>
       </c>
-      <c r="V42" s="3">
+      <c r="W42" s="3">
         <v>222800</v>
       </c>
-      <c r="W42" s="3">
+      <c r="X42" s="3">
         <v>16200</v>
       </c>
-      <c r="X42" s="3">
+      <c r="Y42" s="3">
         <v>38000</v>
       </c>
-      <c r="Y42" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z42" s="3" t="s">
         <v>3</v>
       </c>
@@ -3443,77 +3533,80 @@
       <c r="AE42" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="43" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF42" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="43" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
-        <v>65000</v>
+        <v>70700</v>
       </c>
       <c r="E43" s="3">
+        <v>63500</v>
+      </c>
+      <c r="F43" s="3">
+        <v>57100</v>
+      </c>
+      <c r="G43" s="3">
+        <v>56800</v>
+      </c>
+      <c r="H43" s="3">
+        <v>49400</v>
+      </c>
+      <c r="I43" s="3">
+        <v>53300</v>
+      </c>
+      <c r="J43" s="3">
+        <v>39000</v>
+      </c>
+      <c r="K43" s="3">
         <v>58200</v>
       </c>
-      <c r="F43" s="3">
-        <v>53600</v>
-      </c>
-      <c r="G43" s="3">
-        <v>50900</v>
-      </c>
-      <c r="H43" s="3">
-        <v>54500</v>
-      </c>
-      <c r="I43" s="3">
-        <v>37700</v>
-      </c>
-      <c r="J43" s="3">
-        <v>58200</v>
-      </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>46900</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>49000</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>41500</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>35100</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>35300</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>44300</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>35100</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>38000</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>50100</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>34900</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>36800</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>33200</v>
       </c>
-      <c r="W43" s="3">
+      <c r="X43" s="3">
         <v>27800</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Y43" s="3">
         <v>31100</v>
       </c>
-      <c r="Y43" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z43" s="3" t="s">
         <v>3</v>
       </c>
@@ -3532,77 +3625,80 @@
       <c r="AE43" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="44" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF43" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="44" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
-        <v>27600</v>
+        <v>25500</v>
       </c>
       <c r="E44" s="3">
-        <v>26700</v>
+        <v>26900</v>
       </c>
       <c r="F44" s="3">
+        <v>26200</v>
+      </c>
+      <c r="G44" s="3">
         <v>30600</v>
       </c>
-      <c r="G44" s="3">
-        <v>25000</v>
-      </c>
       <c r="H44" s="3">
-        <v>25800</v>
+        <v>24300</v>
       </c>
       <c r="I44" s="3">
-        <v>30900</v>
+        <v>25200</v>
       </c>
       <c r="J44" s="3">
+        <v>31900</v>
+      </c>
+      <c r="K44" s="3">
         <v>32700</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>23500</v>
-      </c>
-      <c r="L44" s="3">
-        <v>29500</v>
       </c>
       <c r="M44" s="3">
         <v>29500</v>
       </c>
       <c r="N44" s="3">
+        <v>29500</v>
+      </c>
+      <c r="O44" s="3">
         <v>35300</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>38000</v>
       </c>
-      <c r="P44" s="3">
+      <c r="Q44" s="3">
         <v>38600</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="R44" s="3">
         <v>37400</v>
       </c>
-      <c r="R44" s="3">
+      <c r="S44" s="3">
         <v>20700</v>
       </c>
-      <c r="S44" s="3">
+      <c r="T44" s="3">
         <v>13500</v>
       </c>
-      <c r="T44" s="3">
+      <c r="U44" s="3">
         <v>13700</v>
       </c>
-      <c r="U44" s="3">
+      <c r="V44" s="3">
         <v>10300</v>
       </c>
-      <c r="V44" s="3">
+      <c r="W44" s="3">
         <v>11300</v>
       </c>
-      <c r="W44" s="3">
+      <c r="X44" s="3">
         <v>8100</v>
       </c>
-      <c r="X44" s="3">
+      <c r="Y44" s="3">
         <v>5000</v>
       </c>
-      <c r="Y44" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z44" s="3" t="s">
         <v>3</v>
       </c>
@@ -3621,77 +3717,80 @@
       <c r="AE44" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="45" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF44" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="45" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
-        <v>25200</v>
+        <v>23300</v>
       </c>
       <c r="E45" s="3">
-        <v>27700</v>
+        <v>24300</v>
       </c>
       <c r="F45" s="3">
-        <v>24800</v>
+        <v>27100</v>
       </c>
       <c r="G45" s="3">
+        <v>12600</v>
+      </c>
+      <c r="H45" s="3">
+        <v>31900</v>
+      </c>
+      <c r="I45" s="3">
+        <v>26700</v>
+      </c>
+      <c r="J45" s="3">
+        <v>25700</v>
+      </c>
+      <c r="K45" s="3">
+        <v>29400</v>
+      </c>
+      <c r="L45" s="3">
+        <v>59700</v>
+      </c>
+      <c r="M45" s="3">
+        <v>104200</v>
+      </c>
+      <c r="N45" s="3">
+        <v>129100</v>
+      </c>
+      <c r="O45" s="3">
+        <v>128800</v>
+      </c>
+      <c r="P45" s="3">
+        <v>85400</v>
+      </c>
+      <c r="Q45" s="3">
+        <v>33100</v>
+      </c>
+      <c r="R45" s="3">
+        <v>27600</v>
+      </c>
+      <c r="S45" s="3">
         <v>32800</v>
       </c>
-      <c r="H45" s="3">
-        <v>27300</v>
-      </c>
-      <c r="I45" s="3">
-        <v>24900</v>
-      </c>
-      <c r="J45" s="3">
-        <v>29400</v>
-      </c>
-      <c r="K45" s="3">
-        <v>59700</v>
-      </c>
-      <c r="L45" s="3">
-        <v>104200</v>
-      </c>
-      <c r="M45" s="3">
-        <v>129100</v>
-      </c>
-      <c r="N45" s="3">
-        <v>128800</v>
-      </c>
-      <c r="O45" s="3">
-        <v>85400</v>
-      </c>
-      <c r="P45" s="3">
-        <v>33100</v>
-      </c>
-      <c r="Q45" s="3">
-        <v>27600</v>
-      </c>
-      <c r="R45" s="3">
-        <v>32800</v>
-      </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>29600</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>17500</v>
-      </c>
-      <c r="U45" s="3">
-        <v>18600</v>
       </c>
       <c r="V45" s="3">
         <v>18600</v>
       </c>
       <c r="W45" s="3">
+        <v>18600</v>
+      </c>
+      <c r="X45" s="3">
         <v>16200</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Y45" s="3">
         <v>11300</v>
       </c>
-      <c r="Y45" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z45" s="3" t="s">
         <v>3</v>
       </c>
@@ -3710,77 +3809,80 @@
       <c r="AE45" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="46" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF45" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="46" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
-        <v>197300</v>
+        <v>188800</v>
       </c>
       <c r="E46" s="3">
-        <v>158400</v>
+        <v>192500</v>
       </c>
       <c r="F46" s="3">
+        <v>155600</v>
+      </c>
+      <c r="G46" s="3">
         <v>183300</v>
       </c>
-      <c r="G46" s="3">
-        <v>159500</v>
-      </c>
       <c r="H46" s="3">
-        <v>203400</v>
+        <v>155000</v>
       </c>
       <c r="I46" s="3">
-        <v>178300</v>
+        <v>198900</v>
       </c>
       <c r="J46" s="3">
+        <v>184100</v>
+      </c>
+      <c r="K46" s="3">
         <v>263600</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>231500</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>281200</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>258300</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>313400</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>287200</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>380400</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>404400</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>257700</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>260200</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>330000</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>328200</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>312600</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>76800</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Y46" s="3">
         <v>93400</v>
       </c>
-      <c r="Y46" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z46" s="3" t="s">
         <v>3</v>
       </c>
@@ -3799,59 +3901,62 @@
       <c r="AE46" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="47" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF46" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="47" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
-        <v>10900</v>
+        <v>10600</v>
       </c>
       <c r="E47" s="3">
-        <v>7000</v>
+        <v>10700</v>
       </c>
       <c r="F47" s="3">
+        <v>6800</v>
+      </c>
+      <c r="G47" s="3">
         <v>7200</v>
       </c>
-      <c r="G47" s="3">
-        <v>9100</v>
-      </c>
       <c r="H47" s="3">
-        <v>12300</v>
+        <v>8800</v>
       </c>
       <c r="I47" s="3">
+        <v>12100</v>
+      </c>
+      <c r="J47" s="3">
+        <v>13200</v>
+      </c>
+      <c r="K47" s="3">
         <v>12800</v>
       </c>
-      <c r="J47" s="3">
-        <v>12800</v>
-      </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>9300</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>9800</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>3800</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>4500</v>
       </c>
-      <c r="O47" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P47" s="3" t="s">
         <v>3</v>
       </c>
       <c r="Q47" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="R47" s="3">
+      <c r="R47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S47" s="3">
         <v>5900</v>
       </c>
-      <c r="S47" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T47" s="3" t="s">
         <v>3</v>
       </c>
@@ -3864,8 +3969,8 @@
       <c r="W47" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="X47" s="3">
-        <v>0</v>
+      <c r="X47" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="Y47" s="3">
         <v>0</v>
@@ -3888,77 +3993,80 @@
       <c r="AE47" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>18800</v>
+      </c>
+      <c r="E48" s="3">
+        <v>20500</v>
+      </c>
+      <c r="F48" s="3">
+        <v>21500</v>
+      </c>
+      <c r="G48" s="3">
+        <v>22600</v>
+      </c>
+      <c r="H48" s="3">
+        <v>23700</v>
+      </c>
+      <c r="I48" s="3">
+        <v>23100</v>
+      </c>
+      <c r="J48" s="3">
+        <v>23200</v>
+      </c>
+      <c r="K48" s="3">
+        <v>24000</v>
+      </c>
+      <c r="L48" s="3">
+        <v>25700</v>
+      </c>
+      <c r="M48" s="3">
+        <v>27400</v>
+      </c>
+      <c r="N48" s="3">
+        <v>28300</v>
+      </c>
+      <c r="O48" s="3">
+        <v>27400</v>
+      </c>
+      <c r="P48" s="3">
+        <v>31400</v>
+      </c>
+      <c r="Q48" s="3">
+        <v>28600</v>
+      </c>
+      <c r="R48" s="3">
         <v>21000</v>
       </c>
-      <c r="E48" s="3">
-        <v>21900</v>
-      </c>
-      <c r="F48" s="3">
-        <v>22500</v>
-      </c>
-      <c r="G48" s="3">
-        <v>24400</v>
-      </c>
-      <c r="H48" s="3">
-        <v>23600</v>
-      </c>
-      <c r="I48" s="3">
-        <v>22500</v>
-      </c>
-      <c r="J48" s="3">
-        <v>24000</v>
-      </c>
-      <c r="K48" s="3">
-        <v>25700</v>
-      </c>
-      <c r="L48" s="3">
-        <v>27400</v>
-      </c>
-      <c r="M48" s="3">
-        <v>28300</v>
-      </c>
-      <c r="N48" s="3">
-        <v>27400</v>
-      </c>
-      <c r="O48" s="3">
-        <v>31400</v>
-      </c>
-      <c r="P48" s="3">
-        <v>28600</v>
-      </c>
-      <c r="Q48" s="3">
-        <v>21000</v>
-      </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>21100</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>18100</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>11900</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>7600</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>7500</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>6100</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>3500</v>
       </c>
-      <c r="Y48" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z48" s="3" t="s">
         <v>3</v>
       </c>
@@ -3977,46 +4085,49 @@
       <c r="AE48" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="49" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF48" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="49" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
-        <v>15500</v>
+        <v>15700</v>
       </c>
       <c r="E49" s="3">
-        <v>15500</v>
+        <v>15100</v>
       </c>
       <c r="F49" s="3">
-        <v>15500</v>
+        <v>15200</v>
       </c>
       <c r="G49" s="3">
         <v>15500</v>
       </c>
       <c r="H49" s="3">
+        <v>15100</v>
+      </c>
+      <c r="I49" s="3">
+        <v>15200</v>
+      </c>
+      <c r="J49" s="3">
+        <v>16000</v>
+      </c>
+      <c r="K49" s="3">
         <v>15500</v>
       </c>
-      <c r="I49" s="3">
-        <v>15500</v>
-      </c>
-      <c r="J49" s="3">
-        <v>15500</v>
-      </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>15200</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>15300</v>
-      </c>
-      <c r="M49" s="3">
-        <v>15200</v>
       </c>
       <c r="N49" s="3">
         <v>15200</v>
       </c>
-      <c r="O49" s="3" t="s">
-        <v>3</v>
+      <c r="O49" s="3">
+        <v>15200</v>
       </c>
       <c r="P49" s="3" t="s">
         <v>3</v>
@@ -4033,8 +4144,8 @@
       <c r="T49" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="U49" s="3">
-        <v>0</v>
+      <c r="U49" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="V49" s="3">
         <v>0</v>
@@ -4066,8 +4177,11 @@
       <c r="AE49" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="50" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF49" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4155,8 +4269,11 @@
       <c r="AE50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4244,76 +4361,79 @@
       <c r="AE51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
-        <v>6500</v>
+        <v>6100</v>
       </c>
       <c r="E52" s="3">
-        <v>7800</v>
+        <v>6400</v>
       </c>
       <c r="F52" s="3">
+        <v>7700</v>
+      </c>
+      <c r="G52" s="3">
         <v>6300</v>
       </c>
-      <c r="G52" s="3">
-        <v>6600</v>
-      </c>
       <c r="H52" s="3">
-        <v>5400</v>
+        <v>6400</v>
       </c>
       <c r="I52" s="3">
-        <v>4800</v>
+        <v>5300</v>
       </c>
       <c r="J52" s="3">
         <v>4900</v>
       </c>
       <c r="K52" s="3">
+        <v>4900</v>
+      </c>
+      <c r="L52" s="3">
         <v>5300</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>5200</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>5000</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>3200</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>30000</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>14700</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>11000</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>3400</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>3900</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>3200</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>2100</v>
       </c>
-      <c r="V52" s="3">
+      <c r="W52" s="3">
         <v>1300</v>
-      </c>
-      <c r="W52" s="3">
-        <v>800</v>
       </c>
       <c r="X52" s="3">
         <v>800</v>
       </c>
-      <c r="Y52" s="3" t="s">
-        <v>3</v>
+      <c r="Y52" s="3">
+        <v>800</v>
       </c>
       <c r="Z52" s="3" t="s">
         <v>3</v>
@@ -4333,8 +4453,11 @@
       <c r="AE52" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="53" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF52" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="53" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -4422,77 +4545,80 @@
       <c r="AE53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
-        <v>251200</v>
+        <v>240000</v>
       </c>
       <c r="E54" s="3">
-        <v>210600</v>
+        <v>245200</v>
       </c>
       <c r="F54" s="3">
-        <v>234900</v>
+        <v>206900</v>
       </c>
       <c r="G54" s="3">
-        <v>215000</v>
+        <v>235000</v>
       </c>
       <c r="H54" s="3">
-        <v>260300</v>
+        <v>209000</v>
       </c>
       <c r="I54" s="3">
-        <v>233800</v>
+        <v>254500</v>
       </c>
       <c r="J54" s="3">
+        <v>241400</v>
+      </c>
+      <c r="K54" s="3">
         <v>320900</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>286900</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>339000</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>310600</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>363700</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>348600</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>423600</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>436300</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>288200</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>282200</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>345100</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>337900</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>321300</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>83700</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>97700</v>
       </c>
-      <c r="Y54" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z54" s="3" t="s">
         <v>3</v>
       </c>
@@ -4511,8 +4637,11 @@
       <c r="AE54" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="55" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF54" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="55" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -4544,8 +4673,9 @@
       <c r="AC55" s="3"/>
       <c r="AD55" s="3"/>
       <c r="AE55" s="3"/>
-    </row>
-    <row r="56" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF55" s="3"/>
+    </row>
+    <row r="56" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -4577,77 +4707,78 @@
       <c r="AC56" s="3"/>
       <c r="AD56" s="3"/>
       <c r="AE56" s="3"/>
-    </row>
-    <row r="57" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF56" s="3"/>
+    </row>
+    <row r="57" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
-        <v>15600</v>
+        <v>33200</v>
       </c>
       <c r="E57" s="3">
-        <v>16900</v>
+        <v>25400</v>
       </c>
       <c r="F57" s="3">
-        <v>22400</v>
+        <v>26700</v>
       </c>
       <c r="G57" s="3">
-        <v>23000</v>
+        <v>34000</v>
       </c>
       <c r="H57" s="3">
-        <v>18300</v>
+        <v>32000</v>
       </c>
       <c r="I57" s="3">
-        <v>17300</v>
+        <v>26600</v>
       </c>
       <c r="J57" s="3">
+        <v>30700</v>
+      </c>
+      <c r="K57" s="3">
         <v>39800</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>24800</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>21100</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>18400</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>22200</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>16600</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>10600</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>17500</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>19700</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>17600</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>15200</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>14900</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>9700</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>7200</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Y57" s="3">
         <v>5300</v>
       </c>
-      <c r="Y57" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z57" s="3" t="s">
         <v>3</v>
       </c>
@@ -4666,77 +4797,80 @@
       <c r="AE57" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="58" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF57" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="58" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>125200</v>
+      </c>
+      <c r="E58" s="3">
+        <v>120800</v>
+      </c>
+      <c r="F58" s="3">
+        <v>121600</v>
+      </c>
+      <c r="G58" s="3">
+        <v>129300</v>
+      </c>
+      <c r="H58" s="3">
+        <v>120300</v>
+      </c>
+      <c r="I58" s="3">
+        <v>200800</v>
+      </c>
+      <c r="J58" s="3">
+        <v>207800</v>
+      </c>
+      <c r="K58" s="3">
         <v>123800</v>
       </c>
-      <c r="E58" s="3">
-        <v>123800</v>
-      </c>
-      <c r="F58" s="3">
-        <v>123800</v>
-      </c>
-      <c r="G58" s="3">
-        <v>123800</v>
-      </c>
-      <c r="H58" s="3">
-        <v>205300</v>
-      </c>
-      <c r="I58" s="3">
-        <v>201300</v>
-      </c>
-      <c r="J58" s="3">
-        <v>123800</v>
-      </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>121300</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>122100</v>
-      </c>
-      <c r="M58" s="3">
-        <v>121200</v>
       </c>
       <c r="N58" s="3">
         <v>121200</v>
       </c>
       <c r="O58" s="3">
-        <v>124800</v>
+        <v>121200</v>
       </c>
       <c r="P58" s="3">
         <v>124800</v>
       </c>
       <c r="Q58" s="3">
-        <v>122200</v>
+        <v>124800</v>
       </c>
       <c r="R58" s="3">
         <v>122200</v>
       </c>
       <c r="S58" s="3">
-        <v>129400</v>
+        <v>122200</v>
       </c>
       <c r="T58" s="3">
         <v>129400</v>
       </c>
       <c r="U58" s="3">
+        <v>129400</v>
+      </c>
+      <c r="V58" s="3">
         <v>137500</v>
-      </c>
-      <c r="V58" s="3">
-        <v>135200</v>
       </c>
       <c r="W58" s="3">
         <v>135200</v>
       </c>
       <c r="X58" s="3">
+        <v>135200</v>
+      </c>
+      <c r="Y58" s="3">
         <v>134100</v>
       </c>
-      <c r="Y58" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z58" s="3" t="s">
         <v>3</v>
       </c>
@@ -4755,77 +4889,80 @@
       <c r="AE58" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="59" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF58" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="59" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>295800</v>
+        <v>127200</v>
       </c>
       <c r="E59" s="3">
-        <v>239200</v>
+        <v>149500</v>
       </c>
       <c r="F59" s="3">
-        <v>290700</v>
+        <v>114100</v>
       </c>
       <c r="G59" s="3">
-        <v>276800</v>
+        <v>156300</v>
       </c>
       <c r="H59" s="3">
-        <v>315500</v>
+        <v>136900</v>
       </c>
       <c r="I59" s="3">
-        <v>246500</v>
+        <v>175300</v>
       </c>
       <c r="J59" s="3">
+        <v>130400</v>
+      </c>
+      <c r="K59" s="3">
         <v>284500</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>266100</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>298500</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>226700</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>275500</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>293600</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>375700</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>312500</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>330500</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>268200</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>204700</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>157000</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>126000</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>93900</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>76900</v>
       </c>
-      <c r="Y59" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z59" s="3" t="s">
         <v>3</v>
       </c>
@@ -4844,77 +4981,80 @@
       <c r="AE59" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="60" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF59" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="60" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
-        <v>435200</v>
+        <v>413600</v>
       </c>
       <c r="E60" s="3">
-        <v>379800</v>
+        <v>424800</v>
       </c>
       <c r="F60" s="3">
-        <v>436900</v>
+        <v>373200</v>
       </c>
       <c r="G60" s="3">
-        <v>423500</v>
+        <v>437100</v>
       </c>
       <c r="H60" s="3">
-        <v>539000</v>
+        <v>411700</v>
       </c>
       <c r="I60" s="3">
-        <v>465100</v>
+        <v>527200</v>
       </c>
       <c r="J60" s="3">
+        <v>480200</v>
+      </c>
+      <c r="K60" s="3">
         <v>448100</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>412300</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>441700</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>366300</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>418900</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>435000</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>511100</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>452200</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>472400</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>415100</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>349200</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>309300</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>270800</v>
       </c>
-      <c r="W60" s="3">
+      <c r="X60" s="3">
         <v>236300</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Y60" s="3">
         <v>216400</v>
       </c>
-      <c r="Y60" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z60" s="3" t="s">
         <v>3</v>
       </c>
@@ -4933,47 +5073,50 @@
       <c r="AE60" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="61" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF60" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="61" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
-        <v>127700</v>
+        <v>133300</v>
       </c>
       <c r="E61" s="3">
-        <v>124200</v>
+        <v>130400</v>
       </c>
       <c r="F61" s="3">
-        <v>88900</v>
+        <v>128600</v>
       </c>
       <c r="G61" s="3">
-        <v>85000</v>
+        <v>95900</v>
       </c>
       <c r="H61" s="3">
-        <v>0</v>
+        <v>90300</v>
       </c>
       <c r="I61" s="3">
-        <v>0</v>
+        <v>6400</v>
       </c>
       <c r="J61" s="3">
+        <v>5900</v>
+      </c>
+      <c r="K61" s="3">
         <v>73600</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>68700</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>65300</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>48200</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>35200</v>
       </c>
-      <c r="O61" s="3">
-        <v>0</v>
-      </c>
       <c r="P61" s="3">
         <v>0</v>
       </c>
@@ -5022,74 +5165,77 @@
       <c r="AE61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
-        <v>8300</v>
+        <v>2600</v>
       </c>
       <c r="E62" s="3">
-        <v>9200</v>
+        <v>2300</v>
       </c>
       <c r="F62" s="3">
-        <v>9300</v>
+        <v>2400</v>
       </c>
       <c r="G62" s="3">
-        <v>10200</v>
+        <v>2300</v>
       </c>
       <c r="H62" s="3">
-        <v>8200</v>
+        <v>2300</v>
       </c>
       <c r="I62" s="3">
-        <v>7300</v>
+        <v>1700</v>
       </c>
       <c r="J62" s="3">
+        <v>1600</v>
+      </c>
+      <c r="K62" s="3">
         <v>7400</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>8400</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>8700</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>7700</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>10400</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>15100</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>13800</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>10900</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>11700</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>10300</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>6400</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>3900</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>4100</v>
       </c>
-      <c r="W62" s="3">
+      <c r="X62" s="3">
         <v>2100</v>
       </c>
-      <c r="X62" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y62" s="3" t="s">
         <v>3</v>
       </c>
@@ -5102,8 +5248,8 @@
       <c r="AB62" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="AC62" s="3">
-        <v>0</v>
+      <c r="AC62" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="AD62" s="3">
         <v>0</v>
@@ -5111,8 +5257,11 @@
       <c r="AE62" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="63" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF62" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="63" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -5200,8 +5349,11 @@
       <c r="AE63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -5289,8 +5441,11 @@
       <c r="AE64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -5378,77 +5533,80 @@
       <c r="AE65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
-        <v>579500</v>
+        <v>549500</v>
       </c>
       <c r="E66" s="3">
-        <v>521700</v>
+        <v>557600</v>
       </c>
       <c r="F66" s="3">
-        <v>543200</v>
+        <v>504200</v>
       </c>
       <c r="G66" s="3">
-        <v>526900</v>
+        <v>535200</v>
       </c>
       <c r="H66" s="3">
-        <v>554600</v>
+        <v>504300</v>
       </c>
       <c r="I66" s="3">
-        <v>480300</v>
+        <v>535200</v>
       </c>
       <c r="J66" s="3">
+        <v>487800</v>
+      </c>
+      <c r="K66" s="3">
         <v>537300</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>498600</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>525300</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>432700</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>475200</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>464600</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>524800</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>463100</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>484200</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>425500</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>355800</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>313400</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>275100</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>238600</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>216600</v>
       </c>
-      <c r="Y66" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z66" s="3" t="s">
         <v>3</v>
       </c>
@@ -5467,8 +5625,11 @@
       <c r="AE66" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="67" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF66" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="67" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -5500,8 +5661,9 @@
       <c r="AC67" s="3"/>
       <c r="AD67" s="3"/>
       <c r="AE67" s="3"/>
-    </row>
-    <row r="68" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF67" s="3"/>
+    </row>
+    <row r="68" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -5589,8 +5751,11 @@
       <c r="AE68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -5678,8 +5843,11 @@
       <c r="AE69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -5741,14 +5909,14 @@
         <v>0</v>
       </c>
       <c r="W70" s="3">
+        <v>0</v>
+      </c>
+      <c r="X70" s="3">
         <v>75900</v>
       </c>
-      <c r="X70" s="3">
+      <c r="Y70" s="3">
         <v>73600</v>
       </c>
-      <c r="Y70" s="3">
-        <v>0</v>
-      </c>
       <c r="Z70" s="3">
         <v>0</v>
       </c>
@@ -5767,8 +5935,11 @@
       <c r="AE70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -5856,8 +6027,11 @@
       <c r="AE71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
@@ -5867,11 +6041,11 @@
       <c r="E72" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="F72" s="3">
-        <v>-837900</v>
-      </c>
-      <c r="G72" s="3" t="s">
-        <v>3</v>
+      <c r="F72" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G72" s="3">
+        <v>-838200</v>
       </c>
       <c r="H72" s="3" t="s">
         <v>3</v>
@@ -5879,12 +6053,12 @@
       <c r="I72" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="J72" s="3">
+      <c r="J72" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="K72" s="3">
         <v>-760400</v>
       </c>
-      <c r="K72" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L72" s="3" t="s">
         <v>3</v>
       </c>
@@ -5903,30 +6077,30 @@
       <c r="Q72" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="R72" s="3">
+      <c r="R72" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S72" s="3">
         <v>-511000</v>
       </c>
-      <c r="S72" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T72" s="3" t="s">
         <v>3</v>
       </c>
       <c r="U72" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="V72" s="3">
+      <c r="V72" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="W72" s="3">
         <v>-295400</v>
       </c>
-      <c r="W72" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="X72" s="3">
+      <c r="X72" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Y72" s="3">
         <v>-224700</v>
       </c>
-      <c r="Y72" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z72" s="3" t="s">
         <v>3</v>
       </c>
@@ -5945,8 +6119,11 @@
       <c r="AE72" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="73" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF72" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="73" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -6034,8 +6211,11 @@
       <c r="AE73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -6123,8 +6303,11 @@
       <c r="AE74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -6212,77 +6395,80 @@
       <c r="AE75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
-        <v>-328300</v>
+        <v>-318200</v>
       </c>
       <c r="E76" s="3">
-        <v>-311000</v>
+        <v>-320500</v>
       </c>
       <c r="F76" s="3">
-        <v>-308300</v>
+        <v>-305600</v>
       </c>
       <c r="G76" s="3">
-        <v>-311900</v>
+        <v>-308400</v>
       </c>
       <c r="H76" s="3">
-        <v>-294300</v>
+        <v>-303200</v>
       </c>
       <c r="I76" s="3">
-        <v>-246500</v>
+        <v>-287900</v>
       </c>
       <c r="J76" s="3">
+        <v>-254500</v>
+      </c>
+      <c r="K76" s="3">
         <v>-216400</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>-211700</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>-186400</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>-122100</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>-111400</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>-116000</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>-101200</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>-26700</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>-196000</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>-143300</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>-10700</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>24500</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>46200</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>-230800</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>-192500</v>
       </c>
-      <c r="Y76" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z76" s="3" t="s">
         <v>3</v>
       </c>
@@ -6301,8 +6487,11 @@
       <c r="AE76" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="77" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF76" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="77" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -6390,191 +6579,200 @@
       <c r="AE77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:32" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:31" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45565</v>
+      </c>
+      <c r="E80" s="2">
         <v>45473</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45382</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45291</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45199</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45107</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45016</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44926</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44834</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44742</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44651</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44561</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44469</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44377</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44286</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44196</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44104</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44012</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>43921</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>43830</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>43738</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43646</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>43555</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43465</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43373</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43281</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43190</v>
       </c>
-      <c r="AD80" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="AE80" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="81" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF80" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="81" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>12300</v>
+      </c>
+      <c r="E81" s="3">
+        <v>-13700</v>
+      </c>
+      <c r="F81" s="3">
+        <v>1700</v>
+      </c>
+      <c r="G81" s="3">
+        <v>8000</v>
+      </c>
+      <c r="H81" s="3">
+        <v>-14100</v>
+      </c>
+      <c r="I81" s="3">
+        <v>-41300</v>
+      </c>
+      <c r="J81" s="3">
+        <v>-29700</v>
+      </c>
+      <c r="K81" s="3">
+        <v>1700</v>
+      </c>
+      <c r="L81" s="3">
+        <v>-25400</v>
+      </c>
+      <c r="M81" s="3">
+        <v>-63100</v>
+      </c>
+      <c r="N81" s="3">
         <v>-14000</v>
       </c>
-      <c r="E81" s="3">
-        <v>1800</v>
-      </c>
-      <c r="F81" s="3">
-        <v>8000</v>
-      </c>
-      <c r="G81" s="3">
-        <v>-14500</v>
-      </c>
-      <c r="H81" s="3">
-        <v>-42200</v>
-      </c>
-      <c r="I81" s="3">
-        <v>-28800</v>
-      </c>
-      <c r="J81" s="3">
-        <v>1700</v>
-      </c>
-      <c r="K81" s="3">
-        <v>-25400</v>
-      </c>
-      <c r="L81" s="3">
-        <v>-63100</v>
-      </c>
-      <c r="M81" s="3">
-        <v>-14000</v>
-      </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>-137500</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>-18300</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>-74500</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>-45400</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>-62300</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>-129400</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>-38000</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>-26500</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>-31700</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>-37300</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>-13400</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>-15500</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>-10200</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>-11200</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>-4200</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>-8900</v>
       </c>
-      <c r="AD81" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AE81" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="82" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF81" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="82" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -6606,8 +6804,9 @@
       <c r="AC82" s="3"/>
       <c r="AD82" s="3"/>
       <c r="AE82" s="3"/>
-    </row>
-    <row r="83" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF82" s="3"/>
+    </row>
+    <row r="83" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
@@ -6626,41 +6825,41 @@
       <c r="H83" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="I83" s="3">
-        <v>1100</v>
-      </c>
-      <c r="J83" s="3">
-        <v>1600</v>
+      <c r="I83" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J83" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K83" s="3">
         <v>1600</v>
       </c>
       <c r="L83" s="3">
+        <v>1600</v>
+      </c>
+      <c r="M83" s="3">
         <v>1500</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>1100</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>4200</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>1100</v>
-      </c>
-      <c r="P83" s="3">
-        <v>800</v>
       </c>
       <c r="Q83" s="3">
         <v>800</v>
       </c>
       <c r="R83" s="3">
+        <v>800</v>
+      </c>
+      <c r="S83" s="3">
         <v>700</v>
       </c>
-      <c r="S83" s="3">
+      <c r="T83" s="3">
         <v>600</v>
-      </c>
-      <c r="T83" s="3">
-        <v>500</v>
       </c>
       <c r="U83" s="3">
         <v>500</v>
@@ -6669,11 +6868,11 @@
         <v>500</v>
       </c>
       <c r="W83" s="3">
+        <v>500</v>
+      </c>
+      <c r="X83" s="3">
         <v>400</v>
       </c>
-      <c r="X83" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y83" s="3" t="s">
         <v>3</v>
       </c>
@@ -6686,8 +6885,8 @@
       <c r="AB83" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="AC83" s="3">
-        <v>0</v>
+      <c r="AC83" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="AD83" s="3">
         <v>0</v>
@@ -6695,8 +6894,11 @@
       <c r="AE83" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="84" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF83" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -6784,8 +6986,11 @@
       <c r="AE84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -6873,8 +7078,11 @@
       <c r="AE85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -6962,8 +7170,11 @@
       <c r="AE86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -7051,8 +7262,11 @@
       <c r="AE87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -7140,28 +7354,31 @@
       <c r="AE88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
-      <c r="D89" s="3">
-        <v>-19800</v>
-      </c>
-      <c r="E89" s="3">
-        <v>55100</v>
-      </c>
-      <c r="F89" s="3">
-        <v>-103300</v>
-      </c>
-      <c r="G89" s="3">
-        <v>22800</v>
-      </c>
-      <c r="H89" s="3">
-        <v>-42900</v>
-      </c>
-      <c r="I89" s="3">
-        <v>61600</v>
+      <c r="D89" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E89" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F89" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G89" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H89" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I89" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="J89" s="3" t="s">
         <v>3</v>
@@ -7172,42 +7389,42 @@
       <c r="L89" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M89" s="3">
+      <c r="M89" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N89" s="3">
         <v>58800</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>-185900</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>89400</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>35400</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>72100</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>-147200</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>87400</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>21000</v>
       </c>
-      <c r="U89" s="3">
-        <v>0</v>
-      </c>
       <c r="V89" s="3">
+        <v>0</v>
+      </c>
+      <c r="W89" s="3">
         <v>-48300</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>21900</v>
       </c>
-      <c r="X89" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y89" s="3" t="s">
         <v>3</v>
       </c>
@@ -7220,8 +7437,8 @@
       <c r="AB89" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="AC89" s="3">
-        <v>0</v>
+      <c r="AC89" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="AD89" s="3">
         <v>0</v>
@@ -7229,8 +7446,11 @@
       <c r="AE89" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="90" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF89" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="90" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -7262,64 +7482,65 @@
       <c r="AC90" s="3"/>
       <c r="AD90" s="3"/>
       <c r="AE90" s="3"/>
-    </row>
-    <row r="91" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF90" s="3"/>
+    </row>
+    <row r="91" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
-      <c r="D91" s="3">
-        <v>-1300</v>
-      </c>
-      <c r="E91" s="3">
-        <v>-2500</v>
-      </c>
-      <c r="F91" s="3">
-        <v>-13200</v>
-      </c>
-      <c r="G91" s="3">
+      <c r="D91" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E91" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F91" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G91" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H91" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I91" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J91" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="K91" s="3">
+        <v>-62200</v>
+      </c>
+      <c r="L91" s="3">
+        <v>-6500</v>
+      </c>
+      <c r="M91" s="3">
+        <v>-17900</v>
+      </c>
+      <c r="N91" s="3">
+        <v>-3400</v>
+      </c>
+      <c r="O91" s="3">
         <v>-1900</v>
       </c>
-      <c r="H91" s="3">
-        <v>-6100</v>
-      </c>
-      <c r="I91" s="3">
-        <v>-500</v>
-      </c>
-      <c r="J91" s="3">
-        <v>-62200</v>
-      </c>
-      <c r="K91" s="3">
-        <v>-6500</v>
-      </c>
-      <c r="L91" s="3">
-        <v>-17900</v>
-      </c>
-      <c r="M91" s="3">
-        <v>-3400</v>
-      </c>
-      <c r="N91" s="3">
-        <v>-1900</v>
-      </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-11400</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-15900</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-1600</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-2200</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-1800</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-600</v>
-      </c>
-      <c r="U91" s="3">
-        <v>-700</v>
       </c>
       <c r="V91" s="3">
         <v>-700</v>
@@ -7327,8 +7548,8 @@
       <c r="W91" s="3">
         <v>-700</v>
       </c>
-      <c r="X91" s="3" t="s">
-        <v>3</v>
+      <c r="X91" s="3">
+        <v>-700</v>
       </c>
       <c r="Y91" s="3" t="s">
         <v>3</v>
@@ -7342,8 +7563,8 @@
       <c r="AB91" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="AC91" s="3">
-        <v>0</v>
+      <c r="AC91" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="AD91" s="3">
         <v>0</v>
@@ -7351,8 +7572,11 @@
       <c r="AE91" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="92" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF91" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -7440,8 +7664,11 @@
       <c r="AE92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -7529,8 +7756,11 @@
       <c r="AE93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
@@ -7540,8 +7770,8 @@
       <c r="E94" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="F94" s="3">
-        <v>-1900</v>
+      <c r="F94" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="G94" s="3" t="s">
         <v>3</v>
@@ -7558,8 +7788,8 @@
       <c r="K94" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L94" s="3">
-        <v>0</v>
+      <c r="L94" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="M94" s="3">
         <v>0</v>
@@ -7618,8 +7848,11 @@
       <c r="AE94" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="95" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF94" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="95" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -7651,31 +7884,32 @@
       <c r="AC95" s="3"/>
       <c r="AD95" s="3"/>
       <c r="AE95" s="3"/>
-    </row>
-    <row r="96" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF95" s="3"/>
+    </row>
+    <row r="96" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
-      <c r="D96" s="3">
-        <v>0</v>
-      </c>
-      <c r="E96" s="3">
-        <v>0</v>
-      </c>
-      <c r="F96" s="3">
-        <v>0</v>
-      </c>
-      <c r="G96" s="3">
-        <v>0</v>
-      </c>
-      <c r="H96" s="3">
-        <v>0</v>
-      </c>
-      <c r="I96" s="3">
-        <v>0</v>
-      </c>
-      <c r="J96" s="3">
-        <v>0</v>
+      <c r="D96" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E96" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F96" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G96" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H96" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I96" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J96" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K96" s="3">
         <v>0</v>
@@ -7740,8 +7974,11 @@
       <c r="AE96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -7829,8 +8066,11 @@
       <c r="AE97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -7918,8 +8158,11 @@
       <c r="AE98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -8007,31 +8250,34 @@
       <c r="AE99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
-      <c r="D100" s="3">
-        <v>0</v>
-      </c>
-      <c r="E100" s="3">
-        <v>0</v>
-      </c>
-      <c r="F100" s="3">
-        <v>0</v>
-      </c>
-      <c r="G100" s="3">
-        <v>0</v>
-      </c>
-      <c r="H100" s="3">
-        <v>0</v>
-      </c>
-      <c r="I100" s="3">
-        <v>0</v>
-      </c>
-      <c r="J100" s="3">
-        <v>0</v>
+      <c r="D100" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E100" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F100" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G100" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H100" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I100" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J100" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K100" s="3">
         <v>0</v>
@@ -8096,31 +8342,34 @@
       <c r="AE100" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="101" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF100" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="101" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
-      <c r="D101" s="3">
-        <v>0</v>
-      </c>
-      <c r="E101" s="3">
-        <v>0</v>
-      </c>
-      <c r="F101" s="3">
-        <v>0</v>
-      </c>
-      <c r="G101" s="3">
-        <v>0</v>
-      </c>
-      <c r="H101" s="3">
-        <v>0</v>
-      </c>
-      <c r="I101" s="3">
-        <v>0</v>
-      </c>
-      <c r="J101" s="3">
-        <v>0</v>
+      <c r="D101" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E101" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F101" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G101" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H101" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I101" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J101" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K101" s="3">
         <v>0</v>
@@ -8185,31 +8434,34 @@
       <c r="AE101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
-      <c r="D102" s="3">
-        <v>0</v>
-      </c>
-      <c r="E102" s="3">
-        <v>0</v>
-      </c>
-      <c r="F102" s="3">
-        <v>0</v>
-      </c>
-      <c r="G102" s="3">
-        <v>0</v>
-      </c>
-      <c r="H102" s="3">
-        <v>0</v>
-      </c>
-      <c r="I102" s="3">
-        <v>0</v>
-      </c>
-      <c r="J102" s="3">
-        <v>0</v>
+      <c r="D102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J102" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K102" s="3">
         <v>0</v>
@@ -8272,6 +8524,9 @@
         <v>0</v>
       </c>
       <c r="AE102" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF102" s="3">
         <v>0</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/DAO_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/DAO_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="387" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="397" uniqueCount="92">
   <si>
     <t>DAO</t>
   </si>
@@ -656,416 +656,428 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AF102"/>
+  <dimension ref="A5:AG102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="6.42578125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="16" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="20" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="24" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="28" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="32" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="33" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="21" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="25" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="29" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="33" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="34" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:33" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:33" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E7" s="2">
         <v>45565</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45473</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45382</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45291</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45199</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45107</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45016</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44926</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44834</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44742</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44651</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44561</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44469</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44377</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44286</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44196</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44104</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>44012</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>43921</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>43830</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43738</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>43646</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43555</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43465</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43373</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43281</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>43190</v>
       </c>
-      <c r="AE7" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="AF7" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="8" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AG7" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D8" s="3">
+        <v>183600</v>
+      </c>
+      <c r="E8" s="3">
         <v>224200</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>181900</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>192800</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>208800</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>210900</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>166400</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>169300</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>205000</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>193800</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>132900</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>165800</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>554500</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>197200</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>139300</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>132000</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>64900</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>132000</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>91800</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>84800</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>63200</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>53300</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>49300</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>34300</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>33400</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>25300</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AD8" s="3">
         <v>27000</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AE8" s="3">
         <v>19300</v>
       </c>
-      <c r="AE8" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AF8" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="9" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AG8" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="9" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D9" s="3">
+        <v>95800</v>
+      </c>
+      <c r="E9" s="3">
         <v>111600</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>94300</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>98400</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>104600</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>93100</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>88200</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>81700</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>95800</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>88700</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>76000</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>77100</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>279900</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>85500</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>68200</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>62900</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>120900</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>71400</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>50400</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>47900</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>44300</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Y9" s="3">
         <v>39500</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="Z9" s="3">
         <v>33100</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AA9" s="3">
         <v>26300</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AB9" s="3">
         <v>23500</v>
       </c>
-      <c r="AB9" s="3">
+      <c r="AC9" s="3">
         <v>19400</v>
       </c>
-      <c r="AC9" s="3">
+      <c r="AD9" s="3">
         <v>17200</v>
       </c>
-      <c r="AD9" s="3">
+      <c r="AE9" s="3">
         <v>13900</v>
       </c>
-      <c r="AE9" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AF9" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="10" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AG9" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
+        <v>87800</v>
+      </c>
+      <c r="E10" s="3">
         <v>112500</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>87600</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>94400</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>104200</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>117800</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>78200</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>87600</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>109200</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>105000</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>57000</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>88600</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>274600</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>111700</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>71100</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>69100</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>-56100</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>60600</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>41500</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>36900</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>18800</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Y10" s="3">
         <v>13700</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="Z10" s="3">
         <v>16200</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AA10" s="3">
         <v>8000</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AB10" s="3">
         <v>9900</v>
       </c>
-      <c r="AB10" s="3">
+      <c r="AC10" s="3">
         <v>5900</v>
       </c>
-      <c r="AC10" s="3">
+      <c r="AD10" s="3">
         <v>9800</v>
       </c>
-      <c r="AD10" s="3">
+      <c r="AE10" s="3">
         <v>5400</v>
       </c>
-      <c r="AE10" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AF10" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="11" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AG10" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -1098,100 +1110,104 @@
       <c r="AD11" s="3"/>
       <c r="AE11" s="3"/>
       <c r="AF11" s="3"/>
-    </row>
-    <row r="12" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AG11" s="3"/>
+    </row>
+    <row r="12" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D12" s="3">
+        <v>16500</v>
+      </c>
+      <c r="E12" s="3">
         <v>17000</v>
       </c>
-      <c r="E12" s="3">
+      <c r="F12" s="3">
         <v>21100</v>
       </c>
-      <c r="F12" s="3">
+      <c r="G12" s="3">
         <v>20300</v>
       </c>
-      <c r="G12" s="3">
+      <c r="H12" s="3">
         <v>23700</v>
       </c>
-      <c r="H12" s="3">
+      <c r="I12" s="3">
         <v>25700</v>
       </c>
-      <c r="I12" s="3">
+      <c r="J12" s="3">
         <v>28300</v>
       </c>
-      <c r="J12" s="3">
+      <c r="K12" s="3">
         <v>26600</v>
       </c>
-      <c r="K12" s="3">
+      <c r="L12" s="3">
         <v>25300</v>
       </c>
-      <c r="L12" s="3">
+      <c r="M12" s="3">
         <v>29400</v>
       </c>
-      <c r="M12" s="3">
+      <c r="N12" s="3">
         <v>29000</v>
       </c>
-      <c r="N12" s="3">
+      <c r="O12" s="3">
         <v>28000</v>
       </c>
-      <c r="O12" s="3">
+      <c r="P12" s="3">
         <v>83900</v>
       </c>
-      <c r="P12" s="3">
+      <c r="Q12" s="3">
         <v>27500</v>
       </c>
-      <c r="Q12" s="3">
+      <c r="R12" s="3">
         <v>20700</v>
       </c>
-      <c r="R12" s="3">
+      <c r="S12" s="3">
         <v>17800</v>
       </c>
-      <c r="S12" s="3">
+      <c r="T12" s="3">
         <v>10500</v>
       </c>
-      <c r="T12" s="3">
+      <c r="U12" s="3">
         <v>17800</v>
       </c>
-      <c r="U12" s="3">
+      <c r="V12" s="3">
         <v>13500</v>
       </c>
-      <c r="V12" s="3">
+      <c r="W12" s="3">
         <v>13200</v>
       </c>
-      <c r="W12" s="3">
+      <c r="X12" s="3">
         <v>13700</v>
       </c>
-      <c r="X12" s="3">
+      <c r="Y12" s="3">
         <v>11500</v>
       </c>
-      <c r="Y12" s="3">
+      <c r="Z12" s="3">
         <v>8600</v>
       </c>
-      <c r="Z12" s="3">
+      <c r="AA12" s="3">
         <v>8300</v>
       </c>
-      <c r="AA12" s="3">
+      <c r="AB12" s="3">
         <v>7300</v>
       </c>
-      <c r="AB12" s="3">
+      <c r="AC12" s="3">
         <v>7700</v>
       </c>
-      <c r="AC12" s="3">
+      <c r="AD12" s="3">
         <v>5400</v>
       </c>
-      <c r="AD12" s="3">
+      <c r="AE12" s="3">
         <v>6100</v>
       </c>
-      <c r="AE12" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AF12" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="13" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AG12" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1282,8 +1298,11 @@
       <c r="AF13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AG13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -1296,12 +1315,12 @@
       <c r="F14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="G14" s="3">
+      <c r="G14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H14" s="3">
         <v>6100</v>
       </c>
-      <c r="H14" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="I14" s="3" t="s">
         <v>3</v>
       </c>
@@ -1320,12 +1339,12 @@
       <c r="N14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O14" s="3">
+      <c r="O14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P14" s="3">
         <v>7800</v>
       </c>
-      <c r="P14" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q14" s="3" t="s">
         <v>3</v>
       </c>
@@ -1341,8 +1360,8 @@
       <c r="U14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="V14" s="3">
-        <v>0</v>
+      <c r="V14" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="W14" s="3">
         <v>0</v>
@@ -1374,16 +1393,19 @@
       <c r="AF14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AG14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>1000</v>
+      </c>
+      <c r="E15" s="3">
         <v>1100</v>
-      </c>
-      <c r="E15" s="3">
-        <v>1000</v>
       </c>
       <c r="F15" s="3">
         <v>1000</v>
@@ -1392,16 +1414,16 @@
         <v>1000</v>
       </c>
       <c r="H15" s="3">
+        <v>1000</v>
+      </c>
+      <c r="I15" s="3">
         <v>1400</v>
-      </c>
-      <c r="I15" s="3">
-        <v>1500</v>
       </c>
       <c r="J15" s="3">
         <v>1500</v>
       </c>
       <c r="K15" s="3">
-        <v>0</v>
+        <v>1500</v>
       </c>
       <c r="L15" s="3">
         <v>0</v>
@@ -1466,8 +1488,11 @@
       <c r="AF15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AG15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:33" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1497,192 +1522,199 @@
       <c r="AD16" s="3"/>
       <c r="AE16" s="3"/>
       <c r="AF16" s="3"/>
-    </row>
-    <row r="17" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG16" s="3"/>
+    </row>
+    <row r="17" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>172000</v>
+      </c>
+      <c r="E17" s="3">
         <v>208900</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>191900</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>188600</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>198000</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>218800</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>206200</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>197800</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>201500</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>224000</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>196200</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>183000</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>684700</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>215600</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>175500</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>161800</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>-4900</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>263800</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>133600</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>112300</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>94600</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>89400</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>62000</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>46400</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>40700</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>37800</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>31300</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>26700</v>
       </c>
-      <c r="AE17" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AF17" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="18" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG17" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>11500</v>
+      </c>
+      <c r="E18" s="3">
         <v>15300</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>-10000</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>4100</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>10800</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>-7900</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>-39900</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>-28500</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>3500</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>-30300</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>-63300</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>-17300</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>-130200</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>-18400</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>-36200</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>-29800</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>69800</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>-131700</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>-41700</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>-27600</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>-31400</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>-36100</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>-12700</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>-12000</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>-7300</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>-12400</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>-4400</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AE18" s="3">
         <v>-7500</v>
       </c>
-      <c r="AE18" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AF18" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="19" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG18" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1715,169 +1747,173 @@
       <c r="AD19" s="3"/>
       <c r="AE19" s="3"/>
       <c r="AF19" s="3"/>
-    </row>
-    <row r="20" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG19" s="3"/>
+    </row>
+    <row r="20" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>-200</v>
+      </c>
+      <c r="E20" s="3">
         <v>300</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>100</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>-400</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>-5700</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>2900</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>-800</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>-900</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>1000</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>6100</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>700</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>5300</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>7700</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>900</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>4300</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>500</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>700</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>2400</v>
       </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3">
         <v>3700</v>
       </c>
-      <c r="V20" s="3">
+      <c r="W20" s="3">
         <v>1400</v>
       </c>
-      <c r="W20" s="3">
+      <c r="X20" s="3">
         <v>200</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Y20" s="3">
         <v>800</v>
       </c>
-      <c r="Y20" s="3">
+      <c r="Z20" s="3">
         <v>1200</v>
       </c>
-      <c r="Z20" s="3">
+      <c r="AA20" s="3">
         <v>-1800</v>
       </c>
-      <c r="AA20" s="3">
+      <c r="AB20" s="3">
         <v>-800</v>
       </c>
-      <c r="AB20" s="3">
+      <c r="AC20" s="3">
         <v>3200</v>
       </c>
-      <c r="AC20" s="3">
+      <c r="AD20" s="3">
         <v>1700</v>
       </c>
-      <c r="AD20" s="3">
+      <c r="AE20" s="3">
         <v>-1100</v>
       </c>
-      <c r="AE20" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AF20" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="21" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG20" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>12800</v>
+      </c>
+      <c r="E21" s="3">
         <v>16100</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>-9100</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>5600</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>17500</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>-9400</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>-37600</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>-26000</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>6100</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>-22600</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>-61100</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>-10900</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>-118400</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>-16400</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>-31100</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>-28600</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>71200</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>-128700</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>-37500</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>-25600</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>-30700</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>-35000</v>
       </c>
-      <c r="Y21" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z21" s="3" t="s">
         <v>3</v>
       </c>
@@ -1887,61 +1923,64 @@
       <c r="AB21" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AC21" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AD21" s="3">
         <v>-2300</v>
       </c>
-      <c r="AD21" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AE21" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AF21" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="22" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG21" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="22" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>2300</v>
+      </c>
+      <c r="E22" s="3">
         <v>2200</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
         <v>2900</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>2800</v>
       </c>
-      <c r="G22" s="3">
+      <c r="H22" s="3">
         <v>2700</v>
-      </c>
-      <c r="H22" s="3">
-        <v>2400</v>
       </c>
       <c r="I22" s="3">
         <v>2400</v>
       </c>
       <c r="J22" s="3">
+        <v>2400</v>
+      </c>
+      <c r="K22" s="3">
         <v>2300</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>2100</v>
       </c>
-      <c r="L22" s="3">
+      <c r="M22" s="3">
         <v>1700</v>
       </c>
-      <c r="M22" s="3">
+      <c r="N22" s="3">
         <v>1400</v>
       </c>
-      <c r="N22" s="3">
+      <c r="O22" s="3">
         <v>1200</v>
       </c>
-      <c r="O22" s="3">
+      <c r="P22" s="3">
         <v>4400</v>
-      </c>
-      <c r="P22" s="3">
-        <v>1100</v>
       </c>
       <c r="Q22" s="3">
         <v>1100</v>
@@ -1949,8 +1988,8 @@
       <c r="R22" s="3">
         <v>1100</v>
       </c>
-      <c r="S22" s="3" t="s">
-        <v>3</v>
+      <c r="S22" s="3">
+        <v>1100</v>
       </c>
       <c r="T22" s="3" t="s">
         <v>3</v>
@@ -1967,8 +2006,8 @@
       <c r="X22" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Y22" s="3">
-        <v>0</v>
+      <c r="Y22" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="Z22" s="3">
         <v>0</v>
@@ -1991,165 +2030,171 @@
       <c r="AF22" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>9600</v>
+      </c>
+      <c r="E23" s="3">
         <v>13000</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>-12800</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>1900</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>8000</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>-12900</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>-41100</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>-29500</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>2400</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>-25900</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>-63900</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>-13200</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>-127000</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>-18600</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>-33100</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>-30400</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>70600</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>-129400</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>-38000</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>-26200</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>-31200</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>-35400</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>-11500</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>-13900</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>-8100</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>-9300</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>-2600</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>-8500</v>
       </c>
-      <c r="AE23" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AF23" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="24" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG23" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="24" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>-300</v>
+      </c>
+      <c r="E24" s="3">
         <v>300</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>1000</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>-100</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>100</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>400</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>700</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>500</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>2000</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>-200</v>
-      </c>
-      <c r="M24" s="3">
-        <v>100</v>
       </c>
       <c r="N24" s="3">
         <v>100</v>
       </c>
       <c r="O24" s="3">
+        <v>100</v>
+      </c>
+      <c r="P24" s="3">
         <v>900</v>
-      </c>
-      <c r="P24" s="3">
-        <v>400</v>
       </c>
       <c r="Q24" s="3">
         <v>400</v>
       </c>
       <c r="R24" s="3">
+        <v>400</v>
+      </c>
+      <c r="S24" s="3">
         <v>200</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>100</v>
       </c>
-      <c r="T24" s="3">
-        <v>0</v>
-      </c>
       <c r="U24" s="3">
         <v>0</v>
       </c>
       <c r="V24" s="3">
+        <v>0</v>
+      </c>
+      <c r="W24" s="3">
         <v>300</v>
       </c>
-      <c r="W24" s="3">
-        <v>0</v>
-      </c>
       <c r="X24" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="Y24" s="3">
         <v>100</v>
@@ -2158,25 +2203,28 @@
         <v>100</v>
       </c>
       <c r="AA24" s="3">
-        <v>500</v>
+        <v>100</v>
       </c>
       <c r="AB24" s="3">
         <v>500</v>
       </c>
       <c r="AC24" s="3">
+        <v>500</v>
+      </c>
+      <c r="AD24" s="3">
         <v>200</v>
       </c>
-      <c r="AD24" s="3">
+      <c r="AE24" s="3">
         <v>500</v>
       </c>
-      <c r="AE24" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AF24" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="25" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG24" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="25" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2267,192 +2315,201 @@
       <c r="AF25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>9900</v>
+      </c>
+      <c r="E26" s="3">
         <v>12700</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>-13800</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>2000</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>7900</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>-13300</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>-41800</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>-30000</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>400</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>-25700</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>-64000</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>-13300</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>-127900</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>-18900</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>-33500</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>-30600</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>70500</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>-129400</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>-38000</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>-26500</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>-31200</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>-35500</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>-11600</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>-14000</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>-8600</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>-9800</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>-2800</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AE26" s="3">
         <v>-9000</v>
       </c>
-      <c r="AE26" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AF26" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="27" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG26" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="27" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>11400</v>
+      </c>
+      <c r="E27" s="3">
         <v>12300</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>-13700</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>1700</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>8000</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>-14100</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>-41300</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>-29700</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>1700</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>-25400</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>-63100</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>-13200</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>-123600</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>-18300</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>-33400</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>-30500</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>70500</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>-129400</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>-38000</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>-26500</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>-31700</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>-37300</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>-13400</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>-15500</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>-10200</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>-11200</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>-4200</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AE27" s="3">
         <v>-8900</v>
       </c>
-      <c r="AE27" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AF27" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="28" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG27" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="28" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2543,8 +2600,11 @@
       <c r="AF28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2579,31 +2639,31 @@
         <v>0</v>
       </c>
       <c r="N29" s="3">
+        <v>0</v>
+      </c>
+      <c r="O29" s="3">
         <v>-800</v>
       </c>
-      <c r="O29" s="3">
+      <c r="P29" s="3">
         <v>-13800</v>
       </c>
-      <c r="P29" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Q29" s="3">
+      <c r="Q29" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R29" s="3">
         <v>-41200</v>
       </c>
-      <c r="R29" s="3">
+      <c r="S29" s="3">
         <v>-14800</v>
       </c>
-      <c r="S29" s="3">
+      <c r="T29" s="3">
         <v>-132800</v>
       </c>
-      <c r="T29" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U29" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="V29" s="3">
-        <v>0</v>
+      <c r="V29" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="W29" s="3">
         <v>0</v>
@@ -2635,8 +2695,11 @@
       <c r="AF29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2727,8 +2790,11 @@
       <c r="AF30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2819,192 +2885,201 @@
       <c r="AF31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>200</v>
+      </c>
+      <c r="E32" s="3">
         <v>-300</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>-100</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>400</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>5700</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>-2900</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>800</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>900</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>-1000</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>-6100</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>-700</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>-5300</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>-7700</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>-900</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>-4300</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>-500</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>-700</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>-2400</v>
       </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3">
         <v>-3700</v>
       </c>
-      <c r="V32" s="3">
+      <c r="W32" s="3">
         <v>-1400</v>
       </c>
-      <c r="W32" s="3">
+      <c r="X32" s="3">
         <v>-200</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Y32" s="3">
         <v>-800</v>
       </c>
-      <c r="Y32" s="3">
+      <c r="Z32" s="3">
         <v>-1200</v>
       </c>
-      <c r="Z32" s="3">
+      <c r="AA32" s="3">
         <v>1800</v>
       </c>
-      <c r="AA32" s="3">
+      <c r="AB32" s="3">
         <v>800</v>
       </c>
-      <c r="AB32" s="3">
+      <c r="AC32" s="3">
         <v>-3200</v>
       </c>
-      <c r="AC32" s="3">
+      <c r="AD32" s="3">
         <v>-1700</v>
       </c>
-      <c r="AD32" s="3">
+      <c r="AE32" s="3">
         <v>1100</v>
       </c>
-      <c r="AE32" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AF32" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="33" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG32" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="33" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>11400</v>
+      </c>
+      <c r="E33" s="3">
         <v>12300</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>-13700</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>1700</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>8000</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>-14100</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>-41300</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>-29700</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>1700</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>-25400</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>-63100</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>-14000</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>-137500</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>-18300</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>-74500</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>-45400</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>-62300</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>-129400</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>-38000</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>-26500</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>-31700</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>-37300</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>-13400</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>-15500</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>-10200</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>-11200</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>-4200</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3">
         <v>-8900</v>
       </c>
-      <c r="AE33" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AF33" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="34" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG33" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="34" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3095,197 +3170,206 @@
       <c r="AF34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>11400</v>
+      </c>
+      <c r="E35" s="3">
         <v>12300</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>-13700</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>1700</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>8000</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>-14100</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>-41300</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>-29700</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>1700</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>-25400</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>-63100</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>-14000</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>-137500</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>-18300</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>-74500</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>-45400</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>-62300</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>-129400</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>-38000</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>-26500</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>-31700</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>-37300</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>-13400</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>-15500</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>-10200</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>-11200</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>-4200</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3">
         <v>-8900</v>
       </c>
-      <c r="AE35" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AF35" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="37" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG35" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="37" spans="2:33" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E38" s="2">
         <v>45565</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45473</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45382</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45291</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45199</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45107</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45016</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44926</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44834</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44742</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44651</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44561</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44469</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44377</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44286</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44196</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44104</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>44012</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>43921</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>43830</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43738</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>43646</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43555</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43465</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43373</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43281</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>43190</v>
       </c>
-      <c r="AE38" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="AF38" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="39" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG38" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="39" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3318,8 +3402,9 @@
       <c r="AD39" s="3"/>
       <c r="AE39" s="3"/>
       <c r="AF39" s="3"/>
-    </row>
-    <row r="40" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG39" s="3"/>
+    </row>
+    <row r="40" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3352,80 +3437,81 @@
       <c r="AD40" s="3"/>
       <c r="AE40" s="3"/>
       <c r="AF40" s="3"/>
-    </row>
-    <row r="41" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG40" s="3"/>
+    </row>
+    <row r="41" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>81200</v>
+      </c>
+      <c r="E41" s="3">
         <v>60000</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>68900</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>36400</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>64100</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>46300</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>90700</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>84300</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>110500</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>98400</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>95500</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>57300</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>44600</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>70200</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>117900</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>257300</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>84800</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>11500</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>18500</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>20100</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>26700</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>8500</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>8000</v>
       </c>
-      <c r="Z41" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AA41" s="3" t="s">
         <v>3</v>
       </c>
@@ -3444,80 +3530,83 @@
       <c r="AF41" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="42" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG41" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="42" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>8600</v>
+      </c>
+      <c r="E42" s="3">
         <v>9000</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
         <v>8600</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>8700</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>10200</v>
-      </c>
-      <c r="H42" s="3">
-        <v>3000</v>
       </c>
       <c r="I42" s="3">
         <v>3000</v>
       </c>
       <c r="J42" s="3">
+        <v>3000</v>
+      </c>
+      <c r="K42" s="3">
         <v>3200</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>32800</v>
-      </c>
-      <c r="L42" s="3">
-        <v>3000</v>
       </c>
       <c r="M42" s="3">
         <v>3000</v>
       </c>
       <c r="N42" s="3">
+        <v>3000</v>
+      </c>
+      <c r="O42" s="3">
         <v>900</v>
       </c>
-      <c r="O42" s="3">
+      <c r="P42" s="3">
         <v>69600</v>
       </c>
-      <c r="P42" s="3">
+      <c r="Q42" s="3">
         <v>58300</v>
       </c>
-      <c r="Q42" s="3">
+      <c r="R42" s="3">
         <v>146500</v>
       </c>
-      <c r="R42" s="3">
+      <c r="S42" s="3">
         <v>47000</v>
       </c>
-      <c r="S42" s="3">
+      <c r="T42" s="3">
         <v>81500</v>
       </c>
-      <c r="T42" s="3">
+      <c r="U42" s="3">
         <v>155400</v>
       </c>
-      <c r="U42" s="3">
+      <c r="V42" s="3">
         <v>245400</v>
       </c>
-      <c r="V42" s="3">
+      <c r="W42" s="3">
         <v>242400</v>
       </c>
-      <c r="W42" s="3">
+      <c r="X42" s="3">
         <v>222800</v>
       </c>
-      <c r="X42" s="3">
+      <c r="Y42" s="3">
         <v>16200</v>
       </c>
-      <c r="Y42" s="3">
+      <c r="Z42" s="3">
         <v>38000</v>
       </c>
-      <c r="Z42" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AA42" s="3" t="s">
         <v>3</v>
       </c>
@@ -3536,80 +3625,83 @@
       <c r="AF42" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="43" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG42" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="43" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>68300</v>
+      </c>
+      <c r="E43" s="3">
         <v>70700</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>63500</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>57100</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>56800</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>49400</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>53300</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>39000</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>58200</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>46900</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>49000</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>41500</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>35100</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>35300</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>44300</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>35100</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>38000</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>50100</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>34900</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>36800</v>
       </c>
-      <c r="W43" s="3">
+      <c r="X43" s="3">
         <v>33200</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Y43" s="3">
         <v>27800</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="Z43" s="3">
         <v>31100</v>
       </c>
-      <c r="Z43" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AA43" s="3" t="s">
         <v>3</v>
       </c>
@@ -3628,80 +3720,83 @@
       <c r="AF43" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="44" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG43" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="44" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>23900</v>
+      </c>
+      <c r="E44" s="3">
         <v>25500</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>26900</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>26200</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>30600</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>24300</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>25200</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>31900</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>32700</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>23500</v>
-      </c>
-      <c r="M44" s="3">
-        <v>29500</v>
       </c>
       <c r="N44" s="3">
         <v>29500</v>
       </c>
       <c r="O44" s="3">
+        <v>29500</v>
+      </c>
+      <c r="P44" s="3">
         <v>35300</v>
       </c>
-      <c r="P44" s="3">
+      <c r="Q44" s="3">
         <v>38000</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="R44" s="3">
         <v>38600</v>
       </c>
-      <c r="R44" s="3">
+      <c r="S44" s="3">
         <v>37400</v>
       </c>
-      <c r="S44" s="3">
+      <c r="T44" s="3">
         <v>20700</v>
       </c>
-      <c r="T44" s="3">
+      <c r="U44" s="3">
         <v>13500</v>
       </c>
-      <c r="U44" s="3">
+      <c r="V44" s="3">
         <v>13700</v>
       </c>
-      <c r="V44" s="3">
+      <c r="W44" s="3">
         <v>10300</v>
       </c>
-      <c r="W44" s="3">
+      <c r="X44" s="3">
         <v>11300</v>
       </c>
-      <c r="X44" s="3">
+      <c r="Y44" s="3">
         <v>8100</v>
       </c>
-      <c r="Y44" s="3">
+      <c r="Z44" s="3">
         <v>5000</v>
       </c>
-      <c r="Z44" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AA44" s="3" t="s">
         <v>3</v>
       </c>
@@ -3720,80 +3815,83 @@
       <c r="AF44" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="45" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG44" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="45" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>21100</v>
+      </c>
+      <c r="E45" s="3">
         <v>23300</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>24300</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>27100</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>12600</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>31900</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>26700</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>25700</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>29400</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>59700</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>104200</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>129100</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>128800</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>85400</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>33100</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>27600</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>32800</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>29600</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>17500</v>
-      </c>
-      <c r="V45" s="3">
-        <v>18600</v>
       </c>
       <c r="W45" s="3">
         <v>18600</v>
       </c>
       <c r="X45" s="3">
+        <v>18600</v>
+      </c>
+      <c r="Y45" s="3">
         <v>16200</v>
       </c>
-      <c r="Y45" s="3">
+      <c r="Z45" s="3">
         <v>11300</v>
       </c>
-      <c r="Z45" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AA45" s="3" t="s">
         <v>3</v>
       </c>
@@ -3812,80 +3910,83 @@
       <c r="AF45" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="46" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG45" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="46" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>203700</v>
+      </c>
+      <c r="E46" s="3">
         <v>188800</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>192500</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>155600</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>183300</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>155000</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>198900</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>184100</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>263600</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>231500</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>281200</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>258300</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>313400</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>287200</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>380400</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>404400</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>257700</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>260200</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>330000</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>328200</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>312600</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Y46" s="3">
         <v>76800</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="Z46" s="3">
         <v>93400</v>
       </c>
-      <c r="Z46" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AA46" s="3" t="s">
         <v>3</v>
       </c>
@@ -3904,62 +4005,65 @@
       <c r="AF46" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="47" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG46" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="47" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>9900</v>
+      </c>
+      <c r="E47" s="3">
         <v>10600</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>10700</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>6800</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>7200</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>8800</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>12100</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>13200</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>12800</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>9300</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>9800</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>3800</v>
       </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>4500</v>
       </c>
-      <c r="P47" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q47" s="3" t="s">
         <v>3</v>
       </c>
       <c r="R47" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="S47" s="3">
+      <c r="S47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="T47" s="3">
         <v>5900</v>
       </c>
-      <c r="T47" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U47" s="3" t="s">
         <v>3</v>
       </c>
@@ -3972,8 +4076,8 @@
       <c r="X47" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Y47" s="3">
-        <v>0</v>
+      <c r="Y47" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="Z47" s="3">
         <v>0</v>
@@ -3996,80 +4100,83 @@
       <c r="AF47" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>15800</v>
+      </c>
+      <c r="E48" s="3">
         <v>18800</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>20500</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>21500</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>22600</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>23700</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>23100</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>23200</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>24000</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>25700</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>27400</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>28300</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>27400</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>31400</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>28600</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>21000</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>21100</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>18100</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>11900</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>7600</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>7500</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>6100</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="Z48" s="3">
         <v>3500</v>
       </c>
-      <c r="Z48" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AA48" s="3" t="s">
         <v>3</v>
       </c>
@@ -4088,49 +4195,52 @@
       <c r="AF48" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="49" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG48" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="49" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>15100</v>
+      </c>
+      <c r="E49" s="3">
         <v>15700</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>15100</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>15200</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>15500</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>15100</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>15200</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>16000</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>15500</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>15200</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>15300</v>
-      </c>
-      <c r="N49" s="3">
-        <v>15200</v>
       </c>
       <c r="O49" s="3">
         <v>15200</v>
       </c>
-      <c r="P49" s="3" t="s">
-        <v>3</v>
+      <c r="P49" s="3">
+        <v>15200</v>
       </c>
       <c r="Q49" s="3" t="s">
         <v>3</v>
@@ -4147,8 +4257,8 @@
       <c r="U49" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="V49" s="3">
-        <v>0</v>
+      <c r="V49" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="W49" s="3">
         <v>0</v>
@@ -4180,8 +4290,11 @@
       <c r="AF49" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="50" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG49" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4272,8 +4385,11 @@
       <c r="AF50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4364,79 +4480,82 @@
       <c r="AF51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>4100</v>
+      </c>
+      <c r="E52" s="3">
         <v>6100</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>6400</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>7700</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>6300</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>6400</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>5300</v>
-      </c>
-      <c r="J52" s="3">
-        <v>4900</v>
       </c>
       <c r="K52" s="3">
         <v>4900</v>
       </c>
       <c r="L52" s="3">
+        <v>4900</v>
+      </c>
+      <c r="M52" s="3">
         <v>5300</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>5200</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>5000</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>3200</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>30000</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>14700</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>11000</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>3400</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>3900</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>3200</v>
       </c>
-      <c r="V52" s="3">
+      <c r="W52" s="3">
         <v>2100</v>
       </c>
-      <c r="W52" s="3">
+      <c r="X52" s="3">
         <v>1300</v>
-      </c>
-      <c r="X52" s="3">
-        <v>800</v>
       </c>
       <c r="Y52" s="3">
         <v>800</v>
       </c>
-      <c r="Z52" s="3" t="s">
-        <v>3</v>
+      <c r="Z52" s="3">
+        <v>800</v>
       </c>
       <c r="AA52" s="3" t="s">
         <v>3</v>
@@ -4456,8 +4575,11 @@
       <c r="AF52" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="53" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG52" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="53" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -4548,80 +4670,83 @@
       <c r="AF53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>248600</v>
+      </c>
+      <c r="E54" s="3">
         <v>240000</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>245200</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>206900</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>235000</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>209000</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>254500</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>241400</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>320900</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>286900</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>339000</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>310600</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>363700</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>348600</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>423600</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>436300</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>288200</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>282200</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>345100</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>337900</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>321300</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>83700</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>97700</v>
       </c>
-      <c r="Z54" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AA54" s="3" t="s">
         <v>3</v>
       </c>
@@ -4640,8 +4765,11 @@
       <c r="AF54" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="55" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG54" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="55" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -4674,8 +4802,9 @@
       <c r="AD55" s="3"/>
       <c r="AE55" s="3"/>
       <c r="AF55" s="3"/>
-    </row>
-    <row r="56" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG55" s="3"/>
+    </row>
+    <row r="56" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -4708,80 +4837,81 @@
       <c r="AD56" s="3"/>
       <c r="AE56" s="3"/>
       <c r="AF56" s="3"/>
-    </row>
-    <row r="57" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG56" s="3"/>
+    </row>
+    <row r="57" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>22900</v>
+      </c>
+      <c r="E57" s="3">
         <v>33200</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>25400</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>26700</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>34000</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>32000</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>26600</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>30700</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>39800</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>24800</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>21100</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>18400</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>22200</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>16600</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>10600</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>17500</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>19700</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>17600</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>15200</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>14900</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>9700</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Y57" s="3">
         <v>7200</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="Z57" s="3">
         <v>5300</v>
       </c>
-      <c r="Z57" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AA57" s="3" t="s">
         <v>3</v>
       </c>
@@ -4800,80 +4930,83 @@
       <c r="AF57" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="58" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG57" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="58" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>120300</v>
+      </c>
+      <c r="E58" s="3">
         <v>125200</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>120800</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>121600</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>129300</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>120300</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>200800</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>207800</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>123800</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>121300</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>122100</v>
-      </c>
-      <c r="N58" s="3">
-        <v>121200</v>
       </c>
       <c r="O58" s="3">
         <v>121200</v>
       </c>
       <c r="P58" s="3">
-        <v>124800</v>
+        <v>121200</v>
       </c>
       <c r="Q58" s="3">
         <v>124800</v>
       </c>
       <c r="R58" s="3">
-        <v>122200</v>
+        <v>124800</v>
       </c>
       <c r="S58" s="3">
         <v>122200</v>
       </c>
       <c r="T58" s="3">
-        <v>129400</v>
+        <v>122200</v>
       </c>
       <c r="U58" s="3">
         <v>129400</v>
       </c>
       <c r="V58" s="3">
+        <v>129400</v>
+      </c>
+      <c r="W58" s="3">
         <v>137500</v>
-      </c>
-      <c r="W58" s="3">
-        <v>135200</v>
       </c>
       <c r="X58" s="3">
         <v>135200</v>
       </c>
       <c r="Y58" s="3">
+        <v>135200</v>
+      </c>
+      <c r="Z58" s="3">
         <v>134100</v>
       </c>
-      <c r="Z58" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AA58" s="3" t="s">
         <v>3</v>
       </c>
@@ -4892,80 +5025,83 @@
       <c r="AF58" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="59" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG58" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="59" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>136800</v>
+      </c>
+      <c r="E59" s="3">
         <v>127200</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>149500</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>114100</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>156300</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>136900</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>175300</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>130400</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>284500</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>266100</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>298500</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>226700</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>275500</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>293600</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>375700</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>312500</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>330500</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>268200</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>204700</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>157000</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>126000</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>93900</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>76900</v>
       </c>
-      <c r="Z59" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AA59" s="3" t="s">
         <v>3</v>
       </c>
@@ -4984,80 +5120,83 @@
       <c r="AF59" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="60" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG59" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="60" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>403700</v>
+      </c>
+      <c r="E60" s="3">
         <v>413600</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>424800</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>373200</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>437100</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>411700</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>527200</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>480200</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>448100</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>412300</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>441700</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>366300</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>418900</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>435000</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>511100</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>452200</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>472400</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>415100</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>349200</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>309300</v>
       </c>
-      <c r="W60" s="3">
+      <c r="X60" s="3">
         <v>270800</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Y60" s="3">
         <v>236300</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="Z60" s="3">
         <v>216400</v>
       </c>
-      <c r="Z60" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AA60" s="3" t="s">
         <v>3</v>
       </c>
@@ -5076,50 +5215,53 @@
       <c r="AF60" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="61" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG60" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="61" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>128600</v>
+      </c>
+      <c r="E61" s="3">
         <v>133300</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>130400</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>128600</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>95900</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>90300</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>6400</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>5900</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>73600</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>68700</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>65300</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>48200</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>35200</v>
       </c>
-      <c r="P61" s="3">
-        <v>0</v>
-      </c>
       <c r="Q61" s="3">
         <v>0</v>
       </c>
@@ -5168,77 +5310,80 @@
       <c r="AF61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>2500</v>
+      </c>
+      <c r="E62" s="3">
         <v>2600</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>2300</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>2400</v>
-      </c>
-      <c r="G62" s="3">
-        <v>2300</v>
       </c>
       <c r="H62" s="3">
         <v>2300</v>
       </c>
       <c r="I62" s="3">
+        <v>2300</v>
+      </c>
+      <c r="J62" s="3">
         <v>1700</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>1600</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>7400</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>8400</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>8700</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>7700</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>10400</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>15100</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>13800</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>10900</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>11700</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>10300</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>6400</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>3900</v>
       </c>
-      <c r="W62" s="3">
+      <c r="X62" s="3">
         <v>4100</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Y62" s="3">
         <v>2100</v>
       </c>
-      <c r="Y62" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z62" s="3" t="s">
         <v>3</v>
       </c>
@@ -5251,8 +5396,8 @@
       <c r="AC62" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="AD62" s="3">
-        <v>0</v>
+      <c r="AD62" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="AE62" s="3">
         <v>0</v>
@@ -5260,8 +5405,11 @@
       <c r="AF62" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="63" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG62" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="63" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -5352,8 +5500,11 @@
       <c r="AF63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -5444,8 +5595,11 @@
       <c r="AF64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -5536,80 +5690,83 @@
       <c r="AF65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>534800</v>
+      </c>
+      <c r="E66" s="3">
         <v>549500</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>557600</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>504200</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>535200</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>504300</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>535200</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>487800</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>537300</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>498600</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>525300</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>432700</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>475200</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>464600</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>524800</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>463100</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>484200</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>425500</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>355800</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>313400</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>275100</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>238600</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>216600</v>
       </c>
-      <c r="Z66" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AA66" s="3" t="s">
         <v>3</v>
       </c>
@@ -5628,8 +5785,11 @@
       <c r="AF66" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="67" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG66" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="67" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -5662,8 +5822,9 @@
       <c r="AD67" s="3"/>
       <c r="AE67" s="3"/>
       <c r="AF67" s="3"/>
-    </row>
-    <row r="68" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG67" s="3"/>
+    </row>
+    <row r="68" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -5754,8 +5915,11 @@
       <c r="AF68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -5846,8 +6010,11 @@
       <c r="AF69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -5912,14 +6079,14 @@
         <v>0</v>
       </c>
       <c r="X70" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y70" s="3">
         <v>75900</v>
       </c>
-      <c r="Y70" s="3">
+      <c r="Z70" s="3">
         <v>73600</v>
       </c>
-      <c r="Z70" s="3">
-        <v>0</v>
-      </c>
       <c r="AA70" s="3">
         <v>0</v>
       </c>
@@ -5938,8 +6105,11 @@
       <c r="AF70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -6030,8 +6200,11 @@
       <c r="AF71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
@@ -6044,24 +6217,24 @@
       <c r="F72" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="G72" s="3">
+      <c r="G72" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H72" s="3">
         <v>-838200</v>
       </c>
-      <c r="H72" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="I72" s="3" t="s">
         <v>3</v>
       </c>
       <c r="J72" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K72" s="3">
+      <c r="K72" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L72" s="3">
         <v>-760400</v>
       </c>
-      <c r="L72" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M72" s="3" t="s">
         <v>3</v>
       </c>
@@ -6080,30 +6253,30 @@
       <c r="R72" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="S72" s="3">
+      <c r="S72" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="T72" s="3">
         <v>-511000</v>
       </c>
-      <c r="T72" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U72" s="3" t="s">
         <v>3</v>
       </c>
       <c r="V72" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="W72" s="3">
+      <c r="W72" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="X72" s="3">
         <v>-295400</v>
       </c>
-      <c r="X72" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Y72" s="3">
+      <c r="Y72" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Z72" s="3">
         <v>-224700</v>
       </c>
-      <c r="Z72" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AA72" s="3" t="s">
         <v>3</v>
       </c>
@@ -6122,8 +6295,11 @@
       <c r="AF72" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="73" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG72" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="73" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -6214,8 +6390,11 @@
       <c r="AF73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -6306,8 +6485,11 @@
       <c r="AF74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -6398,80 +6580,83 @@
       <c r="AF75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>-293200</v>
+      </c>
+      <c r="E76" s="3">
         <v>-318200</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>-320500</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>-305600</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>-308400</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>-303200</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>-287900</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>-254500</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>-216400</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>-211700</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>-186400</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>-122100</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>-111400</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>-116000</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>-101200</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>-26700</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>-196000</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>-143300</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>-10700</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>24500</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>46200</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>-230800</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>-192500</v>
       </c>
-      <c r="Z76" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AA76" s="3" t="s">
         <v>3</v>
       </c>
@@ -6490,8 +6675,11 @@
       <c r="AF76" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="77" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG76" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="77" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -6582,197 +6770,206 @@
       <c r="AF77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:33" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E80" s="2">
         <v>45565</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45473</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45382</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45291</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45199</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45107</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45016</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44926</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44834</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44742</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44651</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44561</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44469</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44377</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44286</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44196</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44104</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>44012</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>43921</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>43830</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43738</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>43646</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43555</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43465</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43373</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43281</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>43190</v>
       </c>
-      <c r="AE80" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="AF80" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="81" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG80" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="81" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>11400</v>
+      </c>
+      <c r="E81" s="3">
         <v>12300</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>-13700</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>1700</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>8000</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>-14100</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>-41300</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>-29700</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>1700</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>-25400</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>-63100</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>-14000</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>-137500</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>-18300</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>-74500</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>-45400</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>-62300</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>-129400</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>-38000</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>-26500</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>-31700</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>-37300</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>-13400</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>-15500</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>-10200</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>-11200</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>-4200</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3">
         <v>-8900</v>
       </c>
-      <c r="AE81" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AF81" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="82" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG81" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="82" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -6805,8 +7002,9 @@
       <c r="AD82" s="3"/>
       <c r="AE82" s="3"/>
       <c r="AF82" s="3"/>
-    </row>
-    <row r="83" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG82" s="3"/>
+    </row>
+    <row r="83" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
@@ -6831,38 +7029,38 @@
       <c r="J83" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K83" s="3">
-        <v>1600</v>
+      <c r="K83" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="L83" s="3">
         <v>1600</v>
       </c>
       <c r="M83" s="3">
+        <v>1600</v>
+      </c>
+      <c r="N83" s="3">
         <v>1500</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>1100</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>4200</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>1100</v>
-      </c>
-      <c r="Q83" s="3">
-        <v>800</v>
       </c>
       <c r="R83" s="3">
         <v>800</v>
       </c>
       <c r="S83" s="3">
+        <v>800</v>
+      </c>
+      <c r="T83" s="3">
         <v>700</v>
       </c>
-      <c r="T83" s="3">
+      <c r="U83" s="3">
         <v>600</v>
-      </c>
-      <c r="U83" s="3">
-        <v>500</v>
       </c>
       <c r="V83" s="3">
         <v>500</v>
@@ -6871,11 +7069,11 @@
         <v>500</v>
       </c>
       <c r="X83" s="3">
+        <v>500</v>
+      </c>
+      <c r="Y83" s="3">
         <v>400</v>
       </c>
-      <c r="Y83" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z83" s="3" t="s">
         <v>3</v>
       </c>
@@ -6888,8 +7086,8 @@
       <c r="AC83" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="AD83" s="3">
-        <v>0</v>
+      <c r="AD83" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="AE83" s="3">
         <v>0</v>
@@ -6897,8 +7095,11 @@
       <c r="AF83" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="84" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG83" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -6989,8 +7190,11 @@
       <c r="AF84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -7081,8 +7285,11 @@
       <c r="AF85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -7173,8 +7380,11 @@
       <c r="AF86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -7265,8 +7475,11 @@
       <c r="AF87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -7357,8 +7570,11 @@
       <c r="AF88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
@@ -7392,42 +7608,42 @@
       <c r="M89" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N89" s="3">
+      <c r="N89" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O89" s="3">
         <v>58800</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>-185900</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>89400</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>35400</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>72100</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>-147200</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>87400</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>21000</v>
       </c>
-      <c r="V89" s="3">
-        <v>0</v>
-      </c>
       <c r="W89" s="3">
+        <v>0</v>
+      </c>
+      <c r="X89" s="3">
         <v>-48300</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>21900</v>
       </c>
-      <c r="Y89" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z89" s="3" t="s">
         <v>3</v>
       </c>
@@ -7440,8 +7656,8 @@
       <c r="AC89" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="AD89" s="3">
-        <v>0</v>
+      <c r="AD89" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="AE89" s="3">
         <v>0</v>
@@ -7449,8 +7665,11 @@
       <c r="AF89" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="90" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG89" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="90" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -7483,8 +7702,9 @@
       <c r="AD90" s="3"/>
       <c r="AE90" s="3"/>
       <c r="AF90" s="3"/>
-    </row>
-    <row r="91" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG90" s="3"/>
+    </row>
+    <row r="91" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
@@ -7509,41 +7729,41 @@
       <c r="J91" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K91" s="3">
+      <c r="K91" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L91" s="3">
         <v>-62200</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-6500</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-17900</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-3400</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-1900</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-11400</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-15900</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-1600</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-2200</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-1800</v>
       </c>
-      <c r="U91" s="3">
+      <c r="V91" s="3">
         <v>-600</v>
-      </c>
-      <c r="V91" s="3">
-        <v>-700</v>
       </c>
       <c r="W91" s="3">
         <v>-700</v>
@@ -7551,8 +7771,8 @@
       <c r="X91" s="3">
         <v>-700</v>
       </c>
-      <c r="Y91" s="3" t="s">
-        <v>3</v>
+      <c r="Y91" s="3">
+        <v>-700</v>
       </c>
       <c r="Z91" s="3" t="s">
         <v>3</v>
@@ -7566,8 +7786,8 @@
       <c r="AC91" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="AD91" s="3">
-        <v>0</v>
+      <c r="AD91" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="AE91" s="3">
         <v>0</v>
@@ -7575,8 +7795,11 @@
       <c r="AF91" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="92" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG91" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -7667,8 +7890,11 @@
       <c r="AF92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -7759,8 +7985,11 @@
       <c r="AF93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
@@ -7791,8 +8020,8 @@
       <c r="L94" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M94" s="3">
-        <v>0</v>
+      <c r="M94" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="N94" s="3">
         <v>0</v>
@@ -7851,8 +8080,11 @@
       <c r="AF94" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="95" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG94" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="95" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -7885,8 +8117,9 @@
       <c r="AD95" s="3"/>
       <c r="AE95" s="3"/>
       <c r="AF95" s="3"/>
-    </row>
-    <row r="96" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG95" s="3"/>
+    </row>
+    <row r="96" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -7911,8 +8144,8 @@
       <c r="J96" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K96" s="3">
-        <v>0</v>
+      <c r="K96" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="L96" s="3">
         <v>0</v>
@@ -7977,8 +8210,11 @@
       <c r="AF96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -8069,8 +8305,11 @@
       <c r="AF97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -8161,8 +8400,11 @@
       <c r="AF98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -8253,8 +8495,11 @@
       <c r="AF99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
@@ -8279,8 +8524,8 @@
       <c r="J100" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K100" s="3">
-        <v>0</v>
+      <c r="K100" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="L100" s="3">
         <v>0</v>
@@ -8345,8 +8590,11 @@
       <c r="AF100" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="101" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG100" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="101" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -8371,8 +8619,8 @@
       <c r="J101" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K101" s="3">
-        <v>0</v>
+      <c r="K101" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="L101" s="3">
         <v>0</v>
@@ -8437,8 +8685,11 @@
       <c r="AF101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
@@ -8463,8 +8714,8 @@
       <c r="J102" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K102" s="3">
-        <v>0</v>
+      <c r="K102" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="L102" s="3">
         <v>0</v>
@@ -8527,6 +8778,9 @@
         <v>0</v>
       </c>
       <c r="AF102" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG102" s="3">
         <v>0</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/DAO_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/DAO_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="397" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="405" uniqueCount="92">
   <si>
     <t>DAO</t>
   </si>
@@ -656,428 +656,441 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AG102"/>
+  <dimension ref="A5:AH102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="6.42578125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="21" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="25" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="29" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="32" max="33" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="34" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="22" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="26" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="30" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="33" max="34" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="35" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:34" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:34" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45747</v>
+      </c>
+      <c r="E7" s="2">
         <v>45657</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45565</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45473</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45382</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45291</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45199</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45107</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45016</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44926</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44834</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44742</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44651</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44561</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44469</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44377</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44286</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44196</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>44104</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>44012</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>43921</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43830</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>43738</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43646</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43555</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43465</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43373</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>43281</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>43190</v>
       </c>
-      <c r="AF7" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="AG7" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="8" spans="1:33" x14ac:dyDescent="0.2">
+      <c r="AH7" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D8" s="3">
+        <v>178900</v>
+      </c>
+      <c r="E8" s="3">
         <v>183600</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>224200</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>181900</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>192800</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>208800</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>210900</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>166400</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>169300</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>205000</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>193800</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>132900</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>165800</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>554500</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>197200</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>139300</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>132000</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>64900</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>132000</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>91800</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>84800</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>63200</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>53300</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>49300</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>34300</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>33400</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AD8" s="3">
         <v>25300</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AE8" s="3">
         <v>27000</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AF8" s="3">
         <v>19300</v>
       </c>
-      <c r="AF8" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AG8" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="9" spans="1:33" x14ac:dyDescent="0.2">
+      <c r="AH8" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="9" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D9" s="3">
+        <v>94300</v>
+      </c>
+      <c r="E9" s="3">
         <v>95800</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>111600</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>94300</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>98400</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>104600</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>93100</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>88200</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>81700</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>95800</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>88700</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>76000</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>77100</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>279900</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>85500</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>68200</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>62900</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>120900</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>71400</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>50400</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>47900</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Y9" s="3">
         <v>44300</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="Z9" s="3">
         <v>39500</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AA9" s="3">
         <v>33100</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AB9" s="3">
         <v>26300</v>
       </c>
-      <c r="AB9" s="3">
+      <c r="AC9" s="3">
         <v>23500</v>
       </c>
-      <c r="AC9" s="3">
+      <c r="AD9" s="3">
         <v>19400</v>
       </c>
-      <c r="AD9" s="3">
+      <c r="AE9" s="3">
         <v>17200</v>
       </c>
-      <c r="AE9" s="3">
+      <c r="AF9" s="3">
         <v>13900</v>
       </c>
-      <c r="AF9" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AG9" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="10" spans="1:33" x14ac:dyDescent="0.2">
+      <c r="AH9" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
+        <v>84600</v>
+      </c>
+      <c r="E10" s="3">
         <v>87800</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>112500</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>87600</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>94400</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>104200</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>117800</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>78200</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>87600</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>109200</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>105000</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>57000</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>88600</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>274600</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>111700</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>71100</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>69100</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>-56100</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>60600</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>41500</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>36900</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Y10" s="3">
         <v>18800</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="Z10" s="3">
         <v>13700</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AA10" s="3">
         <v>16200</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AB10" s="3">
         <v>8000</v>
       </c>
-      <c r="AB10" s="3">
+      <c r="AC10" s="3">
         <v>9900</v>
       </c>
-      <c r="AC10" s="3">
+      <c r="AD10" s="3">
         <v>5900</v>
       </c>
-      <c r="AD10" s="3">
+      <c r="AE10" s="3">
         <v>9800</v>
       </c>
-      <c r="AE10" s="3">
+      <c r="AF10" s="3">
         <v>5400</v>
       </c>
-      <c r="AF10" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AG10" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="11" spans="1:33" x14ac:dyDescent="0.2">
+      <c r="AH10" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -1111,103 +1124,107 @@
       <c r="AE11" s="3"/>
       <c r="AF11" s="3"/>
       <c r="AG11" s="3"/>
-    </row>
-    <row r="12" spans="1:33" x14ac:dyDescent="0.2">
+      <c r="AH11" s="3"/>
+    </row>
+    <row r="12" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D12" s="3">
+        <v>15900</v>
+      </c>
+      <c r="E12" s="3">
         <v>16500</v>
       </c>
-      <c r="E12" s="3">
+      <c r="F12" s="3">
         <v>17000</v>
       </c>
-      <c r="F12" s="3">
+      <c r="G12" s="3">
         <v>21100</v>
       </c>
-      <c r="G12" s="3">
+      <c r="H12" s="3">
         <v>20300</v>
       </c>
-      <c r="H12" s="3">
+      <c r="I12" s="3">
         <v>23700</v>
       </c>
-      <c r="I12" s="3">
+      <c r="J12" s="3">
         <v>25700</v>
       </c>
-      <c r="J12" s="3">
+      <c r="K12" s="3">
         <v>28300</v>
       </c>
-      <c r="K12" s="3">
+      <c r="L12" s="3">
         <v>26600</v>
       </c>
-      <c r="L12" s="3">
+      <c r="M12" s="3">
         <v>25300</v>
       </c>
-      <c r="M12" s="3">
+      <c r="N12" s="3">
         <v>29400</v>
       </c>
-      <c r="N12" s="3">
+      <c r="O12" s="3">
         <v>29000</v>
       </c>
-      <c r="O12" s="3">
+      <c r="P12" s="3">
         <v>28000</v>
       </c>
-      <c r="P12" s="3">
+      <c r="Q12" s="3">
         <v>83900</v>
       </c>
-      <c r="Q12" s="3">
+      <c r="R12" s="3">
         <v>27500</v>
       </c>
-      <c r="R12" s="3">
+      <c r="S12" s="3">
         <v>20700</v>
       </c>
-      <c r="S12" s="3">
+      <c r="T12" s="3">
         <v>17800</v>
       </c>
-      <c r="T12" s="3">
+      <c r="U12" s="3">
         <v>10500</v>
       </c>
-      <c r="U12" s="3">
+      <c r="V12" s="3">
         <v>17800</v>
       </c>
-      <c r="V12" s="3">
+      <c r="W12" s="3">
         <v>13500</v>
       </c>
-      <c r="W12" s="3">
+      <c r="X12" s="3">
         <v>13200</v>
       </c>
-      <c r="X12" s="3">
+      <c r="Y12" s="3">
         <v>13700</v>
       </c>
-      <c r="Y12" s="3">
+      <c r="Z12" s="3">
         <v>11500</v>
       </c>
-      <c r="Z12" s="3">
+      <c r="AA12" s="3">
         <v>8600</v>
       </c>
-      <c r="AA12" s="3">
+      <c r="AB12" s="3">
         <v>8300</v>
       </c>
-      <c r="AB12" s="3">
+      <c r="AC12" s="3">
         <v>7300</v>
       </c>
-      <c r="AC12" s="3">
+      <c r="AD12" s="3">
         <v>7700</v>
       </c>
-      <c r="AD12" s="3">
+      <c r="AE12" s="3">
         <v>5400</v>
       </c>
-      <c r="AE12" s="3">
+      <c r="AF12" s="3">
         <v>6100</v>
       </c>
-      <c r="AF12" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AG12" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="13" spans="1:33" x14ac:dyDescent="0.2">
+      <c r="AH12" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1301,16 +1318,19 @@
       <c r="AG13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:33" x14ac:dyDescent="0.2">
+      <c r="AH13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="E14" s="3" t="s">
-        <v>3</v>
+      <c r="E14" s="3">
+        <v>100</v>
       </c>
       <c r="F14" s="3" t="s">
         <v>3</v>
@@ -1318,12 +1338,12 @@
       <c r="G14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="H14" s="3">
+      <c r="H14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I14" s="3">
         <v>6100</v>
       </c>
-      <c r="I14" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="J14" s="3" t="s">
         <v>3</v>
       </c>
@@ -1342,12 +1362,12 @@
       <c r="O14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P14" s="3">
+      <c r="P14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q14" s="3">
         <v>7800</v>
       </c>
-      <c r="Q14" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R14" s="3" t="s">
         <v>3</v>
       </c>
@@ -1363,8 +1383,8 @@
       <c r="V14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="W14" s="3">
-        <v>0</v>
+      <c r="W14" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="X14" s="3">
         <v>0</v>
@@ -1396,8 +1416,11 @@
       <c r="AG14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:33" x14ac:dyDescent="0.2">
+      <c r="AH14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1405,10 +1428,10 @@
         <v>1000</v>
       </c>
       <c r="E15" s="3">
+        <v>1000</v>
+      </c>
+      <c r="F15" s="3">
         <v>1100</v>
-      </c>
-      <c r="F15" s="3">
-        <v>1000</v>
       </c>
       <c r="G15" s="3">
         <v>1000</v>
@@ -1417,16 +1440,16 @@
         <v>1000</v>
       </c>
       <c r="I15" s="3">
+        <v>1000</v>
+      </c>
+      <c r="J15" s="3">
         <v>1400</v>
-      </c>
-      <c r="J15" s="3">
-        <v>1500</v>
       </c>
       <c r="K15" s="3">
         <v>1500</v>
       </c>
       <c r="L15" s="3">
-        <v>0</v>
+        <v>1500</v>
       </c>
       <c r="M15" s="3">
         <v>0</v>
@@ -1491,8 +1514,11 @@
       <c r="AG15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:33" x14ac:dyDescent="0.2">
+      <c r="AH15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:34" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1523,198 +1549,205 @@
       <c r="AE16" s="3"/>
       <c r="AF16" s="3"/>
       <c r="AG16" s="3"/>
-    </row>
-    <row r="17" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH16" s="3"/>
+    </row>
+    <row r="17" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>164600</v>
+      </c>
+      <c r="E17" s="3">
         <v>172000</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>208900</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>191900</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>188600</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>198000</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>218800</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>206200</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>197800</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>201500</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>224000</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>196200</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>183000</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>684700</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>215600</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>175500</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>161800</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>-4900</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>263800</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>133600</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>112300</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>94600</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>89400</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>62000</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>46400</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>40700</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>37800</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>31300</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AF17" s="3">
         <v>26700</v>
       </c>
-      <c r="AF17" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AG17" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="18" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH17" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>14300</v>
+      </c>
+      <c r="E18" s="3">
         <v>11500</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>15300</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>-10000</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>4100</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>10800</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>-7900</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>-39900</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>-28500</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>3500</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>-30300</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>-63300</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>-17300</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>-130200</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>-18400</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>-36200</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>-29800</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>69800</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>-131700</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>-41700</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>-27600</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>-31400</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>-36100</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>-12700</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>-12000</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>-7300</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>-12400</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AE18" s="3">
         <v>-4400</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AF18" s="3">
         <v>-7500</v>
       </c>
-      <c r="AF18" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AG18" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="19" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH18" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1748,175 +1781,179 @@
       <c r="AE19" s="3"/>
       <c r="AF19" s="3"/>
       <c r="AG19" s="3"/>
-    </row>
-    <row r="20" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH19" s="3"/>
+    </row>
+    <row r="20" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
-        <v>-200</v>
+        <v>100</v>
       </c>
       <c r="E20" s="3">
+        <v>-300</v>
+      </c>
+      <c r="F20" s="3">
         <v>300</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>100</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>-400</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>-5700</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>2900</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>-800</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>-900</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>1000</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>6100</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>700</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>5300</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>7700</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>900</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>4300</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>500</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>700</v>
       </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3">
         <v>2400</v>
       </c>
-      <c r="V20" s="3">
+      <c r="W20" s="3">
         <v>3700</v>
       </c>
-      <c r="W20" s="3">
+      <c r="X20" s="3">
         <v>1400</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Y20" s="3">
         <v>200</v>
       </c>
-      <c r="Y20" s="3">
+      <c r="Z20" s="3">
         <v>800</v>
       </c>
-      <c r="Z20" s="3">
+      <c r="AA20" s="3">
         <v>1200</v>
       </c>
-      <c r="AA20" s="3">
+      <c r="AB20" s="3">
         <v>-1800</v>
       </c>
-      <c r="AB20" s="3">
+      <c r="AC20" s="3">
         <v>-800</v>
       </c>
-      <c r="AC20" s="3">
+      <c r="AD20" s="3">
         <v>3200</v>
       </c>
-      <c r="AD20" s="3">
+      <c r="AE20" s="3">
         <v>1700</v>
       </c>
-      <c r="AE20" s="3">
+      <c r="AF20" s="3">
         <v>-1100</v>
       </c>
-      <c r="AF20" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AG20" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="21" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH20" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>15200</v>
+      </c>
+      <c r="E21" s="3">
         <v>12800</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>16100</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>-9100</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>5600</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>17500</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>-9400</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>-37600</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>-26000</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>6100</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>-22600</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>-61100</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>-10900</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>-118400</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>-16400</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>-31100</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>-28600</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>71200</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>-128700</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>-37500</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>-25600</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>-30700</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>-35000</v>
       </c>
-      <c r="Z21" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AA21" s="3" t="s">
         <v>3</v>
       </c>
@@ -1926,64 +1963,67 @@
       <c r="AC21" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AD21" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AE21" s="3">
         <v>-2300</v>
       </c>
-      <c r="AE21" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AF21" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AG21" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="22" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH21" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="22" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>2200</v>
+      </c>
+      <c r="E22" s="3">
         <v>2300</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
         <v>2200</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>2900</v>
       </c>
-      <c r="G22" s="3">
+      <c r="H22" s="3">
         <v>2800</v>
       </c>
-      <c r="H22" s="3">
+      <c r="I22" s="3">
         <v>2700</v>
-      </c>
-      <c r="I22" s="3">
-        <v>2400</v>
       </c>
       <c r="J22" s="3">
         <v>2400</v>
       </c>
       <c r="K22" s="3">
+        <v>2400</v>
+      </c>
+      <c r="L22" s="3">
         <v>2300</v>
       </c>
-      <c r="L22" s="3">
+      <c r="M22" s="3">
         <v>2100</v>
       </c>
-      <c r="M22" s="3">
+      <c r="N22" s="3">
         <v>1700</v>
       </c>
-      <c r="N22" s="3">
+      <c r="O22" s="3">
         <v>1400</v>
       </c>
-      <c r="O22" s="3">
+      <c r="P22" s="3">
         <v>1200</v>
       </c>
-      <c r="P22" s="3">
+      <c r="Q22" s="3">
         <v>4400</v>
-      </c>
-      <c r="Q22" s="3">
-        <v>1100</v>
       </c>
       <c r="R22" s="3">
         <v>1100</v>
@@ -1991,8 +2031,8 @@
       <c r="S22" s="3">
         <v>1100</v>
       </c>
-      <c r="T22" s="3" t="s">
-        <v>3</v>
+      <c r="T22" s="3">
+        <v>1100</v>
       </c>
       <c r="U22" s="3" t="s">
         <v>3</v>
@@ -2009,8 +2049,8 @@
       <c r="Y22" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Z22" s="3">
-        <v>0</v>
+      <c r="Z22" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="AA22" s="3">
         <v>0</v>
@@ -2033,171 +2073,177 @@
       <c r="AG22" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>12100</v>
+      </c>
+      <c r="E23" s="3">
         <v>9600</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>13000</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>-12800</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>1900</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>8000</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>-12900</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>-41100</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>-29500</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>2400</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>-25900</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>-63900</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>-13200</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>-127000</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>-18600</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>-33100</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>-30400</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>70600</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>-129400</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>-38000</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>-26200</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>-31200</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>-35400</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>-11500</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>-13900</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>-8100</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>-9300</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>-2600</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AF23" s="3">
         <v>-8500</v>
       </c>
-      <c r="AF23" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AG23" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="24" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH23" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="24" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>1400</v>
+      </c>
+      <c r="E24" s="3">
         <v>-300</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>300</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>1000</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>-100</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>100</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>400</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>700</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>500</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>2000</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>-200</v>
-      </c>
-      <c r="N24" s="3">
-        <v>100</v>
       </c>
       <c r="O24" s="3">
         <v>100</v>
       </c>
       <c r="P24" s="3">
+        <v>100</v>
+      </c>
+      <c r="Q24" s="3">
         <v>900</v>
-      </c>
-      <c r="Q24" s="3">
-        <v>400</v>
       </c>
       <c r="R24" s="3">
         <v>400</v>
       </c>
       <c r="S24" s="3">
+        <v>400</v>
+      </c>
+      <c r="T24" s="3">
         <v>200</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>100</v>
       </c>
-      <c r="U24" s="3">
-        <v>0</v>
-      </c>
       <c r="V24" s="3">
         <v>0</v>
       </c>
       <c r="W24" s="3">
+        <v>0</v>
+      </c>
+      <c r="X24" s="3">
         <v>300</v>
       </c>
-      <c r="X24" s="3">
-        <v>0</v>
-      </c>
       <c r="Y24" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="Z24" s="3">
         <v>100</v>
@@ -2206,25 +2252,28 @@
         <v>100</v>
       </c>
       <c r="AB24" s="3">
-        <v>500</v>
+        <v>100</v>
       </c>
       <c r="AC24" s="3">
         <v>500</v>
       </c>
       <c r="AD24" s="3">
+        <v>500</v>
+      </c>
+      <c r="AE24" s="3">
         <v>200</v>
       </c>
-      <c r="AE24" s="3">
+      <c r="AF24" s="3">
         <v>500</v>
       </c>
-      <c r="AF24" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AG24" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="25" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH24" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="25" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2318,198 +2367,207 @@
       <c r="AG25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>10700</v>
+      </c>
+      <c r="E26" s="3">
         <v>9900</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>12700</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>-13800</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>2000</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>7900</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>-13300</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>-41800</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>-30000</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>400</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>-25700</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>-64000</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>-13300</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>-127900</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>-18900</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>-33500</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>-30600</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>70500</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>-129400</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>-38000</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>-26500</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>-31200</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>-35500</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>-11600</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>-14000</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>-8600</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>-9800</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AE26" s="3">
         <v>-2800</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AF26" s="3">
         <v>-9000</v>
       </c>
-      <c r="AF26" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AG26" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="27" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH26" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="27" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>10600</v>
+      </c>
+      <c r="E27" s="3">
         <v>11400</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>12300</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>-13700</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>1700</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>8000</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>-14100</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>-41300</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>-29700</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>1700</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>-25400</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>-63100</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>-13200</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>-123600</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>-18300</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>-33400</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>-30500</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>70500</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>-129400</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>-38000</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>-26500</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>-31700</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>-37300</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>-13400</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>-15500</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>-10200</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>-11200</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AE27" s="3">
         <v>-4200</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AF27" s="3">
         <v>-8900</v>
       </c>
-      <c r="AF27" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AG27" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="28" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH27" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="28" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2603,8 +2661,11 @@
       <c r="AG28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2642,31 +2703,31 @@
         <v>0</v>
       </c>
       <c r="O29" s="3">
+        <v>0</v>
+      </c>
+      <c r="P29" s="3">
         <v>-800</v>
       </c>
-      <c r="P29" s="3">
+      <c r="Q29" s="3">
         <v>-13800</v>
       </c>
-      <c r="Q29" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="R29" s="3">
+      <c r="R29" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S29" s="3">
         <v>-41200</v>
       </c>
-      <c r="S29" s="3">
+      <c r="T29" s="3">
         <v>-14800</v>
       </c>
-      <c r="T29" s="3">
+      <c r="U29" s="3">
         <v>-132800</v>
       </c>
-      <c r="U29" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V29" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="W29" s="3">
-        <v>0</v>
+      <c r="W29" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="X29" s="3">
         <v>0</v>
@@ -2698,8 +2759,11 @@
       <c r="AG29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2793,8 +2857,11 @@
       <c r="AG30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2888,198 +2955,207 @@
       <c r="AG31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
-        <v>200</v>
+        <v>-100</v>
       </c>
       <c r="E32" s="3">
+        <v>300</v>
+      </c>
+      <c r="F32" s="3">
         <v>-300</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>-100</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>400</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>5700</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>-2900</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>800</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>900</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>-1000</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>-6100</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>-700</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>-5300</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>-7700</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>-900</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>-4300</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>-500</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>-700</v>
       </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3">
         <v>-2400</v>
       </c>
-      <c r="V32" s="3">
+      <c r="W32" s="3">
         <v>-3700</v>
       </c>
-      <c r="W32" s="3">
+      <c r="X32" s="3">
         <v>-1400</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Y32" s="3">
         <v>-200</v>
       </c>
-      <c r="Y32" s="3">
+      <c r="Z32" s="3">
         <v>-800</v>
       </c>
-      <c r="Z32" s="3">
+      <c r="AA32" s="3">
         <v>-1200</v>
       </c>
-      <c r="AA32" s="3">
+      <c r="AB32" s="3">
         <v>1800</v>
       </c>
-      <c r="AB32" s="3">
+      <c r="AC32" s="3">
         <v>800</v>
       </c>
-      <c r="AC32" s="3">
+      <c r="AD32" s="3">
         <v>-3200</v>
       </c>
-      <c r="AD32" s="3">
+      <c r="AE32" s="3">
         <v>-1700</v>
       </c>
-      <c r="AE32" s="3">
+      <c r="AF32" s="3">
         <v>1100</v>
       </c>
-      <c r="AF32" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AG32" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="33" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH32" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="33" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>10600</v>
+      </c>
+      <c r="E33" s="3">
         <v>11400</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>12300</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>-13700</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>1700</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>8000</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>-14100</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>-41300</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>-29700</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>1700</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>-25400</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>-63100</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>-14000</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>-137500</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>-18300</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>-74500</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>-45400</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>-62300</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>-129400</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>-38000</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>-26500</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>-31700</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>-37300</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>-13400</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>-15500</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>-10200</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>-11200</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3">
         <v>-4200</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AF33" s="3">
         <v>-8900</v>
       </c>
-      <c r="AF33" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AG33" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="34" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH33" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="34" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3173,203 +3249,212 @@
       <c r="AG34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>10600</v>
+      </c>
+      <c r="E35" s="3">
         <v>11400</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>12300</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>-13700</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>1700</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>8000</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>-14100</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>-41300</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>-29700</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>1700</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>-25400</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>-63100</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>-14000</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>-137500</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>-18300</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>-74500</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>-45400</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>-62300</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>-129400</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>-38000</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>-26500</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>-31700</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>-37300</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>-13400</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>-15500</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>-10200</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>-11200</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3">
         <v>-4200</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AF35" s="3">
         <v>-8900</v>
       </c>
-      <c r="AF35" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AG35" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="37" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH35" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="37" spans="2:34" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45747</v>
+      </c>
+      <c r="E38" s="2">
         <v>45657</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45565</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45473</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45382</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45291</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45199</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45107</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45016</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44926</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44834</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44742</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44651</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44561</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44469</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44377</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44286</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44196</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>44104</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>44012</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>43921</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43830</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>43738</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43646</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43555</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43465</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43373</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>43281</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>43190</v>
       </c>
-      <c r="AF38" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="AG38" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="39" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH38" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="39" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3403,8 +3488,9 @@
       <c r="AE39" s="3"/>
       <c r="AF39" s="3"/>
       <c r="AG39" s="3"/>
-    </row>
-    <row r="40" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH39" s="3"/>
+    </row>
+    <row r="40" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3438,83 +3524,84 @@
       <c r="AE40" s="3"/>
       <c r="AF40" s="3"/>
       <c r="AG40" s="3"/>
-    </row>
-    <row r="41" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH40" s="3"/>
+    </row>
+    <row r="41" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>46300</v>
+      </c>
+      <c r="E41" s="3">
         <v>81200</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>60000</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>68900</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>36400</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>64100</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>46300</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>90700</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>84300</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>110500</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>98400</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>95500</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>57300</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>44600</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>70200</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>117900</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>257300</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>84800</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>11500</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>18500</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>20100</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>26700</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>8500</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>8000</v>
       </c>
-      <c r="AA41" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AB41" s="3" t="s">
         <v>3</v>
       </c>
@@ -3533,83 +3620,86 @@
       <c r="AG41" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="42" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH41" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="42" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>11400</v>
+      </c>
+      <c r="E42" s="3">
         <v>8600</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
         <v>9000</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>8600</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>8700</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>10200</v>
-      </c>
-      <c r="I42" s="3">
-        <v>3000</v>
       </c>
       <c r="J42" s="3">
         <v>3000</v>
       </c>
       <c r="K42" s="3">
+        <v>3000</v>
+      </c>
+      <c r="L42" s="3">
         <v>3200</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>32800</v>
-      </c>
-      <c r="M42" s="3">
-        <v>3000</v>
       </c>
       <c r="N42" s="3">
         <v>3000</v>
       </c>
       <c r="O42" s="3">
+        <v>3000</v>
+      </c>
+      <c r="P42" s="3">
         <v>900</v>
       </c>
-      <c r="P42" s="3">
+      <c r="Q42" s="3">
         <v>69600</v>
       </c>
-      <c r="Q42" s="3">
+      <c r="R42" s="3">
         <v>58300</v>
       </c>
-      <c r="R42" s="3">
+      <c r="S42" s="3">
         <v>146500</v>
       </c>
-      <c r="S42" s="3">
+      <c r="T42" s="3">
         <v>47000</v>
       </c>
-      <c r="T42" s="3">
+      <c r="U42" s="3">
         <v>81500</v>
       </c>
-      <c r="U42" s="3">
+      <c r="V42" s="3">
         <v>155400</v>
       </c>
-      <c r="V42" s="3">
+      <c r="W42" s="3">
         <v>245400</v>
       </c>
-      <c r="W42" s="3">
+      <c r="X42" s="3">
         <v>242400</v>
       </c>
-      <c r="X42" s="3">
+      <c r="Y42" s="3">
         <v>222800</v>
       </c>
-      <c r="Y42" s="3">
+      <c r="Z42" s="3">
         <v>16200</v>
       </c>
-      <c r="Z42" s="3">
+      <c r="AA42" s="3">
         <v>38000</v>
       </c>
-      <c r="AA42" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AB42" s="3" t="s">
         <v>3</v>
       </c>
@@ -3628,83 +3718,86 @@
       <c r="AG42" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="43" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH42" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="43" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
-        <v>68300</v>
+        <v>66300</v>
       </c>
       <c r="E43" s="3">
+        <v>69000</v>
+      </c>
+      <c r="F43" s="3">
         <v>70700</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>63500</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>57100</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>56800</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>49400</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>53300</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>39000</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>58200</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>46900</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>49000</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>41500</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>35100</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>35300</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>44300</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>35100</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>38000</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>50100</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>34900</v>
       </c>
-      <c r="W43" s="3">
+      <c r="X43" s="3">
         <v>36800</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Y43" s="3">
         <v>33200</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="Z43" s="3">
         <v>27800</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AA43" s="3">
         <v>31100</v>
       </c>
-      <c r="AA43" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AB43" s="3" t="s">
         <v>3</v>
       </c>
@@ -3723,83 +3816,86 @@
       <c r="AG43" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="44" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH43" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="44" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>21400</v>
+      </c>
+      <c r="E44" s="3">
         <v>23900</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>25500</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>26900</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>26200</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>30600</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>24300</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>25200</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>31900</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>32700</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>23500</v>
-      </c>
-      <c r="N44" s="3">
-        <v>29500</v>
       </c>
       <c r="O44" s="3">
         <v>29500</v>
       </c>
       <c r="P44" s="3">
+        <v>29500</v>
+      </c>
+      <c r="Q44" s="3">
         <v>35300</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="R44" s="3">
         <v>38000</v>
       </c>
-      <c r="R44" s="3">
+      <c r="S44" s="3">
         <v>38600</v>
       </c>
-      <c r="S44" s="3">
+      <c r="T44" s="3">
         <v>37400</v>
       </c>
-      <c r="T44" s="3">
+      <c r="U44" s="3">
         <v>20700</v>
       </c>
-      <c r="U44" s="3">
+      <c r="V44" s="3">
         <v>13500</v>
       </c>
-      <c r="V44" s="3">
+      <c r="W44" s="3">
         <v>13700</v>
       </c>
-      <c r="W44" s="3">
+      <c r="X44" s="3">
         <v>10300</v>
       </c>
-      <c r="X44" s="3">
+      <c r="Y44" s="3">
         <v>11300</v>
       </c>
-      <c r="Y44" s="3">
+      <c r="Z44" s="3">
         <v>8100</v>
       </c>
-      <c r="Z44" s="3">
+      <c r="AA44" s="3">
         <v>5000</v>
       </c>
-      <c r="AA44" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AB44" s="3" t="s">
         <v>3</v>
       </c>
@@ -3818,83 +3914,86 @@
       <c r="AG44" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="45" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH44" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="45" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
-        <v>21100</v>
+        <v>23500</v>
       </c>
       <c r="E45" s="3">
+        <v>13400</v>
+      </c>
+      <c r="F45" s="3">
         <v>23300</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>24300</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>27100</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>12600</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>31900</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>26700</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>25700</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>29400</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>59700</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>104200</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>129100</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>128800</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>85400</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>33100</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>27600</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>32800</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>29600</v>
       </c>
-      <c r="V45" s="3">
+      <c r="W45" s="3">
         <v>17500</v>
-      </c>
-      <c r="W45" s="3">
-        <v>18600</v>
       </c>
       <c r="X45" s="3">
         <v>18600</v>
       </c>
       <c r="Y45" s="3">
+        <v>18600</v>
+      </c>
+      <c r="Z45" s="3">
         <v>16200</v>
       </c>
-      <c r="Z45" s="3">
+      <c r="AA45" s="3">
         <v>11300</v>
       </c>
-      <c r="AA45" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AB45" s="3" t="s">
         <v>3</v>
       </c>
@@ -3913,83 +4012,86 @@
       <c r="AG45" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="46" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH45" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="46" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>169300</v>
+      </c>
+      <c r="E46" s="3">
         <v>203700</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>188800</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>192500</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>155600</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>183300</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>155000</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>198900</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>184100</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>263600</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>231500</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>281200</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>258300</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>313400</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>287200</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>380400</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>404400</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>257700</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>260200</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>330000</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>328200</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Y46" s="3">
         <v>312600</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="Z46" s="3">
         <v>76800</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AA46" s="3">
         <v>93400</v>
       </c>
-      <c r="AA46" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AB46" s="3" t="s">
         <v>3</v>
       </c>
@@ -4008,65 +4110,68 @@
       <c r="AG46" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="47" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH46" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="47" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>9500</v>
+      </c>
+      <c r="E47" s="3">
         <v>9900</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>10600</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>10700</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>6800</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>7200</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>8800</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>12100</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>13200</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>12800</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>9300</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>9800</v>
       </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>3800</v>
       </c>
-      <c r="P47" s="3">
+      <c r="Q47" s="3">
         <v>4500</v>
       </c>
-      <c r="Q47" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R47" s="3" t="s">
         <v>3</v>
       </c>
       <c r="S47" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="T47" s="3">
+      <c r="T47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="U47" s="3">
         <v>5900</v>
       </c>
-      <c r="U47" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V47" s="3" t="s">
         <v>3</v>
       </c>
@@ -4079,8 +4184,8 @@
       <c r="Y47" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Z47" s="3">
-        <v>0</v>
+      <c r="Z47" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="AA47" s="3">
         <v>0</v>
@@ -4103,83 +4208,86 @@
       <c r="AG47" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>14000</v>
+      </c>
+      <c r="E48" s="3">
         <v>15800</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>18800</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>20500</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>21500</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>22600</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>23700</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>23100</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>23200</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>24000</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>25700</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>27400</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>28300</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>27400</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>31400</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>28600</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>21000</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>21100</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>18100</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>11900</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>7600</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>7500</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="Z48" s="3">
         <v>6100</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AA48" s="3">
         <v>3500</v>
       </c>
-      <c r="AA48" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AB48" s="3" t="s">
         <v>3</v>
       </c>
@@ -4198,52 +4306,55 @@
       <c r="AG48" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="49" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH48" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="49" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>15200</v>
+      </c>
+      <c r="E49" s="3">
         <v>15100</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>15700</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>15100</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>15200</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>15500</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>15100</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>15200</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>16000</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>15500</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>15200</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>15300</v>
-      </c>
-      <c r="O49" s="3">
-        <v>15200</v>
       </c>
       <c r="P49" s="3">
         <v>15200</v>
       </c>
-      <c r="Q49" s="3" t="s">
-        <v>3</v>
+      <c r="Q49" s="3">
+        <v>15200</v>
       </c>
       <c r="R49" s="3" t="s">
         <v>3</v>
@@ -4260,8 +4371,8 @@
       <c r="V49" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="W49" s="3">
-        <v>0</v>
+      <c r="W49" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="X49" s="3">
         <v>0</v>
@@ -4293,8 +4404,11 @@
       <c r="AG49" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="50" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH49" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4388,8 +4502,11 @@
       <c r="AG50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4483,82 +4600,85 @@
       <c r="AG51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>4200</v>
+      </c>
+      <c r="E52" s="3">
         <v>4100</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>6100</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>6400</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>7700</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>6300</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>6400</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>5300</v>
-      </c>
-      <c r="K52" s="3">
-        <v>4900</v>
       </c>
       <c r="L52" s="3">
         <v>4900</v>
       </c>
       <c r="M52" s="3">
+        <v>4900</v>
+      </c>
+      <c r="N52" s="3">
         <v>5300</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>5200</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>5000</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>3200</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>30000</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>14700</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>11000</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>3400</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>3900</v>
       </c>
-      <c r="V52" s="3">
+      <c r="W52" s="3">
         <v>3200</v>
       </c>
-      <c r="W52" s="3">
+      <c r="X52" s="3">
         <v>2100</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Y52" s="3">
         <v>1300</v>
-      </c>
-      <c r="Y52" s="3">
-        <v>800</v>
       </c>
       <c r="Z52" s="3">
         <v>800</v>
       </c>
-      <c r="AA52" s="3" t="s">
-        <v>3</v>
+      <c r="AA52" s="3">
+        <v>800</v>
       </c>
       <c r="AB52" s="3" t="s">
         <v>3</v>
@@ -4578,8 +4698,11 @@
       <c r="AG52" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="53" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH52" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="53" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -4673,83 +4796,86 @@
       <c r="AG53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>212100</v>
+      </c>
+      <c r="E54" s="3">
         <v>248600</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>240000</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>245200</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>206900</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>235000</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>209000</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>254500</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>241400</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>320900</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>286900</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>339000</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>310600</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>363700</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>348600</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>423600</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>436300</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>288200</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>282200</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>345100</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>337900</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>321300</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>83700</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>97700</v>
       </c>
-      <c r="AA54" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AB54" s="3" t="s">
         <v>3</v>
       </c>
@@ -4768,8 +4894,11 @@
       <c r="AG54" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="55" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH54" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="55" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -4803,8 +4932,9 @@
       <c r="AE55" s="3"/>
       <c r="AF55" s="3"/>
       <c r="AG55" s="3"/>
-    </row>
-    <row r="56" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH55" s="3"/>
+    </row>
+    <row r="56" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -4838,83 +4968,84 @@
       <c r="AE56" s="3"/>
       <c r="AF56" s="3"/>
       <c r="AG56" s="3"/>
-    </row>
-    <row r="57" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH56" s="3"/>
+    </row>
+    <row r="57" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>18800</v>
+      </c>
+      <c r="E57" s="3">
         <v>22900</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>33200</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>25400</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>26700</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>34000</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>32000</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>26600</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>30700</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>39800</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>24800</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>21100</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>18400</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>22200</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>16600</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>10600</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>17500</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>19700</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>17600</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>15200</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>14900</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Y57" s="3">
         <v>9700</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="Z57" s="3">
         <v>7200</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AA57" s="3">
         <v>5300</v>
       </c>
-      <c r="AA57" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AB57" s="3" t="s">
         <v>3</v>
       </c>
@@ -4933,83 +5064,86 @@
       <c r="AG57" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="58" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH57" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="58" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>121000</v>
+      </c>
+      <c r="E58" s="3">
+        <v>125500</v>
+      </c>
+      <c r="F58" s="3">
+        <v>125200</v>
+      </c>
+      <c r="G58" s="3">
+        <v>120800</v>
+      </c>
+      <c r="H58" s="3">
+        <v>121600</v>
+      </c>
+      <c r="I58" s="3">
+        <v>129300</v>
+      </c>
+      <c r="J58" s="3">
         <v>120300</v>
       </c>
-      <c r="E58" s="3">
-        <v>125200</v>
-      </c>
-      <c r="F58" s="3">
-        <v>120800</v>
-      </c>
-      <c r="G58" s="3">
-        <v>121600</v>
-      </c>
-      <c r="H58" s="3">
-        <v>129300</v>
-      </c>
-      <c r="I58" s="3">
-        <v>120300</v>
-      </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>200800</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>207800</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>123800</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>121300</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>122100</v>
-      </c>
-      <c r="O58" s="3">
-        <v>121200</v>
       </c>
       <c r="P58" s="3">
         <v>121200</v>
       </c>
       <c r="Q58" s="3">
-        <v>124800</v>
+        <v>121200</v>
       </c>
       <c r="R58" s="3">
         <v>124800</v>
       </c>
       <c r="S58" s="3">
-        <v>122200</v>
+        <v>124800</v>
       </c>
       <c r="T58" s="3">
         <v>122200</v>
       </c>
       <c r="U58" s="3">
-        <v>129400</v>
+        <v>122200</v>
       </c>
       <c r="V58" s="3">
         <v>129400</v>
       </c>
       <c r="W58" s="3">
+        <v>129400</v>
+      </c>
+      <c r="X58" s="3">
         <v>137500</v>
-      </c>
-      <c r="X58" s="3">
-        <v>135200</v>
       </c>
       <c r="Y58" s="3">
         <v>135200</v>
       </c>
       <c r="Z58" s="3">
+        <v>135200</v>
+      </c>
+      <c r="AA58" s="3">
         <v>134100</v>
       </c>
-      <c r="AA58" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AB58" s="3" t="s">
         <v>3</v>
       </c>
@@ -5028,83 +5162,86 @@
       <c r="AG58" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="59" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH58" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="59" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>136800</v>
+        <v>105300</v>
       </c>
       <c r="E59" s="3">
+        <v>137100</v>
+      </c>
+      <c r="F59" s="3">
         <v>127200</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>149500</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>114100</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>156300</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>136900</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>175300</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>130400</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>284500</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>266100</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>298500</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>226700</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>275500</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>293600</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>375700</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>312500</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>330500</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>268200</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>204700</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>157000</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>126000</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>93900</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AA59" s="3">
         <v>76900</v>
       </c>
-      <c r="AA59" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AB59" s="3" t="s">
         <v>3</v>
       </c>
@@ -5123,83 +5260,86 @@
       <c r="AG59" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="60" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH59" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="60" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>355000</v>
+      </c>
+      <c r="E60" s="3">
         <v>403700</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>413600</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>424800</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>373200</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>437100</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>411700</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>527200</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>480200</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>448100</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>412300</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>441700</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>366300</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>418900</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>435000</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>511100</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>452200</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>472400</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>415100</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>349200</v>
       </c>
-      <c r="W60" s="3">
+      <c r="X60" s="3">
         <v>309300</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Y60" s="3">
         <v>270800</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="Z60" s="3">
         <v>236300</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AA60" s="3">
         <v>216400</v>
       </c>
-      <c r="AA60" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AB60" s="3" t="s">
         <v>3</v>
       </c>
@@ -5218,53 +5358,56 @@
       <c r="AG60" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="61" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH60" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="61" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>130300</v>
+      </c>
+      <c r="E61" s="3">
         <v>128600</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>133300</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>130400</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>128600</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>95900</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>90300</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>6400</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>5900</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>73600</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>68700</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>65300</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>48200</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>35200</v>
       </c>
-      <c r="Q61" s="3">
-        <v>0</v>
-      </c>
       <c r="R61" s="3">
         <v>0</v>
       </c>
@@ -5313,80 +5456,83 @@
       <c r="AG61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>2800</v>
+      </c>
+      <c r="E62" s="3">
         <v>2500</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>2600</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>2300</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>2400</v>
-      </c>
-      <c r="H62" s="3">
-        <v>2300</v>
       </c>
       <c r="I62" s="3">
         <v>2300</v>
       </c>
       <c r="J62" s="3">
+        <v>2300</v>
+      </c>
+      <c r="K62" s="3">
         <v>1700</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>1600</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>7400</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>8400</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>8700</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>7700</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>10400</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>15100</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>13800</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>10900</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>11700</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>10300</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>6400</v>
       </c>
-      <c r="W62" s="3">
+      <c r="X62" s="3">
         <v>3900</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Y62" s="3">
         <v>4100</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="Z62" s="3">
         <v>2100</v>
       </c>
-      <c r="Z62" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AA62" s="3" t="s">
         <v>3</v>
       </c>
@@ -5399,8 +5545,8 @@
       <c r="AD62" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="AE62" s="3">
-        <v>0</v>
+      <c r="AE62" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="AF62" s="3">
         <v>0</v>
@@ -5408,8 +5554,11 @@
       <c r="AG62" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="63" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH62" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="63" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -5503,8 +5652,11 @@
       <c r="AG63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -5598,8 +5750,11 @@
       <c r="AG64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -5693,83 +5848,86 @@
       <c r="AG65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>488100</v>
+      </c>
+      <c r="E66" s="3">
         <v>534800</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>549500</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>557600</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>504200</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>535200</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>504300</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>535200</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>487800</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>537300</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>498600</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>525300</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>432700</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>475200</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>464600</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>524800</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>463100</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>484200</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>425500</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>355800</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>313400</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>275100</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>238600</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>216600</v>
       </c>
-      <c r="AA66" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AB66" s="3" t="s">
         <v>3</v>
       </c>
@@ -5788,8 +5946,11 @@
       <c r="AG66" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="67" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH66" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="67" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -5823,8 +5984,9 @@
       <c r="AE67" s="3"/>
       <c r="AF67" s="3"/>
       <c r="AG67" s="3"/>
-    </row>
-    <row r="68" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH67" s="3"/>
+    </row>
+    <row r="68" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -5918,8 +6080,11 @@
       <c r="AG68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -6013,8 +6178,11 @@
       <c r="AG69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -6082,14 +6250,14 @@
         <v>0</v>
       </c>
       <c r="Y70" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z70" s="3">
         <v>75900</v>
       </c>
-      <c r="Z70" s="3">
+      <c r="AA70" s="3">
         <v>73600</v>
       </c>
-      <c r="AA70" s="3">
-        <v>0</v>
-      </c>
       <c r="AB70" s="3">
         <v>0</v>
       </c>
@@ -6108,8 +6276,11 @@
       <c r="AG70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -6203,16 +6374,19 @@
       <c r="AG71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="E72" s="3" t="s">
-        <v>3</v>
+      <c r="E72" s="3">
+        <v>-803000</v>
       </c>
       <c r="F72" s="3" t="s">
         <v>3</v>
@@ -6220,24 +6394,24 @@
       <c r="G72" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="H72" s="3">
+      <c r="H72" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I72" s="3">
         <v>-838200</v>
       </c>
-      <c r="I72" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="J72" s="3" t="s">
         <v>3</v>
       </c>
       <c r="K72" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L72" s="3">
+      <c r="L72" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M72" s="3">
         <v>-760400</v>
       </c>
-      <c r="M72" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N72" s="3" t="s">
         <v>3</v>
       </c>
@@ -6256,30 +6430,30 @@
       <c r="S72" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="T72" s="3">
+      <c r="T72" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="U72" s="3">
         <v>-511000</v>
       </c>
-      <c r="U72" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V72" s="3" t="s">
         <v>3</v>
       </c>
       <c r="W72" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="X72" s="3">
+      <c r="X72" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Y72" s="3">
         <v>-295400</v>
       </c>
-      <c r="Y72" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Z72" s="3">
+      <c r="Z72" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AA72" s="3">
         <v>-224700</v>
       </c>
-      <c r="AA72" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AB72" s="3" t="s">
         <v>3</v>
       </c>
@@ -6298,8 +6472,11 @@
       <c r="AG72" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="73" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH72" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="73" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -6393,8 +6570,11 @@
       <c r="AG73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -6488,8 +6668,11 @@
       <c r="AG74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -6583,83 +6766,86 @@
       <c r="AG75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>-283000</v>
+      </c>
+      <c r="E76" s="3">
         <v>-293200</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>-318200</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>-320500</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>-305600</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>-308400</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>-303200</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>-287900</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>-254500</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>-216400</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>-211700</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>-186400</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>-122100</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>-111400</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>-116000</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>-101200</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>-26700</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>-196000</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>-143300</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>-10700</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>24500</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>46200</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>-230800</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>-192500</v>
       </c>
-      <c r="AA76" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AB76" s="3" t="s">
         <v>3</v>
       </c>
@@ -6678,8 +6864,11 @@
       <c r="AG76" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="77" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH76" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="77" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -6773,203 +6962,212 @@
       <c r="AG77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:34" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45747</v>
+      </c>
+      <c r="E80" s="2">
         <v>45657</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45565</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45473</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45382</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45291</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45199</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45107</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45016</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44926</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44834</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44742</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44651</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44561</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44469</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44377</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44286</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44196</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>44104</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>44012</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>43921</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43830</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>43738</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43646</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43555</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43465</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43373</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>43281</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>43190</v>
       </c>
-      <c r="AF80" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="AG80" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="81" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH80" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="81" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>10600</v>
+      </c>
+      <c r="E81" s="3">
         <v>11400</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>12300</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>-13700</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>1700</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>8000</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>-14100</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>-41300</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>-29700</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>1700</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>-25400</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>-63100</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>-14000</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>-137500</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>-18300</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>-74500</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>-45400</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>-62300</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>-129400</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>-38000</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>-26500</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>-31700</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>-37300</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>-13400</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>-15500</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>-10200</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>-11200</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3">
         <v>-4200</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AF81" s="3">
         <v>-8900</v>
       </c>
-      <c r="AF81" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AG81" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="82" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH81" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="82" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -7003,8 +7201,9 @@
       <c r="AE82" s="3"/>
       <c r="AF82" s="3"/>
       <c r="AG82" s="3"/>
-    </row>
-    <row r="83" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH82" s="3"/>
+    </row>
+    <row r="83" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
@@ -7032,38 +7231,38 @@
       <c r="K83" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L83" s="3">
-        <v>1600</v>
+      <c r="L83" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="M83" s="3">
         <v>1600</v>
       </c>
       <c r="N83" s="3">
+        <v>1600</v>
+      </c>
+      <c r="O83" s="3">
         <v>1500</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>1100</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>4200</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>1100</v>
-      </c>
-      <c r="R83" s="3">
-        <v>800</v>
       </c>
       <c r="S83" s="3">
         <v>800</v>
       </c>
       <c r="T83" s="3">
+        <v>800</v>
+      </c>
+      <c r="U83" s="3">
         <v>700</v>
       </c>
-      <c r="U83" s="3">
+      <c r="V83" s="3">
         <v>600</v>
-      </c>
-      <c r="V83" s="3">
-        <v>500</v>
       </c>
       <c r="W83" s="3">
         <v>500</v>
@@ -7072,11 +7271,11 @@
         <v>500</v>
       </c>
       <c r="Y83" s="3">
+        <v>500</v>
+      </c>
+      <c r="Z83" s="3">
         <v>400</v>
       </c>
-      <c r="Z83" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AA83" s="3" t="s">
         <v>3</v>
       </c>
@@ -7089,8 +7288,8 @@
       <c r="AD83" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="AE83" s="3">
-        <v>0</v>
+      <c r="AE83" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="AF83" s="3">
         <v>0</v>
@@ -7098,8 +7297,11 @@
       <c r="AG83" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="84" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH83" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -7193,8 +7395,11 @@
       <c r="AG84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -7288,8 +7493,11 @@
       <c r="AG85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -7383,8 +7591,11 @@
       <c r="AG86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -7478,8 +7689,11 @@
       <c r="AG87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -7573,8 +7787,11 @@
       <c r="AG88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
@@ -7611,42 +7828,42 @@
       <c r="N89" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O89" s="3">
+      <c r="O89" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P89" s="3">
         <v>58800</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>-185900</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>89400</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>35400</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>72100</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>-147200</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>87400</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>21000</v>
       </c>
-      <c r="W89" s="3">
-        <v>0</v>
-      </c>
       <c r="X89" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y89" s="3">
         <v>-48300</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>21900</v>
       </c>
-      <c r="Z89" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AA89" s="3" t="s">
         <v>3</v>
       </c>
@@ -7659,8 +7876,8 @@
       <c r="AD89" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="AE89" s="3">
-        <v>0</v>
+      <c r="AE89" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="AF89" s="3">
         <v>0</v>
@@ -7668,8 +7885,11 @@
       <c r="AG89" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="90" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH89" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="90" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -7703,8 +7923,9 @@
       <c r="AE90" s="3"/>
       <c r="AF90" s="3"/>
       <c r="AG90" s="3"/>
-    </row>
-    <row r="91" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH90" s="3"/>
+    </row>
+    <row r="91" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
@@ -7732,41 +7953,41 @@
       <c r="K91" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L91" s="3">
+      <c r="L91" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M91" s="3">
         <v>-62200</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-6500</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-17900</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-3400</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-1900</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-11400</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-15900</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-1600</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-2200</v>
       </c>
-      <c r="U91" s="3">
+      <c r="V91" s="3">
         <v>-1800</v>
       </c>
-      <c r="V91" s="3">
+      <c r="W91" s="3">
         <v>-600</v>
-      </c>
-      <c r="W91" s="3">
-        <v>-700</v>
       </c>
       <c r="X91" s="3">
         <v>-700</v>
@@ -7774,8 +7995,8 @@
       <c r="Y91" s="3">
         <v>-700</v>
       </c>
-      <c r="Z91" s="3" t="s">
-        <v>3</v>
+      <c r="Z91" s="3">
+        <v>-700</v>
       </c>
       <c r="AA91" s="3" t="s">
         <v>3</v>
@@ -7789,8 +8010,8 @@
       <c r="AD91" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="AE91" s="3">
-        <v>0</v>
+      <c r="AE91" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="AF91" s="3">
         <v>0</v>
@@ -7798,8 +8019,11 @@
       <c r="AG91" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="92" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH91" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -7893,8 +8117,11 @@
       <c r="AG92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -7988,8 +8215,11 @@
       <c r="AG93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
@@ -8023,8 +8253,8 @@
       <c r="M94" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N94" s="3">
-        <v>0</v>
+      <c r="N94" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="O94" s="3">
         <v>0</v>
@@ -8083,8 +8313,11 @@
       <c r="AG94" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="95" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH94" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="95" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -8118,8 +8351,9 @@
       <c r="AE95" s="3"/>
       <c r="AF95" s="3"/>
       <c r="AG95" s="3"/>
-    </row>
-    <row r="96" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH95" s="3"/>
+    </row>
+    <row r="96" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -8147,8 +8381,8 @@
       <c r="K96" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L96" s="3">
-        <v>0</v>
+      <c r="L96" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="M96" s="3">
         <v>0</v>
@@ -8213,8 +8447,11 @@
       <c r="AG96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -8308,8 +8545,11 @@
       <c r="AG97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -8403,8 +8643,11 @@
       <c r="AG98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -8498,8 +8741,11 @@
       <c r="AG99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
@@ -8527,8 +8773,8 @@
       <c r="K100" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L100" s="3">
-        <v>0</v>
+      <c r="L100" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="M100" s="3">
         <v>0</v>
@@ -8593,8 +8839,11 @@
       <c r="AG100" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="101" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH100" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="101" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -8622,8 +8871,8 @@
       <c r="K101" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L101" s="3">
-        <v>0</v>
+      <c r="L101" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="M101" s="3">
         <v>0</v>
@@ -8688,8 +8937,11 @@
       <c r="AG101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
@@ -8717,8 +8969,8 @@
       <c r="K102" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L102" s="3">
-        <v>0</v>
+      <c r="L102" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="M102" s="3">
         <v>0</v>
@@ -8781,6 +9033,9 @@
         <v>0</v>
       </c>
       <c r="AG102" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH102" s="3">
         <v>0</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/DAO_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/DAO_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="405" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="481" uniqueCount="92">
   <si>
     <t>DAO</t>
   </si>
@@ -656,441 +656,454 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AH102"/>
+  <dimension ref="A5:AI102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="6.42578125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="22" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="26" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="30" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="32" max="32" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="33" max="34" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="35" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="19" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="23" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="27" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="31" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="33" max="33" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="34" max="35" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="36" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:35" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:35" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45838</v>
+      </c>
+      <c r="E7" s="2">
         <v>45747</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45657</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45565</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45473</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45382</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45291</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45199</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45107</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>45016</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44926</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44834</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44742</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44651</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44561</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44469</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44377</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44286</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>44196</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>44104</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>44012</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43921</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>43830</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43738</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43646</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43555</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43465</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>43373</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>43281</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AG7" s="2">
         <v>43190</v>
       </c>
-      <c r="AG7" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="AH7" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="8" spans="1:34" x14ac:dyDescent="0.2">
+      <c r="AI7" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D8" s="3">
+      <c r="D8" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E8" s="3">
         <v>178900</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>183600</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>224200</v>
       </c>
-      <c r="G8" s="3">
-        <v>181900</v>
-      </c>
-      <c r="H8" s="3">
+      <c r="H8" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I8" s="3">
         <v>192800</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>208800</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>210900</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>166400</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>169300</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>205000</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>193800</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>132900</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>165800</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>554500</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>197200</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>139300</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>132000</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>64900</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>132000</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>91800</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>84800</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>63200</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>53300</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>49300</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>34300</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AD8" s="3">
         <v>33400</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AE8" s="3">
         <v>25300</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AF8" s="3">
         <v>27000</v>
       </c>
-      <c r="AF8" s="3">
+      <c r="AG8" s="3">
         <v>19300</v>
       </c>
-      <c r="AG8" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AH8" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="9" spans="1:34" x14ac:dyDescent="0.2">
+      <c r="AI8" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="9" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="D9" s="3">
+      <c r="D9" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E9" s="3">
         <v>94300</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>95800</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>111600</v>
       </c>
-      <c r="G9" s="3">
-        <v>94300</v>
-      </c>
-      <c r="H9" s="3">
+      <c r="H9" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I9" s="3">
         <v>98400</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>104600</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>93100</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>88200</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>81700</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>95800</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>88700</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>76000</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>77100</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>279900</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>85500</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>68200</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>62900</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>120900</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>71400</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>50400</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Y9" s="3">
         <v>47900</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="Z9" s="3">
         <v>44300</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AA9" s="3">
         <v>39500</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AB9" s="3">
         <v>33100</v>
       </c>
-      <c r="AB9" s="3">
+      <c r="AC9" s="3">
         <v>26300</v>
       </c>
-      <c r="AC9" s="3">
+      <c r="AD9" s="3">
         <v>23500</v>
       </c>
-      <c r="AD9" s="3">
+      <c r="AE9" s="3">
         <v>19400</v>
       </c>
-      <c r="AE9" s="3">
+      <c r="AF9" s="3">
         <v>17200</v>
       </c>
-      <c r="AF9" s="3">
+      <c r="AG9" s="3">
         <v>13900</v>
       </c>
-      <c r="AG9" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AH9" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="10" spans="1:34" x14ac:dyDescent="0.2">
+      <c r="AI9" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="D10" s="3">
+      <c r="D10" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E10" s="3">
         <v>84600</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>87800</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>112500</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I10" s="3">
+        <v>94400</v>
+      </c>
+      <c r="J10" s="3">
+        <v>104200</v>
+      </c>
+      <c r="K10" s="3">
+        <v>117800</v>
+      </c>
+      <c r="L10" s="3">
+        <v>78200</v>
+      </c>
+      <c r="M10" s="3">
         <v>87600</v>
       </c>
-      <c r="H10" s="3">
-        <v>94400</v>
-      </c>
-      <c r="I10" s="3">
-        <v>104200</v>
-      </c>
-      <c r="J10" s="3">
-        <v>117800</v>
-      </c>
-      <c r="K10" s="3">
-        <v>78200</v>
-      </c>
-      <c r="L10" s="3">
-        <v>87600</v>
-      </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>109200</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>105000</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>57000</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>88600</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>274600</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>111700</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>71100</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>69100</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>-56100</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>60600</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>41500</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Y10" s="3">
         <v>36900</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="Z10" s="3">
         <v>18800</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AA10" s="3">
         <v>13700</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AB10" s="3">
         <v>16200</v>
       </c>
-      <c r="AB10" s="3">
+      <c r="AC10" s="3">
         <v>8000</v>
       </c>
-      <c r="AC10" s="3">
+      <c r="AD10" s="3">
         <v>9900</v>
       </c>
-      <c r="AD10" s="3">
+      <c r="AE10" s="3">
         <v>5900</v>
       </c>
-      <c r="AE10" s="3">
+      <c r="AF10" s="3">
         <v>9800</v>
       </c>
-      <c r="AF10" s="3">
+      <c r="AG10" s="3">
         <v>5400</v>
       </c>
-      <c r="AG10" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AH10" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="11" spans="1:34" x14ac:dyDescent="0.2">
+      <c r="AI10" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -1125,106 +1138,110 @@
       <c r="AF11" s="3"/>
       <c r="AG11" s="3"/>
       <c r="AH11" s="3"/>
-    </row>
-    <row r="12" spans="1:34" x14ac:dyDescent="0.2">
+      <c r="AI11" s="3"/>
+    </row>
+    <row r="12" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="D12" s="3">
+      <c r="D12" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E12" s="3">
         <v>15900</v>
       </c>
-      <c r="E12" s="3">
+      <c r="F12" s="3">
         <v>16500</v>
       </c>
-      <c r="F12" s="3">
+      <c r="G12" s="3">
         <v>17000</v>
       </c>
-      <c r="G12" s="3">
-        <v>21100</v>
-      </c>
-      <c r="H12" s="3">
+      <c r="H12" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I12" s="3">
         <v>20300</v>
       </c>
-      <c r="I12" s="3">
+      <c r="J12" s="3">
         <v>23700</v>
       </c>
-      <c r="J12" s="3">
+      <c r="K12" s="3">
         <v>25700</v>
       </c>
-      <c r="K12" s="3">
+      <c r="L12" s="3">
         <v>28300</v>
       </c>
-      <c r="L12" s="3">
+      <c r="M12" s="3">
         <v>26600</v>
       </c>
-      <c r="M12" s="3">
+      <c r="N12" s="3">
         <v>25300</v>
       </c>
-      <c r="N12" s="3">
+      <c r="O12" s="3">
         <v>29400</v>
       </c>
-      <c r="O12" s="3">
+      <c r="P12" s="3">
         <v>29000</v>
       </c>
-      <c r="P12" s="3">
+      <c r="Q12" s="3">
         <v>28000</v>
       </c>
-      <c r="Q12" s="3">
+      <c r="R12" s="3">
         <v>83900</v>
       </c>
-      <c r="R12" s="3">
+      <c r="S12" s="3">
         <v>27500</v>
       </c>
-      <c r="S12" s="3">
+      <c r="T12" s="3">
         <v>20700</v>
       </c>
-      <c r="T12" s="3">
+      <c r="U12" s="3">
         <v>17800</v>
       </c>
-      <c r="U12" s="3">
+      <c r="V12" s="3">
         <v>10500</v>
       </c>
-      <c r="V12" s="3">
+      <c r="W12" s="3">
         <v>17800</v>
       </c>
-      <c r="W12" s="3">
+      <c r="X12" s="3">
         <v>13500</v>
       </c>
-      <c r="X12" s="3">
+      <c r="Y12" s="3">
         <v>13200</v>
       </c>
-      <c r="Y12" s="3">
+      <c r="Z12" s="3">
         <v>13700</v>
       </c>
-      <c r="Z12" s="3">
+      <c r="AA12" s="3">
         <v>11500</v>
       </c>
-      <c r="AA12" s="3">
+      <c r="AB12" s="3">
         <v>8600</v>
       </c>
-      <c r="AB12" s="3">
+      <c r="AC12" s="3">
         <v>8300</v>
       </c>
-      <c r="AC12" s="3">
+      <c r="AD12" s="3">
         <v>7300</v>
       </c>
-      <c r="AD12" s="3">
+      <c r="AE12" s="3">
         <v>7700</v>
       </c>
-      <c r="AE12" s="3">
+      <c r="AF12" s="3">
         <v>5400</v>
       </c>
-      <c r="AF12" s="3">
+      <c r="AG12" s="3">
         <v>6100</v>
       </c>
-      <c r="AG12" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AH12" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="13" spans="1:34" x14ac:dyDescent="0.2">
+      <c r="AI12" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1321,32 +1338,35 @@
       <c r="AH13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:34" x14ac:dyDescent="0.2">
+      <c r="AI13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="E14" s="3">
+      <c r="E14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F14" s="3">
         <v>100</v>
       </c>
-      <c r="F14" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="G14" s="3" t="s">
         <v>3</v>
       </c>
       <c r="H14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="I14" s="3">
+      <c r="I14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J14" s="3">
         <v>6100</v>
       </c>
-      <c r="J14" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="K14" s="3" t="s">
         <v>3</v>
       </c>
@@ -1365,12 +1385,12 @@
       <c r="P14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q14" s="3">
+      <c r="Q14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R14" s="3">
         <v>7800</v>
       </c>
-      <c r="R14" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S14" s="3" t="s">
         <v>3</v>
       </c>
@@ -1386,8 +1406,8 @@
       <c r="W14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="X14" s="3">
-        <v>0</v>
+      <c r="X14" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="Y14" s="3">
         <v>0</v>
@@ -1419,40 +1439,43 @@
       <c r="AH14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:34" x14ac:dyDescent="0.2">
+      <c r="AI14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="E15" s="3">
         <v>1000</v>
       </c>
       <c r="F15" s="3">
+        <v>1000</v>
+      </c>
+      <c r="G15" s="3">
         <v>1100</v>
       </c>
-      <c r="G15" s="3">
-        <v>1000</v>
-      </c>
       <c r="H15" s="3">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="I15" s="3">
         <v>1000</v>
       </c>
       <c r="J15" s="3">
+        <v>1000</v>
+      </c>
+      <c r="K15" s="3">
         <v>1400</v>
-      </c>
-      <c r="K15" s="3">
-        <v>1500</v>
       </c>
       <c r="L15" s="3">
         <v>1500</v>
       </c>
       <c r="M15" s="3">
-        <v>0</v>
+        <v>1500</v>
       </c>
       <c r="N15" s="3">
         <v>0</v>
@@ -1517,8 +1540,11 @@
       <c r="AH15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:34" x14ac:dyDescent="0.2">
+      <c r="AI15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:35" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1550,204 +1576,211 @@
       <c r="AF16" s="3"/>
       <c r="AG16" s="3"/>
       <c r="AH16" s="3"/>
-    </row>
-    <row r="17" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI16" s="3"/>
+    </row>
+    <row r="17" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="D17" s="3">
+      <c r="D17" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E17" s="3">
         <v>164600</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>172000</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>208900</v>
       </c>
-      <c r="G17" s="3">
-        <v>191900</v>
-      </c>
-      <c r="H17" s="3">
+      <c r="H17" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I17" s="3">
         <v>188600</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>198000</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>218800</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>206200</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>197800</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>201500</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>224000</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>196200</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>183000</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>684700</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>215600</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>175500</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>161800</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>-4900</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>263800</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>133600</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>112300</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>94600</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>89400</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>62000</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>46400</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>40700</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>37800</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AF17" s="3">
         <v>31300</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AG17" s="3">
         <v>26700</v>
       </c>
-      <c r="AG17" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AH17" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="18" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI17" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="D18" s="3">
+      <c r="D18" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E18" s="3">
         <v>14300</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>11500</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>15300</v>
       </c>
-      <c r="G18" s="3">
-        <v>-10000</v>
-      </c>
-      <c r="H18" s="3">
+      <c r="H18" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I18" s="3">
         <v>4100</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>10800</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>-7900</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>-39900</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>-28500</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>3500</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>-30300</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>-63300</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>-17300</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>-130200</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>-18400</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>-36200</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>-29800</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>69800</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>-131700</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>-41700</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>-27600</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>-31400</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>-36100</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>-12700</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>-12000</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>-7300</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AE18" s="3">
         <v>-12400</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AF18" s="3">
         <v>-4400</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AG18" s="3">
         <v>-7500</v>
       </c>
-      <c r="AG18" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AH18" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="19" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI18" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1782,181 +1815,185 @@
       <c r="AF19" s="3"/>
       <c r="AG19" s="3"/>
       <c r="AH19" s="3"/>
-    </row>
-    <row r="20" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI19" s="3"/>
+    </row>
+    <row r="20" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="D20" s="3">
+      <c r="D20" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E20" s="3">
         <v>100</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>-300</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>300</v>
       </c>
-      <c r="G20" s="3">
-        <v>100</v>
-      </c>
-      <c r="H20" s="3">
+      <c r="H20" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I20" s="3">
         <v>-400</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>-5700</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>2900</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>-800</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>-900</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>1000</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>6100</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>700</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>5300</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>7700</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>900</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>4300</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>500</v>
       </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3">
         <v>700</v>
       </c>
-      <c r="V20" s="3">
+      <c r="W20" s="3">
         <v>2400</v>
       </c>
-      <c r="W20" s="3">
+      <c r="X20" s="3">
         <v>3700</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Y20" s="3">
         <v>1400</v>
       </c>
-      <c r="Y20" s="3">
+      <c r="Z20" s="3">
         <v>200</v>
       </c>
-      <c r="Z20" s="3">
+      <c r="AA20" s="3">
         <v>800</v>
       </c>
-      <c r="AA20" s="3">
+      <c r="AB20" s="3">
         <v>1200</v>
       </c>
-      <c r="AB20" s="3">
+      <c r="AC20" s="3">
         <v>-1800</v>
       </c>
-      <c r="AC20" s="3">
+      <c r="AD20" s="3">
         <v>-800</v>
       </c>
-      <c r="AD20" s="3">
+      <c r="AE20" s="3">
         <v>3200</v>
       </c>
-      <c r="AE20" s="3">
+      <c r="AF20" s="3">
         <v>1700</v>
       </c>
-      <c r="AF20" s="3">
+      <c r="AG20" s="3">
         <v>-1100</v>
       </c>
-      <c r="AG20" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AH20" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="21" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI20" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>0</v>
+      </c>
+      <c r="E21" s="3">
         <v>15200</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>12800</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>16100</v>
       </c>
-      <c r="G21" s="3">
-        <v>-9100</v>
-      </c>
       <c r="H21" s="3">
+        <v>0</v>
+      </c>
+      <c r="I21" s="3">
         <v>5600</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>17500</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>-9400</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>-37600</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>-26000</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>6100</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>-22600</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>-61100</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>-10900</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>-118400</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>-16400</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>-31100</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>-28600</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>71200</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>-128700</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>-37500</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>-25600</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>-30700</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>-35000</v>
       </c>
-      <c r="AA21" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AB21" s="3" t="s">
         <v>3</v>
       </c>
@@ -1966,67 +2003,70 @@
       <c r="AD21" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="AE21" s="3">
+      <c r="AE21" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AF21" s="3">
         <v>-2300</v>
       </c>
-      <c r="AF21" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AG21" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AH21" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="22" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI21" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="22" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="D22" s="3">
+      <c r="D22" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E22" s="3">
         <v>2200</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
         <v>2300</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>2200</v>
       </c>
-      <c r="G22" s="3">
-        <v>2900</v>
-      </c>
-      <c r="H22" s="3">
+      <c r="H22" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I22" s="3">
         <v>2800</v>
       </c>
-      <c r="I22" s="3">
+      <c r="J22" s="3">
         <v>2700</v>
-      </c>
-      <c r="J22" s="3">
-        <v>2400</v>
       </c>
       <c r="K22" s="3">
         <v>2400</v>
       </c>
       <c r="L22" s="3">
+        <v>2400</v>
+      </c>
+      <c r="M22" s="3">
         <v>2300</v>
       </c>
-      <c r="M22" s="3">
+      <c r="N22" s="3">
         <v>2100</v>
       </c>
-      <c r="N22" s="3">
+      <c r="O22" s="3">
         <v>1700</v>
       </c>
-      <c r="O22" s="3">
+      <c r="P22" s="3">
         <v>1400</v>
       </c>
-      <c r="P22" s="3">
+      <c r="Q22" s="3">
         <v>1200</v>
       </c>
-      <c r="Q22" s="3">
+      <c r="R22" s="3">
         <v>4400</v>
-      </c>
-      <c r="R22" s="3">
-        <v>1100</v>
       </c>
       <c r="S22" s="3">
         <v>1100</v>
@@ -2034,8 +2074,8 @@
       <c r="T22" s="3">
         <v>1100</v>
       </c>
-      <c r="U22" s="3" t="s">
-        <v>3</v>
+      <c r="U22" s="3">
+        <v>1100</v>
       </c>
       <c r="V22" s="3" t="s">
         <v>3</v>
@@ -2052,8 +2092,8 @@
       <c r="Z22" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="AA22" s="3">
-        <v>0</v>
+      <c r="AA22" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="AB22" s="3">
         <v>0</v>
@@ -2076,177 +2116,183 @@
       <c r="AH22" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="D23" s="3">
+      <c r="D23" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E23" s="3">
         <v>12100</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>9600</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>13000</v>
       </c>
-      <c r="G23" s="3">
-        <v>-12800</v>
-      </c>
-      <c r="H23" s="3">
+      <c r="H23" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I23" s="3">
         <v>1900</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>8000</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>-12900</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>-41100</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>-29500</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>2400</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>-25900</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>-63900</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>-13200</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>-127000</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>-18600</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>-33100</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>-30400</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>70600</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>-129400</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>-38000</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>-26200</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>-31200</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>-35400</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>-11500</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>-13900</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>-8100</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>-9300</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AF23" s="3">
         <v>-2600</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AG23" s="3">
         <v>-8500</v>
       </c>
-      <c r="AG23" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AH23" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="24" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI23" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="24" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="D24" s="3">
+      <c r="D24" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E24" s="3">
         <v>1400</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>-300</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>300</v>
       </c>
-      <c r="G24" s="3">
-        <v>1000</v>
-      </c>
-      <c r="H24" s="3">
+      <c r="H24" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I24" s="3">
         <v>-100</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>100</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>400</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>700</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>500</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>2000</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>-200</v>
-      </c>
-      <c r="O24" s="3">
-        <v>100</v>
       </c>
       <c r="P24" s="3">
         <v>100</v>
       </c>
       <c r="Q24" s="3">
+        <v>100</v>
+      </c>
+      <c r="R24" s="3">
         <v>900</v>
-      </c>
-      <c r="R24" s="3">
-        <v>400</v>
       </c>
       <c r="S24" s="3">
         <v>400</v>
       </c>
       <c r="T24" s="3">
+        <v>400</v>
+      </c>
+      <c r="U24" s="3">
         <v>200</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>100</v>
       </c>
-      <c r="V24" s="3">
-        <v>0</v>
-      </c>
       <c r="W24" s="3">
         <v>0</v>
       </c>
       <c r="X24" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y24" s="3">
         <v>300</v>
       </c>
-      <c r="Y24" s="3">
-        <v>0</v>
-      </c>
       <c r="Z24" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="AA24" s="3">
         <v>100</v>
@@ -2255,25 +2301,28 @@
         <v>100</v>
       </c>
       <c r="AC24" s="3">
-        <v>500</v>
+        <v>100</v>
       </c>
       <c r="AD24" s="3">
         <v>500</v>
       </c>
       <c r="AE24" s="3">
+        <v>500</v>
+      </c>
+      <c r="AF24" s="3">
         <v>200</v>
       </c>
-      <c r="AF24" s="3">
+      <c r="AG24" s="3">
         <v>500</v>
       </c>
-      <c r="AG24" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AH24" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="25" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI24" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="25" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2370,204 +2419,213 @@
       <c r="AH25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="D26" s="3">
+      <c r="D26" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E26" s="3">
         <v>10700</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>9900</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>12700</v>
       </c>
-      <c r="G26" s="3">
-        <v>-13800</v>
-      </c>
-      <c r="H26" s="3">
+      <c r="H26" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I26" s="3">
         <v>2000</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>7900</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>-13300</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>-41800</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>-30000</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>400</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>-25700</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>-64000</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>-13300</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>-127900</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>-18900</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>-33500</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>-30600</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>70500</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>-129400</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>-38000</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>-26500</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>-31200</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>-35500</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>-11600</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>-14000</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>-8600</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AE26" s="3">
         <v>-9800</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AF26" s="3">
         <v>-2800</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AG26" s="3">
         <v>-9000</v>
       </c>
-      <c r="AG26" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AH26" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="27" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI26" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="27" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="D27" s="3">
+      <c r="D27" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E27" s="3">
         <v>10600</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>11400</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>12300</v>
       </c>
-      <c r="G27" s="3">
-        <v>-13700</v>
-      </c>
-      <c r="H27" s="3">
+      <c r="H27" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I27" s="3">
         <v>1700</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>8000</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>-14100</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>-41300</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>-29700</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>1700</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>-25400</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>-63100</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>-13200</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>-123600</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>-18300</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>-33400</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>-30500</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>70500</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>-129400</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>-38000</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>-26500</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>-31700</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>-37300</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>-13400</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>-15500</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>-10200</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AE27" s="3">
         <v>-11200</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AF27" s="3">
         <v>-4200</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AG27" s="3">
         <v>-8900</v>
       </c>
-      <c r="AG27" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AH27" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="28" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI27" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="28" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2664,8 +2722,11 @@
       <c r="AH28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2706,31 +2767,31 @@
         <v>0</v>
       </c>
       <c r="P29" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q29" s="3">
         <v>-800</v>
       </c>
-      <c r="Q29" s="3">
+      <c r="R29" s="3">
         <v>-13800</v>
       </c>
-      <c r="R29" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="S29" s="3">
+      <c r="S29" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="T29" s="3">
         <v>-41200</v>
       </c>
-      <c r="T29" s="3">
+      <c r="U29" s="3">
         <v>-14800</v>
       </c>
-      <c r="U29" s="3">
+      <c r="V29" s="3">
         <v>-132800</v>
       </c>
-      <c r="V29" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W29" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="X29" s="3">
-        <v>0</v>
+      <c r="X29" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="Y29" s="3">
         <v>0</v>
@@ -2762,8 +2823,11 @@
       <c r="AH29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2860,8 +2924,11 @@
       <c r="AH30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2958,204 +3025,213 @@
       <c r="AH31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="D32" s="3">
+      <c r="D32" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E32" s="3">
         <v>-100</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>300</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>-300</v>
       </c>
-      <c r="G32" s="3">
-        <v>-100</v>
-      </c>
-      <c r="H32" s="3">
+      <c r="H32" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I32" s="3">
         <v>400</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>5700</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>-2900</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>800</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>900</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>-1000</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>-6100</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>-700</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>-5300</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>-7700</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>-900</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>-4300</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>-500</v>
       </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3">
         <v>-700</v>
       </c>
-      <c r="V32" s="3">
+      <c r="W32" s="3">
         <v>-2400</v>
       </c>
-      <c r="W32" s="3">
+      <c r="X32" s="3">
         <v>-3700</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Y32" s="3">
         <v>-1400</v>
       </c>
-      <c r="Y32" s="3">
+      <c r="Z32" s="3">
         <v>-200</v>
       </c>
-      <c r="Z32" s="3">
+      <c r="AA32" s="3">
         <v>-800</v>
       </c>
-      <c r="AA32" s="3">
+      <c r="AB32" s="3">
         <v>-1200</v>
       </c>
-      <c r="AB32" s="3">
+      <c r="AC32" s="3">
         <v>1800</v>
       </c>
-      <c r="AC32" s="3">
+      <c r="AD32" s="3">
         <v>800</v>
       </c>
-      <c r="AD32" s="3">
+      <c r="AE32" s="3">
         <v>-3200</v>
       </c>
-      <c r="AE32" s="3">
+      <c r="AF32" s="3">
         <v>-1700</v>
       </c>
-      <c r="AF32" s="3">
+      <c r="AG32" s="3">
         <v>1100</v>
       </c>
-      <c r="AG32" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AH32" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="33" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI32" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="33" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="D33" s="3">
+      <c r="D33" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E33" s="3">
         <v>10600</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>11400</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>12300</v>
       </c>
-      <c r="G33" s="3">
-        <v>-13700</v>
-      </c>
-      <c r="H33" s="3">
+      <c r="H33" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I33" s="3">
         <v>1700</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>8000</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>-14100</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>-41300</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>-29700</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>1700</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>-25400</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>-63100</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>-14000</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>-137500</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>-18300</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>-74500</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>-45400</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>-62300</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>-129400</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>-38000</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>-26500</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>-31700</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>-37300</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>-13400</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>-15500</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>-10200</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3">
         <v>-11200</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AF33" s="3">
         <v>-4200</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AG33" s="3">
         <v>-8900</v>
       </c>
-      <c r="AG33" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AH33" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="34" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI33" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="34" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3252,209 +3328,218 @@
       <c r="AH34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="D35" s="3">
+      <c r="D35" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E35" s="3">
         <v>10600</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>11400</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>12300</v>
       </c>
-      <c r="G35" s="3">
-        <v>-13700</v>
-      </c>
-      <c r="H35" s="3">
+      <c r="H35" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I35" s="3">
         <v>1700</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>8000</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>-14100</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>-41300</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>-29700</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>1700</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>-25400</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>-63100</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>-14000</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>-137500</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>-18300</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>-74500</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>-45400</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>-62300</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>-129400</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>-38000</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>-26500</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>-31700</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>-37300</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>-13400</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>-15500</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>-10200</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3">
         <v>-11200</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AF35" s="3">
         <v>-4200</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AG35" s="3">
         <v>-8900</v>
       </c>
-      <c r="AG35" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AH35" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="37" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI35" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="37" spans="2:35" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45838</v>
+      </c>
+      <c r="E38" s="2">
         <v>45747</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45657</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45565</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45473</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45382</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45291</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45199</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45107</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>45016</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44926</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44834</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44742</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44651</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44561</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44469</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44377</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44286</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>44196</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>44104</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>44012</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43921</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>43830</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43738</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43646</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43555</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43465</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>43373</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>43281</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AG38" s="2">
         <v>43190</v>
       </c>
-      <c r="AG38" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="AH38" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="39" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI38" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="39" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3489,8 +3574,9 @@
       <c r="AF39" s="3"/>
       <c r="AG39" s="3"/>
       <c r="AH39" s="3"/>
-    </row>
-    <row r="40" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI39" s="3"/>
+    </row>
+    <row r="40" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3525,86 +3611,87 @@
       <c r="AF40" s="3"/>
       <c r="AG40" s="3"/>
       <c r="AH40" s="3"/>
-    </row>
-    <row r="41" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI40" s="3"/>
+    </row>
+    <row r="41" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="D41" s="3">
+      <c r="D41" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E41" s="3">
         <v>46300</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>81200</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>60000</v>
       </c>
-      <c r="G41" s="3">
-        <v>68900</v>
-      </c>
-      <c r="H41" s="3">
+      <c r="H41" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I41" s="3">
         <v>36400</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>64100</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>46300</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>90700</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>84300</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>110500</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>98400</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>95500</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>57300</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>44600</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>70200</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>117900</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>257300</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>84800</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>11500</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>18500</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>20100</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>26700</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>8500</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>8000</v>
       </c>
-      <c r="AB41" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AC41" s="3" t="s">
         <v>3</v>
       </c>
@@ -3623,86 +3710,89 @@
       <c r="AH41" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="42" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI41" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="42" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>0</v>
+      </c>
+      <c r="E42" s="3">
         <v>11400</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
         <v>8600</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>9000</v>
       </c>
-      <c r="G42" s="3">
-        <v>8600</v>
-      </c>
       <c r="H42" s="3">
+        <v>0</v>
+      </c>
+      <c r="I42" s="3">
         <v>8700</v>
       </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
         <v>10200</v>
-      </c>
-      <c r="J42" s="3">
-        <v>3000</v>
       </c>
       <c r="K42" s="3">
         <v>3000</v>
       </c>
       <c r="L42" s="3">
+        <v>3000</v>
+      </c>
+      <c r="M42" s="3">
         <v>3200</v>
       </c>
-      <c r="M42" s="3">
+      <c r="N42" s="3">
         <v>32800</v>
-      </c>
-      <c r="N42" s="3">
-        <v>3000</v>
       </c>
       <c r="O42" s="3">
         <v>3000</v>
       </c>
       <c r="P42" s="3">
+        <v>3000</v>
+      </c>
+      <c r="Q42" s="3">
         <v>900</v>
       </c>
-      <c r="Q42" s="3">
+      <c r="R42" s="3">
         <v>69600</v>
       </c>
-      <c r="R42" s="3">
+      <c r="S42" s="3">
         <v>58300</v>
       </c>
-      <c r="S42" s="3">
+      <c r="T42" s="3">
         <v>146500</v>
       </c>
-      <c r="T42" s="3">
+      <c r="U42" s="3">
         <v>47000</v>
       </c>
-      <c r="U42" s="3">
+      <c r="V42" s="3">
         <v>81500</v>
       </c>
-      <c r="V42" s="3">
+      <c r="W42" s="3">
         <v>155400</v>
       </c>
-      <c r="W42" s="3">
+      <c r="X42" s="3">
         <v>245400</v>
       </c>
-      <c r="X42" s="3">
+      <c r="Y42" s="3">
         <v>242400</v>
       </c>
-      <c r="Y42" s="3">
+      <c r="Z42" s="3">
         <v>222800</v>
       </c>
-      <c r="Z42" s="3">
+      <c r="AA42" s="3">
         <v>16200</v>
       </c>
-      <c r="AA42" s="3">
+      <c r="AB42" s="3">
         <v>38000</v>
       </c>
-      <c r="AB42" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AC42" s="3" t="s">
         <v>3</v>
       </c>
@@ -3721,86 +3811,89 @@
       <c r="AH42" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="43" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI42" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="43" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="D43" s="3">
+      <c r="D43" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E43" s="3">
         <v>66300</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>69000</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>70700</v>
       </c>
-      <c r="G43" s="3">
-        <v>63500</v>
-      </c>
-      <c r="H43" s="3">
+      <c r="H43" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I43" s="3">
         <v>57100</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>56800</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>49400</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>53300</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>39000</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>58200</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>46900</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>49000</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>41500</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>35100</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>35300</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>44300</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>35100</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>38000</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>50100</v>
       </c>
-      <c r="W43" s="3">
+      <c r="X43" s="3">
         <v>34900</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Y43" s="3">
         <v>36800</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="Z43" s="3">
         <v>33200</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AA43" s="3">
         <v>27800</v>
       </c>
-      <c r="AA43" s="3">
+      <c r="AB43" s="3">
         <v>31100</v>
       </c>
-      <c r="AB43" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AC43" s="3" t="s">
         <v>3</v>
       </c>
@@ -3819,86 +3912,89 @@
       <c r="AH43" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="44" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI43" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="44" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="D44" s="3">
+      <c r="D44" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E44" s="3">
         <v>21400</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>23900</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>25500</v>
       </c>
-      <c r="G44" s="3">
-        <v>26900</v>
-      </c>
-      <c r="H44" s="3">
+      <c r="H44" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I44" s="3">
         <v>26200</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>30600</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>24300</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>25200</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>31900</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>32700</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>23500</v>
-      </c>
-      <c r="O44" s="3">
-        <v>29500</v>
       </c>
       <c r="P44" s="3">
         <v>29500</v>
       </c>
       <c r="Q44" s="3">
+        <v>29500</v>
+      </c>
+      <c r="R44" s="3">
         <v>35300</v>
       </c>
-      <c r="R44" s="3">
+      <c r="S44" s="3">
         <v>38000</v>
       </c>
-      <c r="S44" s="3">
+      <c r="T44" s="3">
         <v>38600</v>
       </c>
-      <c r="T44" s="3">
+      <c r="U44" s="3">
         <v>37400</v>
       </c>
-      <c r="U44" s="3">
+      <c r="V44" s="3">
         <v>20700</v>
       </c>
-      <c r="V44" s="3">
+      <c r="W44" s="3">
         <v>13500</v>
       </c>
-      <c r="W44" s="3">
+      <c r="X44" s="3">
         <v>13700</v>
       </c>
-      <c r="X44" s="3">
+      <c r="Y44" s="3">
         <v>10300</v>
       </c>
-      <c r="Y44" s="3">
+      <c r="Z44" s="3">
         <v>11300</v>
       </c>
-      <c r="Z44" s="3">
+      <c r="AA44" s="3">
         <v>8100</v>
       </c>
-      <c r="AA44" s="3">
+      <c r="AB44" s="3">
         <v>5000</v>
       </c>
-      <c r="AB44" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AC44" s="3" t="s">
         <v>3</v>
       </c>
@@ -3917,86 +4013,89 @@
       <c r="AH44" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="45" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI44" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="45" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="D45" s="3">
+      <c r="D45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E45" s="3">
         <v>23500</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>13400</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>23300</v>
       </c>
-      <c r="G45" s="3">
-        <v>24300</v>
-      </c>
-      <c r="H45" s="3">
+      <c r="H45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I45" s="3">
         <v>27100</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>12600</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>31900</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>26700</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>25700</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>29400</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>59700</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>104200</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>129100</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>128800</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>85400</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>33100</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>27600</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>32800</v>
       </c>
-      <c r="V45" s="3">
+      <c r="W45" s="3">
         <v>29600</v>
       </c>
-      <c r="W45" s="3">
+      <c r="X45" s="3">
         <v>17500</v>
-      </c>
-      <c r="X45" s="3">
-        <v>18600</v>
       </c>
       <c r="Y45" s="3">
         <v>18600</v>
       </c>
       <c r="Z45" s="3">
+        <v>18600</v>
+      </c>
+      <c r="AA45" s="3">
         <v>16200</v>
       </c>
-      <c r="AA45" s="3">
+      <c r="AB45" s="3">
         <v>11300</v>
       </c>
-      <c r="AB45" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AC45" s="3" t="s">
         <v>3</v>
       </c>
@@ -4015,86 +4114,89 @@
       <c r="AH45" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="46" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI45" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="46" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="D46" s="3">
+      <c r="D46" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E46" s="3">
         <v>169300</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>203700</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>188800</v>
       </c>
-      <c r="G46" s="3">
-        <v>192500</v>
-      </c>
-      <c r="H46" s="3">
+      <c r="H46" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I46" s="3">
         <v>155600</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>183300</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>155000</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>198900</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>184100</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>263600</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>231500</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>281200</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>258300</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>313400</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>287200</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>380400</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>404400</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>257700</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>260200</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>330000</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Y46" s="3">
         <v>328200</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="Z46" s="3">
         <v>312600</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AA46" s="3">
         <v>76800</v>
       </c>
-      <c r="AA46" s="3">
+      <c r="AB46" s="3">
         <v>93400</v>
       </c>
-      <c r="AB46" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AC46" s="3" t="s">
         <v>3</v>
       </c>
@@ -4113,68 +4215,71 @@
       <c r="AH46" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="47" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI46" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="47" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="D47" s="3">
+      <c r="D47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E47" s="3">
         <v>9500</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>9900</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>10600</v>
       </c>
-      <c r="G47" s="3">
-        <v>10700</v>
-      </c>
-      <c r="H47" s="3">
+      <c r="H47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I47" s="3">
         <v>6800</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>7200</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>8800</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>12100</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>13200</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>12800</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>9300</v>
       </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>9800</v>
       </c>
-      <c r="P47" s="3">
+      <c r="Q47" s="3">
         <v>3800</v>
       </c>
-      <c r="Q47" s="3">
+      <c r="R47" s="3">
         <v>4500</v>
       </c>
-      <c r="R47" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S47" s="3" t="s">
         <v>3</v>
       </c>
       <c r="T47" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="U47" s="3">
+      <c r="U47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="V47" s="3">
         <v>5900</v>
       </c>
-      <c r="V47" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W47" s="3" t="s">
         <v>3</v>
       </c>
@@ -4187,8 +4292,8 @@
       <c r="Z47" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="AA47" s="3">
-        <v>0</v>
+      <c r="AA47" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="AB47" s="3">
         <v>0</v>
@@ -4211,86 +4316,89 @@
       <c r="AH47" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="D48" s="3">
+      <c r="D48" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E48" s="3">
         <v>14000</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>15800</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>18800</v>
       </c>
-      <c r="G48" s="3">
-        <v>20500</v>
-      </c>
-      <c r="H48" s="3">
+      <c r="H48" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I48" s="3">
         <v>21500</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>22600</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>23700</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>23100</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>23200</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>24000</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>25700</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>27400</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>28300</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>27400</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>31400</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>28600</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>21000</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>21100</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>18100</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>11900</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>7600</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="Z48" s="3">
         <v>7500</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AA48" s="3">
         <v>6100</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AB48" s="3">
         <v>3500</v>
       </c>
-      <c r="AB48" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AC48" s="3" t="s">
         <v>3</v>
       </c>
@@ -4309,55 +4417,58 @@
       <c r="AH48" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="49" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI48" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="49" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="D49" s="3">
+      <c r="D49" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E49" s="3">
         <v>15200</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>15100</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>15700</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I49" s="3">
+        <v>15200</v>
+      </c>
+      <c r="J49" s="3">
+        <v>15500</v>
+      </c>
+      <c r="K49" s="3">
         <v>15100</v>
       </c>
-      <c r="H49" s="3">
+      <c r="L49" s="3">
         <v>15200</v>
       </c>
-      <c r="I49" s="3">
+      <c r="M49" s="3">
+        <v>16000</v>
+      </c>
+      <c r="N49" s="3">
         <v>15500</v>
       </c>
-      <c r="J49" s="3">
-        <v>15100</v>
-      </c>
-      <c r="K49" s="3">
+      <c r="O49" s="3">
         <v>15200</v>
       </c>
-      <c r="L49" s="3">
-        <v>16000</v>
-      </c>
-      <c r="M49" s="3">
-        <v>15500</v>
-      </c>
-      <c r="N49" s="3">
-        <v>15200</v>
-      </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>15300</v>
-      </c>
-      <c r="P49" s="3">
-        <v>15200</v>
       </c>
       <c r="Q49" s="3">
         <v>15200</v>
       </c>
-      <c r="R49" s="3" t="s">
-        <v>3</v>
+      <c r="R49" s="3">
+        <v>15200</v>
       </c>
       <c r="S49" s="3" t="s">
         <v>3</v>
@@ -4374,8 +4485,8 @@
       <c r="W49" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="X49" s="3">
-        <v>0</v>
+      <c r="X49" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="Y49" s="3">
         <v>0</v>
@@ -4407,8 +4518,11 @@
       <c r="AH49" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="50" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI49" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4505,8 +4619,11 @@
       <c r="AH50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4603,85 +4720,88 @@
       <c r="AH51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="D52" s="3">
+      <c r="D52" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E52" s="3">
         <v>4200</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>4100</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>6100</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I52" s="3">
+        <v>7700</v>
+      </c>
+      <c r="J52" s="3">
+        <v>6300</v>
+      </c>
+      <c r="K52" s="3">
         <v>6400</v>
       </c>
-      <c r="H52" s="3">
-        <v>7700</v>
-      </c>
-      <c r="I52" s="3">
-        <v>6300</v>
-      </c>
-      <c r="J52" s="3">
-        <v>6400</v>
-      </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>5300</v>
-      </c>
-      <c r="L52" s="3">
-        <v>4900</v>
       </c>
       <c r="M52" s="3">
         <v>4900</v>
       </c>
       <c r="N52" s="3">
+        <v>4900</v>
+      </c>
+      <c r="O52" s="3">
         <v>5300</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>5200</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>5000</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>3200</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>30000</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>14700</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>11000</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>3400</v>
       </c>
-      <c r="V52" s="3">
+      <c r="W52" s="3">
         <v>3900</v>
       </c>
-      <c r="W52" s="3">
+      <c r="X52" s="3">
         <v>3200</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Y52" s="3">
         <v>2100</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="Z52" s="3">
         <v>1300</v>
-      </c>
-      <c r="Z52" s="3">
-        <v>800</v>
       </c>
       <c r="AA52" s="3">
         <v>800</v>
       </c>
-      <c r="AB52" s="3" t="s">
-        <v>3</v>
+      <c r="AB52" s="3">
+        <v>800</v>
       </c>
       <c r="AC52" s="3" t="s">
         <v>3</v>
@@ -4701,8 +4821,11 @@
       <c r="AH52" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="53" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI52" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="53" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -4799,86 +4922,89 @@
       <c r="AH53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="D54" s="3">
+      <c r="D54" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E54" s="3">
         <v>212100</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>248600</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>240000</v>
       </c>
-      <c r="G54" s="3">
-        <v>245200</v>
-      </c>
-      <c r="H54" s="3">
+      <c r="H54" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I54" s="3">
         <v>206900</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>235000</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>209000</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>254500</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>241400</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>320900</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>286900</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>339000</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>310600</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>363700</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>348600</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>423600</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>436300</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>288200</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>282200</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>345100</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>337900</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>321300</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>83700</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>97700</v>
       </c>
-      <c r="AB54" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AC54" s="3" t="s">
         <v>3</v>
       </c>
@@ -4897,8 +5023,11 @@
       <c r="AH54" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="55" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI54" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="55" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -4933,8 +5062,9 @@
       <c r="AF55" s="3"/>
       <c r="AG55" s="3"/>
       <c r="AH55" s="3"/>
-    </row>
-    <row r="56" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI55" s="3"/>
+    </row>
+    <row r="56" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -4969,86 +5099,87 @@
       <c r="AF56" s="3"/>
       <c r="AG56" s="3"/>
       <c r="AH56" s="3"/>
-    </row>
-    <row r="57" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI56" s="3"/>
+    </row>
+    <row r="57" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="D57" s="3">
+      <c r="D57" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E57" s="3">
         <v>18800</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>22900</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>33200</v>
       </c>
-      <c r="G57" s="3">
-        <v>25400</v>
-      </c>
-      <c r="H57" s="3">
+      <c r="H57" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I57" s="3">
         <v>26700</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>34000</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>32000</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>26600</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>30700</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>39800</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>24800</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>21100</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>18400</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>22200</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>16600</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>10600</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>17500</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>19700</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>17600</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>15200</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Y57" s="3">
         <v>14900</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="Z57" s="3">
         <v>9700</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AA57" s="3">
         <v>7200</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AB57" s="3">
         <v>5300</v>
       </c>
-      <c r="AB57" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AC57" s="3" t="s">
         <v>3</v>
       </c>
@@ -5067,86 +5198,89 @@
       <c r="AH57" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="58" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI57" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="58" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
-      <c r="D58" s="3">
+      <c r="D58" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E58" s="3">
         <v>121000</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>125500</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>125200</v>
       </c>
-      <c r="G58" s="3">
-        <v>120800</v>
-      </c>
-      <c r="H58" s="3">
+      <c r="H58" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I58" s="3">
         <v>121600</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>129300</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>120300</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>200800</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>207800</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>123800</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>121300</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>122100</v>
-      </c>
-      <c r="P58" s="3">
-        <v>121200</v>
       </c>
       <c r="Q58" s="3">
         <v>121200</v>
       </c>
       <c r="R58" s="3">
-        <v>124800</v>
+        <v>121200</v>
       </c>
       <c r="S58" s="3">
         <v>124800</v>
       </c>
       <c r="T58" s="3">
-        <v>122200</v>
+        <v>124800</v>
       </c>
       <c r="U58" s="3">
         <v>122200</v>
       </c>
       <c r="V58" s="3">
-        <v>129400</v>
+        <v>122200</v>
       </c>
       <c r="W58" s="3">
         <v>129400</v>
       </c>
       <c r="X58" s="3">
+        <v>129400</v>
+      </c>
+      <c r="Y58" s="3">
         <v>137500</v>
-      </c>
-      <c r="Y58" s="3">
-        <v>135200</v>
       </c>
       <c r="Z58" s="3">
         <v>135200</v>
       </c>
       <c r="AA58" s="3">
+        <v>135200</v>
+      </c>
+      <c r="AB58" s="3">
         <v>134100</v>
       </c>
-      <c r="AB58" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AC58" s="3" t="s">
         <v>3</v>
       </c>
@@ -5165,86 +5299,89 @@
       <c r="AH58" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="59" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI58" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="59" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
-      <c r="D59" s="3">
+      <c r="D59" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E59" s="3">
         <v>105300</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>137100</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>127200</v>
       </c>
-      <c r="G59" s="3">
-        <v>149500</v>
-      </c>
-      <c r="H59" s="3">
+      <c r="H59" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I59" s="3">
         <v>114100</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>156300</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>136900</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>175300</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>130400</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>284500</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>266100</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>298500</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>226700</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>275500</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>293600</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>375700</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>312500</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>330500</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>268200</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>204700</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>157000</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>126000</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AA59" s="3">
         <v>93900</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AB59" s="3">
         <v>76900</v>
       </c>
-      <c r="AB59" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AC59" s="3" t="s">
         <v>3</v>
       </c>
@@ -5263,86 +5400,89 @@
       <c r="AH59" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="60" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI59" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="60" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
-      <c r="D60" s="3">
+      <c r="D60" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E60" s="3">
         <v>355000</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>403700</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>413600</v>
       </c>
-      <c r="G60" s="3">
-        <v>424800</v>
-      </c>
-      <c r="H60" s="3">
+      <c r="H60" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I60" s="3">
         <v>373200</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>437100</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>411700</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>527200</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>480200</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>448100</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>412300</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>441700</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>366300</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>418900</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>435000</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>511100</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>452200</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>472400</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>415100</v>
       </c>
-      <c r="W60" s="3">
+      <c r="X60" s="3">
         <v>349200</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Y60" s="3">
         <v>309300</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="Z60" s="3">
         <v>270800</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AA60" s="3">
         <v>236300</v>
       </c>
-      <c r="AA60" s="3">
+      <c r="AB60" s="3">
         <v>216400</v>
       </c>
-      <c r="AB60" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AC60" s="3" t="s">
         <v>3</v>
       </c>
@@ -5361,56 +5501,59 @@
       <c r="AH60" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="61" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI60" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="61" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>0</v>
+      </c>
+      <c r="E61" s="3">
         <v>130300</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>128600</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>133300</v>
       </c>
-      <c r="G61" s="3">
-        <v>130400</v>
-      </c>
       <c r="H61" s="3">
+        <v>0</v>
+      </c>
+      <c r="I61" s="3">
         <v>128600</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>95900</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>90300</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>6400</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>5900</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>73600</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>68700</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>65300</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>48200</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>35200</v>
       </c>
-      <c r="R61" s="3">
-        <v>0</v>
-      </c>
       <c r="S61" s="3">
         <v>0</v>
       </c>
@@ -5459,83 +5602,86 @@
       <c r="AH61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
-      <c r="D62" s="3">
+      <c r="D62" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E62" s="3">
         <v>2800</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>2500</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>2600</v>
       </c>
-      <c r="G62" s="3">
-        <v>2300</v>
-      </c>
-      <c r="H62" s="3">
+      <c r="H62" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I62" s="3">
         <v>2400</v>
-      </c>
-      <c r="I62" s="3">
-        <v>2300</v>
       </c>
       <c r="J62" s="3">
         <v>2300</v>
       </c>
       <c r="K62" s="3">
+        <v>2300</v>
+      </c>
+      <c r="L62" s="3">
         <v>1700</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>1600</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>7400</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>8400</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>8700</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>7700</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>10400</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>15100</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>13800</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>10900</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>11700</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>10300</v>
       </c>
-      <c r="W62" s="3">
+      <c r="X62" s="3">
         <v>6400</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Y62" s="3">
         <v>3900</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="Z62" s="3">
         <v>4100</v>
       </c>
-      <c r="Z62" s="3">
+      <c r="AA62" s="3">
         <v>2100</v>
       </c>
-      <c r="AA62" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AB62" s="3" t="s">
         <v>3</v>
       </c>
@@ -5548,8 +5694,8 @@
       <c r="AE62" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="AF62" s="3">
-        <v>0</v>
+      <c r="AF62" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="AG62" s="3">
         <v>0</v>
@@ -5557,8 +5703,11 @@
       <c r="AH62" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="63" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI62" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="63" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -5655,8 +5804,11 @@
       <c r="AH63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -5753,8 +5905,11 @@
       <c r="AH64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -5851,86 +6006,89 @@
       <c r="AH65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
-      <c r="D66" s="3">
+      <c r="D66" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E66" s="3">
         <v>488100</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>534800</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>549500</v>
       </c>
-      <c r="G66" s="3">
-        <v>557600</v>
-      </c>
-      <c r="H66" s="3">
+      <c r="H66" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I66" s="3">
         <v>504200</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>535200</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>504300</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>535200</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>487800</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>537300</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>498600</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>525300</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>432700</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>475200</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>464600</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>524800</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>463100</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>484200</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>425500</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>355800</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>313400</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>275100</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>238600</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>216600</v>
       </c>
-      <c r="AB66" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AC66" s="3" t="s">
         <v>3</v>
       </c>
@@ -5949,8 +6107,11 @@
       <c r="AH66" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="67" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI66" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="67" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -5985,8 +6146,9 @@
       <c r="AF67" s="3"/>
       <c r="AG67" s="3"/>
       <c r="AH67" s="3"/>
-    </row>
-    <row r="68" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI67" s="3"/>
+    </row>
+    <row r="68" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -6083,8 +6245,11 @@
       <c r="AH68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -6181,8 +6346,11 @@
       <c r="AH69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -6253,14 +6421,14 @@
         <v>0</v>
       </c>
       <c r="Z70" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA70" s="3">
         <v>75900</v>
       </c>
-      <c r="AA70" s="3">
+      <c r="AB70" s="3">
         <v>73600</v>
       </c>
-      <c r="AB70" s="3">
-        <v>0</v>
-      </c>
       <c r="AC70" s="3">
         <v>0</v>
       </c>
@@ -6279,8 +6447,11 @@
       <c r="AH70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -6377,44 +6548,47 @@
       <c r="AH71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="E72" s="3">
+      <c r="E72" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F72" s="3">
         <v>-803000</v>
       </c>
-      <c r="F72" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="G72" s="3" t="s">
         <v>3</v>
       </c>
       <c r="H72" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="I72" s="3">
+      <c r="I72" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J72" s="3">
         <v>-838200</v>
       </c>
-      <c r="J72" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="K72" s="3" t="s">
         <v>3</v>
       </c>
       <c r="L72" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M72" s="3">
+      <c r="M72" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N72" s="3">
         <v>-760400</v>
       </c>
-      <c r="N72" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O72" s="3" t="s">
         <v>3</v>
       </c>
@@ -6433,30 +6607,30 @@
       <c r="T72" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="U72" s="3">
+      <c r="U72" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="V72" s="3">
         <v>-511000</v>
       </c>
-      <c r="V72" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W72" s="3" t="s">
         <v>3</v>
       </c>
       <c r="X72" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Y72" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Z72" s="3">
         <v>-295400</v>
       </c>
-      <c r="Z72" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="AA72" s="3">
+      <c r="AA72" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AB72" s="3">
         <v>-224700</v>
       </c>
-      <c r="AB72" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AC72" s="3" t="s">
         <v>3</v>
       </c>
@@ -6475,8 +6649,11 @@
       <c r="AH72" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="73" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI72" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="73" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -6573,8 +6750,11 @@
       <c r="AH73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -6671,8 +6851,11 @@
       <c r="AH74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -6769,86 +6952,89 @@
       <c r="AH75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
-      <c r="D76" s="3">
+      <c r="D76" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E76" s="3">
         <v>-283000</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>-293200</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>-318200</v>
       </c>
-      <c r="G76" s="3">
-        <v>-320500</v>
-      </c>
-      <c r="H76" s="3">
+      <c r="H76" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I76" s="3">
         <v>-305600</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>-308400</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>-303200</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>-287900</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>-254500</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>-216400</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>-211700</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>-186400</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>-122100</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>-111400</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>-116000</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>-101200</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>-26700</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>-196000</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>-143300</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>-10700</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>24500</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>46200</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>-230800</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>-192500</v>
       </c>
-      <c r="AB76" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AC76" s="3" t="s">
         <v>3</v>
       </c>
@@ -6867,8 +7053,11 @@
       <c r="AH76" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="77" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI76" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="77" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -6965,209 +7154,218 @@
       <c r="AH77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:35" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45838</v>
+      </c>
+      <c r="E80" s="2">
         <v>45747</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45657</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45565</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45473</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45382</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45291</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45199</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45107</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>45016</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44926</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44834</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44742</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44651</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44561</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44469</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44377</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44286</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>44196</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>44104</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>44012</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43921</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>43830</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43738</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43646</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43555</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43465</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>43373</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>43281</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AG80" s="2">
         <v>43190</v>
       </c>
-      <c r="AG80" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="AH80" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="81" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI80" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="81" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="D81" s="3">
+      <c r="D81" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E81" s="3">
         <v>10600</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>11400</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>12300</v>
       </c>
-      <c r="G81" s="3">
-        <v>-13700</v>
-      </c>
-      <c r="H81" s="3">
+      <c r="H81" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I81" s="3">
         <v>1700</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>8000</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>-14100</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>-41300</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>-29700</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>1700</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>-25400</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>-63100</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>-14000</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>-137500</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>-18300</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>-74500</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>-45400</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>-62300</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>-129400</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>-38000</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>-26500</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>-31700</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>-37300</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>-13400</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>-15500</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>-10200</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3">
         <v>-11200</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AF81" s="3">
         <v>-4200</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AG81" s="3">
         <v>-8900</v>
       </c>
-      <c r="AG81" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AH81" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="82" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI81" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="82" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -7202,8 +7400,9 @@
       <c r="AF82" s="3"/>
       <c r="AG82" s="3"/>
       <c r="AH82" s="3"/>
-    </row>
-    <row r="83" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI82" s="3"/>
+    </row>
+    <row r="83" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
@@ -7234,38 +7433,38 @@
       <c r="L83" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M83" s="3">
-        <v>1600</v>
+      <c r="M83" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="N83" s="3">
         <v>1600</v>
       </c>
       <c r="O83" s="3">
+        <v>1600</v>
+      </c>
+      <c r="P83" s="3">
         <v>1500</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>1100</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>4200</v>
       </c>
-      <c r="R83" s="3">
+      <c r="S83" s="3">
         <v>1100</v>
-      </c>
-      <c r="S83" s="3">
-        <v>800</v>
       </c>
       <c r="T83" s="3">
         <v>800</v>
       </c>
       <c r="U83" s="3">
+        <v>800</v>
+      </c>
+      <c r="V83" s="3">
         <v>700</v>
       </c>
-      <c r="V83" s="3">
+      <c r="W83" s="3">
         <v>600</v>
-      </c>
-      <c r="W83" s="3">
-        <v>500</v>
       </c>
       <c r="X83" s="3">
         <v>500</v>
@@ -7274,11 +7473,11 @@
         <v>500</v>
       </c>
       <c r="Z83" s="3">
+        <v>500</v>
+      </c>
+      <c r="AA83" s="3">
         <v>400</v>
       </c>
-      <c r="AA83" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AB83" s="3" t="s">
         <v>3</v>
       </c>
@@ -7291,8 +7490,8 @@
       <c r="AE83" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="AF83" s="3">
-        <v>0</v>
+      <c r="AF83" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="AG83" s="3">
         <v>0</v>
@@ -7300,8 +7499,11 @@
       <c r="AH83" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="84" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI83" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -7398,8 +7600,11 @@
       <c r="AH84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -7496,8 +7701,11 @@
       <c r="AH85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -7594,8 +7802,11 @@
       <c r="AH86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -7692,8 +7903,11 @@
       <c r="AH87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -7790,8 +8004,11 @@
       <c r="AH88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
@@ -7831,42 +8048,42 @@
       <c r="O89" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P89" s="3">
+      <c r="P89" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q89" s="3">
         <v>58800</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>-185900</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>89400</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>35400</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>72100</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>-147200</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>87400</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>21000</v>
       </c>
-      <c r="X89" s="3">
-        <v>0</v>
-      </c>
       <c r="Y89" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z89" s="3">
         <v>-48300</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>21900</v>
       </c>
-      <c r="AA89" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AB89" s="3" t="s">
         <v>3</v>
       </c>
@@ -7879,8 +8096,8 @@
       <c r="AE89" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="AF89" s="3">
-        <v>0</v>
+      <c r="AF89" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="AG89" s="3">
         <v>0</v>
@@ -7888,8 +8105,11 @@
       <c r="AH89" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="90" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI89" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="90" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -7924,8 +8144,9 @@
       <c r="AF90" s="3"/>
       <c r="AG90" s="3"/>
       <c r="AH90" s="3"/>
-    </row>
-    <row r="91" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI90" s="3"/>
+    </row>
+    <row r="91" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
@@ -7956,41 +8177,41 @@
       <c r="L91" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M91" s="3">
+      <c r="M91" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N91" s="3">
         <v>-62200</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-6500</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-17900</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-3400</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-1900</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-11400</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-15900</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-1600</v>
       </c>
-      <c r="U91" s="3">
+      <c r="V91" s="3">
         <v>-2200</v>
       </c>
-      <c r="V91" s="3">
+      <c r="W91" s="3">
         <v>-1800</v>
       </c>
-      <c r="W91" s="3">
+      <c r="X91" s="3">
         <v>-600</v>
-      </c>
-      <c r="X91" s="3">
-        <v>-700</v>
       </c>
       <c r="Y91" s="3">
         <v>-700</v>
@@ -7998,8 +8219,8 @@
       <c r="Z91" s="3">
         <v>-700</v>
       </c>
-      <c r="AA91" s="3" t="s">
-        <v>3</v>
+      <c r="AA91" s="3">
+        <v>-700</v>
       </c>
       <c r="AB91" s="3" t="s">
         <v>3</v>
@@ -8013,8 +8234,8 @@
       <c r="AE91" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="AF91" s="3">
-        <v>0</v>
+      <c r="AF91" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="AG91" s="3">
         <v>0</v>
@@ -8022,8 +8243,11 @@
       <c r="AH91" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="92" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI91" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -8120,8 +8344,11 @@
       <c r="AH92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -8218,8 +8445,11 @@
       <c r="AH93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
@@ -8256,8 +8486,8 @@
       <c r="N94" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O94" s="3">
-        <v>0</v>
+      <c r="O94" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="P94" s="3">
         <v>0</v>
@@ -8316,8 +8546,11 @@
       <c r="AH94" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="95" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI94" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="95" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -8352,8 +8585,9 @@
       <c r="AF95" s="3"/>
       <c r="AG95" s="3"/>
       <c r="AH95" s="3"/>
-    </row>
-    <row r="96" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI95" s="3"/>
+    </row>
+    <row r="96" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -8384,8 +8618,8 @@
       <c r="L96" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M96" s="3">
-        <v>0</v>
+      <c r="M96" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="N96" s="3">
         <v>0</v>
@@ -8450,8 +8684,11 @@
       <c r="AH96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -8548,8 +8785,11 @@
       <c r="AH97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -8646,8 +8886,11 @@
       <c r="AH98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -8744,8 +8987,11 @@
       <c r="AH99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
@@ -8776,8 +9022,8 @@
       <c r="L100" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M100" s="3">
-        <v>0</v>
+      <c r="M100" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="N100" s="3">
         <v>0</v>
@@ -8842,8 +9088,11 @@
       <c r="AH100" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="101" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI100" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="101" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -8874,8 +9123,8 @@
       <c r="L101" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M101" s="3">
-        <v>0</v>
+      <c r="M101" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="N101" s="3">
         <v>0</v>
@@ -8940,8 +9189,11 @@
       <c r="AH101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
@@ -8972,8 +9224,8 @@
       <c r="L102" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M102" s="3">
-        <v>0</v>
+      <c r="M102" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="N102" s="3">
         <v>0</v>
@@ -9036,6 +9288,9 @@
         <v>0</v>
       </c>
       <c r="AH102" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI102" s="3">
         <v>0</v>
       </c>
     </row>
